--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -629,7 +629,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-12 05:00 UTC</t>
+          <t>Generated 2026-09-13 15:11 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-206</t>
+          <t>failureScenarios.test.ts: receipt reassertion after a reconnect with many owed conversations</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -14692,7 +14692,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA26" s="5" t="inlineStr"/>
+      <c r="AA26" s="5" t="inlineStr">
+        <is>
+          <t>FIX: flushReceipts() (SyncEngine.ts) sent one frame per owed conversation in a single synchronous tick on every reconnect reassert, with no cap — the gateway silently drops inbound frames past ~40/sec per connection (ws-fabric.ts), and the client never learns which ones were dropped since socket.send() only checks readyState, so noteSent() recorded them all as delivered regardless. Added a per-tick cap (MAX_RECEIPT_FRAMES_PER_FLUSH=20, comfortably under the shared 40/sec budget) and, when a flush goes over budget, re-marks the remaining conversations dirty and reschedules a continuation chunk 1100ms later (longer than the gateway rate-limit window, so consecutive chunks land in separate windows) via the existing scheduleReceiptFlush/receiptTimer machinery. Nothing is ever dropped, only spread across more ticks. Verified: full jest suite 485/485 pass, tsc --noEmit clean, eslint 0 errors. Added 2 new tests (failureScenarios.test.ts) with 60 owed conversations (past the real ~40/sec budget): the first synchronous flush stays under 60, and every owed receipt eventually goes out across later chunks.</t>
+        </is>
+      </c>
       <c r="AB26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
@@ -14848,7 +14852,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-208</t>
+          <t>failureScenarios.test.ts: loading older history across a wide deletion hole</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -14868,7 +14872,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -14967,7 +14971,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA28" s="5" t="inlineStr"/>
+      <c r="AA28" s="5" t="inlineStr">
+        <is>
+          <t>FIX: fetchOlderMessages() (SyncEngine.ts) treated an empty page from the server as end-of-history, but the backend filters deleted:false — a contiguous deleted run wider than one page comes back completely empty even though real history exists further back. Since the UI (useMessages.ts) only grows its window when loadOlderMessages returns true, and only fires another load on a scroll past a NEW oldest bubble, a false end-of-history report is a permanent dead end with no way for the user to retry. Converted the single fetch into a loop that steps the cursor back over an empty page and tries again, up to a generous safety cap (MAX_HOLE_HOPS=200, purely a circuit breaker against a pathological/corrupt history) before genuinely giving up. One loadOlderMessages() call now reaches all the way past a hole (or to the true start of history) in one go. Verified: full jest suite 485/485 pass, tsc --noEmit clean, eslint 0 errors. Added 2 new tests (failureScenarios.test.ts) with a 70-message-wide deletion hole (wider than the 50-message page): one call steps past it and loads the older page, and the true end-of-history case is unaffected.</t>
+        </is>
+      </c>
       <c r="AB28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
@@ -15257,7 +15265,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-211</t>
+          <t>messageOrdering.test.ts: VC-030 — a device clock running ahead of the server</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -15277,7 +15285,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -15377,7 +15385,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA31" s="5" t="inlineStr"/>
+      <c r="AA31" s="5" t="inlineStr">
+        <is>
+          <t>FIX: two causes, both in the created_at-as-sort-key design. (1) markMessageSent() re-stamped createdAt to the server clock FORWARD ONLY (if (ack.serverTs &gt; m.createdAt)), a rule meant to stop a slow server clock re-burying an offline-composed bubble. Forward-only mixes two clocks in one sort key: on a device whose clock leads the server, an own message keeps its future local stamp and beats every server timestamp that follows it, permanently. The server clock is the same authority that assigns seq, so its timestamp is now adopted in EITHER direction. (2) messageWindowClauses() (extracted from observeMessages so the real query is testable rather than duplicated in a test) now sorts by created_at DESC then seq DESC — seq is the ordering identity per backend-integration-reference §5, and the gateway fans bursts out inside one millisecond, so identical created_at values are normal and were previously resolved by whatever order rows happened to be written. seq is the SECOND key, not the first, because an unsent message has no seq and sorting on it first would file every pending bubble under a null and drag it out of the newest-first window. The pre-existing test never drags a message backwards in time encoded the defect; it was rewritten to assert the concern it actually cared about — that a backwards re-stamp does not change the bubble POSITION — which now holds because seq decides the order. Verified: full jest suite 492/492 pass, tsc --noEmit clean, eslint 0 errors.</t>
+        </is>
+      </c>
       <c r="AB31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
@@ -17888,7 +17900,11 @@
           <t>VC-49</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr"/>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>profileGate.test.ts: VC-049</t>
+        </is>
+      </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
@@ -17906,7 +17922,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -18003,7 +18019,7 @@
       </c>
       <c r="AA50" s="5" t="inlineStr">
         <is>
-          <t>Reported by Tusha Bhadouriya during production QA testing.</t>
+          <t>FIX (root-caused): the email is NOT a directory-profile field — profileShape.ts states it is a separately-verified identifier owned by the auth-service (GET /auth/account). useProfileGate decided purely from the LOCAL MMKV mirror, and purgeAccountData() wipes KVKeys.email on every sign-out, so immediately after any login the mirror is empty and the gate prompted unconditionally. useAccountInfo() does fetch the real email and mirror it, but it runs in parallel from AppTabs, so its answer always lost the race — and dismissal is session-only, which is why it returned every single login. The gate now asks the auth-service itself before deciding, via a new pure shouldPromptForProfile() (features/user/model/profileGate.ts): a mirrored email means never prompt; a server email means never prompt (and is re-mirrored so later launches short-circuit with no network); an UNANSWERED server (in flight or unreachable) means WAIT rather than prompt, which also removes the flash of the sheet before the answer lands. Only a definitive server no-email prompts. Verified: full jest suite 492/492 pass (5 new decision tests), tsc --noEmit clean, eslint 0 errors, no eslint-plugin-boundaries violation for the user→auth import (authApi depends only on infra, so no cycle). Not reproduced on a device — no Android hardware attached to this machine; fix is verified at the unit level against the exact reported condition.</t>
         </is>
       </c>
       <c r="AB50" s="5" t="inlineStr">
@@ -18024,7 +18040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -18210,7 +18226,7 @@
         </is>
       </c>
       <c r="B18" s="22" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C18" s="23" t="inlineStr"/>
     </row>
@@ -18221,7 +18237,7 @@
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C19" s="23" t="inlineStr"/>
     </row>
@@ -18280,7 +18296,7 @@
       </c>
       <c r="C26" s="25" t="inlineStr">
         <is>
-          <t>22 open P0/P1 defect(s) block the build.</t>
+          <t>19 open P0/P1 defect(s) block the build.</t>
         </is>
       </c>
     </row>
@@ -18483,7 +18499,7 @@
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>VC-025</t>
+          <t>VC-028</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
@@ -18493,14 +18509,14 @@
       </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>reassertReceipts() on every connect emits an unbounded burst the gateway silently drops</t>
+          <t>No event_id dedup anywhere — the documented at-least-once guard does not exist</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>VC-028</t>
+          <t>VC-032</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
@@ -18510,14 +18526,14 @@
       </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>No event_id dedup anywhere — the documented at-least-once guard does not exist</t>
+          <t>No duplicate-notification suppression, though the monotonic watermark to do it already exists</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
-          <t>VC-030</t>
+          <t>VC-033</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
@@ -18527,31 +18543,31 @@
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>Message window sorts by created_at, not seq — a device clock ahead of the server permanently mis-orders own messages</t>
+          <t>Native pending-event queue is a lock-free read-modify-write that can wipe a reply enqueued mid-drain</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
         <is>
-          <t>VC-032</t>
+          <t>VC-039</t>
         </is>
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C43" s="23" t="inlineStr">
         <is>
-          <t>No duplicate-notification suppression, though the monotonic watermark to do it already exists</t>
+          <t>Any authenticated user can READ and WRITE any conversation — no authorization on the chat routes, and conversation ids are derivable offline</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="inlineStr">
         <is>
-          <t>VC-033</t>
+          <t>VC-040</t>
         </is>
       </c>
       <c r="B44" s="22" t="inlineStr">
@@ -18561,31 +18577,31 @@
       </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
-          <t>Native pending-event queue is a lock-free read-modify-write that can wipe a reply enqueued mid-drain</t>
+          <t>A push endpoint can be registered against another account's userId, redirecting their push wake-ups</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="inlineStr">
         <is>
-          <t>VC-039</t>
+          <t>VC-041</t>
         </is>
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C45" s="23" t="inlineStr">
         <is>
-          <t>Any authenticated user can READ and WRITE any conversation — no authorization on the chat routes, and conversation ids are derivable offline</t>
+          <t>POST /chat/messages accepts a conversationId that does not exist</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="21" t="inlineStr">
         <is>
-          <t>VC-040</t>
+          <t>VC-043</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
@@ -18595,14 +18611,14 @@
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>A push endpoint can be registered against another account's userId, redirecting their push wake-ups</t>
+          <t>Concurrent refresh-token requests can all succeed — rotation is not race-safe</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="21" t="inlineStr">
         <is>
-          <t>VC-041</t>
+          <t>VC-045</t>
         </is>
       </c>
       <c r="B47" s="22" t="inlineStr">
@@ -18612,58 +18628,7 @@
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>POST /chat/messages accepts a conversationId that does not exist</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="21" t="inlineStr">
-        <is>
-          <t>VC-043</t>
-        </is>
-      </c>
-      <c r="B48" s="22" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C48" s="23" t="inlineStr">
-        <is>
-          <t>Concurrent refresh-token requests can all succeed — rotation is not race-safe</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="21" t="inlineStr">
-        <is>
-          <t>VC-045</t>
-        </is>
-      </c>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C49" s="23" t="inlineStr">
-        <is>
           <t>Real-time messaging and notification-reply sync needs multi-scenario two-device verification</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="21" t="inlineStr">
-        <is>
-          <t>VC-049</t>
-        </is>
-      </c>
-      <c r="B50" s="22" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C50" s="23" t="inlineStr">
-        <is>
-          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
         </is>
       </c>
     </row>
@@ -18816,7 +18781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19292,12 +19257,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>VC-026</t>
+          <t>VC-025</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Unread count climbs and the read watermark stalls for messages backfilled into the chat you are reading</t>
+          <t>reassertReceipts() on every connect emits an unbounded burst the gateway silently drops</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -19312,7 +19277,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-207</t>
+          <t>failureScenarios.test.ts: receipt reassertion after a reconnect with many owed conversations</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
@@ -19323,24 +19288,24 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>VC-001 makes backfills constant, so this fires often. FIX: pageBackfill now mirrors the live-message path: if the backfilled page lands in the conversation on screen, it marks read (noteRead + clearUnread) instead of only noteDelivered. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: flushReceipts() (SyncEngine.ts) sent one frame per owed conversation in a single synchronous tick on every reconnect reassert, with no cap — the gateway silently drops inbound frames past ~40/sec per connection (ws-fabric.ts), and the client never learns which ones were dropped since socket.send() only checks readyState, so noteSent() recorded them all as delivered regardless. Added a per-tick cap (MAX_RECEIPT_FRAMES_PER_FLUSH=20, comfortably under the shared 40/sec budget) and, when a flush goes over budget, re-marks the remaining conversations dirty and reschedules a continuation chunk 1100ms later (longer than the gateway rate-limit window, so consecutive chunks land in separate windows) via the existing scheduleReceiptFlush/receiptTimer machinery. Nothing is ever dropped, only spread across more ticks. Verified: full jest suite 485/485 pass, tsc --noEmit clean, eslint 0 errors. Added 2 new tests (failureScenarios.test.ts) with 60 owed conversations (past the real ~40/sec budget): the first synchronous flush stays under 60, and every owed receipt eventually goes out across later chunks.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>VC-029</t>
+          <t>VC-026</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Outbox backoff exhaustion is unreachable — MAX_SEND_ATTEMPTS can never fire</t>
+          <t>Unread count climbs and the read watermark stalls for messages backfilled into the chat you are reading</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -19350,7 +19315,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-210</t>
+          <t>VC-UNIT-207</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
@@ -19361,19 +19326,19 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>FIX: removed the dead attempt-count exhaustion path (MAX_SEND_ATTEMPTS/nextOutboxRetry in syncLogic.ts) that markFailed() fell back to only when permanent was omitted — a fallback no real call site ever triggered (SyncEngine.ts always passes a classified boolean from classifySendFailure()). This mechanism contradicted the documented WhatsApp-style policy (sendFailurePolicy.ts: reachability failures retry forever, never auto-fail by attempt count) and had no basis in the HLD/LLD spec (§L6 outbox semantics: classification-based retryable-vs-permanent only, no attempt cap). Made markFailed()'s permanent parameter required (compiler now prevents the dead path from ever coming back), updated the one test that accidentally relied on the old default (realtime-hardening.test.ts) to pass permanent explicitly, removed the 4 tests for the deleted dead function, and added a new regression test proving a retryable cause stays queued past a high attempt count. Verified: full jest suite 452/452 pass (455 - 4 removed + 1 added), tsc --noEmit clean, eslint 0 errors.</t>
+          <t>VC-001 makes backfills constant, so this fires often. FIX: pageBackfill now mirrors the live-message path: if the backfilled page lands in the conversation on screen, it marks read (noteRead + clearUnread) instead of only noteDelivered. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>VC-034</t>
+          <t>VC-027</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Retry-After is honored with an unbounded, uncancellable sleep</t>
+          <t>'Load older' dead-ends permanently on a deletion hole wider than one page</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -19388,7 +19353,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-215</t>
+          <t>failureScenarios.test.ts: loading older history across a wide deletion hole</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
@@ -19399,19 +19364,19 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>FIX: Retry-After is now clamped to [0, 10s] (MAX_RETRY_AFTER_MS, client.ts) before the wait, instead of obeying a server-supplied value unbounded. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: fetchOlderMessages() (SyncEngine.ts) treated an empty page from the server as end-of-history, but the backend filters deleted:false — a contiguous deleted run wider than one page comes back completely empty even though real history exists further back. Since the UI (useMessages.ts) only grows its window when loadOlderMessages returns true, and only fires another load on a scroll past a NEW oldest bubble, a false end-of-history report is a permanent dead end with no way for the user to retry. Converted the single fetch into a loop that steps the cursor back over an empty page and tries again, up to a generous safety cap (MAX_HOLE_HOPS=200, purely a circuit breaker against a pathological/corrupt history) before genuinely giving up. One loadOlderMessages() call now reaches all the way past a hole (or to the true start of history) in one go. Verified: full jest suite 485/485 pass, tsc --noEmit clean, eslint 0 errors. Added 2 new tests (failureScenarios.test.ts) with a 70-message-wide deletion hole (wider than the 50-message page): one call steps past it and loads the older page, and the true end-of-history case is unaffected.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>VC-035</t>
+          <t>VC-029</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>A misbuilt binary reports env:'dev' while talking to production</t>
+          <t>Outbox backoff exhaustion is unreachable — MAX_SEND_ATTEMPTS can never fire</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -19426,7 +19391,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-216</t>
+          <t>VC-UNIT-210</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
@@ -19437,34 +19402,34 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>The prod URL fallback direction is defensible; make `name` fall back to 'prod' alongside it, or log.error when Config.API_BASE_URL is absent. FIX: Extracted the pure resolveAppEnv(rawName, rawApiBaseUrl, rawWsUrl) so the fallback logic is unit-testable. An unrecognised/missing ENV now falls back to 'prod' alongside the URL fallback (previously 'dev'), so a misbuilt binary can never report a safe-sounding name while actually pointing at production. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: removed the dead attempt-count exhaustion path (MAX_SEND_ATTEMPTS/nextOutboxRetry in syncLogic.ts) that markFailed() fell back to only when permanent was omitted — a fallback no real call site ever triggered (SyncEngine.ts always passes a classified boolean from classifySendFailure()). This mechanism contradicted the documented WhatsApp-style policy (sendFailurePolicy.ts: reachability failures retry forever, never auto-fail by attempt count) and had no basis in the HLD/LLD spec (§L6 outbox semantics: classification-based retryable-vs-permanent only, no attempt cap). Made markFailed()'s permanent parameter required (compiler now prevents the dead path from ever coming back), updated the one test that accidentally relied on the old default (realtime-hardening.test.ts) to pass permanent explicitly, removed the 4 tests for the deleted dead function, and added a new regression test proving a retryable cause stays queued past a high attempt count. Verified: full jest suite 452/452 pass (455 - 4 removed + 1 added), tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>VC-036</t>
+          <t>VC-030</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Cold start after &gt;15 min idle opens the WebSocket with a certainly-expired token</t>
+          <t>Message window sorts by created_at, not seq — a device clock ahead of the server permanently mis-orders own messages</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-12</t>
+          <t>dev branch, 2026-09-13</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-217</t>
+          <t>messageOrdering.test.ts: VC-030 — a device clock running ahead of the server</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
@@ -19475,7 +19440,159 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
+          <t>FIX: two causes, both in the created_at-as-sort-key design. (1) markMessageSent() re-stamped createdAt to the server clock FORWARD ONLY (if (ack.serverTs &gt; m.createdAt)), a rule meant to stop a slow server clock re-burying an offline-composed bubble. Forward-only mixes two clocks in one sort key: on a device whose clock leads the server, an own message keeps its future local stamp and beats every server timestamp that follows it, permanently. The server clock is the same authority that assigns seq, so its timestamp is now adopted in EITHER direction. (2) messageWindowClauses() (extracted from observeMessages so the real query is testable rather than duplicated in a test) now sorts by created_at DESC then seq DESC — seq is the ordering identity per backend-integration-reference §5, and the gateway fans bursts out inside one millisecond, so identical created_at values are normal and were previously resolved by whatever order rows happened to be written. seq is the SECOND key, not the first, because an unsent message has no seq and sorting on it first would file every pending bubble under a null and drag it out of the newest-first window. The pre-existing test never drags a message backwards in time encoded the defect; it was rewritten to assert the concern it actually cared about — that a backwards re-stamp does not change the bubble POSITION — which now holds because seq decides the order. Verified: full jest suite 492/492 pass, tsc --noEmit clean, eslint 0 errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>VC-034</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Retry-After is honored with an unbounded, uncancellable sleep</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-12</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>VC-UNIT-215</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>FIX: Retry-After is now clamped to [0, 10s] (MAX_RETRY_AFTER_MS, client.ts) before the wait, instead of obeying a server-supplied value unbounded. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>VC-035</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>A misbuilt binary reports env:'dev' while talking to production</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-12</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>VC-UNIT-216</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>The prod URL fallback direction is defensible; make `name` fall back to 'prod' alongside it, or log.error when Config.API_BASE_URL is absent. FIX: Extracted the pure resolveAppEnv(rawName, rawApiBaseUrl, rawWsUrl) so the fallback logic is unit-testable. An unrecognised/missing ENV now falls back to 'prod' alongside the URL fallback (previously 'dev'), so a misbuilt binary can never report a safe-sounding name while actually pointing at production. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>VC-036</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Cold start after &gt;15 min idle opens the WebSocket with a certainly-expired token</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-12</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>VC-UNIT-217</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
           <t>FIX: hasValidSession() added (tokens.ts); useAuthBootstrap now refreshes before hydrating on an expired-but-present token. hasSession() deliberately left presence-only to protect SyncEngine reconnect guards. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>VC-049</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-13</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>profileGate.test.ts: VC-049</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>FIX (root-caused): the email is NOT a directory-profile field — profileShape.ts states it is a separately-verified identifier owned by the auth-service (GET /auth/account). useProfileGate decided purely from the LOCAL MMKV mirror, and purgeAccountData() wipes KVKeys.email on every sign-out, so immediately after any login the mirror is empty and the gate prompted unconditionally. useAccountInfo() does fetch the real email and mirror it, but it runs in parallel from AppTabs, so its answer always lost the race — and dismissal is session-only, which is why it returned every single login. The gate now asks the auth-service itself before deciding, via a new pure shouldPromptForProfile() (features/user/model/profileGate.ts): a mirrored email means never prompt; a server email means never prompt (and is re-mirrored so later launches short-circuit with no network); an UNANSWERED server (in flight or unreachable) means WAIT rather than prompt, which also removes the flash of the sheet before the answer lands. Only a definitive server no-email prompts. Verified: full jest suite 492/492 pass (5 new decision tests), tsc --noEmit clean, eslint 0 errors, no eslint-plugin-boundaries violation for the user→auth import (authApi depends only on infra, so no cycle). Not reproduced on a device — no Android hardware attached to this machine; fix is verified at the unit level against the exact reported condition.</t>
         </is>
       </c>
     </row>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -629,7 +629,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-13 15:11 UTC</t>
+          <t>Generated 2026-09-13 15:24 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -17334,7 +17334,7 @@
       </c>
       <c r="AA45" s="5" t="inlineStr">
         <is>
-          <t>Reported by Tusha Bhadouriya during production QA testing.</t>
+          <t>PARTIALLY FIXED — still open pending the remaining half. The name-precedence half is done (see VC-047): a saved contact name now wins over the registered one and resolves at READ time in the chat list and chat header, so it no longer requires opening the chat first, and a background revalidation can no longer overwrite it. What is NOT fixed, and why this stays open: the residual complaint is DISCOVERY TIMING, not precedence — a contact saved in the phone while VelChat is running is not matched until the next discovery run (app resume / prewarm), so until then that peer is genuinely unknown to the client and still renders as the number. Making that immediate needs the address-book snapshot to notify its readers (or a contacts-changed observer) so an already-mounted chat list re-renders, which is a separate change and is deliberately NOT bolted on here. Re-test after the VC-047 fix: the wrong-name-shown symptoms should be gone; only the just-saved-while-app-open case should remain.</t>
         </is>
       </c>
       <c r="AB45" s="5" t="inlineStr">
@@ -17626,7 +17626,11 @@
           <t>VC-47</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr"/>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>peerDisplayName.test.ts: VC-044 / VC-047, conversationRow.test.ts: VC-044 / VC-047</t>
+        </is>
+      </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
@@ -17644,7 +17648,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -17743,7 +17747,7 @@
       </c>
       <c r="AA48" s="5" t="inlineStr">
         <is>
-          <t>Reported by Tusha Bhadouriya during production QA testing. May share a root cause with the contact-sync issue reported as a separate entry.</t>
+          <t>FIX (root-caused): the address book was consulted on exactly ONE path. startDm() writes the saved name when a chat is opened from New Chat / Message Yourself — which is why the name corrected itself after opening — while every other path used server data, and refreshPeerIdentity() actively OVERWROTE a saved name with the registered one on its next background revalidation (once per TTL/session). Introduced peerDisplayName() (features/contacts/model), the single precedence rule: the name YOU saved wins over the name the peer registered; falls back to the registered name for someone not in your book or when the book has not loaded; returns undefined when neither side has a usable name so callers keep what they have; group rows are untouched (no peerId to look up). Applied at both the WRITE side (refreshPeerIdentity, both the TTL path and the profile-changed push, so a revalidation can no longer downgrade a saved name) and the READ side (toConversationRow for the chat list, useConversationIdentity for the chat header), the latter being what makes a saved name appear WITHOUT having to open the chat first. Exposed discoveredContacts() from the contacts barrel as a cache read (no re-discovery). Verified: full jest suite 502/502 pass (10 new tests), tsc --noEmit clean, eslint 0 errors and no boundary violation. Not re-tested on a device — no Android hardware attached to this machine.</t>
         </is>
       </c>
       <c r="AB48" s="5" t="inlineStr">
@@ -18226,7 +18230,7 @@
         </is>
       </c>
       <c r="B18" s="22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" s="23" t="inlineStr"/>
     </row>
@@ -18237,7 +18241,7 @@
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" s="23" t="inlineStr"/>
     </row>
@@ -18781,7 +18785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19561,17 +19565,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>VC-049</t>
+          <t>VC-047</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
+          <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -19581,7 +19585,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>profileGate.test.ts: VC-049</t>
+          <t>peerDisplayName.test.ts: VC-044 / VC-047, conversationRow.test.ts: VC-044 / VC-047</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
@@ -19591,6 +19595,44 @@
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>FIX (root-caused): the address book was consulted on exactly ONE path. startDm() writes the saved name when a chat is opened from New Chat / Message Yourself — which is why the name corrected itself after opening — while every other path used server data, and refreshPeerIdentity() actively OVERWROTE a saved name with the registered one on its next background revalidation (once per TTL/session). Introduced peerDisplayName() (features/contacts/model), the single precedence rule: the name YOU saved wins over the name the peer registered; falls back to the registered name for someone not in your book or when the book has not loaded; returns undefined when neither side has a usable name so callers keep what they have; group rows are untouched (no peerId to look up). Applied at both the WRITE side (refreshPeerIdentity, both the TTL path and the profile-changed push, so a revalidation can no longer downgrade a saved name) and the READ side (toConversationRow for the chat list, useConversationIdentity for the chat header), the latter being what makes a saved name appear WITHOUT having to open the chat first. Exposed discoveredContacts() from the contacts barrel as a cache read (no re-discovery). Verified: full jest suite 502/502 pass (10 new tests), tsc --noEmit clean, eslint 0 errors and no boundary violation. Not re-tested on a device — no Android hardware attached to this machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>VC-049</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-13</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>profileGate.test.ts: VC-049</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>FIX (root-caused): the email is NOT a directory-profile field — profileShape.ts states it is a separately-verified identifier owned by the auth-service (GET /auth/account). useProfileGate decided purely from the LOCAL MMKV mirror, and purgeAccountData() wipes KVKeys.email on every sign-out, so immediately after any login the mirror is empty and the gate prompted unconditionally. useAccountInfo() does fetch the real email and mirror it, but it runs in parallel from AppTabs, so its answer always lost the race — and dismissal is session-only, which is why it returned every single login. The gate now asks the auth-service itself before deciding, via a new pure shouldPromptForProfile() (features/user/model/profileGate.ts): a mirrored email means never prompt; a server email means never prompt (and is re-mirrored so later launches short-circuit with no network); an UNANSWERED server (in flight or unreachable) means WAIT rather than prompt, which also removes the flash of the sheet before the answer lands. Only a definitive server no-email prompts. Verified: full jest suite 492/492 pass (5 new decision tests), tsc --noEmit clean, eslint 0 errors, no eslint-plugin-boundaries violation for the user→auth import (authApi depends only on infra, so no cycle). Not reproduced on a device — no Android hardware attached to this machine; fix is verified at the unit level against the exact reported condition.</t>
         </is>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -629,7 +629,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-13 15:24 UTC</t>
+          <t>Generated 2026-09-13 15:30 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Won't Fix</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -15110,7 +15110,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA29" s="5" t="inlineStr"/>
+      <c r="AA29" s="5" t="inlineStr">
+        <is>
+          <t>NO CODE CHANGE — not reproducible as filed; closing with evidence rather than building the suggested LRU. Two points. (1) The premise has been overtaken: the report says dedup relies on DB client_msg_id/seq paths "which VC-020 shows are not race-safe" — VC-020 was fixed earlier in this run (the batch lookups were moved INSIDE db.write, making check-and-act atomic), so those paths ARE now race-safe. (2) The reported impact (duplicate bubbles on redelivery) is already covered by passing tests: failureScenarios.test.ts "a duplicate realtime frame produces one row, one unread and one preview — however many times it lands" delivers the IDENTICAL frame three times and asserts a single row, and "does not duplicate when a whole catch-up is replayed" re-serves an entire window. Also note socket.ts:7 does not promise an LRU — it documents where event_id LIVES in the envelope, not that the client indexes it. An event_id LRU would be a second, redundant dedup layer in front of one the database already provides idempotently (seq is the server-assigned identity), with its own memory and eviction to get wrong. Recommend reopening only if a real duplicate is ever observed on a device.</t>
+        </is>
+      </c>
       <c r="AB29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
@@ -15405,7 +15409,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-212</t>
+          <t>runSequentially.test.ts: VC-031</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -15425,7 +15429,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -15527,7 +15531,7 @@
       </c>
       <c r="AA32" s="5" t="inlineStr">
         <is>
-          <t>The existing test passes only because sendText is invoked synchronously at the top of each handler — it cannot fail for the reason it claims.</t>
+          <t>FIX: the drain mapped each queued event to a thunk and then IMMEDIATELY mapped again to call it — events.map(e =&gt; () =&gt; handle(e)).map(run =&gt; run()) — so every handler was already in flight before Promise.allSettled waited on anything. The code did the exact opposite of the comment directly above it. Replaced with a new runSequentially() helper (features/notifications/model) that awaits each action in turn while still collecting per-item outcomes, so one failing action cannot abandon the rest (a reply must go out even if a preceding mute threw) — allSettle gives that second property but cannot give the first, since it can only wait on promises that have already been started. Verified: full jest suite 506/506 pass (4 new tests, including a max-concurrency assertion that fails against the old eager implementation), tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
       <c r="AB32" s="5" t="inlineStr"/>
@@ -18044,7 +18048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -18230,7 +18234,7 @@
         </is>
       </c>
       <c r="B18" s="22" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C18" s="23" t="inlineStr"/>
     </row>
@@ -18241,7 +18245,7 @@
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" s="23" t="inlineStr"/>
     </row>
@@ -18300,7 +18304,7 @@
       </c>
       <c r="C26" s="25" t="inlineStr">
         <is>
-          <t>19 open P0/P1 defect(s) block the build.</t>
+          <t>18 open P0/P1 defect(s) block the build.</t>
         </is>
       </c>
     </row>
@@ -18503,7 +18507,7 @@
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>VC-028</t>
+          <t>VC-032</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
@@ -18513,14 +18517,14 @@
       </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>No event_id dedup anywhere — the documented at-least-once guard does not exist</t>
+          <t>No duplicate-notification suppression, though the monotonic watermark to do it already exists</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>VC-032</t>
+          <t>VC-033</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
@@ -18530,48 +18534,48 @@
       </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>No duplicate-notification suppression, though the monotonic watermark to do it already exists</t>
+          <t>Native pending-event queue is a lock-free read-modify-write that can wipe a reply enqueued mid-drain</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
-          <t>VC-033</t>
+          <t>VC-039</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>Native pending-event queue is a lock-free read-modify-write that can wipe a reply enqueued mid-drain</t>
+          <t>Any authenticated user can READ and WRITE any conversation — no authorization on the chat routes, and conversation ids are derivable offline</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
         <is>
-          <t>VC-039</t>
+          <t>VC-040</t>
         </is>
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C43" s="23" t="inlineStr">
         <is>
-          <t>Any authenticated user can READ and WRITE any conversation — no authorization on the chat routes, and conversation ids are derivable offline</t>
+          <t>A push endpoint can be registered against another account's userId, redirecting their push wake-ups</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="inlineStr">
         <is>
-          <t>VC-040</t>
+          <t>VC-041</t>
         </is>
       </c>
       <c r="B44" s="22" t="inlineStr">
@@ -18581,14 +18585,14 @@
       </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
-          <t>A push endpoint can be registered against another account's userId, redirecting their push wake-ups</t>
+          <t>POST /chat/messages accepts a conversationId that does not exist</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="inlineStr">
         <is>
-          <t>VC-041</t>
+          <t>VC-043</t>
         </is>
       </c>
       <c r="B45" s="22" t="inlineStr">
@@ -18598,14 +18602,14 @@
       </c>
       <c r="C45" s="23" t="inlineStr">
         <is>
-          <t>POST /chat/messages accepts a conversationId that does not exist</t>
+          <t>Concurrent refresh-token requests can all succeed — rotation is not race-safe</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="21" t="inlineStr">
         <is>
-          <t>VC-043</t>
+          <t>VC-045</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
@@ -18614,23 +18618,6 @@
         </is>
       </c>
       <c r="C46" s="23" t="inlineStr">
-        <is>
-          <t>Concurrent refresh-token requests can all succeed — rotation is not race-safe</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="21" t="inlineStr">
-        <is>
-          <t>VC-045</t>
-        </is>
-      </c>
-      <c r="B47" s="22" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C47" s="23" t="inlineStr">
         <is>
           <t>Real-time messaging and notification-reply sync needs multi-scenario two-device verification</t>
         </is>
@@ -18785,7 +18772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19451,12 +19438,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>VC-034</t>
+          <t>VC-031</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Retry-After is honored with an unbounded, uncancellable sleep</t>
+          <t>runQueuedPushActions runs queued notification actions concurrently while claiming to serialize them</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -19466,12 +19453,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-12</t>
+          <t>dev branch, 2026-09-13</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-215</t>
+          <t>runSequentially.test.ts: VC-031</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
@@ -19482,19 +19469,19 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>FIX: Retry-After is now clamped to [0, 10s] (MAX_RETRY_AFTER_MS, client.ts) before the wait, instead of obeying a server-supplied value unbounded. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: the drain mapped each queued event to a thunk and then IMMEDIATELY mapped again to call it — events.map(e =&gt; () =&gt; handle(e)).map(run =&gt; run()) — so every handler was already in flight before Promise.allSettled waited on anything. The code did the exact opposite of the comment directly above it. Replaced with a new runSequentially() helper (features/notifications/model) that awaits each action in turn while still collecting per-item outcomes, so one failing action cannot abandon the rest (a reply must go out even if a preceding mute threw) — allSettle gives that second property but cannot give the first, since it can only wait on promises that have already been started. Verified: full jest suite 506/506 pass (4 new tests, including a max-concurrency assertion that fails against the old eager implementation), tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>VC-035</t>
+          <t>VC-034</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>A misbuilt binary reports env:'dev' while talking to production</t>
+          <t>Retry-After is honored with an unbounded, uncancellable sleep</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -19509,7 +19496,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-216</t>
+          <t>VC-UNIT-215</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
@@ -19520,19 +19507,19 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>The prod URL fallback direction is defensible; make `name` fall back to 'prod' alongside it, or log.error when Config.API_BASE_URL is absent. FIX: Extracted the pure resolveAppEnv(rawName, rawApiBaseUrl, rawWsUrl) so the fallback logic is unit-testable. An unrecognised/missing ENV now falls back to 'prod' alongside the URL fallback (previously 'dev'), so a misbuilt binary can never report a safe-sounding name while actually pointing at production. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: Retry-After is now clamped to [0, 10s] (MAX_RETRY_AFTER_MS, client.ts) before the wait, instead of obeying a server-supplied value unbounded. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>VC-036</t>
+          <t>VC-035</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Cold start after &gt;15 min idle opens the WebSocket with a certainly-expired token</t>
+          <t>A misbuilt binary reports env:'dev' while talking to production</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -19547,7 +19534,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-217</t>
+          <t>VC-UNIT-216</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
@@ -19558,19 +19545,19 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>FIX: hasValidSession() added (tokens.ts); useAuthBootstrap now refreshes before hydrating on an expired-but-present token. hasSession() deliberately left presence-only to protect SyncEngine reconnect guards. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>The prod URL fallback direction is defensible; make `name` fall back to 'prod' alongside it, or log.error when Config.API_BASE_URL is absent. FIX: Extracted the pure resolveAppEnv(rawName, rawApiBaseUrl, rawWsUrl) so the fallback logic is unit-testable. An unrecognised/missing ENV now falls back to 'prod' alongside the URL fallback (previously 'dev'), so a misbuilt binary can never report a safe-sounding name while actually pointing at production. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>VC-047</t>
+          <t>VC-036</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
+          <t>Cold start after &gt;15 min idle opens the WebSocket with a certainly-expired token</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -19580,12 +19567,12 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-13</t>
+          <t>dev branch, 2026-09-12</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>peerDisplayName.test.ts: VC-044 / VC-047, conversationRow.test.ts: VC-044 / VC-047</t>
+          <t>VC-UNIT-217</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
@@ -19596,24 +19583,24 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>FIX (root-caused): the address book was consulted on exactly ONE path. startDm() writes the saved name when a chat is opened from New Chat / Message Yourself — which is why the name corrected itself after opening — while every other path used server data, and refreshPeerIdentity() actively OVERWROTE a saved name with the registered one on its next background revalidation (once per TTL/session). Introduced peerDisplayName() (features/contacts/model), the single precedence rule: the name YOU saved wins over the name the peer registered; falls back to the registered name for someone not in your book or when the book has not loaded; returns undefined when neither side has a usable name so callers keep what they have; group rows are untouched (no peerId to look up). Applied at both the WRITE side (refreshPeerIdentity, both the TTL path and the profile-changed push, so a revalidation can no longer downgrade a saved name) and the READ side (toConversationRow for the chat list, useConversationIdentity for the chat header), the latter being what makes a saved name appear WITHOUT having to open the chat first. Exposed discoveredContacts() from the contacts barrel as a cache read (no re-discovery). Verified: full jest suite 502/502 pass (10 new tests), tsc --noEmit clean, eslint 0 errors and no boundary violation. Not re-tested on a device — no Android hardware attached to this machine.</t>
+          <t>FIX: hasValidSession() added (tokens.ts); useAuthBootstrap now refreshes before hydrating on an expired-but-present token. hasSession() deliberately left presence-only to protect SyncEngine reconnect guards. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>VC-049</t>
+          <t>VC-047</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
+          <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -19623,7 +19610,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>profileGate.test.ts: VC-049</t>
+          <t>peerDisplayName.test.ts: VC-044 / VC-047, conversationRow.test.ts: VC-044 / VC-047</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
@@ -19633,6 +19620,44 @@
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>FIX (root-caused): the address book was consulted on exactly ONE path. startDm() writes the saved name when a chat is opened from New Chat / Message Yourself — which is why the name corrected itself after opening — while every other path used server data, and refreshPeerIdentity() actively OVERWROTE a saved name with the registered one on its next background revalidation (once per TTL/session). Introduced peerDisplayName() (features/contacts/model), the single precedence rule: the name YOU saved wins over the name the peer registered; falls back to the registered name for someone not in your book or when the book has not loaded; returns undefined when neither side has a usable name so callers keep what they have; group rows are untouched (no peerId to look up). Applied at both the WRITE side (refreshPeerIdentity, both the TTL path and the profile-changed push, so a revalidation can no longer downgrade a saved name) and the READ side (toConversationRow for the chat list, useConversationIdentity for the chat header), the latter being what makes a saved name appear WITHOUT having to open the chat first. Exposed discoveredContacts() from the contacts barrel as a cache read (no re-discovery). Verified: full jest suite 502/502 pass (10 new tests), tsc --noEmit clean, eslint 0 errors and no boundary violation. Not re-tested on a device — no Android hardware attached to this machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>VC-049</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-13</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>profileGate.test.ts: VC-049</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>FIX (root-caused): the email is NOT a directory-profile field — profileShape.ts states it is a separately-verified identifier owned by the auth-service (GET /auth/account). useProfileGate decided purely from the LOCAL MMKV mirror, and purgeAccountData() wipes KVKeys.email on every sign-out, so immediately after any login the mirror is empty and the gate prompted unconditionally. useAccountInfo() does fetch the real email and mirror it, but it runs in parallel from AppTabs, so its answer always lost the race — and dismissal is session-only, which is why it returned every single login. The gate now asks the auth-service itself before deciding, via a new pure shouldPromptForProfile() (features/user/model/profileGate.ts): a mirrored email means never prompt; a server email means never prompt (and is re-mirrored so later launches short-circuit with no network); an UNANSWERED server (in flight or unreachable) means WAIT rather than prompt, which also removes the flash of the sheet before the answer lands. Only a definitive server no-email prompts. Verified: full jest suite 492/492 pass (5 new decision tests), tsc --noEmit clean, eslint 0 errors, no eslint-plugin-boundaries violation for the user→auth import (authApi depends only on infra, so no cycle). Not reproduced on a device — no Android hardware attached to this machine; fix is verified at the unit level against the exact reported condition.</t>
         </is>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -629,7 +629,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-13 15:30 UTC</t>
+          <t>Generated 2026-09-13 15:47 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -16504,7 +16504,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA39" s="5" t="inlineStr"/>
+      <c r="AA39" s="5" t="inlineStr">
+        <is>
+          <t>FIX (root cause found by instrumentation, not guesswork): --detectOpenHandles reported NOTHING, so the leak was invisible to it. A probe dumping process.getActiveResourcesInfo() in afterAll showed four live Timeouts while _getActiveHandles() was empty. Traced to WatermelonDB: adapters/lokijs/worker/lokiExtensions.js constructs the Loki database with autosave:true, autosaveInterval:500 — a 500ms setInterval that is only ever cleared by loki.close(), which the app never calls because its database lives for the life of the process. Correct in production (which uses the real native SQLite adapter and never sees this code) but under Jest that interval outlives the run and holds the worker event loop open. Fixed at the source by passing extraLokiOptions:{autosave:false} to the LokiJSAdapter mock in jest.setup.ts — a first-class documented adapter option that WatermelonDB spreads AFTER its own defaults, so it overrides them; there is nothing to autosave in an in-memory adapter that starts fresh every run. MEASURED before/after with the same command: a DB-touching suite went from never exiting (killed at 90-120s, exit 124) to exit 0, and the full suite from blowing past a 120s timeout to completing and exiting in ~18s — --forceExit is no longer needed. RESIDUAL, stated honestly: the "worker process has failed to exit gracefully" text can still appear with &gt;=2 jest workers. That is worker-pool teardown timing, not a leak in our test code — verified by the warning being absent at --maxWorkers=1 (35s) and absent for every heavy suite run individually (failureScenarios, restart, realtime-hardening all clean), while present at --maxWorkers=2 (19s) and 4 (12s). Verified: full jest suite 506/506 pass, tsc --noEmit clean, eslint clean.</t>
+        </is>
+      </c>
       <c r="AB39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
@@ -18234,7 +18238,7 @@
         </is>
       </c>
       <c r="B18" s="22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" s="23" t="inlineStr"/>
     </row>
@@ -18245,7 +18249,7 @@
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" s="23" t="inlineStr"/>
     </row>
@@ -18772,7 +18776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19590,17 +19594,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>VC-047</t>
+          <t>VC-038</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
+          <t>Jest reports a worker that failed to exit gracefully — a leaked timer or handle in the test path</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -19610,7 +19614,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>peerDisplayName.test.ts: VC-044 / VC-047, conversationRow.test.ts: VC-044 / VC-047</t>
+          <t>VC-UNIT-001</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
@@ -19621,24 +19625,24 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>FIX (root-caused): the address book was consulted on exactly ONE path. startDm() writes the saved name when a chat is opened from New Chat / Message Yourself — which is why the name corrected itself after opening — while every other path used server data, and refreshPeerIdentity() actively OVERWROTE a saved name with the registered one on its next background revalidation (once per TTL/session). Introduced peerDisplayName() (features/contacts/model), the single precedence rule: the name YOU saved wins over the name the peer registered; falls back to the registered name for someone not in your book or when the book has not loaded; returns undefined when neither side has a usable name so callers keep what they have; group rows are untouched (no peerId to look up). Applied at both the WRITE side (refreshPeerIdentity, both the TTL path and the profile-changed push, so a revalidation can no longer downgrade a saved name) and the READ side (toConversationRow for the chat list, useConversationIdentity for the chat header), the latter being what makes a saved name appear WITHOUT having to open the chat first. Exposed discoveredContacts() from the contacts barrel as a cache read (no re-discovery). Verified: full jest suite 502/502 pass (10 new tests), tsc --noEmit clean, eslint 0 errors and no boundary violation. Not re-tested on a device — no Android hardware attached to this machine.</t>
+          <t>FIX (root cause found by instrumentation, not guesswork): --detectOpenHandles reported NOTHING, so the leak was invisible to it. A probe dumping process.getActiveResourcesInfo() in afterAll showed four live Timeouts while _getActiveHandles() was empty. Traced to WatermelonDB: adapters/lokijs/worker/lokiExtensions.js constructs the Loki database with autosave:true, autosaveInterval:500 — a 500ms setInterval that is only ever cleared by loki.close(), which the app never calls because its database lives for the life of the process. Correct in production (which uses the real native SQLite adapter and never sees this code) but under Jest that interval outlives the run and holds the worker event loop open. Fixed at the source by passing extraLokiOptions:{autosave:false} to the LokiJSAdapter mock in jest.setup.ts — a first-class documented adapter option that WatermelonDB spreads AFTER its own defaults, so it overrides them; there is nothing to autosave in an in-memory adapter that starts fresh every run. MEASURED before/after with the same command: a DB-touching suite went from never exiting (killed at 90-120s, exit 124) to exit 0, and the full suite from blowing past a 120s timeout to completing and exiting in ~18s — --forceExit is no longer needed. RESIDUAL, stated honestly: the "worker process has failed to exit gracefully" text can still appear with &gt;=2 jest workers. That is worker-pool teardown timing, not a leak in our test code — verified by the warning being absent at --maxWorkers=1 (35s) and absent for every heavy suite run individually (failureScenarios, restart, realtime-hardening all clean), while present at --maxWorkers=2 (19s) and 4 (12s). Verified: full jest suite 506/506 pass, tsc --noEmit clean, eslint clean.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>VC-049</t>
+          <t>VC-047</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
+          <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -19648,7 +19652,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>profileGate.test.ts: VC-049</t>
+          <t>peerDisplayName.test.ts: VC-044 / VC-047, conversationRow.test.ts: VC-044 / VC-047</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
@@ -19658,6 +19662,44 @@
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>FIX (root-caused): the address book was consulted on exactly ONE path. startDm() writes the saved name when a chat is opened from New Chat / Message Yourself — which is why the name corrected itself after opening — while every other path used server data, and refreshPeerIdentity() actively OVERWROTE a saved name with the registered one on its next background revalidation (once per TTL/session). Introduced peerDisplayName() (features/contacts/model), the single precedence rule: the name YOU saved wins over the name the peer registered; falls back to the registered name for someone not in your book or when the book has not loaded; returns undefined when neither side has a usable name so callers keep what they have; group rows are untouched (no peerId to look up). Applied at both the WRITE side (refreshPeerIdentity, both the TTL path and the profile-changed push, so a revalidation can no longer downgrade a saved name) and the READ side (toConversationRow for the chat list, useConversationIdentity for the chat header), the latter being what makes a saved name appear WITHOUT having to open the chat first. Exposed discoveredContacts() from the contacts barrel as a cache read (no re-discovery). Verified: full jest suite 502/502 pass (10 new tests), tsc --noEmit clean, eslint 0 errors and no boundary violation. Not re-tested on a device — no Android hardware attached to this machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>VC-049</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-13</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>profileGate.test.ts: VC-049</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>FIX (root-caused): the email is NOT a directory-profile field — profileShape.ts states it is a separately-verified identifier owned by the auth-service (GET /auth/account). useProfileGate decided purely from the LOCAL MMKV mirror, and purgeAccountData() wipes KVKeys.email on every sign-out, so immediately after any login the mirror is empty and the gate prompted unconditionally. useAccountInfo() does fetch the real email and mirror it, but it runs in parallel from AppTabs, so its answer always lost the race — and dismissal is session-only, which is why it returned every single login. The gate now asks the auth-service itself before deciding, via a new pure shouldPromptForProfile() (features/user/model/profileGate.ts): a mirrored email means never prompt; a server email means never prompt (and is re-mirrored so later launches short-circuit with no network); an UNANSWERED server (in flight or unreachable) means WAIT rather than prompt, which also removes the flash of the sheet before the answer lands. Only a definitive server no-email prompts. Verified: full jest suite 492/492 pass (5 new decision tests), tsc --noEmit clean, eslint 0 errors, no eslint-plugin-boundaries violation for the user→auth import (authApi depends only on infra, so no cycle). Not reproduced on a device — no Android hardware attached to this machine; fix is verified at the unit level against the exact reported condition.</t>
         </is>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -629,7 +629,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-13 15:47 UTC</t>
+          <t>Generated 2026-09-13 15:49 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -17588,12 +17588,12 @@
       </c>
       <c r="U47" s="5" t="inlineStr">
         <is>
-          <t>Not yet investigated — could be a client-side polling/debounce delay or a backend presence-propagation delay.</t>
+          <t>Polling + server TTL, because the backend has no presence push. Not a client defect.</t>
         </is>
       </c>
       <c r="V47" s="5" t="inlineStr">
         <is>
-          <t>Not yet investigated.</t>
+          <t>Root-caused, but the fix is NOT client-side. Quantified below.</t>
         </is>
       </c>
       <c r="W47" s="5" t="inlineStr"/>
@@ -17614,7 +17614,7 @@
       </c>
       <c r="AA47" s="5" t="inlineStr">
         <is>
-          <t>Reported by Tusha Bhadouriya during production QA testing. Root cause (client vs backend) not yet isolated.</t>
+          <t>INVESTIGATED — left OPEN deliberately, no code change. The client side is already correct: activatePresence() does a LEADING await refreshPeerPresence() before it starts the interval, so there is no missing first read, and the poll is correctly scoped to the open chat and paused when suspended/offline (§M13 battery). The delay is architectural and has two additive parts. (1) There is NO live presence push to wait for: the realtime gateway FanoutConsumer subscribes to message/receipt/caption only, never presence.changed, so a presence change cannot reach a socket — this is already documented at the top of infra/network/presence.ts and is why a REST snapshot poll exists at all. (2) The numbers: peer COMES ONLINE is seen at the next poll, PEER_PRESENCE_POLL_MS = 20s, so up to ~20s. Peer GOES OFFLINE is worse, because nobody publishes a leaving event — their online:{userId} Redis key has to EXPIRE server-side (PRESENCE_ONLINE_TTL_MS = 30s from their last 20s heartbeat) and only then can our next poll observe it, so up to ~50s. That matches the reported "noticeable delay" exactly. THE REAL FIX IS BACKEND: have the gateway fan out presence.changed over the WS; the client already has the receiving path (onInboundPresence + normalizePresenceEvent are written and forward-compatible), so it would light up with no client change. The only client-side lever is lowering PEER_PRESENCE_POLL_MS, which buys latency with a REST request per interval per open chat and is a direct trade against the §R5/§R6 battery and request budgets on the 3GB reference device — a product call, not one to make silently, so it is NOT done here. Needs a decision: accept the delay, lower the poll interval (say what latency is acceptable), or schedule the backend fan-out.</t>
         </is>
       </c>
       <c r="AB47" s="5" t="inlineStr">

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -30,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,6 +66,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="009A3412"/>
+    </font>
+    <font>
+      <b val="1"/>
       <i val="1"/>
       <color rgb="001E3A8A"/>
     </font>
@@ -98,7 +102,7 @@
       <color rgb="0092400E"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -118,6 +122,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEDD5"/>
       </patternFill>
     </fill>
     <fill>
@@ -172,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -203,40 +212,43 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -629,7 +641,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-13 15:49 UTC</t>
+          <t>Generated 2026-09-13 16:07 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1981,9 +1993,9 @@
           <t>node-harness</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>FLAKY</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -1993,7 +2005,7 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Logs + Repro script</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -2795,7 +2807,7 @@
           <t>node-harness</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr">
+      <c r="C62" s="13" t="inlineStr">
         <is>
           <t>PASS (verified from phone by Aayush)</t>
         </is>
@@ -2869,19 +2881,19 @@
           <t>node-harness</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>FLAKY</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>VC-002</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
@@ -4257,11 +4269,11 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:23</t>
+          <t>2026-09-13 16:05:03</t>
         </is>
       </c>
       <c r="N2" s="5" t="n">
-        <v>1061</v>
+        <v>1232</v>
       </c>
       <c r="O2" s="5" t="inlineStr">
         <is>
@@ -4330,11 +4342,11 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:24</t>
+          <t>2026-09-13 16:05:04</t>
         </is>
       </c>
       <c r="N3" s="5" t="n">
-        <v>810</v>
+        <v>939</v>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
@@ -4407,11 +4419,11 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:27</t>
+          <t>2026-09-13 16:05:08</t>
         </is>
       </c>
       <c r="N4" s="5" t="n">
-        <v>3579</v>
+        <v>3920</v>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
@@ -4482,11 +4494,11 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:34</t>
+          <t>2026-09-13 16:05:15</t>
         </is>
       </c>
       <c r="N5" s="5" t="n">
-        <v>6413</v>
+        <v>6483</v>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
@@ -4558,11 +4570,11 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:36</t>
+          <t>2026-09-13 16:05:17</t>
         </is>
       </c>
       <c r="N6" s="5" t="n">
-        <v>2393</v>
+        <v>2484</v>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
@@ -4632,11 +4644,11 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:39</t>
+          <t>2026-09-13 16:05:20</t>
         </is>
       </c>
       <c r="N7" s="5" t="n">
-        <v>2533</v>
+        <v>2437</v>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
@@ -4706,11 +4718,11 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:39</t>
+          <t>2026-09-13 16:05:20</t>
         </is>
       </c>
       <c r="N8" s="5" t="n">
-        <v>379</v>
+        <v>484</v>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
@@ -4779,11 +4791,11 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:42</t>
+          <t>2026-09-13 16:05:23</t>
         </is>
       </c>
       <c r="N9" s="5" t="n">
-        <v>3016</v>
+        <v>3160</v>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
@@ -4852,11 +4864,11 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:48</t>
+          <t>2026-09-13 16:05:33</t>
         </is>
       </c>
       <c r="N10" s="5" t="n">
-        <v>5807</v>
+        <v>9469</v>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
@@ -4924,11 +4936,11 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:53</t>
+          <t>2026-09-13 16:05:41</t>
         </is>
       </c>
       <c r="N11" s="5" t="n">
-        <v>4937</v>
+        <v>6752</v>
       </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
@@ -4996,11 +5008,11 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:58</t>
+          <t>2026-09-13 16:05:50</t>
         </is>
       </c>
       <c r="N12" s="5" t="n">
-        <v>5297</v>
+        <v>9615</v>
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
@@ -5069,11 +5081,11 @@
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:59</t>
+          <t>2026-09-13 16:05:51</t>
         </is>
       </c>
       <c r="N13" s="5" t="n">
-        <v>650</v>
+        <v>567</v>
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
@@ -5121,7 +5133,7 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5143,11 +5155,11 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:59</t>
+          <t>2026-09-13 16:05:51</t>
         </is>
       </c>
       <c r="N14" s="5" t="n">
-        <v>270</v>
+        <v>361</v>
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
@@ -5197,7 +5209,7 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -5219,11 +5231,11 @@
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:09:00</t>
+          <t>2026-09-13 16:05:52</t>
         </is>
       </c>
       <c r="N15" s="5" t="n">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
@@ -5297,11 +5309,11 @@
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:09</t>
+          <t>2026-09-13 16:03:01</t>
         </is>
       </c>
       <c r="N16" s="5" t="n">
-        <v>370</v>
+        <v>448</v>
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
@@ -5369,7 +5381,7 @@
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:09</t>
+          <t>2026-09-13 16:03:01</t>
         </is>
       </c>
       <c r="N17" s="5" t="n">
@@ -5419,7 +5431,7 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -5441,11 +5453,11 @@
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:09</t>
+          <t>2026-09-13 16:03:01</t>
         </is>
       </c>
       <c r="N18" s="5" t="n">
-        <v>279</v>
+        <v>217</v>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
@@ -5495,7 +5507,7 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I19" s="13" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -5517,11 +5529,11 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:10</t>
+          <t>2026-09-13 16:03:01</t>
         </is>
       </c>
       <c r="N19" s="5" t="n">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
@@ -5593,11 +5605,11 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:10</t>
+          <t>2026-09-13 16:03:01</t>
         </is>
       </c>
       <c r="N20" s="5" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
@@ -5665,11 +5677,11 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:10</t>
+          <t>2026-09-13 16:03:01</t>
         </is>
       </c>
       <c r="N21" s="5" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
@@ -5739,11 +5751,11 @@
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:12</t>
+          <t>2026-09-13 16:03:03</t>
         </is>
       </c>
       <c r="N22" s="5" t="n">
-        <v>1722</v>
+        <v>1541</v>
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
@@ -5812,11 +5824,11 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:13</t>
+          <t>2026-09-13 16:03:04</t>
         </is>
       </c>
       <c r="N23" s="5" t="n">
-        <v>1409</v>
+        <v>1545</v>
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
@@ -5885,11 +5897,11 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:13</t>
+          <t>2026-09-13 16:03:05</t>
         </is>
       </c>
       <c r="N24" s="5" t="n">
-        <v>364</v>
+        <v>420</v>
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
@@ -5957,11 +5969,11 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:14</t>
+          <t>2026-09-13 16:03:05</t>
         </is>
       </c>
       <c r="N25" s="5" t="n">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
@@ -6029,11 +6041,11 @@
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:14</t>
+          <t>2026-09-13 16:03:06</t>
         </is>
       </c>
       <c r="N26" s="5" t="n">
-        <v>321</v>
+        <v>370</v>
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
@@ -6101,11 +6113,11 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:14</t>
+          <t>2026-09-13 16:03:06</t>
         </is>
       </c>
       <c r="N27" s="5" t="n">
-        <v>334</v>
+        <v>376</v>
       </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
@@ -6173,11 +6185,11 @@
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:15</t>
+          <t>2026-09-13 16:03:06</t>
         </is>
       </c>
       <c r="N28" s="5" t="n">
-        <v>306</v>
+        <v>347</v>
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
@@ -6245,11 +6257,11 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:15</t>
+          <t>2026-09-13 16:03:06</t>
         </is>
       </c>
       <c r="N29" s="5" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
@@ -6319,11 +6331,11 @@
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:17</t>
+          <t>2026-09-13 16:03:09</t>
         </is>
       </c>
       <c r="N30" s="5" t="n">
-        <v>583</v>
+        <v>752</v>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
@@ -6393,11 +6405,11 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:17</t>
+          <t>2026-09-13 16:03:09</t>
         </is>
       </c>
       <c r="N31" s="5" t="n">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
@@ -6467,11 +6479,11 @@
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:18</t>
+          <t>2026-09-13 16:03:10</t>
         </is>
       </c>
       <c r="N32" s="5" t="n">
-        <v>804</v>
+        <v>867</v>
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
@@ -6539,11 +6551,11 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:20</t>
+          <t>2026-09-13 16:03:12</t>
         </is>
       </c>
       <c r="N33" s="5" t="n">
-        <v>1855</v>
+        <v>2000</v>
       </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
@@ -6614,11 +6626,11 @@
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:22</t>
+          <t>2026-09-13 16:03:14</t>
         </is>
       </c>
       <c r="N34" s="5" t="n">
-        <v>2243</v>
+        <v>2451</v>
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
@@ -6686,11 +6698,11 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:22</t>
+          <t>2026-09-13 16:03:14</t>
         </is>
       </c>
       <c r="N35" s="5" t="n">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
@@ -6760,11 +6772,11 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:24</t>
+          <t>2026-09-13 16:03:16</t>
         </is>
       </c>
       <c r="N36" s="5" t="n">
-        <v>1736</v>
+        <v>1931</v>
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
@@ -6803,17 +6815,17 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>at most one concurrent refresh may succeed; 3 of 3 did</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>As expected</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -6833,11 +6845,11 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:25</t>
+          <t>2026-09-13 16:03:19</t>
         </is>
       </c>
       <c r="N37" s="5" t="n">
-        <v>1724</v>
+        <v>2346</v>
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
@@ -6909,11 +6921,11 @@
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:26</t>
+          <t>2026-09-13 16:03:19</t>
         </is>
       </c>
       <c r="N38" s="5" t="n">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
@@ -6981,11 +6993,11 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:26</t>
+          <t>2026-09-13 16:03:19</t>
         </is>
       </c>
       <c r="N39" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
@@ -7054,11 +7066,11 @@
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:26</t>
+          <t>2026-09-13 16:03:19</t>
         </is>
       </c>
       <c r="N40" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
@@ -7127,11 +7139,11 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:26</t>
+          <t>2026-09-13 16:03:19</t>
         </is>
       </c>
       <c r="N41" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
@@ -7200,11 +7212,11 @@
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:27</t>
+          <t>2026-09-13 16:03:20</t>
         </is>
       </c>
       <c r="N42" s="5" t="n">
-        <v>1573</v>
+        <v>1530</v>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
@@ -7272,11 +7284,11 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:27</t>
+          <t>2026-09-13 16:03:20</t>
         </is>
       </c>
       <c r="N43" s="5" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
@@ -7344,7 +7356,7 @@
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:27</t>
+          <t>2026-09-13 16:03:20</t>
         </is>
       </c>
       <c r="N44" s="5" t="n">
@@ -7416,11 +7428,11 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:27</t>
+          <t>2026-09-13 16:03:20</t>
         </is>
       </c>
       <c r="N45" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
@@ -7490,11 +7502,11 @@
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:23</t>
+          <t>2026-09-13 16:03:53</t>
         </is>
       </c>
       <c r="N46" s="5" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
@@ -7562,11 +7574,11 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:23</t>
+          <t>2026-09-13 16:03:53</t>
         </is>
       </c>
       <c r="N47" s="5" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
@@ -7634,11 +7646,11 @@
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:23</t>
+          <t>2026-09-13 16:03:53</t>
         </is>
       </c>
       <c r="N48" s="5" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
@@ -7707,7 +7719,7 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:23</t>
+          <t>2026-09-13 16:03:53</t>
         </is>
       </c>
       <c r="N49" s="5" t="n">
@@ -7780,11 +7792,11 @@
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:24</t>
+          <t>2026-09-13 16:03:53</t>
         </is>
       </c>
       <c r="N50" s="5" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
@@ -7853,11 +7865,11 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:24</t>
+          <t>2026-09-13 16:03:53</t>
         </is>
       </c>
       <c r="N51" s="5" t="n">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
@@ -7926,11 +7938,11 @@
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:24</t>
+          <t>2026-09-13 16:03:53</t>
         </is>
       </c>
       <c r="N52" s="5" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
@@ -7998,11 +8010,11 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:24</t>
+          <t>2026-09-13 16:03:54</t>
         </is>
       </c>
       <c r="N53" s="5" t="n">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
@@ -8070,11 +8082,11 @@
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:24</t>
+          <t>2026-09-13 16:03:54</t>
         </is>
       </c>
       <c r="N54" s="5" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
@@ -8142,11 +8154,11 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:25</t>
+          <t>2026-09-13 16:03:54</t>
         </is>
       </c>
       <c r="N55" s="5" t="n">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
@@ -8214,11 +8226,11 @@
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:25</t>
+          <t>2026-09-13 16:03:54</t>
         </is>
       </c>
       <c r="N56" s="5" t="n">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="O56" s="5" t="inlineStr">
         <is>
@@ -8288,11 +8300,11 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:31</t>
+          <t>2026-09-13 16:04:00</t>
         </is>
       </c>
       <c r="N57" s="5" t="n">
-        <v>5753</v>
+        <v>5246</v>
       </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
@@ -8361,11 +8373,11 @@
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:32</t>
+          <t>2026-09-13 16:04:01</t>
         </is>
       </c>
       <c r="N58" s="5" t="n">
-        <v>1143</v>
+        <v>1051</v>
       </c>
       <c r="O58" s="5" t="inlineStr">
         <is>
@@ -8416,19 +8428,19 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DURABLE MESSAGE LOSS: REST acked seqs [2,3,4,5,6,7,8,9,10,11] but the recipient's socket only received [4,6,9] — missing [2,3,5,7,8,10,11]. Durable frames must never be dropped.
+          <t xml:space="preserve">DURABLE MESSAGE LOSS: REST acked seqs [2,3,4,5,6,7,8,9,10,11] but the recipient's socket only received [2,5,8,11] — missing [3,4,6,7,9,10]. Durable frames must never be dropped.
 + actual - expected
   [
--   2,
+    2,
 -   3,
-    4,
--   5,
-    6,
+-   4,
+    5,
+-   6,
 -   7,
--   8,
-    9,
+    8,
+-   9,
 -   10,
--   11
+    11
   ]
 </t>
         </is>
@@ -8438,7 +8450,7 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I59" s="15" t="inlineStr">
+      <c r="I59" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -8460,11 +8472,11 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:41</t>
+          <t>2026-09-13 16:04:10</t>
         </is>
       </c>
       <c r="N59" s="5" t="n">
-        <v>9342</v>
+        <v>9044</v>
       </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
@@ -8539,11 +8551,11 @@
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:43</t>
+          <t>2026-09-13 16:04:12</t>
         </is>
       </c>
       <c r="N60" s="5" t="n">
-        <v>1285</v>
+        <v>1523</v>
       </c>
       <c r="O60" s="5" t="inlineStr">
         <is>
@@ -8588,17 +8600,17 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>As expected</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>[VC-RT-030-A] timed out after 10000ms awaiting delivered receipt for seq 17</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
@@ -8618,11 +8630,11 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:44</t>
+          <t>2026-09-13 16:04:22</t>
         </is>
       </c>
       <c r="N61" s="5" t="n">
-        <v>1095</v>
+        <v>10398</v>
       </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
@@ -8674,7 +8686,7 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I62" s="15" t="inlineStr">
+      <c r="I62" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -8696,11 +8708,11 @@
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:54</t>
+          <t>2026-09-13 16:04:33</t>
         </is>
       </c>
       <c r="N62" s="5" t="n">
-        <v>10395</v>
+        <v>10409</v>
       </c>
       <c r="O62" s="5" t="inlineStr">
         <is>
@@ -8757,7 +8769,7 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I63" s="15" t="inlineStr">
+      <c r="I63" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -8779,11 +8791,11 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:00</t>
+          <t>2026-09-13 16:04:38</t>
         </is>
       </c>
       <c r="N63" s="5" t="n">
-        <v>5418</v>
+        <v>5467</v>
       </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
@@ -8857,11 +8869,11 @@
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:01</t>
+          <t>2026-09-13 16:04:40</t>
         </is>
       </c>
       <c r="N64" s="5" t="n">
-        <v>1649</v>
+        <v>1664</v>
       </c>
       <c r="O64" s="5" t="inlineStr">
         <is>
@@ -8929,11 +8941,11 @@
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:06</t>
+          <t>2026-09-13 16:04:45</t>
         </is>
       </c>
       <c r="N65" s="5" t="n">
-        <v>4907</v>
+        <v>4981</v>
       </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
@@ -8983,7 +8995,7 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I66" s="15" t="inlineStr">
+      <c r="I66" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9005,11 +9017,11 @@
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:12</t>
+          <t>2026-09-13 16:04:51</t>
         </is>
       </c>
       <c r="N66" s="5" t="n">
-        <v>5981</v>
+        <v>6080</v>
       </c>
       <c r="O66" s="5" t="inlineStr">
         <is>
@@ -9082,11 +9094,11 @@
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:13</t>
+          <t>2026-09-13 16:04:52</t>
         </is>
       </c>
       <c r="N67" s="5" t="n">
-        <v>353</v>
+        <v>447</v>
       </c>
       <c r="O67" s="5" t="inlineStr">
         <is>
@@ -9155,11 +9167,11 @@
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:15</t>
+          <t>2026-09-13 16:04:54</t>
         </is>
       </c>
       <c r="N68" s="5" t="n">
-        <v>1815</v>
+        <v>1971</v>
       </c>
       <c r="O68" s="5" t="inlineStr">
         <is>
@@ -9227,11 +9239,11 @@
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:08:19</t>
+          <t>2026-09-13 16:04:59</t>
         </is>
       </c>
       <c r="N69" s="5" t="n">
-        <v>4527</v>
+        <v>4763</v>
       </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
@@ -9299,11 +9311,11 @@
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:28</t>
+          <t>2026-09-13 16:03:00</t>
         </is>
       </c>
       <c r="N70" s="5" t="n">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="O70" s="5" t="inlineStr">
         <is>
@@ -9371,11 +9383,11 @@
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:28</t>
+          <t>2026-09-13 16:03:00</t>
         </is>
       </c>
       <c r="N71" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O71" s="5" t="inlineStr">
         <is>
@@ -9443,11 +9455,11 @@
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:28</t>
+          <t>2026-09-13 16:03:00</t>
         </is>
       </c>
       <c r="N72" s="5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O72" s="5" t="inlineStr">
         <is>
@@ -9515,11 +9527,11 @@
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:28</t>
+          <t>2026-09-13 16:03:00</t>
         </is>
       </c>
       <c r="N73" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
@@ -9588,11 +9600,11 @@
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:29</t>
+          <t>2026-09-13 16:03:02</t>
         </is>
       </c>
       <c r="N74" s="5" t="n">
-        <v>1352</v>
+        <v>1749</v>
       </c>
       <c r="O74" s="5" t="inlineStr">
         <is>
@@ -9662,11 +9674,11 @@
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:30</t>
+          <t>2026-09-13 16:03:04</t>
         </is>
       </c>
       <c r="N75" s="5" t="n">
-        <v>1417</v>
+        <v>1497</v>
       </c>
       <c r="O75" s="5" t="inlineStr">
         <is>
@@ -9735,11 +9747,11 @@
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:30</t>
+          <t>2026-09-13 16:03:04</t>
         </is>
       </c>
       <c r="N76" s="5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O76" s="5" t="inlineStr">
         <is>
@@ -9788,7 +9800,7 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I77" s="15" t="inlineStr">
+      <c r="I77" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9810,11 +9822,11 @@
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:34</t>
+          <t>2026-09-13 16:03:08</t>
         </is>
       </c>
       <c r="N77" s="5" t="n">
-        <v>2018</v>
+        <v>2056</v>
       </c>
       <c r="O77" s="5" t="inlineStr">
         <is>
@@ -9888,11 +9900,11 @@
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:34</t>
+          <t>2026-09-13 16:03:08</t>
         </is>
       </c>
       <c r="N78" s="5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O78" s="5" t="inlineStr">
         <is>
@@ -9960,11 +9972,11 @@
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:34</t>
+          <t>2026-09-13 16:03:08</t>
         </is>
       </c>
       <c r="N79" s="5" t="n">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="O79" s="5" t="inlineStr">
         <is>
@@ -10032,11 +10044,11 @@
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:34</t>
+          <t>2026-09-13 16:03:08</t>
         </is>
       </c>
       <c r="N80" s="5" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="O80" s="5" t="inlineStr">
         <is>
@@ -10082,7 +10094,7 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I81" s="14" t="inlineStr">
+      <c r="I81" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -10104,11 +10116,11 @@
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:34</t>
+          <t>2026-09-13 16:03:08</t>
         </is>
       </c>
       <c r="N81" s="5" t="n">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="O81" s="5" t="inlineStr">
         <is>
@@ -10180,11 +10192,11 @@
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:36</t>
+          <t>2026-09-13 16:03:10</t>
         </is>
       </c>
       <c r="N82" s="5" t="n">
-        <v>1442</v>
+        <v>1502</v>
       </c>
       <c r="O82" s="5" t="inlineStr">
         <is>
@@ -10253,11 +10265,11 @@
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:38</t>
+          <t>2026-09-13 16:03:12</t>
         </is>
       </c>
       <c r="N83" s="5" t="n">
-        <v>1736</v>
+        <v>1962</v>
       </c>
       <c r="O83" s="5" t="inlineStr">
         <is>
@@ -10326,11 +10338,11 @@
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:39</t>
+          <t>2026-09-13 16:03:13</t>
         </is>
       </c>
       <c r="N84" s="5" t="n">
-        <v>1768</v>
+        <v>1817</v>
       </c>
       <c r="O84" s="5" t="inlineStr">
         <is>
@@ -10382,7 +10394,7 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I85" s="14" t="inlineStr">
+      <c r="I85" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -10404,11 +10416,11 @@
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:40</t>
+          <t>2026-09-13 16:03:14</t>
         </is>
       </c>
       <c r="N85" s="5" t="n">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="O85" s="5" t="inlineStr">
         <is>
@@ -10460,7 +10472,7 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I86" s="14" t="inlineStr">
+      <c r="I86" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -10482,11 +10494,11 @@
       </c>
       <c r="M86" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:40</t>
+          <t>2026-09-13 16:03:14</t>
         </is>
       </c>
       <c r="N86" s="5" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="O86" s="5" t="inlineStr">
         <is>
@@ -10542,7 +10554,7 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I87" s="15" t="inlineStr">
+      <c r="I87" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10564,11 +10576,11 @@
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:41</t>
+          <t>2026-09-13 16:03:15</t>
         </is>
       </c>
       <c r="N87" s="5" t="n">
-        <v>1288</v>
+        <v>1377</v>
       </c>
       <c r="O87" s="5" t="inlineStr">
         <is>
@@ -10640,11 +10652,11 @@
       </c>
       <c r="M88" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:41</t>
+          <t>2026-09-13 16:03:15</t>
         </is>
       </c>
       <c r="N88" s="5" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="O88" s="5" t="inlineStr">
         <is>
@@ -10712,11 +10724,11 @@
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:43</t>
+          <t>2026-09-13 16:03:17</t>
         </is>
       </c>
       <c r="N89" s="5" t="n">
-        <v>1426</v>
+        <v>1579</v>
       </c>
       <c r="O89" s="5" t="inlineStr">
         <is>
@@ -10785,11 +10797,11 @@
       </c>
       <c r="M90" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:43</t>
+          <t>2026-09-13 16:03:17</t>
         </is>
       </c>
       <c r="N90" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O90" s="5" t="inlineStr">
         <is>
@@ -10860,11 +10872,11 @@
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:44</t>
+          <t>2026-09-13 16:03:19</t>
         </is>
       </c>
       <c r="N91" s="5" t="n">
-        <v>1592</v>
+        <v>2349</v>
       </c>
       <c r="O91" s="5" t="inlineStr">
         <is>
@@ -10934,11 +10946,11 @@
       </c>
       <c r="M92" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:46</t>
+          <t>2026-09-13 16:03:21</t>
         </is>
       </c>
       <c r="N92" s="5" t="n">
-        <v>2102</v>
+        <v>2109</v>
       </c>
       <c r="O92" s="5" t="inlineStr">
         <is>
@@ -11006,11 +11018,11 @@
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 15:07:48</t>
+          <t>2026-09-13 16:03:23</t>
         </is>
       </c>
       <c r="N93" s="5" t="n">
-        <v>1616</v>
+        <v>1597</v>
       </c>
       <c r="O93" s="5" t="inlineStr">
         <is>
@@ -11207,7 +11219,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>VC-001</t>
         </is>
@@ -11227,17 +11239,17 @@
           <t>Realtime fan-out silently drops up to 63% of durable messages sent within ~250ms of each other</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="18" t="inlineStr">
         <is>
           <t>In Progress (Aayush is fixing this now)</t>
         </is>
@@ -11331,12 +11343,12 @@
       </c>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Y2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z2" s="5" t="inlineStr">
@@ -11352,7 +11364,7 @@
       <c r="AB2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>VC-002</t>
         </is>
@@ -11372,12 +11384,12 @@
           <t>Blue tick never arrives: a `read` receipt sent in the same tick as `delivered` is lost</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -11472,12 +11484,12 @@
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Y3" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z3" s="5" t="inlineStr">
@@ -11493,7 +11505,7 @@
       <c r="AB3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>VC-003</t>
         </is>
@@ -11513,12 +11525,12 @@
           <t>Read watermark can regress: the higher receipt is lost and a lower one survives</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -11614,12 +11626,12 @@
       </c>
       <c r="X4" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Y4" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z4" s="5" t="inlineStr">
@@ -11631,7 +11643,7 @@
       <c r="AB4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>VC-004</t>
         </is>
@@ -11651,12 +11663,12 @@
           <t>POST /auth/register accepts an arbitrary non-phone string and provisions a full account with real tokens</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -11750,12 +11762,12 @@
       </c>
       <c r="X5" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Y5" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z5" s="5" t="inlineStr">
@@ -11767,7 +11779,7 @@
       <c r="AB5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>VC-005</t>
         </is>
@@ -11787,12 +11799,12 @@
           <t>POST /auth/register accepts a non-base64 device public key, permanently breaking device-key login for that install</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -11886,12 +11898,12 @@
       </c>
       <c r="X6" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Y6" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z6" s="5" t="inlineStr">
@@ -11903,7 +11915,7 @@
       <c r="AB6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>VC-006</t>
         </is>
@@ -11923,12 +11935,12 @@
           <t>POST /auth/revotp/webhook is @Public with no shared secret — an unauthenticated account-provisioning primitive</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -12022,12 +12034,12 @@
       </c>
       <c r="X7" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Y7" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z7" s="5" t="inlineStr">
@@ -12043,7 +12055,7 @@
       <c r="AB7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>VC-007</t>
         </is>
@@ -12063,12 +12075,12 @@
           <t>Edge gateway 502s every proxied route while all upstream services are healthy (dev Render deployment)</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -12184,7 +12196,7 @@
       <c r="AB8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>VC-008</t>
         </is>
@@ -12204,12 +12216,12 @@
           <t>warmBackend() cannot warm the services it targets on the Render topology</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -12324,7 +12336,7 @@
       <c r="AB9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>VC-009</t>
         </is>
@@ -12344,12 +12356,12 @@
           <t>POST /conversations/dm returns 404 through the gateway — 'New chat' cannot work</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -12463,7 +12475,7 @@
       <c r="AB10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>VC-010</t>
         </is>
@@ -12483,12 +12495,12 @@
           <t>Sign-out's authenticated calls ship with no Authorization header, so the server-side push endpoint is never cleared</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -12602,7 +12614,7 @@
       <c r="AB11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>VC-011</t>
         </is>
@@ -12622,12 +12634,12 @@
           <t>Sign-out then sign-in in one process silently destroys every notification action</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -12743,7 +12755,7 @@
       <c r="AB12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>VC-012</t>
         </is>
@@ -12763,12 +12775,12 @@
           <t>Android &lt;= 12 reports notifications as granted even when disabled, so the sync engine drops its background socket</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -12884,7 +12896,7 @@
       <c r="AB13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>VC-013</t>
         </is>
@@ -12904,12 +12916,12 @@
           <t>clearSession() is not a session teardown — the previous account's chat DB, profile and contacts survive into the next sign-in</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -13024,7 +13036,7 @@
       <c r="AB14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>VC-014</t>
         </is>
@@ -13044,12 +13056,12 @@
           <t>Rotating-refresh replay is structurally inevitable on a lost response, and the family revoke is then silently swallowed</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -13166,7 +13178,7 @@
       <c r="AB15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>VC-015</t>
         </is>
@@ -13186,12 +13198,12 @@
           <t>The cnfJkt DPoP binding is dead code — the refresh token is bound to nothing</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -13306,7 +13318,7 @@
       <c r="AB16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>VC-016</t>
         </is>
@@ -13326,12 +13338,12 @@
           <t>MMKV's encryption key is a hardcoded bundle constant, and the Ed25519 device private key is stored inside it</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -13446,7 +13458,7 @@
       <c r="AB17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>VC-017</t>
         </is>
@@ -13466,12 +13478,12 @@
           <t>Message plaintext and the user's own typed replies persist in plaintext SharedPreferences</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -13586,7 +13598,7 @@
       <c r="AB18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>VC-018</t>
         </is>
@@ -13606,12 +13618,12 @@
           <t>No certificate pinning anywhere, in JS or native</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -13725,7 +13737,7 @@
       <c r="AB19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>VC-019</t>
         </is>
@@ -13745,12 +13757,12 @@
           <t>Threat-model controls absent: no FLAG_SECURE, no Play Integrity, no clipboard auto-clear, no root signal</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -13863,7 +13875,7 @@
       <c r="AB20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>VC-020</t>
         </is>
@@ -13883,12 +13895,12 @@
           <t>Concurrent applyServerMessages duplicates every row in the overlap, and can lose a whole batch on a conversation PK clash</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -14003,7 +14015,7 @@
       <c r="AB21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>VC-021</t>
         </is>
@@ -14023,12 +14035,12 @@
           <t>applyReceipt is a non-atomic read-modify-write, so blue ticks can regress to grey</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -14142,7 +14154,7 @@
       <c r="AB22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>VC-022</t>
         </is>
@@ -14162,12 +14174,12 @@
           <t>A SendAck with seq 0 leaves the message permanently un-tickable and permanently duplicated</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -14281,7 +14293,7 @@
       <c r="AB23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>VC-023</t>
         </is>
@@ -14301,12 +14313,12 @@
           <t>One 401 on send turns the entire outbox into permanently failed messages</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -14421,7 +14433,7 @@
       <c r="AB24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>VC-024</t>
         </is>
@@ -14441,12 +14453,12 @@
           <t>Migration-v3's five composite indexes never exist on a fresh install</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14560,7 +14572,7 @@
       <c r="AB25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>VC-025</t>
         </is>
@@ -14580,12 +14592,12 @@
           <t>reassertReceipts() on every connect emits an unbounded burst the gateway silently drops</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -14700,7 +14712,7 @@
       <c r="AB26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>VC-026</t>
         </is>
@@ -14720,12 +14732,12 @@
           <t>Unread count climbs and the read watermark stalls for messages backfilled into the chat you are reading</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -14840,7 +14852,7 @@
       <c r="AB27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>VC-027</t>
         </is>
@@ -14860,12 +14872,12 @@
           <t>'Load older' dead-ends permanently on a deletion hole wider than one page</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="F28" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14979,7 +14991,7 @@
       <c r="AB28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>VC-028</t>
         </is>
@@ -14999,12 +15011,12 @@
           <t>No event_id dedup anywhere — the documented at-least-once guard does not exist</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F29" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -15118,7 +15130,7 @@
       <c r="AB29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>VC-029</t>
         </is>
@@ -15138,12 +15150,12 @@
           <t>Outbox backoff exhaustion is unreachable — MAX_SEND_ATTEMPTS can never fire</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="F30" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -15257,7 +15269,7 @@
       <c r="AB30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>VC-030</t>
         </is>
@@ -15277,12 +15289,12 @@
           <t>Message window sorts by created_at, not seq — a device clock ahead of the server permanently mis-orders own messages</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -15397,7 +15409,7 @@
       <c r="AB31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>VC-031</t>
         </is>
@@ -15417,12 +15429,12 @@
           <t>runQueuedPushActions runs queued notification actions concurrently while claiming to serialize them</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -15537,7 +15549,7 @@
       <c r="AB32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>VC-032</t>
         </is>
@@ -15557,12 +15569,12 @@
           <t>No duplicate-notification suppression, though the monotonic watermark to do it already exists</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -15676,7 +15688,7 @@
       <c r="AB33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>VC-033</t>
         </is>
@@ -15696,12 +15708,12 @@
           <t>Native pending-event queue is a lock-free read-modify-write that can wipe a reply enqueued mid-drain</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="F34" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -15816,7 +15828,7 @@
       <c r="AB34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>VC-034</t>
         </is>
@@ -15836,12 +15848,12 @@
           <t>Retry-After is honored with an unbounded, uncancellable sleep</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F35" s="13" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -15955,7 +15967,7 @@
       <c r="AB35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>VC-035</t>
         </is>
@@ -15975,12 +15987,12 @@
           <t>A misbuilt binary reports env:'dev' while talking to production</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="E36" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16094,7 +16106,7 @@
       <c r="AB36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>VC-036</t>
         </is>
@@ -16114,12 +16126,12 @@
           <t>Cold start after &gt;15 min idle opens the WebSocket with a certainly-expired token</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16234,7 +16246,7 @@
       <c r="AB37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>VC-037</t>
         </is>
@@ -16254,12 +16266,12 @@
           <t>The access token travels in the WebSocket query string</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="F38" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -16373,7 +16385,7 @@
       <c r="AB38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>VC-038</t>
         </is>
@@ -16393,12 +16405,12 @@
           <t>Jest reports a worker that failed to exit gracefully — a leaked timer or handle in the test path</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
+      <c r="E39" s="19" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="F39" s="18" t="inlineStr">
+      <c r="F39" s="19" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -16512,7 +16524,7 @@
       <c r="AB39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>VC-039</t>
         </is>
@@ -16532,12 +16544,12 @@
           <t>Any authenticated user can READ and WRITE any conversation — no authorization on the chat routes, and conversation ids are derivable offline</t>
         </is>
       </c>
-      <c r="E40" s="15" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -16637,12 +16649,12 @@
       </c>
       <c r="X40" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Y40" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z40" s="5" t="inlineStr">
@@ -16658,7 +16670,7 @@
       <c r="AB40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>VC-040</t>
         </is>
@@ -16678,12 +16690,12 @@
           <t>A push endpoint can be registered against another account's userId, redirecting their push wake-ups</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="E41" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="F41" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -16776,12 +16788,12 @@
       </c>
       <c r="X41" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Y41" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z41" s="5" t="inlineStr">
@@ -16797,7 +16809,7 @@
       <c r="AB41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>VC-041</t>
         </is>
@@ -16817,12 +16829,12 @@
           <t>POST /chat/messages accepts a conversationId that does not exist</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F42" s="14" t="inlineStr">
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -16914,12 +16926,12 @@
       </c>
       <c r="X42" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Y42" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z42" s="5" t="inlineStr">
@@ -16935,7 +16947,7 @@
       <c r="AB42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>VC-042</t>
         </is>
@@ -16955,12 +16967,12 @@
           <t>POST /chat/messages accepts an empty or whitespace-only message</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F43" s="13" t="inlineStr">
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17053,12 +17065,12 @@
       </c>
       <c r="X43" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Y43" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z43" s="5" t="inlineStr">
@@ -17074,7 +17086,7 @@
       <c r="AB43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>VC-043</t>
         </is>
@@ -17094,12 +17106,12 @@
           <t>Concurrent refresh-token requests can all succeed — rotation is not race-safe</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F44" s="14" t="inlineStr">
+      <c r="F44" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -17193,12 +17205,12 @@
       </c>
       <c r="X44" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Y44" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z44" s="5" t="inlineStr">
@@ -17214,7 +17226,7 @@
       <c r="AB44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>VC-044</t>
         </is>
@@ -17230,12 +17242,12 @@
           <t>Contact name/contact update does not sync immediately in chat UI</t>
         </is>
       </c>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F45" s="13" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17352,7 +17364,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>VC-045</t>
         </is>
@@ -17368,12 +17380,12 @@
           <t>Real-time messaging and notification-reply sync needs multi-scenario two-device verification</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F46" s="14" t="inlineStr">
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -17489,7 +17501,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>VC-046</t>
         </is>
@@ -17505,12 +17517,12 @@
           <t>Online/offline presence status updates with a noticeable delay</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E47" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17624,7 +17636,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>VC-047</t>
         </is>
@@ -17644,12 +17656,12 @@
           <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="E48" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="F48" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17765,7 +17777,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>VC-048</t>
         </is>
@@ -17781,12 +17793,12 @@
           <t>Message notification omits the sender's name and tapping it does not open the chat</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="E49" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr">
+      <c r="F49" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -17902,7 +17914,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>VC-049</t>
         </is>
@@ -17922,12 +17934,12 @@
           <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="F50" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -18068,560 +18080,560 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Execution</t>
         </is>
       </c>
-      <c r="B3" s="20" t="n"/>
-      <c r="C3" s="20" t="n"/>
+      <c r="B3" s="21" t="n"/>
+      <c r="C3" s="21" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Total tests tracked</t>
         </is>
       </c>
-      <c r="B4" s="22" t="n">
+      <c r="B4" s="23" t="n">
         <v>92</v>
       </c>
-      <c r="C4" s="23" t="inlineStr"/>
+      <c r="C4" s="24" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
-        <v>79</v>
-      </c>
-      <c r="C5" s="23" t="inlineStr"/>
+      <c r="B5" s="23" t="n">
+        <v>78</v>
+      </c>
+      <c r="C5" s="24" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="C6" s="23" t="inlineStr"/>
+      <c r="B6" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="C6" s="24" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>Environment invalid — never counted as a product defect (§47)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="23" t="inlineStr"/>
+      <c r="C8" s="24" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Manually verified</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>A human set this verdict directly in Excel — preserved across every rebuild</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Flaky</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>Result changed across runs — investigated, never auto-passed (§42)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Pass percentage</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>84.8%</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Defects by severity</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="21" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>P0 — Critical</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="24" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C15" s="24" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>P2 — Medium</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" s="24" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>P3 — Low</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="24" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Open bugs</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="C18" s="24" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Fixed bugs</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="C19" s="24" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Regression bugs</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>Result changed across runs — investigated, never auto-passed (§42)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>Pass percentage</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>85.9%</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>Defects by severity</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="20" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>P0 — Critical</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="C14" s="23" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>P1 — High</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="n">
-        <v>22</v>
-      </c>
-      <c r="C15" s="23" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>P2 — Medium</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="C16" s="23" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>P3 — Low</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="23" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>Open bugs</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="n">
-        <v>25</v>
-      </c>
-      <c r="C18" s="23" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>Fixed bugs</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="n">
-        <v>23</v>
-      </c>
-      <c r="C19" s="23" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>Regression bugs</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="23" t="inlineStr"/>
+      <c r="C20" s="24" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Build under test</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>com.velchat.dev 1.0-dev (apk-out/velchat-20260909-2025.apk)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr"/>
+      <c r="C23" s="24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Release gate (§41)</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
+      <c r="B25" s="21" t="n"/>
+      <c r="C25" s="21" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>NO-GO</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>18 open P0/P1 defect(s) block the build.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Blocking defects</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
+      <c r="B28" s="21" t="n"/>
+      <c r="C28" s="21" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>VC-001</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>Realtime fan-out silently drops up to 63% of durable messages sent within ~250ms of each other</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>VC-002</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>Blue tick never arrives: a `read` receipt sent in the same tick as `delivered` is lost</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>VC-003</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>Read watermark can regress: the higher receipt is lost and a lower one survives</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>VC-004</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>POST /auth/register accepts an arbitrary non-phone string and provisions a full account with real tokens</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>VC-005</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>POST /auth/register accepts a non-base64 device public key, permanently breaking device-key login for that install</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>VC-006</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>POST /auth/revotp/webhook is @Public with no shared secret — an unauthenticated account-provisioning primitive</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>VC-007</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>Edge gateway 502s every proxied route while all upstream services are healthy (dev Render deployment)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>VC-009</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>POST /conversations/dm returns 404 through the gateway — 'New chat' cannot work</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>VC-016</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C37" s="23" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>MMKV's encryption key is a hardcoded bundle constant, and the Ed25519 device private key is stored inside it</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>VC-017</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>Message plaintext and the user's own typed replies persist in plaintext SharedPreferences</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>VC-018</t>
         </is>
       </c>
-      <c r="B39" s="22" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C39" s="24" t="inlineStr">
         <is>
           <t>No certificate pinning anywhere, in JS or native</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>VC-032</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C40" s="23" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>No duplicate-notification suppression, though the monotonic watermark to do it already exists</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>VC-033</t>
         </is>
       </c>
-      <c r="B41" s="22" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C41" s="23" t="inlineStr">
+      <c r="C41" s="24" t="inlineStr">
         <is>
           <t>Native pending-event queue is a lock-free read-modify-write that can wipe a reply enqueued mid-drain</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>VC-039</t>
         </is>
       </c>
-      <c r="B42" s="22" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C42" s="23" t="inlineStr">
+      <c r="C42" s="24" t="inlineStr">
         <is>
           <t>Any authenticated user can READ and WRITE any conversation — no authorization on the chat routes, and conversation ids are derivable offline</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="21" t="inlineStr">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>VC-040</t>
         </is>
       </c>
-      <c r="B43" s="22" t="inlineStr">
+      <c r="B43" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C43" s="23" t="inlineStr">
+      <c r="C43" s="24" t="inlineStr">
         <is>
           <t>A push endpoint can be registered against another account's userId, redirecting their push wake-ups</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>VC-041</t>
         </is>
       </c>
-      <c r="B44" s="22" t="inlineStr">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C44" s="23" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>POST /chat/messages accepts a conversationId that does not exist</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="inlineStr">
+      <c r="A45" s="22" t="inlineStr">
         <is>
           <t>VC-043</t>
         </is>
       </c>
-      <c r="B45" s="22" t="inlineStr">
+      <c r="B45" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C45" s="23" t="inlineStr">
+      <c r="C45" s="24" t="inlineStr">
         <is>
           <t>Concurrent refresh-token requests can all succeed — rotation is not race-safe</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="22" t="inlineStr">
         <is>
           <t>VC-045</t>
         </is>
       </c>
-      <c r="B46" s="22" t="inlineStr">
+      <c r="B46" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C46" s="24" t="inlineStr">
         <is>
           <t>Real-time messaging and notification-reply sync needs multi-scenario two-device verification</t>
         </is>
@@ -18709,10 +18721,10 @@
         <v>92</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>0</v>
@@ -18724,41 +18736,41 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Devices NOT covered in this run</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>3 GB Android 10 handset</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Android 10 (API 29)</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>The §M0 reference device. No such device or AVD available. VC-006/VC-012-class is Android &lt;= 12 only and needs it.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>iOS (any)</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>iOS 17+</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Cannot be built on Windows — no macOS/Xcode/CocoaPods.</t>
         </is>
@@ -19717,7 +19729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19767,9 +19779,68 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="23" t="inlineStr">
-        <is>
-          <t>No test has produced different results across runs. A retry that changes a result is recorded as FLAKY and investigated — never silently promoted to PASS (§42/§46).</t>
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>VC-AUTH-027</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>concurrent refreshes of the same token do not both succeed</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>node-harness</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>http://localhost:8080</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>VC-RT-030</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>a `delivered` receipt from B reaches A (grey double tick)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>node-harness</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>http://localhost:8080</t>
         </is>
       </c>
     </row>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -641,7 +641,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-13 16:07 UTC</t>
+          <t>Generated 2026-09-14 04:21 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -11043,7 +11043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB50"/>
+  <dimension ref="A1:AB62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="AA9" s="5" t="inlineStr">
         <is>
-          <t>Blocked on VC-007: if the gateway reached its upstreams, a proxied ping would wake them and this would resolve itself.</t>
+          <t>INVESTIGATED — BLOCKED on information the client does not have. warmBackend() can only ping hosts it knows, and the only per-service origins in config are API_BASE_URL (velchat-edge-gateway-2aje.onrender.com) and WS_URL (velchat-realtime-service-2aje.onrender.com). identity/messaging/content/platform have no hostname anywhere in the repo, so there is nothing to warm them WITH. They appear to share a Render instance suffix (-2aje), which makes a pattern like velchat-identity-service-2aje.onrender.com plausible — but deliberately NOT guessed and baked into a shipping app: a wrong host is at best a wasted request on every cold start and at worst traffic aimed at somebody elses service. To fix, add the real per-service origins to .env.dev/.env.prod (e.g. WARM_ORIGINS as a comma-separated list) and have warmBackend fan its health pings across them; the function already fires them fire-and-forget off the render path, so only the list is missing. Needs the actual Render hostnames from the owner.</t>
         </is>
       </c>
       <c r="AB9" s="5" t="inlineStr"/>
@@ -17392,7 +17392,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -17491,7 +17491,8 @@
       </c>
       <c r="AA46" s="5" t="inlineStr">
         <is>
-          <t>This entry tracks a two-device manual verification pass, not a confirmed defect. Assigned to Tusha Bhadouriya to execute and report actual pass/fail per scenario back into this bug.</t>
+          <t>This entry tracks a two-device manual verification pass, not a confirmed defect. Assigned to Tusha Bhadouriya to execute and report actual pass/fail per scenario back into this bug.
+VERIFIED 2026-09-14 by a live two-device session (A = OPPO CPH2643 Android 16 real device, B = Pixel emulator Android 16), production build against the live backend. PASSED: single-message real-time delivery; an 8-message burst delivered complete and in order; notification posted with the correct sender name, avatar and per-message lines while backgrounded; notification posted after the process was killed with am kill (FCM woke the dead process and it displayed correctly); tapping a notification opens the right conversation and clears the tray; NO notification is posted while that conversation is on screen (active-conversation suppression works); inline notification Reply sends the message, clears the notification and clears the unread badge; typing indicator appears on the peer header; presence shows online and last-seen; offline send queues and flushes in order on reconnect (airplane mode on/off); unread badges and chat-list ordering correct; cold start COLD TotalTime 1367 ms. FAILED, filed separately: VC-051 (message loss with a false read receipt), VC-052 (thread does not follow new messages), VC-053 (notification tap-through titles the chat Chats), VC-054, VC-055, VC-056, VC-057, VC-058, VC-059, VC-060, VC-061.</t>
         </is>
       </c>
       <c r="AB46" s="5" t="inlineStr">
@@ -17626,7 +17627,8 @@
       </c>
       <c r="AA47" s="5" t="inlineStr">
         <is>
-          <t>INVESTIGATED — left OPEN deliberately, no code change. The client side is already correct: activatePresence() does a LEADING await refreshPeerPresence() before it starts the interval, so there is no missing first read, and the poll is correctly scoped to the open chat and paused when suspended/offline (§M13 battery). The delay is architectural and has two additive parts. (1) There is NO live presence push to wait for: the realtime gateway FanoutConsumer subscribes to message/receipt/caption only, never presence.changed, so a presence change cannot reach a socket — this is already documented at the top of infra/network/presence.ts and is why a REST snapshot poll exists at all. (2) The numbers: peer COMES ONLINE is seen at the next poll, PEER_PRESENCE_POLL_MS = 20s, so up to ~20s. Peer GOES OFFLINE is worse, because nobody publishes a leaving event — their online:{userId} Redis key has to EXPIRE server-side (PRESENCE_ONLINE_TTL_MS = 30s from their last 20s heartbeat) and only then can our next poll observe it, so up to ~50s. That matches the reported "noticeable delay" exactly. THE REAL FIX IS BACKEND: have the gateway fan out presence.changed over the WS; the client already has the receiving path (onInboundPresence + normalizePresenceEvent are written and forward-compatible), so it would light up with no client change. The only client-side lever is lowering PEER_PRESENCE_POLL_MS, which buys latency with a REST request per interval per open chat and is a direct trade against the §R5/§R6 battery and request budgets on the 3GB reference device — a product call, not one to make silently, so it is NOT done here. Needs a decision: accept the delay, lower the poll interval (say what latency is acceptable), or schedule the backend fan-out.</t>
+          <t>INVESTIGATED — left OPEN deliberately, no code change. The client side is already correct: activatePresence() does a LEADING await refreshPeerPresence() before it starts the interval, so there is no missing first read, and the poll is correctly scoped to the open chat and paused when suspended/offline (§M13 battery). The delay is architectural and has two additive parts. (1) There is NO live presence push to wait for: the realtime gateway FanoutConsumer subscribes to message/receipt/caption only, never presence.changed, so a presence change cannot reach a socket — this is already documented at the top of infra/network/presence.ts and is why a REST snapshot poll exists at all. (2) The numbers: peer COMES ONLINE is seen at the next poll, PEER_PRESENCE_POLL_MS = 20s, so up to ~20s. Peer GOES OFFLINE is worse, because nobody publishes a leaving event — their online:{userId} Redis key has to EXPIRE server-side (PRESENCE_ONLINE_TTL_MS = 30s from their last 20s heartbeat) and only then can our next poll observe it, so up to ~50s. That matches the reported "noticeable delay" exactly. THE REAL FIX IS BACKEND: have the gateway fan out presence.changed over the WS; the client already has the receiving path (onInboundPresence + normalizePresenceEvent are written and forward-compatible), so it would light up with no client change. The only client-side lever is lowering PEER_PRESENCE_POLL_MS, which buys latency with a REST request per interval per open chat and is a direct trade against the §R5/§R6 battery and request budgets on the 3GB reference device — a product call, not one to make silently, so it is NOT done here. Needs a decision: accept the delay, lower the poll interval (say what latency is acceptable), or schedule the backend fan-out.
+LIVE CHECK 2026-09-14 (two devices, production build): presence did update — the chat header showed "online" while the peer had the app open and switched to "last seen 9:39 am" after the peer backgrounded, and the typing indicator appeared within about 2 s of the peer typing. Latency was not instrumented, so this observation does not close the report; it narrows it to a latency question rather than a functional failure.</t>
         </is>
       </c>
       <c r="AB47" s="5" t="inlineStr">
@@ -17805,7 +17807,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -17904,7 +17906,8 @@
       </c>
       <c r="AA49" s="5" t="inlineStr">
         <is>
-          <t>Reported by Tusha Bhadouriya during production QA testing.</t>
+          <t>Reported by Tusha Bhadouriya during production QA testing.
+RE-TESTED LIVE 2026-09-14 on a production build against the live backend, two devices. Both halves of this report are now correct: the notification DOES carry the sender name (dumpsys shows android.title="Aayush Jain 🤗" with the sender photo and per-message MessagingStyle lines), and tapping it DOES open that conversation (topResumedActivity becomes com.velchat/.MainActivity on the Chat route and every VelChat notification is cleared). Evidence: scratchpad/shots/b_shade.png, b_tapthrough.png. One residual defect on the same path is filed separately as VC-053: the deep link carries no name param, so ChatHeader falls back to the tabs.chats label and the header reads "Chats". A second residual, the chat not opening at the newest message, is covered by VC-052.</t>
         </is>
       </c>
       <c r="AB49" s="5" t="inlineStr">
@@ -18051,6 +18054,1552 @@
           <t>Tusha Bhadouriya</t>
         </is>
       </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>VC-050</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>VC-51</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>authBootstrap.test.ts: cold start with a session already on the device</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Cold start holds a splash screen on a network refresh — up to minutes before home appears</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>App launch / Auth bootstrap</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/features/auth/hooks/useAuth.ts (useAuthBootstrap) + app/App.tsx</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>Every launch more than 15 minutes after the last one</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>Deterministic — access tokens live 15 minutes</t>
+        </is>
+      </c>
+      <c r="P51" s="5" t="inlineStr">
+        <is>
+          <t>A signed-in install that has not been opened for more than 15 minutes, against a hibernating free-tier backend.</t>
+        </is>
+      </c>
+      <c r="Q51" s="5" t="inlineStr">
+        <is>
+          <t>1. Leave the app closed for more than 15 minutes so the access token expires and the Render services hibernate.
+2. Open the app.
+3. Time how long the splash screen stays up before the home screen appears.</t>
+        </is>
+      </c>
+      <c r="R51" s="5" t="inlineStr">
+        <is>
+          <t>Home renders immediately from local data. The app is offline-first — §M0 rule 2 is that the UI never waits on the network on the render path.</t>
+        </is>
+      </c>
+      <c r="S51" s="5" t="inlineStr">
+        <is>
+          <t>App.tsx renders &lt;Splash/&gt; until useAuthBootstrap reports ready, and the hook awaited a token refresh whenever the stored access token was expired. Against a hibernating free-tier backend that refresh alone takes 40-60s (client.ts documents a measured 44s wake, DEFAULT_TIMEOUT is 60s), and on timeout the hook then awaited TWO more network calls (requestChallenge, loginWithDeviceKey) before giving up — so the splash could hold for minutes.</t>
+        </is>
+      </c>
+      <c r="T51" s="5" t="inlineStr">
+        <is>
+          <t>The app looks hung on every real launch. This is the first thing a user sees, so it reads as the whole app being broken rather than one slow request.</t>
+        </is>
+      </c>
+      <c r="U51" s="5" t="inlineStr">
+        <is>
+          <t>The bootstrap conflated 'can we show the app' with 'is the access token fresh enough to open a socket'.</t>
+        </is>
+      </c>
+      <c r="V51" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed by reading the boot path and reproduced in a hook test: with the refresh mocked to never resolve, `ready` never became true.</t>
+        </is>
+      </c>
+      <c r="W51" s="5" t="inlineStr"/>
+      <c r="X51" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y51" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA51" s="5" t="inlineStr">
+        <is>
+          <t>FIX: split the two questions the bootstrap had conflated — "can we show the app" and "is the access token fresh enough for a socket". If a session exists on the device at all (hasSession(), presence-only), the app now hydrates and reports ready IMMEDIATELY, whatever the token age; the chat list renders from the local DB, the HTTP client refreshes on its first 401, and the socket heals itself via 4001 -&gt; refresh -&gt; reconnect. VC-036 is not regressed: a fresh token is still wanted as early as possible so the first handshake is not doomed, so the refresh is still fired at once — it just runs BEHIND the app instead of in front of it. The no-session path (signed out but a device key survives) still attempts a silent restore, but is now bounded by MAX_SILENT_RESTORE_MS = 4000 so a hibernating backend cannot freeze the splash; a restore that lands later still navigates home on its own, because RootNavigator follows the auth store (state === active). Verified: full jest suite 521/521 pass (5 new hook tests, two of which fail against the old code by hanging until waitFor times out), tsc --noEmit clean, eslint 0 errors. Measured on device: not yet — needs a launch on real hardware to confirm the wall-clock improvement.</t>
+        </is>
+      </c>
+      <c r="AB51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>VC-051</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>VC-52</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr"/>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>A message the device was pushed for never reaches the chat, and no reconnect ever heals it — the sender still sees blue read ticks</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Chat / messaging — inbound persistence + reconnect backfill</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/domain/sync (applyServerMessages / cursor sync) + apps/mobile/src/infra/push</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>Production build, live backend</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>Pixel emulator (Android 16, x86_64) receiving; OPPO CPH2643 (Android 16) sending</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>Intermittent — 2 confirmed occurrences in a 45-minute two-device session</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>Intermittent. Reproduced once deliberately (recipient process killed with `am kill`, sender sends, push wakes the process); a second identical attempt persisted correctly.</t>
+        </is>
+      </c>
+      <c r="P52" s="5" t="inlineStr">
+        <is>
+          <t>Two signed-in devices in the same DM. Recipient's app process is not running (killed by the OS or by the user), so the inbound message arrives via an FCM wake rather than the live WebSocket.</t>
+        </is>
+      </c>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>1. Device A and device B are signed in to the same DM.
+2. Kill B's app PROCESS without force-stopping the package: adb -s &lt;B&gt; shell am kill com.velchat (confirm with `pidof com.velchat` returning empty).
+3. From A, send a message (test used the text 'KILL2').
+4. On B, confirm the push arrived: adb -s &lt;B&gt; shell dumpsys notification --noredact | grep android.text  -&gt;  shows 'KILL2'.
+5. Open VelChat on B from the launcher and open that DM.
+6. Scroll the whole thread. Cold-start B several times and reopen the thread.</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="inlineStr">
+        <is>
+          <t>A message the device was woken for is persisted to the local DB by the wake, or — failing that — pulled in by the next `sync {cursor}` + `?afterSeq=` backfill on reconnect (§L6). The recipient must end up holding every message the sender sees, and a read receipt must only ever be sent for a message that was actually stored.</t>
+        </is>
+      </c>
+      <c r="S52" s="5" t="inlineStr">
+        <is>
+          <t>KILL2 produced a notification on B (proved by dumpsys) but never appeared in B's conversation. It is still absent after 3 app cold starts and multiple reconnects, i.e. the loss is permanent, not a render delay. Meanwhile A shows KILL2 with BLUE double ticks (read). The same signature was seen earlier in the session for two messages ('G' and 'M', 08:59) that A shows as read and B has never held.</t>
+        </is>
+      </c>
+      <c r="T52" s="5" t="inlineStr">
+        <is>
+          <t>Silent, permanent message loss with a POSITIVE read confirmation to the sender. This is the worst failure a messenger can have: the sender believes the recipient read it, the recipient never saw it, and nothing in either UI indicates anything went wrong. No user action can recover the message.</t>
+        </is>
+      </c>
+      <c r="U52" s="5" t="inlineStr">
+        <is>
+          <t>Two candidates, not yet separated: (a) the headless push wake posts the notification but its DB write is lost when the process is reaped before the WatermelonDB write commits; (b) the message is never durably fanned out (see VC-001) and the reconnect backfill does not re-request it. Either way the CLIENT-side defect is the same: the `sync {cursor}` + `afterSeq` backfill is not self-healing — a gap that exists once stays forever. The false `read` receipt means a receipt is being emitted from a path that does not require the message row to exist locally.</t>
+        </is>
+      </c>
+      <c r="V52" s="5" t="inlineStr"/>
+      <c r="W52" s="5" t="inlineStr"/>
+      <c r="X52" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y52" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA52" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: scratchpad/shots/a_inline_rx.png (A shows KILL2 09:39 with blue ticks) vs scratchpad/shots/b_kill2_check.png (B's thread jumps BG1 09:37 -&gt; KILL1 09:37 -&gt; hhh 09:40, no KILL2). Related backend defect VC-001 may be the upstream cause, but the client must still heal the gap on reconnect and must not report `read` for a message it does not hold.</t>
+        </is>
+      </c>
+      <c r="AB52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>VC-052</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>VC-53</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr"/>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Chat thread does not follow the newest message — incoming and own-sent bubbles land hidden behind the composer</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Chat / messaging — message list scroll behaviour</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/features/chat/ui/ChatScreen.tsx (FlashList + follow effect) with @shopify/flash-list 2.3.2</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>Production build, live backend</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>Reproduced on BOTH the OPPO CPH2643 (Android 16) and the Pixel emulator (Android 16)</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>Intermittent but very common — hit on the majority of message arrivals in a 45-minute session</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>Reproduced repeatedly on both devices, for incoming messages, for the user's own sent messages, and after opening the chat from a notification.</t>
+        </is>
+      </c>
+      <c r="P53" s="5" t="inlineStr">
+        <is>
+          <t>A DM with enough history to be scrollable (the thread used had ~40 messages). The list is already at the bottom, showing the newest message.</t>
+        </is>
+      </c>
+      <c r="Q53" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a DM and make sure the newest message is visible at the bottom (tap the jump-to-latest button if it is showing).
+2. Have the peer send a message — or type and send one yourself.
+3. Watch the bottom of the thread.</t>
+        </is>
+      </c>
+      <c r="R53" s="5" t="inlineStr">
+        <is>
+          <t>The thread follows the newest message: the new bubble scrolls into view above the composer, the way WhatsApp does. This is what `shouldScrollToLatest` + `scrollToOffset({offset: 0})` in ChatScreen were added to guarantee.</t>
+        </is>
+      </c>
+      <c r="S53" s="5" t="inlineStr">
+        <is>
+          <t>The list stays anchored on the OLD content. The new bubble is left below the fold — typically clipped behind the composer, so only a sliver of it shows — and after two or three arrivals the jump-to-latest button appears and the user has to scroll by hand. The offset ends up wrong by almost exactly the height of the newly inserted bubbles.</t>
+        </is>
+      </c>
+      <c r="T53" s="5" t="inlineStr">
+        <is>
+          <t>The single most-used interaction in the app feels broken. A user sends a message and cannot see it; a message arrives and they do not know. Reported directly by the product owner as 'new message ane ya krne pe chup jata hai, scroll krke upar krna pdta hai'.</t>
+        </is>
+      </c>
+      <c r="U53" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED by reading @shopify/flash-list@2.3.2: `maintainVisibleContentPosition` is ENABLED BY DEFAULT (RecyclerView.js -&gt; maintainVisibleContentPositionInternal sets `minIndexForVisible: 0` whenever `maintainVisibleContentPosition?.disabled` is not true). The chat list is `inverted`, which FlashList implements purely as a scaleY(-1) transform, so a NEW message is inserted at internal index 0 — the scroll START. The native anchor therefore pins the viewport and pushes the scroll offset out by the inserted height, undoing the `scrollToOffset({offset: 0})` the follow effect issues in the same commit. The library's own follow knob does not help: `autoscrollToBottomThreshold` defaults to -1 (disabled) and targets the internal END (the OLDEST messages in an inverted list), and `autoscrollToTopThreshold` is declared in FlashListProps.d.ts but is NEVER READ anywhere in the 2.3.2 implementation.</t>
+        </is>
+      </c>
+      <c r="V53" s="5" t="inlineStr"/>
+      <c r="W53" s="5" t="inlineStr"/>
+      <c r="X53" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y53" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z53" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA53" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: scratchpad/shots/b_fg_follow.png (B at the bottom, F1-F3 arrive, list stays on S8 and the jump FAB appears), scratchpad/shots/b_one.png (single message ONE1 arrives, list left exactly one bubble short), scratchpad/shots/a_own_follow.png (A's OWN sent ONE1 clipped behind the composer), scratchpad/shots/b_offline_send.png (own offline sends clipped). The race explains the intermittency: sometimes the manual scroll lands after the anchor adjustment and it looks fine.</t>
+        </is>
+      </c>
+      <c r="AB53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>VC-053</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>VC-54</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr"/>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Chat opened from a notification is titled "Chats" instead of the contact's name, and the avatar loses its initial</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F54" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Notifications — tap-through / deep link</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/features/chat/ui/chat/ChatHeader.tsx:95 + apps/mobile/src/navigation/RootNavigator.tsx (linking: 'chat/:conversationId')</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>Production build, live backend</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>Pixel emulator (Android 16)</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>Every time — deterministic</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P54" s="5" t="inlineStr">
+        <is>
+          <t>A DM with an unread message notification in the tray.</t>
+        </is>
+      </c>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>1. Background VelChat on the recipient device.
+2. Have the peer send a message so a notification is posted.
+3. Pull down the shade and tap the notification body (not an action).
+4. Look at the chat header.</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="inlineStr">
+        <is>
+          <t>The header reads the contact's name — exactly what the same chat shows when opened from the chat list ('Aayush Jain 🤗').</t>
+        </is>
+      </c>
+      <c r="S54" s="5" t="inlineStr">
+        <is>
+          <t>The header reads 'Chats' — the bottom-tab label — while the avatar and the 'online' presence line underneath are correct. Opening the same conversation from the chat list immediately afterwards shows the right name, which isolates it to the deep-link entry point.</t>
+        </is>
+      </c>
+      <c r="T54" s="5" t="inlineStr">
+        <is>
+          <t>Tapping a notification lands the user in a chat that does not say who they are talking to. On a device with several conversations it is genuinely ambiguous, and it makes the deep-link path look unfinished.</t>
+        </is>
+      </c>
+      <c r="U54" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED in code. The linking config maps `Chat: 'chat/:conversationId'`, so a deep link supplies `conversationId` and NOTHING else; `route.params.name` is `undefined`. ChatHeader.tsx:95 then does `const title = name ?? tr('tabs.chats')` and line 96 `const initial = (name ?? '').trim().charAt(0).toUpperCase()`, so the title falls back to the tab label and the avatar's placeholder letter goes blank. The header already subscribes to the conversation row via `useConversationIdentity(conversationId)` and reads `peerAvatarUrl` off it — the row's `name` column is right there and simply is not used.</t>
+        </is>
+      </c>
+      <c r="V54" s="5" t="inlineStr"/>
+      <c r="W54" s="5" t="inlineStr"/>
+      <c r="X54" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y54" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA54" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: scratchpad/shots/b_tapthrough.png and b_jump.png (header 'Chats' after notification tap) vs scratchpad/shots/b_off_kbd.png (header 'Aayush Jain 🤗' for the same chat opened from the list). Relates to VC-048, which reported the tap-through as not opening the chat at all; the open now works, this is the remaining defect on that path.</t>
+        </is>
+      </c>
+      <c r="AB54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>VC-054</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>VC-55</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Notification group summary says "N new messages" but N is the number of chats, not the number of messages</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Notifications — bundled group summary</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/android/app/src/main/java/com/velchat/push/PushNotifications.kt (postSummary) + res/values/push_strings.xml (push_summary_text)</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>Production build, live backend</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>Pixel emulator (Android 16)</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>Every time two or more conversations have notifications</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P55" s="5" t="inlineStr">
+        <is>
+          <t>At least two conversations holding undismissed message notifications, so the group summary is posted at all.</t>
+        </is>
+      </c>
+      <c r="Q55" s="5" t="inlineStr">
+        <is>
+          <t>1. With VelChat backgrounded and notifications from more than one chat pending, have a peer send 8 messages in one conversation.
+2. Read the summary: adb shell dumpsys notification --noredact | grep -A2 GROUP_SUMMARY
+3. Repeat with exactly ONE new message arriving.</t>
+        </is>
+      </c>
+      <c r="R55" s="5" t="inlineStr">
+        <is>
+          <t>The summary states how many new MESSAGES are waiting — or is reworded to state how many chats.</t>
+        </is>
+      </c>
+      <c r="S55" s="5" t="inlineStr">
+        <is>
+          <t>The summary read 'VelChat — 5 new messages' after 8 messages arrived, and read 'VelChat — 5 new messages' again after a single message arrived. The number is the count of conversations with a non-zero counter and never changes with the message count.</t>
+        </is>
+      </c>
+      <c r="T55" s="5" t="inlineStr">
+        <is>
+          <t>The collapsed notification — often the only thing a user sees on a locked phone — lies about how much is waiting, and does so in both directions (under-reports a burst, over-reports a single message).</t>
+        </is>
+      </c>
+      <c r="U55" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED in code. `postSummary` does `val active = store.countedConversations()` then `val total = active` and formats it with `R.plurals.push_summary_text` ('%d new messages'). `PushStore.countedConversations()` returns the number of KEYS whose count is &gt; 0, discarding the per-conversation counts it just read. The per-conversation counts are already stored, so summing them is a one-line change.</t>
+        </is>
+      </c>
+      <c r="V55" s="5" t="inlineStr"/>
+      <c r="W55" s="5" t="inlineStr"/>
+      <c r="X55" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y55" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z55" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA55" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: dumpsys output captured twice in the live session (8 messages -&gt; '5 new messages'; 1 message -&gt; '5 new messages').</t>
+        </is>
+      </c>
+      <c r="AB55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>VC-055</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>VC-56</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr"/>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Every notification is tinted the abandoned violet #7C5CFF, which matches nothing in the shipped monochrome theme</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Notifications — visual identity</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/android/app/src/main/res/values/push_strings.xml (color push_accent) consumed by PushNotifications.kt setColor()</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>Pixel emulator (Android 16); applies to every Android device</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>Every notification</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P56" s="5" t="inlineStr">
+        <is>
+          <t>Any VelChat message notification.</t>
+        </is>
+      </c>
+      <c r="Q56" s="5" t="inlineStr">
+        <is>
+          <t>1. Receive any message notification.
+2. adb shell dumpsys notification --noredact | grep 'pkg=com.velchat'  -&gt;  the record shows color=0xff7c5cff.
+3. Compare against the app's own accent: apps/mobile/src/design-system/tokens.ts brandFrom.</t>
+        </is>
+      </c>
+      <c r="R56" s="5" t="inlineStr">
+        <is>
+          <t>The notification accent matches the app's brand. The shipped theme is monochrome — `brandFrom` is #0B0B0C in light and #F5F5F7 in dark — so the notification tint should be the neutral brand colour, not a hue the app never uses.</t>
+        </is>
+      </c>
+      <c r="S56" s="5" t="inlineStr">
+        <is>
+          <t>push_accent is hardcoded to #7C5CFF and the resource comment still describes it as 'Brand violet — the notification accent, matching the app's gradient start'. The violet-&gt;pink gradient direction it refers to was dropped; nothing in the running app is violet, so every notification carries an accent from a design that no longer exists.</t>
+        </is>
+      </c>
+      <c r="T56" s="5" t="inlineStr">
+        <is>
+          <t>Notifications are the app's most public surface — they appear on the lock screen next to every other app. A tint that appears nowhere in the product reads as an unfinished or mismatched build and weakens brand recognition.</t>
+        </is>
+      </c>
+      <c r="U56" s="5" t="inlineStr">
+        <is>
+          <t>Leftover from the abandoned violet-&gt;pink design direction in docs/design-direction.md. The app tokens were migrated to monochrome; the native notification colour was not.</t>
+        </is>
+      </c>
+      <c r="V56" s="5" t="inlineStr"/>
+      <c r="W56" s="5" t="inlineStr"/>
+      <c r="X56" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y56" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z56" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA56" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed by reading tokens.ts (brandFrom '#0B0B0C' / '#F5F5F7') against push_strings.xml (#7C5CFF) and by the live dumpsys record color=0xff7c5cff.</t>
+        </is>
+      </c>
+      <c r="AB56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>VC-056</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>VC-57</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr"/>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Notification message lines are ordered by arrival, not by message time — an out-of-order push shows the wrong 'latest' message</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Notifications — MessagingStyle thread</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/android/app/src/main/java/com/velchat/push/PushNotifications.kt (line store -&gt; MessagingStyle) + PushStore lines</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>Production build, live backend</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>Pixel emulator (Android 16)</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>Whenever FCM delivers two messages out of order — not rare, FCM gives no ordering guarantee</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
+          <t>Reproduced once by holding one push back (recipient package force-stopped) and letting a later one land first.</t>
+        </is>
+      </c>
+      <c r="P57" s="5" t="inlineStr">
+        <is>
+          <t>Two messages for the same conversation where the second-sent one is delivered to the device first.</t>
+        </is>
+      </c>
+      <c r="Q57" s="5" t="inlineStr">
+        <is>
+          <t>1. Send message 1 while the recipient package is in the stopped state, so FCM holds it.
+2. Launch the recipient app (clearing FLAG_STOPPED) and send message 2 — FCM releases the held message 1 after message 2 lands.
+3. Expand the notification and read the message lines.</t>
+        </is>
+      </c>
+      <c r="R57" s="5" t="inlineStr">
+        <is>
+          <t>The MessagingStyle thread is ordered by the message's own time / seq, so the last line is the newest message — matching what the chat itself shows.</t>
+        </is>
+      </c>
+      <c r="S57" s="5" t="inlineStr">
+        <is>
+          <t>The thread listed '... BG1, KILL2, KILL1' — KILL1 (09:37) below KILL2 (09:39) — and the collapsed notification therefore advertised KILL1 as the latest message. The in-app conversation ordered the same two messages correctly, so this is purely the notification's own line store.</t>
+        </is>
+      </c>
+      <c r="T57" s="5" t="inlineStr">
+        <is>
+          <t>The notification tells the user the wrong thing is the most recent message, and the preview they glance at on the lock screen can be a message they have already seen.</t>
+        </is>
+      </c>
+      <c r="U57" s="5" t="inlineStr">
+        <is>
+          <t>Lines are appended to the per-conversation store in arrival order and rendered in that order. The push payload already carries `seq`, which the reply/mark-read actions use — sorting the stored lines by it before building MessagingStyle would make the order independent of FCM's (explicitly unguaranteed) delivery order.</t>
+        </is>
+      </c>
+      <c r="V57" s="5" t="inlineStr"/>
+      <c r="W57" s="5" t="inlineStr"/>
+      <c r="X57" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y57" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z57" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA57" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: scratchpad/shots/b_reply_open.png (expanded notification shows S6, S7, S8, BG1, KILL2, KILL1) vs scratchpad/shots/a_inline_rx.png (chat shows KILL1 09:37 then KILL2 09:39, correct).</t>
+        </is>
+      </c>
+      <c r="AB57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>VC-057</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>VC-58</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr"/>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Notification re-lists messages the user has already read once the chat is reopened and a new message arrives</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Notifications — thread clearing on chat open</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/android/app/src/main/java/com/velchat/push/PushNotifications.kt (cancel -&gt; store.clearLines) + apps/mobile/src/infra/push/pushService.ts (clearConversationNotification)</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>Production build, live backend</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Pixel emulator (Android 16)</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>Every time a chat is opened from its own notification and a later message then arrives</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>Reproduced in the live session</t>
+        </is>
+      </c>
+      <c r="P58" s="5" t="inlineStr">
+        <is>
+          <t>A conversation whose notification the user has already opened and read.</t>
+        </is>
+      </c>
+      <c r="Q58" s="5" t="inlineStr">
+        <is>
+          <t>1. Receive several messages while backgrounded (test used S1..S8) so the notification thread holds them.
+2. Tap the notification to open the chat and read them; the tray entry disappears.
+3. Background the app again and have the peer send ONE new message.
+4. Expand the new notification.</t>
+        </is>
+      </c>
+      <c r="R58" s="5" t="inlineStr">
+        <is>
+          <t>The thread starts fresh from the new message. PushNotifications.cancel() already calls store.clearLines(conversationId) precisely for this, and its comment says so: 'opening a chat and then receiving one new message would rebuild the notification with every line the user had already read.'</t>
+        </is>
+      </c>
+      <c r="S58" s="5" t="inlineStr">
+        <is>
+          <t>The rebuilt notification listed S6, S7, S8, BG1 and then the new lines — messages the user had already read in the app minutes earlier.</t>
+        </is>
+      </c>
+      <c r="T58" s="5" t="inlineStr">
+        <is>
+          <t>The user is re-notified about messages they have already read, so the notification badge and preview overstate what is actually new and the thread is cluttered with stale content. It also undermines trust that opening a chat actually clears it.</t>
+        </is>
+      </c>
+      <c r="U58" s="5" t="inlineStr">
+        <is>
+          <t>The chat-open path does not reach `PushNotifications.cancel()`. The tray entry vanishing on tap is explained by the notification's own AUTO_CANCEL flag, which removes the posted notification but does NOT run the app's clearing code, so `store.clearLines()` never executes and the stored lines survive to be rebuilt into the next notification. Needs a check that `setActiveConversationForPush`/`clearConversationNotification` fires on chat mount and that it routes into `cancel()` rather than only `NotificationManager.cancel()`.</t>
+        </is>
+      </c>
+      <c r="V58" s="5" t="inlineStr"/>
+      <c r="W58" s="5" t="inlineStr"/>
+      <c r="X58" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y58" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA58" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: scratchpad/shots/b_shade.png (S3..S8 before opening), scratchpad/shots/b_tapthrough.png (chat opened, tray cleared, all read), scratchpad/shots/b_reply_open.png (next notification still carries S6, S7, S8, BG1).</t>
+        </is>
+      </c>
+      <c r="AB58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>VC-058</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>VC-59</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr"/>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Chat-list preview can regress to an older message — the preview is written unconditionally while the timestamp is guarded</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Chat list — last-message preview</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/infra/db/queries.ts (upsertConversation)</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>Production build, live backend</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>Pixel emulator (Android 16)</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>Whenever messages are applied out of order (out-of-order push, or a backfill landing after a live message)</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t>Observed once live; the code path is deterministic once an older patch arrives after a newer one.</t>
+        </is>
+      </c>
+      <c r="P59" s="5" t="inlineStr">
+        <is>
+          <t>Two messages for one conversation applied in the wrong order.</t>
+        </is>
+      </c>
+      <c r="Q59" s="5" t="inlineStr">
+        <is>
+          <t>1. Arrange for message 2 (newer) to be applied to the local DB before message 1 (older) — e.g. an FCM-held push released after a later one.
+2. Open the Chats list and read that row's preview and timestamp.</t>
+        </is>
+      </c>
+      <c r="R59" s="5" t="inlineStr">
+        <is>
+          <t>The row previews the newest message. A stale patch must not be able to move the preview backwards, exactly as it cannot move the sort key backwards.</t>
+        </is>
+      </c>
+      <c r="S59" s="5" t="inlineStr">
+        <is>
+          <t>The row previewed 'KILL1' while 'KILL2' was the newer message, and stayed that way until a still-newer message arrived.</t>
+        </is>
+      </c>
+      <c r="T59" s="5" t="inlineStr">
+        <is>
+          <t>The chat list — the app's home screen — shows the wrong 'last message' for a conversation, so the user's summary of their inbox is wrong and can point at a message they have already read.</t>
+        </is>
+      </c>
+      <c r="U59" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED in code. In `upsertConversation` the sort key is protected: `if (patch.lastMessageAt !== undefined &amp;&amp; patch.lastMessageAt &gt;= (c.lastMessageAt ?? 0)) c.lastMessageAt = patch.lastMessageAt;` with the comment 'Never move the sort key backwards (a stale patch mustn't reorder the list)'. The preview immediately above it has no such guard: `if (patch.lastMessagePreview !== undefined) c.lastMessagePreview = patch.lastMessagePreview;`. So a stale patch is prevented from reordering the list but is still allowed to overwrite what the row says.</t>
+        </is>
+      </c>
+      <c r="V59" s="5" t="inlineStr"/>
+      <c r="W59" s="5" t="inlineStr"/>
+      <c r="X59" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y59" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA59" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: scratchpad/shots/b_after_reply.png (row reads 'KILL1' while KILL2 was newer). Fix is to move the preview write inside the same freshness check as the timestamp.</t>
+        </is>
+      </c>
+      <c r="AB59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>VC-059</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>VC-60</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr"/>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Composer's emoji, attach, camera and mic buttons are dead controls that look and behave as if they work</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F60" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Chat / messaging — composer</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/features/chat/ui/chat/Composer.tsx</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>Both test devices</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>Every time</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P60" s="5" t="inlineStr">
+        <is>
+          <t>Any open chat.</t>
+        </is>
+      </c>
+      <c r="Q60" s="5" t="inlineStr">
+        <is>
+          <t>1. Open any chat.
+2. Tap the smiley, the paperclip, the camera, and (with the field empty) the round mic button.</t>
+        </is>
+      </c>
+      <c r="R60" s="5" t="inlineStr">
+        <is>
+          <t>A control the user can press either does something or is visibly unavailable. Four of the five controls on the primary input surface should not be indistinguishable from working ones.</t>
+        </is>
+      </c>
+      <c r="S60" s="5" t="inlineStr">
+        <is>
+          <t>All four are wired to `noop`. They render at full opacity, carry `accessibilityRole="button"` with a real label, and give press feedback (opacity dips to 0.6, and the mic shares the send button's full brand fill), so nothing tells the user they are inert. Tapping does nothing at all — no sheet, no toast, no disabled state.</t>
+        </is>
+      </c>
+      <c r="T60" s="5" t="inlineStr">
+        <is>
+          <t>Four of the five affordances in the composer are dead. A user tapping the paperclip or the mic concludes the app is broken rather than that the feature is not built yet, and a screen-reader user is told they are buttons with no indication they do nothing.</t>
+        </is>
+      </c>
+      <c r="U60" s="5" t="inlineStr">
+        <is>
+          <t>Intentional stubs — the file's own header says 'Only send is wired ... emoji / attach / camera / mic are no-op stubs for now' — but they ship looking fully enabled.</t>
+        </is>
+      </c>
+      <c r="V60" s="5" t="inlineStr"/>
+      <c r="W60" s="5" t="inlineStr"/>
+      <c r="X60" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y60" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z60" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA60" s="5" t="inlineStr">
+        <is>
+          <t>Minimum viable fix for a release build: hide the unimplemented controls, or render them disabled (reduced opacity + accessibilityState disabled) so neither sighted nor screen-reader users are misled.</t>
+        </is>
+      </c>
+      <c r="AB60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>VC-060</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>VC-61</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr"/>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Incoming message bubbles are nearly invisible in light theme — #F7F7F8 on #FFFFFF with no border (1.04:1)</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F61" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Chat / messaging — message bubble</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/features/chat/ui/chat/MessageBubble.tsx + design-system/tokens.ts</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>OPPO CPH2643 (Android 16), light theme, default 'plain' wallpaper</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>Every incoming message in light theme on the plain wallpaper</t>
+        </is>
+      </c>
+      <c r="O61" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P61" s="5" t="inlineStr">
+        <is>
+          <t>Light theme, chat wallpaper left on the default 'plain'.</t>
+        </is>
+      </c>
+      <c r="Q61" s="5" t="inlineStr">
+        <is>
+          <t>1. Set the app to light theme and leave the chat wallpaper on 'plain'.
+2. Open a chat containing messages from the other person.
+3. Look at where each incoming bubble ends and the background begins.</t>
+        </is>
+      </c>
+      <c r="R61" s="5" t="inlineStr">
+        <is>
+          <t>An incoming bubble reads as a distinct shape. WCAG 1.4.11 asks for 3:1 between a UI component's boundary and its background.</t>
+        </is>
+      </c>
+      <c r="S61" s="5" t="inlineStr">
+        <is>
+          <t>The bubble is `bgSubtle` #F7F7F8 on `bgBase` #FFFFFF — a contrast ratio of about 1.04:1 — and no border is drawn, so the bubble has essentially no edge. MessageBubble only adds a hairline when `t.scheme === 'dark'` or when a decorated wallpaper supplies `incomingBorder`; the light + plain combination, which is the default, gets neither.</t>
+        </is>
+      </c>
+      <c r="T61" s="5" t="inlineStr">
+        <is>
+          <t>Incoming messages read as floating text rather than as bubbles, the incoming/outgoing distinction weakens, and the effect is worst in bright light and for low-vision users. Own messages are fine (solid black fill), so the thread looks lopsided.</t>
+        </is>
+      </c>
+      <c r="U61" s="5" t="inlineStr">
+        <is>
+          <t>The dark-mode hairline was added deliberately ('shadows don't register on a near-black ground') but the light + plain case was assumed to have enough contrast from the fill alone. It does not: the two tokens are 1.04:1 apart.</t>
+        </is>
+      </c>
+      <c r="V61" s="5" t="inlineStr"/>
+      <c r="W61" s="5" t="inlineStr"/>
+      <c r="X61" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y61" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z61" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA61" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: scratchpad/shots/a_relaunch.png — the 'kkr' and 'h' bubbles in light theme. Fix options: give the incoming bubble a hairline in BOTH schemes, or darken `bgSubtle` for this use.</t>
+        </is>
+      </c>
+      <c r="AB61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>VC-061</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>VC-62</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr"/>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>A 48dp empty band sits between the composer and the keyboard whenever the keyboard is open</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F62" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Chat / messaging — composer layout</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/features/chat/ui/chat/Composer.tsx (paddingBottom: keyboardUp ? t.spacing.huge : ...)</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>OPPO CPH2643 (Android 16)</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>Every time the keyboard opens in a chat</t>
+        </is>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P62" s="5" t="inlineStr">
+        <is>
+          <t>Any open chat.</t>
+        </is>
+      </c>
+      <c r="Q62" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a chat and tap the message field so the keyboard comes up.
+2. Look at the gap between the bottom of the composer pill and the top of the keyboard.</t>
+        </is>
+      </c>
+      <c r="R62" s="5" t="inlineStr">
+        <is>
+          <t>The composer sits close above the keyboard, the way WhatsApp and every other messenger do — a few dp at most.</t>
+        </is>
+      </c>
+      <c r="S62" s="5" t="inlineStr">
+        <is>
+          <t>`paddingBottom` is `t.spacing.huge` (48dp) when the keyboard is up, leaving a wide empty strip between the input bar and the keyboard. On a 2412px screen this is roughly 144px of dead space that could be showing another message.</t>
+        </is>
+      </c>
+      <c r="T62" s="5" t="inlineStr">
+        <is>
+          <t>With the keyboard open — the state the user is in while actually writing — the app shows one fewer message than it needs to and the input bar looks detached from the keyboard. It reads as a layout mistake rather than a design choice.</t>
+        </is>
+      </c>
+      <c r="U62" s="5" t="inlineStr">
+        <is>
+          <t>The keyboard-up branch was tuned while the manual keyboard-height lift was being worked out and the compensation was left larger than it needs to be.</t>
+        </is>
+      </c>
+      <c r="V62" s="5" t="inlineStr"/>
+      <c r="W62" s="5" t="inlineStr"/>
+      <c r="X62" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y62" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z62" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA62" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: scratchpad/shots/a_cal.png and a_own_follow.png — the white band between the composer pill and the keyboard's suggestion strip. Same file also sets `borderTopWidth: 0` alongside a `borderTopColor`, so the intended separator between the thread and the composer never draws.</t>
+        </is>
+      </c>
+      <c r="AB62" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AB1"/>
@@ -18064,7 +19613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -18206,7 +19755,7 @@
         </is>
       </c>
       <c r="B14" s="23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14" s="24" t="inlineStr"/>
     </row>
@@ -18217,7 +19766,7 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" s="24" t="inlineStr"/>
     </row>
@@ -18228,7 +19777,7 @@
         </is>
       </c>
       <c r="B16" s="23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C16" s="24" t="inlineStr"/>
     </row>
@@ -18239,7 +19788,7 @@
         </is>
       </c>
       <c r="B17" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C17" s="24" t="inlineStr"/>
     </row>
@@ -18250,7 +19799,7 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C18" s="24" t="inlineStr"/>
     </row>
@@ -18261,7 +19810,7 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C19" s="24" t="inlineStr"/>
     </row>
@@ -18320,7 +19869,7 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>18 open P0/P1 defect(s) block the build.</t>
+          <t>20 open P0/P1 defect(s) block the build.</t>
         </is>
       </c>
     </row>
@@ -18625,17 +20174,51 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>VC-045</t>
+          <t>VC-051</t>
         </is>
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>A message the device was pushed for never reaches the chat, and no reconnect ever heals it — the sender still sees blue read ticks</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>VC-052</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>Real-time messaging and notification-reply sync needs multi-scenario two-device verification</t>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>Chat thread does not follow the newest message — incoming and own-sent bubbles land hidden behind the composer</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>VC-053</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>Chat opened from a notification is titled "Chats" instead of the contact's name, and the avatar loses its initial</t>
         </is>
       </c>
     </row>
@@ -18788,7 +20371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19644,29 +21227,25 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>VC-047</t>
+          <t>VC-045</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
+          <t>Real-time messaging and notification-reply sync needs multi-scenario two-device verification</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-13</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>peerDisplayName.test.ts: VC-044 / VC-047, conversationRow.test.ts: VC-044 / VC-047</t>
-        </is>
-      </c>
+          <t>Verified on dev, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="5" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr">
         <is>
@@ -19675,24 +21254,25 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>FIX (root-caused): the address book was consulted on exactly ONE path. startDm() writes the saved name when a chat is opened from New Chat / Message Yourself — which is why the name corrected itself after opening — while every other path used server data, and refreshPeerIdentity() actively OVERWROTE a saved name with the registered one on its next background revalidation (once per TTL/session). Introduced peerDisplayName() (features/contacts/model), the single precedence rule: the name YOU saved wins over the name the peer registered; falls back to the registered name for someone not in your book or when the book has not loaded; returns undefined when neither side has a usable name so callers keep what they have; group rows are untouched (no peerId to look up). Applied at both the WRITE side (refreshPeerIdentity, both the TTL path and the profile-changed push, so a revalidation can no longer downgrade a saved name) and the READ side (toConversationRow for the chat list, useConversationIdentity for the chat header), the latter being what makes a saved name appear WITHOUT having to open the chat first. Exposed discoveredContacts() from the contacts barrel as a cache read (no re-discovery). Verified: full jest suite 502/502 pass (10 new tests), tsc --noEmit clean, eslint 0 errors and no boundary violation. Not re-tested on a device — no Android hardware attached to this machine.</t>
+          <t>This entry tracks a two-device manual verification pass, not a confirmed defect. Assigned to Tusha Bhadouriya to execute and report actual pass/fail per scenario back into this bug.
+VERIFIED 2026-09-14 by a live two-device session (A = OPPO CPH2643 Android 16 real device, B = Pixel emulator Android 16), production build against the live backend. PASSED: single-message real-time delivery; an 8-message burst delivered complete and in order; notification posted with the correct sender name, avatar and per-message lines while backgrounded; notification posted after the process was killed with am kill (FCM woke the dead process and it displayed correctly); tapping a notification opens the right conversation and clears the tray; NO notification is posted while that conversation is on screen (active-conversation suppression works); inline notification Reply sends the message, clears the notification and clears the unread badge; typing indicator appears on the peer header; presence shows online and last-seen; offline send queues and flushes in order on reconnect (airplane mode on/off); unread badges and chat-list ordering correct; cold start COLD TotalTime 1367 ms. FAILED, filed separately: VC-051 (message loss with a false read receipt), VC-052 (thread does not follow new messages), VC-053 (notification tap-through titles the chat Chats), VC-054, VC-055, VC-056, VC-057, VC-058, VC-059, VC-060, VC-061.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>VC-049</t>
+          <t>VC-047</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
+          <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -19702,7 +21282,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>profileGate.test.ts: VC-049</t>
+          <t>peerDisplayName.test.ts: VC-044 / VC-047, conversationRow.test.ts: VC-044 / VC-047</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
@@ -19713,7 +21293,118 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
+          <t>FIX (root-caused): the address book was consulted on exactly ONE path. startDm() writes the saved name when a chat is opened from New Chat / Message Yourself — which is why the name corrected itself after opening — while every other path used server data, and refreshPeerIdentity() actively OVERWROTE a saved name with the registered one on its next background revalidation (once per TTL/session). Introduced peerDisplayName() (features/contacts/model), the single precedence rule: the name YOU saved wins over the name the peer registered; falls back to the registered name for someone not in your book or when the book has not loaded; returns undefined when neither side has a usable name so callers keep what they have; group rows are untouched (no peerId to look up). Applied at both the WRITE side (refreshPeerIdentity, both the TTL path and the profile-changed push, so a revalidation can no longer downgrade a saved name) and the READ side (toConversationRow for the chat list, useConversationIdentity for the chat header), the latter being what makes a saved name appear WITHOUT having to open the chat first. Exposed discoveredContacts() from the contacts barrel as a cache read (no re-discovery). Verified: full jest suite 502/502 pass (10 new tests), tsc --noEmit clean, eslint 0 errors and no boundary violation. Not re-tested on a device — no Android hardware attached to this machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>VC-048</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Message notification omits the sender's name and tapping it does not open the chat</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Verified on dev, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Reported by Tusha Bhadouriya during production QA testing.
+RE-TESTED LIVE 2026-09-14 on a production build against the live backend, two devices. Both halves of this report are now correct: the notification DOES carry the sender name (dumpsys shows android.title="Aayush Jain 🤗" with the sender photo and per-message MessagingStyle lines), and tapping it DOES open that conversation (topResumedActivity becomes com.velchat/.MainActivity on the Chat route and every VelChat notification is cleared). Evidence: scratchpad/shots/b_shade.png, b_tapthrough.png. One residual defect on the same path is filed separately as VC-053: the deep link carries no name param, so ChatHeader falls back to the tabs.chats label and the header reads "Chats". A second residual, the chat not opening at the newest message, is covered by VC-052.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>VC-049</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-13</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>profileGate.test.ts: VC-049</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
           <t>FIX (root-caused): the email is NOT a directory-profile field — profileShape.ts states it is a separately-verified identifier owned by the auth-service (GET /auth/account). useProfileGate decided purely from the LOCAL MMKV mirror, and purgeAccountData() wipes KVKeys.email on every sign-out, so immediately after any login the mirror is empty and the gate prompted unconditionally. useAccountInfo() does fetch the real email and mirror it, but it runs in parallel from AppTabs, so its answer always lost the race — and dismissal is session-only, which is why it returned every single login. The gate now asks the auth-service itself before deciding, via a new pure shouldPromptForProfile() (features/user/model/profileGate.ts): a mirrored email means never prompt; a server email means never prompt (and is re-mirrored so later launches short-circuit with no network); an UNANSWERED server (in flight or unreachable) means WAIT rather than prompt, which also removes the flash of the sheet before the answer lands. Only a definitive server no-email prompts. Verified: full jest suite 492/492 pass (5 new decision tests), tsc --noEmit clean, eslint 0 errors, no eslint-plugin-boundaries violation for the user→auth import (authApi depends only on infra, so no cycle). Not reproduced on a device — no Android hardware attached to this machine; fix is verified at the unit level against the exact reported condition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VC-050</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Cold start holds a splash screen on a network refresh — up to minutes before home appears</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-13</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>authBootstrap.test.ts: cold start with a session already on the device</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>FIX: split the two questions the bootstrap had conflated — "can we show the app" and "is the access token fresh enough for a socket". If a session exists on the device at all (hasSession(), presence-only), the app now hydrates and reports ready IMMEDIATELY, whatever the token age; the chat list renders from the local DB, the HTTP client refreshes on its first 401, and the socket heals itself via 4001 -&gt; refresh -&gt; reconnect. VC-036 is not regressed: a fresh token is still wanted as early as possible so the first handshake is not doomed, so the refresh is still fired at once — it just runs BEHIND the app instead of in front of it. The no-session path (signed out but a device key survives) still attempts a silent restore, but is now bounded by MAX_SILENT_RESTORE_MS = 4000 so a hibernating backend cannot freeze the splash; a restore that lands later still navigates home on its own, because RootNavigator follows the auth store (state === active). Verified: full jest suite 521/521 pass (5 new hook tests, two of which fail against the old code by hanging until waitFor times out), tsc --noEmit clean, eslint 0 errors. Measured on device: not yet — needs a launch on real hardware to confirm the wall-clock improvement.</t>
         </is>
       </c>
     </row>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -641,7 +641,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-14 04:21 UTC</t>
+          <t>Generated 2026-09-14 04:40 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -18351,7 +18351,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -18445,7 +18445,8 @@
       </c>
       <c r="AA53" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/b_fg_follow.png (B at the bottom, F1-F3 arrive, list stays on S8 and the jump FAB appears), scratchpad/shots/b_one.png (single message ONE1 arrives, list left exactly one bubble short), scratchpad/shots/a_own_follow.png (A's OWN sent ONE1 clipped behind the composer), scratchpad/shots/b_offline_send.png (own offline sends clipped). The race explains the intermittency: sometimes the manual scroll lands after the anchor adjustment and it looks fine.</t>
+          <t>Evidence: scratchpad/shots/b_fg_follow.png (B at the bottom, F1-F3 arrive, list stays on S8 and the jump FAB appears), scratchpad/shots/b_one.png (single message ONE1 arrives, list left exactly one bubble short), scratchpad/shots/a_own_follow.png (A's OWN sent ONE1 clipped behind the composer), scratchpad/shots/b_offline_send.png (own offline sends clipped). The race explains the intermittency: sometimes the manual scroll lands after the anchor adjustment and it looks fine.
+FIX: the follow now goes through FlashList's `scrollToIndex({index:0})` instead of `scrollToOffset({offset:0})`, fired from `onContentSizeChange` rather than the data effect. Root cause confirmed by reading useRecyclerViewController.js: on every data change FlashList measures how far the FIRST VISIBLE item moved and calls scrollAnchorRef.scrollBy(diff) to cancel the shift, gated on a `pauseOffsetCorrection` ref that ONLY scrollToIndex raises — so a plain offset scroll was undone every time and the thread landed exactly one bubble short. Firing from onContentSizeChange means index 0 has a real layout instead of the stale one it would have in the same commit. Anchoring is deliberately kept: it is the right behaviour for a reader scrolled up in history, whom shouldScrollToLatest still leaves alone; a drag cancels any pending follow so loadOlder growing the content is never mistaken for a new message. An intermediate attempt using scrollToOffset from onContentSizeChange plus a requestAnimationFrame retry was built and tested on device and still landed one bubble short — that is what identified the pauseOffsetCorrection gate. VERIFIED ON DEVICE: a four-message burst now ends with the newest message fully visible above the composer (scratchpad/shots/v2_own_follow.png) where the same burst on the previous build left it clipped (v_own_follow.png). Still to verify with a second device: the INCOMING-message path, and the notification tap-through landing position.</t>
         </is>
       </c>
       <c r="AB53" s="5" t="inlineStr"/>
@@ -18479,7 +18480,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -18574,7 +18575,8 @@
       </c>
       <c r="AA54" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/b_tapthrough.png and b_jump.png (header 'Chats' after notification tap) vs scratchpad/shots/b_off_kbd.png (header 'Aayush Jain 🤗' for the same chat opened from the list). Relates to VC-048, which reported the tap-through as not opening the chat at all; the open now works, this is the remaining defect on that path.</t>
+          <t>Evidence: scratchpad/shots/b_tapthrough.png and b_jump.png (header 'Chats' after notification tap) vs scratchpad/shots/b_off_kbd.png (header 'Aayush Jain 🤗' for the same chat opened from the list). Relates to VC-048, which reported the tap-through as not opening the chat at all; the open now works, this is the remaining defect on that path.
+FIX: new pure helper `chatTitle(routeName, rowName, fallback)` in ui/chat/chatModel.ts, covered by chatTitle.test.ts (4 cases, RED first). ChatHeader now resolves the title from the route name, then the conversation row it was already observing for the avatar, and only then a generic label; blank counts as absent in both sources. The avatar initial is taken from the resolved name with an empty fallback, so a genuinely unnamed conversation still falls back to the person glyph instead of showing the initial of a tab label. Needs a second device to re-verify the live tap-through.</t>
         </is>
       </c>
       <c r="AB54" s="5" t="inlineStr"/>
@@ -18608,7 +18610,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -18702,7 +18704,8 @@
       </c>
       <c r="AA55" s="5" t="inlineStr">
         <is>
-          <t>Evidence: dumpsys output captured twice in the live session (8 messages -&gt; '5 new messages'; 1 message -&gt; '5 new messages').</t>
+          <t>Evidence: dumpsys output captured twice in the live session (8 messages -&gt; '5 new messages'; 1 message -&gt; '5 new messages').
+FIX: added `PushStore.countedMessages()`, which sums the per-conversation counters the store already held, and postSummary now formats that instead of `countedConversations()`. The &lt;=1 guard that suppresses the summary for a single chat still uses the conversation count, which is correct. Needs a second device to re-verify live.</t>
         </is>
       </c>
       <c r="AB55" s="5" t="inlineStr"/>
@@ -18736,7 +18739,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -18830,7 +18833,8 @@
       </c>
       <c r="AA56" s="5" t="inlineStr">
         <is>
-          <t>Confirmed by reading tokens.ts (brandFrom '#0B0B0C' / '#F5F5F7') against push_strings.xml (#7C5CFF) and by the live dumpsys record color=0xff7c5cff.</t>
+          <t>Confirmed by reading tokens.ts (brandFrom '#0B0B0C' / '#F5F5F7') against push_strings.xml (#7C5CFF) and by the live dumpsys record color=0xff7c5cff.
+FIX: push_accent is now #0B0B0C, the monochrome brand accent from design-system/tokens.ts, and the misleading resource comment about a violet gradient is replaced. Android resolves this against the shade background for contrast. Needs a second device to re-verify live.</t>
         </is>
       </c>
       <c r="AB56" s="5" t="inlineStr"/>
@@ -19121,7 +19125,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -19214,7 +19218,8 @@
       </c>
       <c r="AA59" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/b_after_reply.png (row reads 'KILL1' while KILL2 was newer). Fix is to move the preview write inside the same freshness check as the timestamp.</t>
+          <t>Evidence: scratchpad/shots/b_after_reply.png (row reads 'KILL1' while KILL2 was newer). Fix is to move the preview write inside the same freshness check as the timestamp.
+FIX: the preview write now sits behind the same freshness check as the sort key in upsertConversation — a single `fresher` predicate gates both, so a stale patch can no longer overwrite what the row says while being correctly refused a reorder.</t>
         </is>
       </c>
       <c r="AB59" s="5" t="inlineStr"/>
@@ -19375,7 +19380,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -19469,7 +19474,8 @@
       </c>
       <c r="AA61" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/a_relaunch.png — the 'kkr' and 'h' bubbles in light theme. Fix options: give the incoming bubble a hairline in BOTH schemes, or darken `bgSubtle` for this use.</t>
+          <t>Evidence: scratchpad/shots/a_relaunch.png — the 'kkr' and 'h' bubbles in light theme. Fix options: give the incoming bubble a hairline in BOTH schemes, or darken `bgSubtle` for this use.
+FIX: the incoming-bubble hairline is no longer dark-only; it applies in both schemes, using the wallpaper-supplied border when the chat has a decorated ground and t.colors.hairline otherwise.</t>
         </is>
       </c>
       <c r="AB61" s="5" t="inlineStr"/>
@@ -19503,7 +19509,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -19596,7 +19602,8 @@
       </c>
       <c r="AA62" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/a_cal.png and a_own_follow.png — the white band between the composer pill and the keyboard's suggestion strip. Same file also sets `borderTopWidth: 0` alongside a `borderTopColor`, so the intended separator between the thread and the composer never draws.</t>
+          <t>Evidence: scratchpad/shots/a_cal.png and a_own_follow.png — the white band between the composer pill and the keyboard's suggestion strip. Same file also sets `borderTopWidth: 0` alongside a `borderTopColor`, so the intended separator between the thread and the composer never draws.
+FIX: keyboard-up paddingBottom drops from spacing.huge (48dp) to spacing.xs (8dp), and borderTopWidth goes from 0 to 1 so the separator the style always declared actually draws. VERIFIED ON DEVICE: scratchpad/shots/v2_own_follow.png shows the hairline above the composer and the composer sitting close to the keyboard.</t>
         </is>
       </c>
       <c r="AB62" s="5" t="inlineStr"/>
@@ -19613,7 +19620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -19799,7 +19806,7 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C18" s="24" t="inlineStr"/>
     </row>
@@ -19810,7 +19817,7 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C19" s="24" t="inlineStr"/>
     </row>
@@ -19869,7 +19876,7 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>20 open P0/P1 defect(s) block the build.</t>
+          <t>18 open P0/P1 defect(s) block the build.</t>
         </is>
       </c>
     </row>
@@ -20185,40 +20192,6 @@
       <c r="C46" s="24" t="inlineStr">
         <is>
           <t>A message the device was pushed for never reaches the chat, and no reconnect ever heals it — the sender still sees blue read ticks</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="22" t="inlineStr">
-        <is>
-          <t>VC-052</t>
-        </is>
-      </c>
-      <c r="B47" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>Chat thread does not follow the newest message — incoming and own-sent bubbles land hidden behind the composer</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="22" t="inlineStr">
-        <is>
-          <t>VC-053</t>
-        </is>
-      </c>
-      <c r="B48" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>Chat opened from a notification is titled "Chats" instead of the contact's name, and the avatar loses its initial</t>
         </is>
       </c>
     </row>
@@ -20371,7 +20344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21405,6 +21378,251 @@
       <c r="H27" s="5" t="inlineStr">
         <is>
           <t>FIX: split the two questions the bootstrap had conflated — "can we show the app" and "is the access token fresh enough for a socket". If a session exists on the device at all (hasSession(), presence-only), the app now hydrates and reports ready IMMEDIATELY, whatever the token age; the chat list renders from the local DB, the HTTP client refreshes on its first 401, and the socket heals itself via 4001 -&gt; refresh -&gt; reconnect. VC-036 is not regressed: a fresh token is still wanted as early as possible so the first handshake is not doomed, so the refresh is still fired at once — it just runs BEHIND the app instead of in front of it. The no-session path (signed out but a device key survives) still attempts a silent restore, but is now bounded by MAX_SILENT_RESTORE_MS = 4000 so a hibernating backend cannot freeze the splash; a restore that lands later still navigates home on its own, because RootNavigator follows the auth store (state === active). Verified: full jest suite 521/521 pass (5 new hook tests, two of which fail against the old code by hanging until waitFor times out), tsc --noEmit clean, eslint 0 errors. Measured on device: not yet — needs a launch on real hardware to confirm the wall-clock improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>VC-052</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Chat thread does not follow the newest message — incoming and own-sent bubbles land hidden behind the composer</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: scratchpad/shots/b_fg_follow.png (B at the bottom, F1-F3 arrive, list stays on S8 and the jump FAB appears), scratchpad/shots/b_one.png (single message ONE1 arrives, list left exactly one bubble short), scratchpad/shots/a_own_follow.png (A's OWN sent ONE1 clipped behind the composer), scratchpad/shots/b_offline_send.png (own offline sends clipped). The race explains the intermittency: sometimes the manual scroll lands after the anchor adjustment and it looks fine.
+FIX: the follow now goes through FlashList's `scrollToIndex({index:0})` instead of `scrollToOffset({offset:0})`, fired from `onContentSizeChange` rather than the data effect. Root cause confirmed by reading useRecyclerViewController.js: on every data change FlashList measures how far the FIRST VISIBLE item moved and calls scrollAnchorRef.scrollBy(diff) to cancel the shift, gated on a `pauseOffsetCorrection` ref that ONLY scrollToIndex raises — so a plain offset scroll was undone every time and the thread landed exactly one bubble short. Firing from onContentSizeChange means index 0 has a real layout instead of the stale one it would have in the same commit. Anchoring is deliberately kept: it is the right behaviour for a reader scrolled up in history, whom shouldScrollToLatest still leaves alone; a drag cancels any pending follow so loadOlder growing the content is never mistaken for a new message. An intermediate attempt using scrollToOffset from onContentSizeChange plus a requestAnimationFrame retry was built and tested on device and still landed one bubble short — that is what identified the pauseOffsetCorrection gate. VERIFIED ON DEVICE: a four-message burst now ends with the newest message fully visible above the composer (scratchpad/shots/v2_own_follow.png) where the same burst on the previous build left it clipped (v_own_follow.png). Still to verify with a second device: the INCOMING-message path, and the notification tap-through landing position.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>VC-053</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Chat opened from a notification is titled "Chats" instead of the contact's name, and the avatar loses its initial</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: scratchpad/shots/b_tapthrough.png and b_jump.png (header 'Chats' after notification tap) vs scratchpad/shots/b_off_kbd.png (header 'Aayush Jain 🤗' for the same chat opened from the list). Relates to VC-048, which reported the tap-through as not opening the chat at all; the open now works, this is the remaining defect on that path.
+FIX: new pure helper `chatTitle(routeName, rowName, fallback)` in ui/chat/chatModel.ts, covered by chatTitle.test.ts (4 cases, RED first). ChatHeader now resolves the title from the route name, then the conversation row it was already observing for the avatar, and only then a generic label; blank counts as absent in both sources. The avatar initial is taken from the resolved name with an empty fallback, so a genuinely unnamed conversation still falls back to the person glyph instead of showing the initial of a tab label. Needs a second device to re-verify the live tap-through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>VC-054</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Notification group summary says "N new messages" but N is the number of chats, not the number of messages</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: dumpsys output captured twice in the live session (8 messages -&gt; '5 new messages'; 1 message -&gt; '5 new messages').
+FIX: added `PushStore.countedMessages()`, which sums the per-conversation counters the store already held, and postSummary now formats that instead of `countedConversations()`. The &lt;=1 guard that suppresses the summary for a single chat still uses the conversation count, which is correct. Needs a second device to re-verify live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>VC-055</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Every notification is tinted the abandoned violet #7C5CFF, which matches nothing in the shipped monochrome theme</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed by reading tokens.ts (brandFrom '#0B0B0C' / '#F5F5F7') against push_strings.xml (#7C5CFF) and by the live dumpsys record color=0xff7c5cff.
+FIX: push_accent is now #0B0B0C, the monochrome brand accent from design-system/tokens.ts, and the misleading resource comment about a violet gradient is replaced. Android resolves this against the shade background for contrast. Needs a second device to re-verify live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>VC-058</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Chat-list preview can regress to an older message — the preview is written unconditionally while the timestamp is guarded</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: scratchpad/shots/b_after_reply.png (row reads 'KILL1' while KILL2 was newer). Fix is to move the preview write inside the same freshness check as the timestamp.
+FIX: the preview write now sits behind the same freshness check as the sort key in upsertConversation — a single `fresher` predicate gates both, so a stale patch can no longer overwrite what the row says while being correctly refused a reorder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>VC-060</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Incoming message bubbles are nearly invisible in light theme — #F7F7F8 on #FFFFFF with no border (1.04:1)</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: scratchpad/shots/a_relaunch.png — the 'kkr' and 'h' bubbles in light theme. Fix options: give the incoming bubble a hairline in BOTH schemes, or darken `bgSubtle` for this use.
+FIX: the incoming-bubble hairline is no longer dark-only; it applies in both schemes, using the wallpaper-supplied border when the chat has a decorated ground and t.colors.hairline otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>VC-061</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>A 48dp empty band sits between the composer and the keyboard whenever the keyboard is open</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: scratchpad/shots/a_cal.png and a_own_follow.png — the white band between the composer pill and the keyboard's suggestion strip. Same file also sets `borderTopWidth: 0` alongside a `borderTopColor`, so the intended separator between the thread and the composer never draws.
+FIX: keyboard-up paddingBottom drops from spacing.huge (48dp) to spacing.xs (8dp), and borderTopWidth goes from 0 to 1 so the separator the style always declared actually draws. VERIFIED ON DEVICE: scratchpad/shots/v2_own_follow.png shows the hairline above the composer and the composer sitting close to the keyboard.</t>
         </is>
       </c>
     </row>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -641,7 +641,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-14 04:40 UTC</t>
+          <t>Generated 2026-09-14 04:45 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -11043,7 +11043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB62"/>
+  <dimension ref="A1:AB63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18996,7 +18996,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -19091,7 +19091,8 @@
       </c>
       <c r="AA58" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/b_shade.png (S3..S8 before opening), scratchpad/shots/b_tapthrough.png (chat opened, tray cleared, all read), scratchpad/shots/b_reply_open.png (next notification still carries S6, S7, S8, BG1).</t>
+          <t>Evidence: scratchpad/shots/b_shade.png (S3..S8 before opening), scratchpad/shots/b_tapthrough.png (chat opened, tray cleared, all read), scratchpad/shots/b_reply_open.png (next notification still carries S6, S7, S8, BG1).
+ROOT CAUSE FOUND and FIXED via VC-062. The clearing path was wired correctly all along — clearConversationNotification -&gt; VelChatPushModule.clearConversation -&gt; PushNotifications.cancel -&gt; store.clearLines — but it only ran from the chat screen's MOUNT effect. A notification tap RESUMES an already-mounted ChatScreen, so that effect never re-ran, and the tray entry disappearing was just the notification's own AUTO_CANCEL flag removing the posted notification while the stored lines and counters survived. useMessages now also clears on every return to the foreground. Live re-verification pending a second device.</t>
         </is>
       </c>
       <c r="AB58" s="5" t="inlineStr"/>
@@ -19607,6 +19608,140 @@
         </is>
       </c>
       <c r="AB62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>VC-062</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>VC-63</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>chatVisibility.test.tsx: the chat only counts as on screen while it is visible</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>A chat left open while the app is backgrounded keeps marking arriving messages read — the sender gets a blue tick for a message nobody has seen</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Chat / messaging — read receipts</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/features/chat/hooks/useMessages.ts (AppState listener) + domain/sync/SyncEngine.ts:1057 (read-on-arrival)</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>Production build, live backend</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>Both test devices</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>Every message that arrives while the app is backgrounded on a chat screen — i.e. constantly in normal use</t>
+        </is>
+      </c>
+      <c r="O63" s="5" t="inlineStr">
+        <is>
+          <t>Deterministic once the state is set up; confirmed by reading the code path.</t>
+        </is>
+      </c>
+      <c r="P63" s="5" t="inlineStr">
+        <is>
+          <t>The recipient has a conversation OPEN and then leaves the app or locks the screen. The chat screen stays mounted, because backgrounding does not unmount it.</t>
+        </is>
+      </c>
+      <c r="Q63" s="5" t="inlineStr">
+        <is>
+          <t>1. On device B open a DM and leave it open.
+2. Press Home, or lock the screen. Do not go back to the chat list.
+3. From device A send a message.
+4. Look at the tick state on A.</t>
+        </is>
+      </c>
+      <c r="R63" s="5" t="inlineStr">
+        <is>
+          <t>A message is only 'read' once the recipient can actually see it. A backgrounded app is showing nothing, so the ticks stay grey until the user returns to the chat — which is exactly the rule the push layer beside this already follows.</t>
+        </is>
+      </c>
+      <c r="S63" s="5" t="inlineStr">
+        <is>
+          <t>The sender's bubble goes blue immediately. The SyncEngine reads every message landing in `activeConversationId` on arrival, and `useMessages` only ever cleared that id on UNMOUNT.</t>
+        </is>
+      </c>
+      <c r="T63" s="5" t="inlineStr">
+        <is>
+          <t>Read receipts stop meaning anything: a sender is told their message was read by someone whose phone was in their pocket. It also silently clears the recipient's unread badge for messages they have never seen, so those messages can be lost in the list. This is very likely the read-receipt half of VC-051, where the sender saw blue ticks for a message the recipient never received at all.</t>
+        </is>
+      </c>
+      <c r="U63" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED in code. `SyncEngine.setActiveConversation` is called on chat mount and in the cleanup on unmount, and nowhere else. The AppState listener in the same effect correctly does `setActiveConversationForPush(state === 'active' ? conversationId : null)` — it simply never does the equivalent for the engine, so the engine's idea of 'on screen' survives backgrounding.</t>
+        </is>
+      </c>
+      <c r="V63" s="5" t="inlineStr"/>
+      <c r="W63" s="5" t="inlineStr"/>
+      <c r="X63" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y63" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z63" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA63" s="5" t="inlineStr">
+        <is>
+          <t>Found while tracing VC-057. Same listener is also the only place a notification TAP can clear a conversation's stored notification lines, because tapping resumes an ALREADY-MOUNTED chat screen and the mount effect never re-runs.
+FIX: the AppState listener in useMessages now withdraws and re-asserts the ENGINE's active conversation alongside the push layer's, and on returning to the foreground it re-reports the read and clears the conversation notification. Three new hook tests (chatVisibility.test.tsx) cover it, written RED first: before the change the background case recorded zero setActiveConversation calls, which is the bug exactly. Clearing on resume is also what fixes VC-057 — a notification TAP resumes an ALREADY-MOUNTED chat screen, so the mount effect never re-ran and the stored MessagingStyle lines were never dropped. Verified: 534/534 jest, tsc clean, eslint 0 errors. Live two-device re-verification still pending — the test phone was disconnected before it could be run.</t>
+        </is>
+      </c>
+      <c r="AB63" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AB1"/>
@@ -19773,7 +19908,7 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" s="24" t="inlineStr"/>
     </row>
@@ -19806,7 +19941,7 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" s="24" t="inlineStr"/>
     </row>
@@ -19817,7 +19952,7 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C19" s="24" t="inlineStr"/>
     </row>
@@ -20344,7 +20479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21524,12 +21659,12 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>VC-058</t>
+          <t>VC-057</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Chat-list preview can regress to an older message — the preview is written unconditionally while the timestamp is guarded</t>
+          <t>Notification re-lists messages the user has already read once the chat is reopened and a new message arrives</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -21551,25 +21686,25 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/b_after_reply.png (row reads 'KILL1' while KILL2 was newer). Fix is to move the preview write inside the same freshness check as the timestamp.
-FIX: the preview write now sits behind the same freshness check as the sort key in upsertConversation — a single `fresher` predicate gates both, so a stale patch can no longer overwrite what the row says while being correctly refused a reorder.</t>
+          <t>Evidence: scratchpad/shots/b_shade.png (S3..S8 before opening), scratchpad/shots/b_tapthrough.png (chat opened, tray cleared, all read), scratchpad/shots/b_reply_open.png (next notification still carries S6, S7, S8, BG1).
+ROOT CAUSE FOUND and FIXED via VC-062. The clearing path was wired correctly all along — clearConversationNotification -&gt; VelChatPushModule.clearConversation -&gt; PushNotifications.cancel -&gt; store.clearLines — but it only ran from the chat screen's MOUNT effect. A notification tap RESUMES an already-mounted ChatScreen, so that effect never re-ran, and the tray entry disappearing was just the notification's own AUTO_CANCEL flag removing the posted notification while the stored lines and counters survived. useMessages now also clears on every return to the foreground. Live re-verification pending a second device.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>VC-060</t>
+          <t>VC-058</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Incoming message bubbles are nearly invisible in light theme — #F7F7F8 on #FFFFFF with no border (1.04:1)</t>
+          <t>Chat-list preview can regress to an older message — the preview is written unconditionally while the timestamp is guarded</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -21586,20 +21721,20 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/a_relaunch.png — the 'kkr' and 'h' bubbles in light theme. Fix options: give the incoming bubble a hairline in BOTH schemes, or darken `bgSubtle` for this use.
-FIX: the incoming-bubble hairline is no longer dark-only; it applies in both schemes, using the wallpaper-supplied border when the chat has a decorated ground and t.colors.hairline otherwise.</t>
+          <t>Evidence: scratchpad/shots/b_after_reply.png (row reads 'KILL1' while KILL2 was newer). Fix is to move the preview write inside the same freshness check as the timestamp.
+FIX: the preview write now sits behind the same freshness check as the sort key in upsertConversation — a single `fresher` predicate gates both, so a stale patch can no longer overwrite what the row says while being correctly refused a reorder.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>VC-061</t>
+          <t>VC-060</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>A 48dp empty band sits between the composer and the keyboard whenever the keyboard is open</t>
+          <t>Incoming message bubbles are nearly invisible in light theme — #F7F7F8 on #FFFFFF with no border (1.04:1)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -21621,8 +21756,82 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
+          <t>Evidence: scratchpad/shots/a_relaunch.png — the 'kkr' and 'h' bubbles in light theme. Fix options: give the incoming bubble a hairline in BOTH schemes, or darken `bgSubtle` for this use.
+FIX: the incoming-bubble hairline is no longer dark-only; it applies in both schemes, using the wallpaper-supplied border when the chat has a decorated ground and t.colors.hairline otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>VC-061</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>A 48dp empty band sits between the composer and the keyboard whenever the keyboard is open</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
           <t>Evidence: scratchpad/shots/a_cal.png and a_own_follow.png — the white band between the composer pill and the keyboard's suggestion strip. Same file also sets `borderTopWidth: 0` alongside a `borderTopColor`, so the intended separator between the thread and the composer never draws.
 FIX: keyboard-up paddingBottom drops from spacing.huge (48dp) to spacing.xs (8dp), and borderTopWidth goes from 0 to 1 so the separator the style always declared actually draws. VERIFIED ON DEVICE: scratchpad/shots/v2_own_follow.png shows the hairline above the composer and the composer sitting close to the keyboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>VC-062</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>A chat left open while the app is backgrounded keeps marking arriving messages read — the sender gets a blue tick for a message nobody has seen</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>chatVisibility.test.tsx: the chat only counts as on screen while it is visible</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Found while tracing VC-057. Same listener is also the only place a notification TAP can clear a conversation's stored notification lines, because tapping resumes an ALREADY-MOUNTED chat screen and the mount effect never re-runs.
+FIX: the AppState listener in useMessages now withdraws and re-asserts the ENGINE's active conversation alongside the push layer's, and on returning to the foreground it re-reports the read and clears the conversation notification. Three new hook tests (chatVisibility.test.tsx) cover it, written RED first: before the change the background case recorded zero setActiveConversation calls, which is the bug exactly. Clearing on resume is also what fixes VC-057 — a notification TAP resumes an ALREADY-MOUNTED chat screen, so the mount effect never re-ran and the stored MessagingStyle lines were never dropped. Verified: 534/534 jest, tsc clean, eslint 0 errors. Live two-device re-verification still pending — the test phone was disconnected before it could be run.</t>
         </is>
       </c>
     </row>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -641,7 +641,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-14 04:45 UTC</t>
+          <t>Generated 2026-09-19 08:20 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -11043,7 +11043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB63"/>
+  <dimension ref="A1:AB70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18202,7 +18202,11 @@
           <t>VC-52</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr"/>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>failureScenarios.test.ts: a message dropped by fan-out</t>
+        </is>
+      </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
           <t>A message the device was pushed for never reaches the chat, and no reconnect ever heals it — the sender still sees blue read ticks</t>
@@ -18220,7 +18224,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -18298,7 +18302,11 @@
           <t>Two candidates, not yet separated: (a) the headless push wake posts the notification but its DB write is lost when the process is reaped before the WatermelonDB write commits; (b) the message is never durably fanned out (see VC-001) and the reconnect backfill does not re-request it. Either way the CLIENT-side defect is the same: the `sync {cursor}` + `afterSeq` backfill is not self-healing — a gap that exists once stays forever. The false `read` receipt means a receipt is being emitted from a path that does not require the message row to exist locally.</t>
         </is>
       </c>
-      <c r="V52" s="5" t="inlineStr"/>
+      <c r="V52" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED by tracing the whole path. THREE facts compose into permanent loss. (1) A data push delivered to a DEAD process is handled entirely in Kotlin — VelChatMessagingService.handleMessage posts the notification and acks "delivered", then calls PushBridge.emit whose return value is discarded; PushBridge.liveContext() returns null when there is no JS to emit to and, unlike onNewToken/onDeletedMessages, there is NO store.enqueueEvent fallback. So the wake never writes the message to WatermelonDB and leaves no durable record that anything was missed. The only remaining route to the DB is a later REST backfill. (2) Every backfill cursor in the client is MAX(seq) — SyncEngine.pageBackfill, backfillInbox, and the content-fill and load-older paths all derive from maxSeqForConversation/minSeqForConversation — so once ANY newer message lands, the missing seq sits below the cursor and no afterSeq request can ever reach it again. (3) onInboundMessage already did the hard part: it reads localMax BEFORE applying, and shouldProbeGap correctly proves a hole exists — then it called backfillConversation, which re-reads MAX *after* applyServerMessage has moved it up to the revealing seq, so it fetched from ABOVE the hole and repaired nothing. The precisely-correct lower edge was captured, used for the predicate and the loop-guard memo, and then thrown away instead of being used as the fetch cursor.</t>
+        </is>
+      </c>
       <c r="W52" s="5" t="inlineStr"/>
       <c r="X52" s="5" t="inlineStr">
         <is>
@@ -18317,7 +18325,9 @@
       </c>
       <c r="AA52" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/a_inline_rx.png (A shows KILL2 09:39 with blue ticks) vs scratchpad/shots/b_kill2_check.png (B's thread jumps BG1 09:37 -&gt; KILL1 09:37 -&gt; hhh 09:40, no KILL2). Related backend defect VC-001 may be the upstream cause, but the client must still heal the gap on reconnect and must not report `read` for a message it does not hold.</t>
+          <t>Evidence: scratchpad/shots/a_inline_rx.png (A shows KILL2 09:39 with blue ticks) vs scratchpad/shots/b_kill2_check.png (B's thread jumps BG1 09:37 -&gt; KILL1 09:37 -&gt; hhh 09:40, no KILL2). Related backend defect VC-001 may be the upstream cause, but the client must still heal the gap on reconnect and must not report `read` for a message it does not hold.
+FIX (frontend): pageBackfill/backfillConversation take an optional `fromSeq`, and the gap probe passes the pre-apply `localMax` — so the repair asks the server from the LOWER edge of the hole instead of from the message that revealed it. Re-fetching the rows already held between localMax and the incoming seq is free: applyServerMessages dedups on (conversation_id, seq) and on client_msg_id inside the write lock. Three end-to-end tests added to failureScenarios.test.ts, driving the real engine against the fake server, written RED first — and rewritten once when the first version passed for the wrong reason (bootConnected’s own reconnect backfill was healing the hole), so each test now brings the socket up while the device is already caught up. Verified: 537/537 jest, tsc clean, eslint 0 errors.
+STILL OPEN, tracked separately: (a) the FALSE READ TICK is not this fix — markConversationRead and read-on-arrival emit a CUMULATIVE read watermark at the local MAX, which covers a missing seq beneath it; clamping every read/delivered watermark to the highest CONTIGUOUS seq actually held is the correct fix and is filed as its own bug because it changes tick semantics everywhere and needs its own tests. (b) a hole detected once is only remembered in memory (gapProbedFrom), so a hole that a probe fails to close is forgotten on restart — persisting unhealed holes for retry is follow-up work. (c) VelChatMessagingService could enqueue a durable `resync` marker when JS is dead, the same fallback its siblings already have. (d) If the backend never durably stored or re-serves the message, no client change recovers it (see VC-001) — the fix then converts silent loss into an honest grey tick rather than a recovery.</t>
         </is>
       </c>
       <c r="AB52" s="5" t="inlineStr"/>
@@ -19742,6 +19752,904 @@
         </is>
       </c>
       <c r="AB63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>VC-063</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>VC-64</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr"/>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>A message whose realtime frame carries no body renders a permanently blank bubble — the REST recovery is dead code and the list would not re-render anyway</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F64" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Chat / messaging — inbound content fill</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/domain/sync/SyncEngine.ts:1009-1023 + infra/db/syncLogic.ts:20-22 + infra/db/messages.ts:56</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>Any Android</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>Every inbound message whose fan-out frame has no body</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t>Deterministic by code inspection; not yet reproduced live because today's plaintext messages happen to carry `text` on the wire.</t>
+        </is>
+      </c>
+      <c r="P64" s="5" t="inlineStr">
+        <is>
+          <t>A peer sends a message the gateway relays WITHOUT a body — per docs/backend-integration-reference.md §4 the WS payload carries an optional `text`, so media and (at the E2EE phase) every message arrive metadata-only.</t>
+        </is>
+      </c>
+      <c r="Q64" s="5" t="inlineStr">
+        <is>
+          <t>1. Have a peer send a message the gateway relays with no `text` field while the chat is open.
+2. Watch the bubble that appears.
+3. Leave the chat and come back.</t>
+        </is>
+      </c>
+      <c r="R64" s="5" t="inlineStr">
+        <is>
+          <t>The bubble shows the message. SyncEngine already tries: `if (m.content === undefined || m.content === '') { const filled = await fetchMessagesAfter(conv, m.seq - 1); await applyServerMessages(filled); }`.</t>
+        </is>
+      </c>
+      <c r="S64" s="5" t="inlineStr">
+        <is>
+          <t>An empty bubble with only a timestamp, and an empty preview on the chat list. The recovery cannot work, for two independent reasons, and both must be fixed or the bubble stays blank.</t>
+        </is>
+      </c>
+      <c r="T64" s="5" t="inlineStr">
+        <is>
+          <t>A received message shows as blank. The user has no idea what was said and no way to recover it inside the app. At the E2EE phase this would be every single inbound message.</t>
+        </is>
+      </c>
+      <c r="U64" s="5" t="inlineStr">
+        <is>
+          <t>(a) THE FILL IS SKIPPED AS A DUPLICATE. `fetchMessagesAfter(conv, seq-1)` returns the same message, and `reconcileDecision` (syncLogic.ts:20-22) is `if (hasClientMsgIdRow) return 'update'; if (hasSeqRow) return 'skip';`. `hasSeqRow` is true — the row was inserted milliseconds earlier by the `applyServerMessage` on the line above. `hasClientMsgIdRow` can never be true for a peer's message: there is no client_msg_id on the wire, so the insert synthesises `srv_&lt;conversationId&gt;_&lt;seq&gt;` while the REST row carries the sender's real id. The decision is always 'skip', so content_plain is never written and the whole block is dead code for exactly the case its comment names. Every later catch-up funnels through the same decision, so the comment 'content syncs on next catch-up' is also untrue. (b) EVEN IF (a) IS FIXED, NOTHING RE-RENDERS. `observeMessages` is `.observeWithColumns(['state'])`, and WatermelonDB only emits when the matched-record SET changes or a NAMED column changes — a content_plain-only update on an already-matched row emits nothing.</t>
+        </is>
+      </c>
+      <c r="V64" s="5" t="inlineStr"/>
+      <c r="W64" s="5" t="inlineStr"/>
+      <c r="X64" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y64" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z64" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA64" s="5" t="inlineStr">
+        <is>
+          <t>Found by a code-level audit after the live session. Fix needs both halves: let the fill update a row matched by seq (e.g. treat a seq row with empty content as 'update'), and name `content_plain` in observeMessages' column list.</t>
+        </is>
+      </c>
+      <c r="AB64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>VC-064</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>VC-65</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr"/>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Opening a chat from a notification while another chat is on screen keeps the unsent draft — one tap can send it to the wrong person</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Chat / messaging — notification deep link into a live screen</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/features/chat/ui/ChatScreen.tsx (local useState) + navigation/RootNavigator.tsx (no getId on the Chat screen)</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Any Android</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>Every notification tap taken while a different chat is already open</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="inlineStr">
+        <is>
+          <t>Deterministic by code inspection — the same param-update path that VC-053 was filed and fixed on.</t>
+        </is>
+      </c>
+      <c r="P65" s="5" t="inlineStr">
+        <is>
+          <t>The user is on a chat screen with unsent text in the composer, and taps a notification for a DIFFERENT conversation.</t>
+        </is>
+      </c>
+      <c r="Q65" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the chat with contact A and type a message WITHOUT sending it.
+2. Lock the phone or switch apps, leaving the chat screen mounted.
+3. Receive a message from contact B and tap its notification.
+4. Look at the composer, then press send.</t>
+        </is>
+      </c>
+      <c r="R65" s="5" t="inlineStr">
+        <is>
+          <t>Opening a different conversation starts with an empty composer. A draft belongs to the chat it was written in.</t>
+        </is>
+      </c>
+      <c r="S65" s="5" t="inlineStr">
+        <is>
+          <t>The screen is REUSED, not remounted: the deep link dispatches a NAVIGATE to `Chat`, and with no `getId` configured on the Chat screen the stack router reuses the current route's key and only swaps `route.params`. `useMessages`, `useConversationIdentity` and `useChatHeaderPresence` all re-run on the new conversationId, but every `useState` in ChatScreen survives — so the composer still holds A's text while `send` is now bound to B. One tap sends A's private message to B.</t>
+        </is>
+      </c>
+      <c r="T65" s="5" t="inlineStr">
+        <is>
+          <t>A private message can be delivered to the wrong person with a single tap and no warning. That is a confidentiality failure, not just a UX slip. Lesser symptoms from the same cause: the first keystroke after the switch emits a typing signal to B while the field shows A's words; `offsetRef` carries over, so if the user had scrolled up in A's chat the auto-follow is silently disabled in B's until they scroll once; the jump-to-latest button can appear for a chat already at the bottom.</t>
+        </is>
+      </c>
+      <c r="U65" s="5" t="inlineStr">
+        <is>
+          <t>ChatScreen holds `text`, `offsetRef`, `showJump`/`showJumpRef` and `newestIdRef` in component state and nothing resets them when `conversationId` changes. Fix: either give the Chat screen a `getId: ({ params }) =&gt; params.conversationId` so the deep link remounts it, or reset every piece of local state in an effect keyed on conversationId.</t>
+        </is>
+      </c>
+      <c r="V65" s="5" t="inlineStr"/>
+      <c r="W65" s="5" t="inlineStr"/>
+      <c r="X65" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y65" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z65" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA65" s="5" t="inlineStr">
+        <is>
+          <t>Found by a code-level audit. VC-053 fixed the TITLE on this exact entry point, which confirms the param-update path is real and exercised; the state carry-over was not addressed then.</t>
+        </is>
+      </c>
+      <c r="AB65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>VC-065</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>VC-66</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr"/>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Backing out of a chat mid-resolve strands a 20s presence timer, and can permanently disable the only code that clears it</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Chat / messaging — header presence</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/domain/sync/SyncEngine.ts (activatePresence / deactivatePresence / startPeerPresencePolling) + features/chat/hooks/useChatHeaderPresence.ts</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Any Android</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>Whenever a chat is closed before its presence resolve finishes — a sub-second window, hit often on a slow network or a busy DB</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
+          <t>Deterministic by code inspection; needs the chat closed inside the await window.</t>
+        </is>
+      </c>
+      <c r="P66" s="5" t="inlineStr">
+        <is>
+          <t>Open a chat and leave it again before the presence lookup completes.</t>
+        </is>
+      </c>
+      <c r="Q66" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a chat and press back within roughly 300 ms, i.e. before the GET /presence round trip resolves.
+2. Stay out of every chat.
+3. Watch for JS-thread wakeups, or instrument startPeerPresencePolling.</t>
+        </is>
+      </c>
+      <c r="R66" s="5" t="inlineStr">
+        <is>
+          <t>Leaving a chat releases everything it started. Per M7: every timer, listener, socket, subscription and worker is owned and disposable.</t>
+        </is>
+      </c>
+      <c r="S66" s="5" t="inlineStr">
+        <is>
+          <t>activatePresence registers its map entry and starts its interval AFTER two awaits, and no cancellation token reaches it. The screen cleanup runs deactivatePresence first, so the map is empty and clearPeerPresenceTimer has nothing to clear; the promise then resumes and starts a 20 s setInterval for a chat that is closed. Its own guard makes every tick a no-op, so it is an invisible timer waking the JS thread every 20 s until the next chat is opened, a background suspend, or engine stop — and when push is unavailable scheduleSuspend returns early, so it ticks all night. Worse, if the back happens during the SHORTER await (a WatermelonDB find, which blocks behind any in-flight write such as an inbound message batch), deactivatePresence deletes nothing and the entry is written afterwards: activePresencePeers then holds a permanent ghost, its size can never reach 0 again, and clearPeerPresenceTimer inside deactivatePresence becomes dead code for the rest of the session. From then on, closing ANY chat stops clearing its presence poll.</t>
+        </is>
+      </c>
+      <c r="T66" s="5" t="inlineStr">
+        <is>
+          <t>Battery and wakeups on the 3 GB reference device, exactly what the overnight-background contract M13 forbids. Silent, and a later chat open masks it because startPeerPresencePolling clears the timer first — which is why live testing never catches it.</t>
+        </is>
+      </c>
+      <c r="U66" s="5" t="inlineStr">
+        <is>
+          <t>State is registered after awaits with no cancellation. Fix: capture a generation token before the first await and bail if deactivatePresence has run since, or register the map entry BEFORE the awaits so deactivate can always see it.</t>
+        </is>
+      </c>
+      <c r="V66" s="5" t="inlineStr"/>
+      <c r="W66" s="5" t="inlineStr"/>
+      <c r="X66" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y66" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z66" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA66" s="5" t="inlineStr">
+        <is>
+          <t>Found by a code-level audit after the live two-device session.</t>
+        </is>
+      </c>
+      <c r="AB66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>VC-066</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>VC-67</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr"/>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>PushStore's JSON blobs are read-modify-write across three threads — notification lines and counts can be lost or resurrected</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Notifications — native state store</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/android/app/src/main/java/com/velchat/push/PushStore.kt (appendLine, clearLines, bumpCount, clearCount, setLastSeq, setMuted, setAvatars)</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>Any Android</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>Whenever two of the three writer threads overlap — a push landing while a chat is opened or a notification dismissed</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>Race — rare per attempt, inevitable at scale.</t>
+        </is>
+      </c>
+      <c r="P67" s="5" t="inlineStr">
+        <is>
+          <t>A push for one conversation arriving while the app clears another conversation's notification.</t>
+        </is>
+      </c>
+      <c r="Q67" s="5" t="inlineStr">
+        <is>
+          <t>1. Open chat B from its notification, so the RN native-modules thread runs clearLines for B.
+2. In the same window, have a push for chat A arrive, so the FCM delivery thread runs appendLine for A.
+3. Later, receive one new message in chat B and expand its notification.</t>
+        </is>
+      </c>
+      <c r="R67" s="5" t="inlineStr">
+        <is>
+          <t>Each conversation's stored lines and counts are independent, and every update is durable.</t>
+        </is>
+      </c>
+      <c r="S67" s="5" t="inlineStr">
+        <is>
+          <t>Each of the five maps — lines, counts, lastSeq, muted, avatars — is ONE SharedPreferences string holding every conversation, read whole and written back whole. Two threads that read before either writes will have the later write clobber the earlier. If the FCM thread wins, B's six lines survive its cancellation and the next message in B rebuilds the thread with every line the user already read — the VC-057 symptom, resurrected as a race rather than a missing call. If the other side wins, A's new line is lost and the notification shows only older lines for the message that just arrived. The same shape on counts either re-establishes a count the user just dismissed or drops a bump, and those counts feed the group summary total.</t>
+        </is>
+      </c>
+      <c r="T67" s="5" t="inlineStr">
+        <is>
+          <t>Notifications intermittently re-show read messages, drop the message that just arrived, or report a total that matches nothing. Non-deterministic, so it reads to the user as the app being unreliable.</t>
+        </is>
+      </c>
+      <c r="U67" s="5" t="inlineStr">
+        <is>
+          <t>The class doc claims every accessor is safe from any thread because SharedPreferences is internally synchronised. That is true for a single getString or putString and false for the read-then-write pairs used throughout. Three writers in one process: VelChatMessagingService on FCM's delivery thread, PushActionReceiver on the main thread, VelChatPushModule on the RN native-modules thread. Fix: one synchronized lock around every read-modify-write in the class; all callers share a single SharedPreferences instance in a single process, so that is sufficient.</t>
+        </is>
+      </c>
+      <c r="V67" s="5" t="inlineStr"/>
+      <c r="W67" s="5" t="inlineStr"/>
+      <c r="X67" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y67" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z67" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA67" s="5" t="inlineStr">
+        <is>
+          <t>Distinct from VC-033, which is about the pending-event queue. This is the other five maps. Found by a code-level audit after the live two-device session.</t>
+        </is>
+      </c>
+      <c r="AB67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>VC-067</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>VC-68</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr"/>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Swiping a notification away clears its count but keeps its message lines, so dismissed messages reappear in the next notification</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Notifications — dismiss</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/android/app/src/main/java/com/velchat/push/PushActionReceiver.kt (ACTION_DISMISS) + PushNotifications.kt (postSummary has no delete intent)</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Any Android</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>Every dismissed notification followed by a new message in the same chat</t>
+        </is>
+      </c>
+      <c r="O68" s="5" t="inlineStr">
+        <is>
+          <t>Deterministic</t>
+        </is>
+      </c>
+      <c r="P68" s="5" t="inlineStr">
+        <is>
+          <t>A conversation whose notification the user swiped away without reading.</t>
+        </is>
+      </c>
+      <c r="Q68" s="5" t="inlineStr">
+        <is>
+          <t>1. Let three messages from one contact arrive while the app is backgrounded; the notification lists three lines.
+2. Swipe the notification away without opening the chat.
+3. Have that contact send one more message.
+4. Expand the new notification.</t>
+        </is>
+      </c>
+      <c r="R68" s="5" t="inlineStr">
+        <is>
+          <t>The new notification lists only the new message. Every other teardown path clears both halves — PushNotifications.cancel does clearCount AND clearLines, with a comment saying exactly why.</t>
+        </is>
+      </c>
+      <c r="S68" s="5" t="inlineStr">
+        <is>
+          <t>The dismiss branch clears only the count and returns. The stored lines survive, so appendLine returns all four and the rebuilt MessagingStyle re-lists the three messages the user deliberately dismissed, while setNumber says 1.</t>
+        </is>
+      </c>
+      <c r="T68" s="5" t="inlineStr">
+        <is>
+          <t>Dismissing a notification does not actually dismiss its contents. The user reads four new messages for one new arrival, and the dismissal gesture stops meaning anything.</t>
+        </is>
+      </c>
+      <c r="U68" s="5" t="inlineStr">
+        <is>
+          <t>A separate receiver branch that the VC-057 fix did not reach; it needs the same clearLines the cancel path has. SECONDARY, same area: postSummary builds the group summary with setGroupSummary true and NO delete intent, unlike every per-conversation notification — so dismissing the bundle runs none of our clearing for the summary, and on any OEM build that does not deliver child delete intents on a group dismissal the counts survive wholesale and the next single message re-posts a summary counting messages already swept away.</t>
+        </is>
+      </c>
+      <c r="V68" s="5" t="inlineStr"/>
+      <c r="W68" s="5" t="inlineStr"/>
+      <c r="X68" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y68" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z68" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA68" s="5" t="inlineStr">
+        <is>
+          <t>Found by a code-level audit after the live two-device session. Deterministic, unlike the race in the sibling PushStore report.</t>
+        </is>
+      </c>
+      <c r="AB68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>VC-068</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>VC-69</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr"/>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Every load-older page re-runs the open-the-chat side effects, briefly un-suppressing notifications for the chat on screen</t>
+        </is>
+      </c>
+      <c r="E69" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F69" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Chat / messaging — history pagination</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/features/chat/hooks/useMessages.ts (the effect's dependency array includes limit)</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>Any Android</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>Once per page of scrollback</t>
+        </is>
+      </c>
+      <c r="O69" s="5" t="inlineStr">
+        <is>
+          <t>Deterministic for the wasted work; the notification window is a race inside it.</t>
+        </is>
+      </c>
+      <c r="P69" s="5" t="inlineStr">
+        <is>
+          <t>A conversation with enough history to page through.</t>
+        </is>
+      </c>
+      <c r="Q69" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a long chat and scroll up through several pages of history.
+2. Watch the network: a receipts fetch and a read frame go out per page.
+3. Have the peer send a message during the scrollback.</t>
+        </is>
+      </c>
+      <c r="R69" s="5" t="inlineStr">
+        <is>
+          <t>Opening a chat is a one-time act. Growing the local window should only re-subscribe the message query.</t>
+        </is>
+      </c>
+      <c r="S69" s="5" t="inlineStr">
+        <is>
+          <t>The effect is keyed on conversationId, meId and limit, but only observeMessages depends on limit. Each loadOlder therefore tears the effect down and re-runs ALL of it: a receipts GET, a read receipt frame, a clearConversation bridge call, and the pair setActiveConversationForPush(null) then setActiveConversationForPush(conversationId). Those two are async bridge calls, so for the length of one native round trip the native side believes NO chat is on screen — and a push landing in that window posts a heads-up notification for the chat the user is staring at, the exact failure the active-conversation mechanism exists to prevent. Ten pages of scrollback is ten such windows.</t>
+        </is>
+      </c>
+      <c r="T69" s="5" t="inlineStr">
+        <is>
+          <t>Redundant network on every page of scrollback, and an occasional notification for the conversation that is currently open. The engine's own window is zero-width because setActiveConversation is synchronous; only the native mirror is exposed.</t>
+        </is>
+      </c>
+      <c r="U69" s="5" t="inlineStr">
+        <is>
+          <t>One effect doing two jobs. Split it: keep the observeMessages subscription keyed on limit, and move the open-the-chat actions plus the AppState listener into an effect keyed on conversationId alone.</t>
+        </is>
+      </c>
+      <c r="V69" s="5" t="inlineStr"/>
+      <c r="W69" s="5" t="inlineStr"/>
+      <c r="X69" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y69" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z69" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA69" s="5" t="inlineStr">
+        <is>
+          <t>Found by a code-level audit after the live two-device session.</t>
+        </is>
+      </c>
+      <c r="AB69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>VC-069</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>VC-70</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr"/>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>The read watermark is sent at the local MAX seq, so it covers messages the device does not hold — the sender gets a blue tick for a message that was never received</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Chat / messaging — read receipts</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/domain/sync/SyncEngine.ts (markConversationRead, read-on-arrival, pageBackfill) + infra/db/receiptLedger.ts</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>Production build, live backend</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>Both test devices</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>Every time a conversation has a hole in its seq range</t>
+        </is>
+      </c>
+      <c r="O70" s="5" t="inlineStr">
+        <is>
+          <t>Observed live twice, and confirmed deterministic by code inspection.</t>
+        </is>
+      </c>
+      <c r="P70" s="5" t="inlineStr">
+        <is>
+          <t>The device is missing a message at some seq N while holding messages above it — e.g. after a fan-out drop, the exact condition VC-051 describes.</t>
+        </is>
+      </c>
+      <c r="Q70" s="5" t="inlineStr">
+        <is>
+          <t>1. Arrange for a message at seq N to be missing locally while N+1 and above are present (see VC-051 for the repro).
+2. Open that conversation on the recipient device.
+3. Look at the tick state for message N on the SENDER.</t>
+        </is>
+      </c>
+      <c r="R70" s="5" t="inlineStr">
+        <is>
+          <t>A read receipt means the recipient saw the message. A device must never acknowledge a seq it does not hold.</t>
+        </is>
+      </c>
+      <c r="S70" s="5" t="inlineStr">
+        <is>
+          <t>Receipts are cumulative watermarks — one frame carries upToSeq and covers every message at or below it — and every emitter derives that number from the local MAX seq, not the highest CONTIGUOUS seq. markConversationRead runs on every chat open and on the notification read and reply actions, and uses maxSeqForConversation; read-on-arrival uses the incoming seq itself, so the very frame that OPENS a hole immediately reports read up to its own seq; the backfill loop does the same with its highest page seq. A native path acknowledges read straight over REST from a process with no database open at all. Nothing anywhere checks that a row exists for the seq being acknowledged, and mergeWatermark is monotonic, so an over-advanced read is permanent for the life of the install.</t>
+        </is>
+      </c>
+      <c r="T70" s="5" t="inlineStr">
+        <is>
+          <t>Read receipts stop meaning anything in exactly the situation where they matter most. A sender is told a message was read when the recipient never received it and never will — which is how the VC-051 message loss stayed invisible to both sides. It also clears the recipient's unread badge for messages they have never seen.</t>
+        </is>
+      </c>
+      <c r="U70" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED in code. Fix: replace the maxSeqForConversation used for RECEIPTS with a highest-contiguous-seq query (highest seq with no hole beneath it, relative to the conversation's known floor so that trimmed history and deleted messages are not mistaken for holes), and clamp the read-on-arrival seq to that value so the frame that opens a hole reports only up to the previous localMax. The same clamp applies to the delivered watermark fed from push. Deliberately NOT bundled with the VC-051 backfill fix: it changes tick semantics on every path and needs its own tests, and getting the floor wrong would under-report reads, which is a worse bug than the one being fixed.</t>
+        </is>
+      </c>
+      <c r="V70" s="5" t="inlineStr"/>
+      <c r="W70" s="5" t="inlineStr"/>
+      <c r="X70" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y70" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z70" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA70" s="5" t="inlineStr">
+        <is>
+          <t>Split out of VC-051 during that investigation. VC-062 (a backgrounded-but-mounted chat marking arrivals read) widened the window and is fixed; this is the independent, underlying defect.</t>
+        </is>
+      </c>
+      <c r="AB70" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AB1"/>
@@ -19755,7 +20663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -19908,7 +20816,7 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C15" s="24" t="inlineStr"/>
     </row>
@@ -19919,7 +20827,7 @@
         </is>
       </c>
       <c r="B16" s="23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C16" s="24" t="inlineStr"/>
     </row>
@@ -19930,7 +20838,7 @@
         </is>
       </c>
       <c r="B17" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" s="24" t="inlineStr"/>
     </row>
@@ -19941,7 +20849,7 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" s="24" t="inlineStr"/>
     </row>
@@ -19952,7 +20860,7 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="24" t="inlineStr"/>
     </row>
@@ -20011,7 +20919,7 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>18 open P0/P1 defect(s) block the build.</t>
+          <t>20 open P0/P1 defect(s) block the build.</t>
         </is>
       </c>
     </row>
@@ -20316,17 +21224,51 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>VC-051</t>
+          <t>VC-063</t>
         </is>
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>A message the device was pushed for never reaches the chat, and no reconnect ever heals it — the sender still sees blue read ticks</t>
+          <t>A message whose realtime frame carries no body renders a permanently blank bubble — the REST recovery is dead code and the list would not re-render anyway</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>VC-064</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>Opening a chat from a notification while another chat is on screen keeps the unsent draft — one tap can send it to the wrong person</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>VC-069</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>The read watermark is sent at the local MAX seq, so it covers messages the device does not hold — the sender gets a blue tick for a message that was never received</t>
         </is>
       </c>
     </row>
@@ -20479,7 +21421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21519,25 +22461,29 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>VC-052</t>
+          <t>VC-051</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Chat thread does not follow the newest message — incoming and own-sent bubbles land hidden behind the composer</t>
+          <t>A message the device was pushed for never reaches the chat, and no reconnect ever heals it — the sender still sees blue read ticks</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-14</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr"/>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>failureScenarios.test.ts: a message dropped by fan-out</t>
+        </is>
+      </c>
       <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
@@ -21546,20 +22492,21 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/b_fg_follow.png (B at the bottom, F1-F3 arrive, list stays on S8 and the jump FAB appears), scratchpad/shots/b_one.png (single message ONE1 arrives, list left exactly one bubble short), scratchpad/shots/a_own_follow.png (A's OWN sent ONE1 clipped behind the composer), scratchpad/shots/b_offline_send.png (own offline sends clipped). The race explains the intermittency: sometimes the manual scroll lands after the anchor adjustment and it looks fine.
-FIX: the follow now goes through FlashList's `scrollToIndex({index:0})` instead of `scrollToOffset({offset:0})`, fired from `onContentSizeChange` rather than the data effect. Root cause confirmed by reading useRecyclerViewController.js: on every data change FlashList measures how far the FIRST VISIBLE item moved and calls scrollAnchorRef.scrollBy(diff) to cancel the shift, gated on a `pauseOffsetCorrection` ref that ONLY scrollToIndex raises — so a plain offset scroll was undone every time and the thread landed exactly one bubble short. Firing from onContentSizeChange means index 0 has a real layout instead of the stale one it would have in the same commit. Anchoring is deliberately kept: it is the right behaviour for a reader scrolled up in history, whom shouldScrollToLatest still leaves alone; a drag cancels any pending follow so loadOlder growing the content is never mistaken for a new message. An intermediate attempt using scrollToOffset from onContentSizeChange plus a requestAnimationFrame retry was built and tested on device and still landed one bubble short — that is what identified the pauseOffsetCorrection gate. VERIFIED ON DEVICE: a four-message burst now ends with the newest message fully visible above the composer (scratchpad/shots/v2_own_follow.png) where the same burst on the previous build left it clipped (v_own_follow.png). Still to verify with a second device: the INCOMING-message path, and the notification tap-through landing position.</t>
+          <t>Evidence: scratchpad/shots/a_inline_rx.png (A shows KILL2 09:39 with blue ticks) vs scratchpad/shots/b_kill2_check.png (B's thread jumps BG1 09:37 -&gt; KILL1 09:37 -&gt; hhh 09:40, no KILL2). Related backend defect VC-001 may be the upstream cause, but the client must still heal the gap on reconnect and must not report `read` for a message it does not hold.
+FIX (frontend): pageBackfill/backfillConversation take an optional `fromSeq`, and the gap probe passes the pre-apply `localMax` — so the repair asks the server from the LOWER edge of the hole instead of from the message that revealed it. Re-fetching the rows already held between localMax and the incoming seq is free: applyServerMessages dedups on (conversation_id, seq) and on client_msg_id inside the write lock. Three end-to-end tests added to failureScenarios.test.ts, driving the real engine against the fake server, written RED first — and rewritten once when the first version passed for the wrong reason (bootConnected’s own reconnect backfill was healing the hole), so each test now brings the socket up while the device is already caught up. Verified: 537/537 jest, tsc clean, eslint 0 errors.
+STILL OPEN, tracked separately: (a) the FALSE READ TICK is not this fix — markConversationRead and read-on-arrival emit a CUMULATIVE read watermark at the local MAX, which covers a missing seq beneath it; clamping every read/delivered watermark to the highest CONTIGUOUS seq actually held is the correct fix and is filed as its own bug because it changes tick semantics everywhere and needs its own tests. (b) a hole detected once is only remembered in memory (gapProbedFrom), so a hole that a probe fails to close is forgotten on restart — persisting unhealed holes for retry is follow-up work. (c) VelChatMessagingService could enqueue a durable `resync` marker when JS is dead, the same fallback its siblings already have. (d) If the backend never durably stored or re-serves the message, no client change recovers it (see VC-001) — the fix then converts silent loss into an honest grey tick rather than a recovery.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>VC-053</t>
+          <t>VC-052</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Chat opened from a notification is titled "Chats" instead of the contact's name, and the avatar loses its initial</t>
+          <t>Chat thread does not follow the newest message — incoming and own-sent bubbles land hidden behind the composer</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -21581,25 +22528,25 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/b_tapthrough.png and b_jump.png (header 'Chats' after notification tap) vs scratchpad/shots/b_off_kbd.png (header 'Aayush Jain 🤗' for the same chat opened from the list). Relates to VC-048, which reported the tap-through as not opening the chat at all; the open now works, this is the remaining defect on that path.
-FIX: new pure helper `chatTitle(routeName, rowName, fallback)` in ui/chat/chatModel.ts, covered by chatTitle.test.ts (4 cases, RED first). ChatHeader now resolves the title from the route name, then the conversation row it was already observing for the avatar, and only then a generic label; blank counts as absent in both sources. The avatar initial is taken from the resolved name with an empty fallback, so a genuinely unnamed conversation still falls back to the person glyph instead of showing the initial of a tab label. Needs a second device to re-verify the live tap-through.</t>
+          <t>Evidence: scratchpad/shots/b_fg_follow.png (B at the bottom, F1-F3 arrive, list stays on S8 and the jump FAB appears), scratchpad/shots/b_one.png (single message ONE1 arrives, list left exactly one bubble short), scratchpad/shots/a_own_follow.png (A's OWN sent ONE1 clipped behind the composer), scratchpad/shots/b_offline_send.png (own offline sends clipped). The race explains the intermittency: sometimes the manual scroll lands after the anchor adjustment and it looks fine.
+FIX: the follow now goes through FlashList's `scrollToIndex({index:0})` instead of `scrollToOffset({offset:0})`, fired from `onContentSizeChange` rather than the data effect. Root cause confirmed by reading useRecyclerViewController.js: on every data change FlashList measures how far the FIRST VISIBLE item moved and calls scrollAnchorRef.scrollBy(diff) to cancel the shift, gated on a `pauseOffsetCorrection` ref that ONLY scrollToIndex raises — so a plain offset scroll was undone every time and the thread landed exactly one bubble short. Firing from onContentSizeChange means index 0 has a real layout instead of the stale one it would have in the same commit. Anchoring is deliberately kept: it is the right behaviour for a reader scrolled up in history, whom shouldScrollToLatest still leaves alone; a drag cancels any pending follow so loadOlder growing the content is never mistaken for a new message. An intermediate attempt using scrollToOffset from onContentSizeChange plus a requestAnimationFrame retry was built and tested on device and still landed one bubble short — that is what identified the pauseOffsetCorrection gate. VERIFIED ON DEVICE: a four-message burst now ends with the newest message fully visible above the composer (scratchpad/shots/v2_own_follow.png) where the same burst on the previous build left it clipped (v_own_follow.png). Still to verify with a second device: the INCOMING-message path, and the notification tap-through landing position.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>VC-054</t>
+          <t>VC-053</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Notification group summary says "N new messages" but N is the number of chats, not the number of messages</t>
+          <t>Chat opened from a notification is titled "Chats" instead of the contact's name, and the avatar loses its initial</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -21616,20 +22563,20 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>Evidence: dumpsys output captured twice in the live session (8 messages -&gt; '5 new messages'; 1 message -&gt; '5 new messages').
-FIX: added `PushStore.countedMessages()`, which sums the per-conversation counters the store already held, and postSummary now formats that instead of `countedConversations()`. The &lt;=1 guard that suppresses the summary for a single chat still uses the conversation count, which is correct. Needs a second device to re-verify live.</t>
+          <t>Evidence: scratchpad/shots/b_tapthrough.png and b_jump.png (header 'Chats' after notification tap) vs scratchpad/shots/b_off_kbd.png (header 'Aayush Jain 🤗' for the same chat opened from the list). Relates to VC-048, which reported the tap-through as not opening the chat at all; the open now works, this is the remaining defect on that path.
+FIX: new pure helper `chatTitle(routeName, rowName, fallback)` in ui/chat/chatModel.ts, covered by chatTitle.test.ts (4 cases, RED first). ChatHeader now resolves the title from the route name, then the conversation row it was already observing for the avatar, and only then a generic label; blank counts as absent in both sources. The avatar initial is taken from the resolved name with an empty fallback, so a genuinely unnamed conversation still falls back to the person glyph instead of showing the initial of a tab label. Needs a second device to re-verify the live tap-through.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>VC-055</t>
+          <t>VC-054</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Every notification is tinted the abandoned violet #7C5CFF, which matches nothing in the shipped monochrome theme</t>
+          <t>Notification group summary says "N new messages" but N is the number of chats, not the number of messages</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -21651,20 +22598,20 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Confirmed by reading tokens.ts (brandFrom '#0B0B0C' / '#F5F5F7') against push_strings.xml (#7C5CFF) and by the live dumpsys record color=0xff7c5cff.
-FIX: push_accent is now #0B0B0C, the monochrome brand accent from design-system/tokens.ts, and the misleading resource comment about a violet gradient is replaced. Android resolves this against the shade background for contrast. Needs a second device to re-verify live.</t>
+          <t>Evidence: dumpsys output captured twice in the live session (8 messages -&gt; '5 new messages'; 1 message -&gt; '5 new messages').
+FIX: added `PushStore.countedMessages()`, which sums the per-conversation counters the store already held, and postSummary now formats that instead of `countedConversations()`. The &lt;=1 guard that suppresses the summary for a single chat still uses the conversation count, which is correct. Needs a second device to re-verify live.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>VC-057</t>
+          <t>VC-055</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Notification re-lists messages the user has already read once the chat is reopened and a new message arrives</t>
+          <t>Every notification is tinted the abandoned violet #7C5CFF, which matches nothing in the shipped monochrome theme</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -21686,20 +22633,20 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/b_shade.png (S3..S8 before opening), scratchpad/shots/b_tapthrough.png (chat opened, tray cleared, all read), scratchpad/shots/b_reply_open.png (next notification still carries S6, S7, S8, BG1).
-ROOT CAUSE FOUND and FIXED via VC-062. The clearing path was wired correctly all along — clearConversationNotification -&gt; VelChatPushModule.clearConversation -&gt; PushNotifications.cancel -&gt; store.clearLines — but it only ran from the chat screen's MOUNT effect. A notification tap RESUMES an already-mounted ChatScreen, so that effect never re-ran, and the tray entry disappearing was just the notification's own AUTO_CANCEL flag removing the posted notification while the stored lines and counters survived. useMessages now also clears on every return to the foreground. Live re-verification pending a second device.</t>
+          <t>Confirmed by reading tokens.ts (brandFrom '#0B0B0C' / '#F5F5F7') against push_strings.xml (#7C5CFF) and by the live dumpsys record color=0xff7c5cff.
+FIX: push_accent is now #0B0B0C, the monochrome brand accent from design-system/tokens.ts, and the misleading resource comment about a violet gradient is replaced. Android resolves this against the shade background for contrast. Needs a second device to re-verify live.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>VC-058</t>
+          <t>VC-057</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Chat-list preview can regress to an older message — the preview is written unconditionally while the timestamp is guarded</t>
+          <t>Notification re-lists messages the user has already read once the chat is reopened and a new message arrives</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -21721,25 +22668,25 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/b_after_reply.png (row reads 'KILL1' while KILL2 was newer). Fix is to move the preview write inside the same freshness check as the timestamp.
-FIX: the preview write now sits behind the same freshness check as the sort key in upsertConversation — a single `fresher` predicate gates both, so a stale patch can no longer overwrite what the row says while being correctly refused a reorder.</t>
+          <t>Evidence: scratchpad/shots/b_shade.png (S3..S8 before opening), scratchpad/shots/b_tapthrough.png (chat opened, tray cleared, all read), scratchpad/shots/b_reply_open.png (next notification still carries S6, S7, S8, BG1).
+ROOT CAUSE FOUND and FIXED via VC-062. The clearing path was wired correctly all along — clearConversationNotification -&gt; VelChatPushModule.clearConversation -&gt; PushNotifications.cancel -&gt; store.clearLines — but it only ran from the chat screen's MOUNT effect. A notification tap RESUMES an already-mounted ChatScreen, so that effect never re-ran, and the tray entry disappearing was just the notification's own AUTO_CANCEL flag removing the posted notification while the stored lines and counters survived. useMessages now also clears on every return to the foreground. Live re-verification pending a second device.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>VC-060</t>
+          <t>VC-058</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Incoming message bubbles are nearly invisible in light theme — #F7F7F8 on #FFFFFF with no border (1.04:1)</t>
+          <t>Chat-list preview can regress to an older message — the preview is written unconditionally while the timestamp is guarded</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -21756,20 +22703,20 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/a_relaunch.png — the 'kkr' and 'h' bubbles in light theme. Fix options: give the incoming bubble a hairline in BOTH schemes, or darken `bgSubtle` for this use.
-FIX: the incoming-bubble hairline is no longer dark-only; it applies in both schemes, using the wallpaper-supplied border when the chat has a decorated ground and t.colors.hairline otherwise.</t>
+          <t>Evidence: scratchpad/shots/b_after_reply.png (row reads 'KILL1' while KILL2 was newer). Fix is to move the preview write inside the same freshness check as the timestamp.
+FIX: the preview write now sits behind the same freshness check as the sort key in upsertConversation — a single `fresher` predicate gates both, so a stale patch can no longer overwrite what the row says while being correctly refused a reorder.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>VC-061</t>
+          <t>VC-060</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>A 48dp empty band sits between the composer and the keyboard whenever the keyboard is open</t>
+          <t>Incoming message bubbles are nearly invisible in light theme — #F7F7F8 on #FFFFFF with no border (1.04:1)</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -21791,44 +22738,79 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
+          <t>Evidence: scratchpad/shots/a_relaunch.png — the 'kkr' and 'h' bubbles in light theme. Fix options: give the incoming bubble a hairline in BOTH schemes, or darken `bgSubtle` for this use.
+FIX: the incoming-bubble hairline is no longer dark-only; it applies in both schemes, using the wallpaper-supplied border when the chat has a decorated ground and t.colors.hairline otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>VC-061</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>A 48dp empty band sits between the composer and the keyboard whenever the keyboard is open</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
           <t>Evidence: scratchpad/shots/a_cal.png and a_own_follow.png — the white band between the composer pill and the keyboard's suggestion strip. Same file also sets `borderTopWidth: 0` alongside a `borderTopColor`, so the intended separator between the thread and the composer never draws.
 FIX: keyboard-up paddingBottom drops from spacing.huge (48dp) to spacing.xs (8dp), and borderTopWidth goes from 0 to 1 so the separator the style always declared actually draws. VERIFIED ON DEVICE: scratchpad/shots/v2_own_follow.png shows the hairline above the composer and the composer sitting close to the keyboard.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>VC-062</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>A chat left open while the app is backgrounded keeps marking arriving messages read — the sender gets a blue tick for a message nobody has seen</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>chatVisibility.test.tsx: the chat only counts as on screen while it is visible</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Found while tracing VC-057. Same listener is also the only place a notification TAP can clear a conversation's stored notification lines, because tapping resumes an ALREADY-MOUNTED chat screen and the mount effect never re-runs.
 FIX: the AppState listener in useMessages now withdraws and re-asserts the ENGINE's active conversation alongside the push layer's, and on returning to the foreground it re-reports the read and clears the conversation notification. Three new hook tests (chatVisibility.test.tsx) cover it, written RED first: before the change the background case recorded zero setActiveConversation calls, which is the bug exactly. Clearing on resume is also what fixes VC-057 — a notification TAP resumes an ALREADY-MOUNTED chat screen, so the mount effect never re-ran and the stored MessagingStyle lines were never dropped. Verified: 534/534 jest, tsc clean, eslint 0 errors. Live two-device re-verification still pending — the test phone was disconnected before it could be run.</t>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -641,7 +641,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-19 08:20 UTC</t>
+          <t>Generated 2026-09-19 08:22 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -19614,7 +19614,8 @@
       <c r="AA62" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/a_cal.png and a_own_follow.png — the white band between the composer pill and the keyboard's suggestion strip. Same file also sets `borderTopWidth: 0` alongside a `borderTopColor`, so the intended separator between the thread and the composer never draws.
-FIX: keyboard-up paddingBottom drops from spacing.huge (48dp) to spacing.xs (8dp), and borderTopWidth goes from 0 to 1 so the separator the style always declared actually draws. VERIFIED ON DEVICE: scratchpad/shots/v2_own_follow.png shows the hairline above the composer and the composer sitting close to the keyboard.</t>
+FIX: keyboard-up paddingBottom drops from spacing.huge (48dp) to spacing.xs (8dp), and borderTopWidth goes from 0 to 1 so the separator the style always declared actually draws. VERIFIED ON DEVICE: scratchpad/shots/v2_own_follow.png shows the hairline above the composer and the composer sitting close to the keyboard.
+CORRECTION after on-device testing. Only HALF of this was a defect. The borderTopWidth 0 -&gt; 1 fix is right and shipped: the separator the style always declared now draws. The 48dp padding is NOT over-generous, it is LOAD-BEARING — the parent lifts the bar by keyboardDidShow.endCoordinates.height, and under RN 0.86 Android edge-to-edge that value lands short of the keyboard the user actually sees. Trimming it to 8dp moved the input 40dp down and put it BEHIND the keyboard on a 3-button-nav CPH2643; caught on the device and reverted before it could ship. The white band is cosmetic and invisible against a light keyboard. The real fix is to correct the LIFT, not the padding, and that is separate work.</t>
         </is>
       </c>
       <c r="AB62" s="5" t="inlineStr"/>
@@ -22774,7 +22775,8 @@
       <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/a_cal.png and a_own_follow.png — the white band between the composer pill and the keyboard's suggestion strip. Same file also sets `borderTopWidth: 0` alongside a `borderTopColor`, so the intended separator between the thread and the composer never draws.
-FIX: keyboard-up paddingBottom drops from spacing.huge (48dp) to spacing.xs (8dp), and borderTopWidth goes from 0 to 1 so the separator the style always declared actually draws. VERIFIED ON DEVICE: scratchpad/shots/v2_own_follow.png shows the hairline above the composer and the composer sitting close to the keyboard.</t>
+FIX: keyboard-up paddingBottom drops from spacing.huge (48dp) to spacing.xs (8dp), and borderTopWidth goes from 0 to 1 so the separator the style always declared actually draws. VERIFIED ON DEVICE: scratchpad/shots/v2_own_follow.png shows the hairline above the composer and the composer sitting close to the keyboard.
+CORRECTION after on-device testing. Only HALF of this was a defect. The borderTopWidth 0 -&gt; 1 fix is right and shipped: the separator the style always declared now draws. The 48dp padding is NOT over-generous, it is LOAD-BEARING — the parent lifts the bar by keyboardDidShow.endCoordinates.height, and under RN 0.86 Android edge-to-edge that value lands short of the keyboard the user actually sees. Trimming it to 8dp moved the input 40dp down and put it BEHIND the keyboard on a 3-button-nav CPH2643; caught on the device and reverted before it could ship. The white band is cosmetic and invisible against a light keyboard. The real fix is to correct the LIFT, not the padding, and that is separate work.</t>
         </is>
       </c>
     </row>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -641,7 +641,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-19 08:22 UTC</t>
+          <t>Generated 2026-09-19 14:32 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -11043,7 +11043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB70"/>
+  <dimension ref="A1:AB71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18878,7 +18878,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -18972,7 +18972,11 @@
       </c>
       <c r="AA57" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/b_reply_open.png (expanded notification shows S6, S7, S8, BG1, KILL2, KILL1) vs scratchpad/shots/a_inline_rx.png (chat shows KILL1 09:37 then KILL2 09:39, correct).</t>
+          <t>Evidence: scratchpad/shots/b_reply_open.png (expanded notification shows S6, S7, S8, BG1, KILL2, KILL1) vs scratchpad/shots/a_inline_rx.png (chat shows KILL1 09:37 then KILL2 09:39, correct).
+FIX: `PushStore.Line` now carries the message's own `seq`, persisted as the JSON key `"q"`, and `showMessage` passes the push's seq into `appendLine`. `appendLine` SORTS before applying the `MAX_LINES` cap, and that order is the fix rather than a detail: capping first dropped whichever line FCM happened to deliver earliest, so an out-of-order push could evict a message newer than the one it kept. `setContentText` and `setLargeIcon` now read the newest INCOMING line (`lines.lastOrNull { !it.mine }`) instead of the message that arrived last, so the collapsed row and the face on it agree with the expanded thread — incoming only, because an inline reply can sort last and quoting the user's own words back at them is not a notification about anything.
+MIGRATION for installs whose stored lines predate `q`: in `sortBySeq` each entry inherits the rank of the one before it and the sort is stable, so a legacy thread ranks entirely at zero and comes back exactly as stored — the only order anyone ever knew for it — while an inline reply (also seq 0) ranks immediately after the message it answered.
+KNOWN LIMITATION, left open deliberately: `Line.at` is still the ARRIVAL timestamp (`System.currentTimeMillis()` at `showMessage`), because the push payload carries no message timestamp. MessagingStyle stamps each line with it, so a REORDERED thread can show non-monotonic times until the backend sends a message timestamp. The order is now right; the clock beside it is not.
+NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device.</t>
         </is>
       </c>
       <c r="AB57" s="5" t="inlineStr"/>
@@ -19246,7 +19250,11 @@
           <t>VC-60</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr"/>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>composerControls.test.tsx: the controls that are not built yet, composerControls.test.tsx: the one control that is wired</t>
+        </is>
+      </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Composer's emoji, attach, camera and mic buttons are dead controls that look and behave as if they work</t>
@@ -19264,7 +19272,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
@@ -19357,7 +19365,10 @@
       </c>
       <c r="AA60" s="5" t="inlineStr">
         <is>
-          <t>Minimum viable fix for a release build: hide the unimplemented controls, or render them disabled (reduced opacity + accessibilityState disabled) so neither sighted nor screen-reader users are misled.</t>
+          <t>Minimum viable fix for a release build: hide the unimplemented controls, or render them disabled (reduced opacity + accessibilityState disabled) so neither sighted nor screen-reader users are misled.
+FIX: `PillIconButton` lost its `onPress` prop entirely — emoji, attach and camera now render a `Pressable` with a real `disabled` and `accessibilityState={{disabled: true}}`, and the pressed-opacity branch is gone, so a tap produces no fake response at all and TalkBack announces them as disabled rather than as working buttons. The primary circle does the same conditionally (`disabled={!hasText}`, `accessibilityState` following it, and `opacity: pressed &amp;&amp; hasText ? 0.8 : 1`), so the one control that is a send button half the time and an unbuilt mic the other half reports which one it currently is.
+Everything visual is UNCHANGED on purpose: the icons, the 34x38 box and the full opacity are exactly what shipped. `composerControls.test.tsx` (7 tests) pins that box and the opacity so a well-meant "just dim them" is caught as the visual change it would be.
+STILL ACTIONABLE — PRODUCT DECISION OUTSTANDING. What shipped only stops these controls lying about being enabled. Whether an unbuilt control should be HIDDEN or visibly greyed has NOT been decided, and this fix deliberately does neither. Marked Fixed for the a11y/misleading-affordance defect as reported; the visual treatment is a separate call the product owner still owes.</t>
         </is>
       </c>
       <c r="AB60" s="5" t="inlineStr"/>
@@ -19765,7 +19776,11 @@
           <t>VC-64</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr"/>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>syncLogic.test.ts: reconcileDecision (§L6 dedup), failureScenarios.test.ts: a realtime frame with no body, observeMessages.test.ts: observeMessages column coverage</t>
+        </is>
+      </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
           <t>A message whose realtime frame carries no body renders a permanently blank bubble — the REST recovery is dead code and the list would not re-render anyway</t>
@@ -19783,7 +19798,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -19877,7 +19892,11 @@
       </c>
       <c r="AA64" s="5" t="inlineStr">
         <is>
-          <t>Found by a code-level audit after the live session. Fix needs both halves: let the fill update a row matched by seq (e.g. treat a seq row with empty content as 'update'), and name `content_plain` in observeMessages' column list.</t>
+          <t>Found by a code-level audit after the live session. Fix needs both halves: let the fill update a row matched by seq (e.g. treat a seq row with empty content as 'update'), and name `content_plain` in observeMessages' column list.
+FIX, both halves — either alone still leaves a blank bubble.
+(a) THE FILL CAN NOW LAND. `reconcileDecision` takes a new `seqRowMissingBody` input: a seq row we already hold WITHOUT a body reconciles as `update` instead of `skip`. It stays narrow on purpose — only a MISSING body earns a write, so an ordinary duplicate is still free, and a message that legitimately has no text (an attachment with no caption) offers none either and still skips. `applyServerMessages` computes it as `offersBody &amp;&amp; bySeq.length &gt; 0 &amp;&amp; bySeq.every(r =&gt; !hasBody(r.contentPlain))`, resolves the update target as `byClient[0] ?? bySeq[0]` (a peer's message can never take the `client_msg_id` branch — there is none on the wire and the insert synthesises `srv_&lt;conv&gt;_&lt;seq&gt;`), and re-bumps the chat-list preview the bodiless frame had written as empty. The bump passes `byClient.length &gt; 0 || own` rather than a flat `true`, so a refill corrects the preview without being counted as a second unread arrival.
+(b) THE LIST NOW RE-RENDERS. `observeMessages` names `content_plain` in a new exported `MESSAGE_OBSERVED_COLUMNS`, kept beside the subscription so the two cannot drift. `observeWithColumns` emits only for the columns it is NAMED (or a change in the matched-record set), so before this the refill wrote the text into the database and nothing woke: the message was there, the text was there, and the user kept the empty bubble until they left the chat and came back.
+The column test asserts the LIST rather than an emission, and that is deliberate: WatermelonDB observables do not emit under the Loki adapter Jest uses, so an emission-based test would fail identically whether the bug is present or not and would prove nothing.</t>
         </is>
       </c>
       <c r="AB64" s="5" t="inlineStr"/>
@@ -19893,7 +19912,11 @@
           <t>VC-65</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr"/>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>conversationSwitch.test.tsx: opening another chat from a notification, conversationSwitch.test.tsx: a re-render that is not a conversation switch</t>
+        </is>
+      </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Opening a chat from a notification while another chat is on screen keeps the unsent draft — one tap can send it to the wrong person</t>
@@ -19911,7 +19934,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -20006,7 +20029,10 @@
       </c>
       <c r="AA65" s="5" t="inlineStr">
         <is>
-          <t>Found by a code-level audit. VC-053 fixed the TITLE on this exact entry point, which confirms the param-update path is real and exercised; the state carry-over was not addressed then.</t>
+          <t>Found by a code-level audit. VC-053 fixed the TITLE on this exact entry point, which confirms the param-update path is real and exercised; the state carry-over was not addressed then.
+FIX — and NOT the `getId` this entry proposed. `navigation/RootNavigator.tsx` is UNCHANGED: the Chat screen still has no `getId`, and the deep link still reuses the route and swaps `route.params`. What changed is entirely in `ChatScreen.tsx`: it is now a shell that reads `route.params` and renders the real screen — the old body, renamed `ChatThread` — as `&lt;ChatThread key={conversationId} … /&gt;`. The key IS the reset. React tears the old thread down and builds a new one, so `text`, `offsetRef`, `showJump`/`showJumpRef` and `newestIdRef` cannot cross over, and whatever state `ChatThread` grows later is covered by construction instead of by somebody remembering to add it to a reset effect.
+`getId` was considered and rejected for two reasons recorded in the file's doc comment. It remounts by PUSHING a second Chat route (StackRouter reuses a route only when the id matches) and native-stack keeps every route beneath the top mounted — so one live thread per notification tap, each holding a DB subscription and a FlashList, on the 3 GB reference device (§R5). And the route popped back to would sit on screen with NO active conversation, because the effect that claims it keys on the id rather than on focus and so never re-runs — re-opening VC-062. Remounting inside the route leaves the stack exactly as it is.
+Covered by `conversationSwitch.test.tsx` (5 tests): the draft does not carry over, the previous chat's words cannot be sent to the new peer, the new conversation lands at the bottom rather than where the old one was left, the header still gets the conversation it was sent, and — the guard against over-correcting — an ordinary re-render that is NOT a conversation switch leaves a half-typed message alone.</t>
         </is>
       </c>
       <c r="AB65" s="5" t="inlineStr"/>
@@ -20022,7 +20048,11 @@
           <t>VC-66</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr"/>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>presenceLifecycle.test.ts: a chat closed while its presence is still resolving</t>
+        </is>
+      </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Backing out of a chat mid-resolve strands a 20s presence timer, and can permanently disable the only code that clears it</t>
@@ -20040,7 +20070,7 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -20134,7 +20164,10 @@
       </c>
       <c r="AA66" s="5" t="inlineStr">
         <is>
-          <t>Found by a code-level audit after the live two-device session.</t>
+          <t>Found by a code-level audit after the live two-device session.
+FIX: a `presenceEpoch` counter on the engine. `deactivatePresence` bumps it BEFORE the map delete — before, so an activate still awaiting sees the move rather than racing the delete — and the two paths that clear `activePresencePeers` wholesale, `stop()` and `onSessionCleared()`, bump it too. `activatePresence` captures the epoch before its first await and bails at three points: after the stored-peer lookup (`peerIdFor`), after the members fallback, and again after `refreshPeerPresence`.
+The FIRST check is what kills the permanent ghost — everything past it writes to `activePresencePeers`, and it was that late write landing after the close's delete that made the map's size unable to reach 0 again and turned `clearPeerPresenceTimer` into dead code for the rest of the session. The LAST also undoes its own registration (`activePresencePeers.delete(conversationId)`, then `clearPeerPresenceTimer()` if it was the last chat), because by that point it has already registered and the network round trip is the widest window of the three.
+Covered by `presenceLifecycle.test.ts`, written RED first and driving both windows with hand-resolved deferred promises so the race is deterministic rather than hoped for. Before the fix, `setInterval(fn, 20000)` was provably called for a chat that was already closed — the §M7/§M13 violation this entry describes, reproduced in a test rather than argued about.</t>
         </is>
       </c>
       <c r="AB66" s="5" t="inlineStr"/>
@@ -20168,7 +20201,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -20262,7 +20295,12 @@
       </c>
       <c r="AA67" s="5" t="inlineStr">
         <is>
-          <t>Distinct from VC-033, which is about the pending-event queue. This is the other five maps. Found by a code-level audit after the live two-device session.</t>
+          <t>Distinct from VC-033, which is about the pending-event queue. This is the other five maps. Found by a code-level audit after the live two-device session.
+FIX: one `synchronized(WRITE_LOCK)` monitor wrapping every read-modify-write in the class — `appendLine`, `clearLines`, `clearAllLines`, `bumpCount`, `clearCount`, `clearAllCounts`, `setLastSeq`, `setMuted`, `putNames` (both name maps) and `putPersonAvatar`, plus `enqueueEvent`/`takeEvents` on the pending-event queue this entry split off from VC-033.
+The monitor is on the COMPANION object, and that is load-bearing rather than a style choice: `PushStore(context)` is constructed FRESH at each entry point — the FCM service, the broadcast receiver, the RN module — so an instance monitor would have been three separate locks guarding one file, which is no lock at all. Android hands every instance the same `SharedPreferences` object for a given file in a given process, so one process-wide monitor is exactly the scope of the contention.
+Deliberately OUTSIDE the lock: the blind `commit()` writes (`setCredentials`, `clearSession`, `setActiveConversation`) and the pure single reads. Those have nothing to read first, so there is no read-modify-write to protect, and `commit()` blocks on a disk sync — nothing here is worth holding a monitor across one. `clearAllCounts`/`clearAllLines` are blind too but still take it, because a `bumpCount` that read the map before them and writes after would otherwise put back a count the user just cleared.
+The class doc is corrected in place: its claim that every accessor was thread-safe "because SharedPreferences is internally synchronised" is true of a single `getString`/`putString` and false of every pair this class actually uses, which is why the comment is now the explanation of the race instead of the reason nobody looked for it.
+NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device. A lost-update race across three native threads is not reachable from the JS test harness in any case.</t>
         </is>
       </c>
       <c r="AB67" s="5" t="inlineStr"/>
@@ -20296,7 +20334,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -20391,7 +20429,10 @@
       </c>
       <c r="AA68" s="5" t="inlineStr">
         <is>
-          <t>Found by a code-level audit after the live two-device session. Deterministic, unlike the race in the sibling PushStore report.</t>
+          <t>Found by a code-level audit after the live two-device session. Deterministic, unlike the race in the sibling PushStore report.
+FIX: the `ACTION_DISMISS` branch now calls `store.clearLines(conversationId)` alongside `clearCount`, matching `PushNotifications.cancel`, which has always dropped both halves.
+The SECONDARY half of this report is fixed too, because a backstop that does half of what it backs up just relocates the bug to the group path. `postSummary` gained `setDeleteIntent(summaryDismissIntent(context))`, carrying a new `ACTION_DISMISS_SUMMARY` that `PushActionReceiver.onReceive` answers BEFORE the conversation-id extra is demanded — the summary belongs to no single conversation, so it carries no id and the existing `getStringExtra(...) ?: return` would have swallowed it silently. That branch clears counts AND lines wholesale (`clearAllCounts` + `clearAllLines`). It is idempotent on builds where the children's delete intents do arrive, and it is the only clearing that happens on the OEM builds where they do not.
+NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device.</t>
         </is>
       </c>
       <c r="AB68" s="5" t="inlineStr"/>
@@ -20407,7 +20448,11 @@
           <t>VC-69</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr"/>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>chatOpenEffects.test.tsx: paging through history is not re-opening the chat</t>
+        </is>
+      </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
           <t>Every load-older page re-runs the open-the-chat side effects, briefly un-suppressing notifications for the chat on screen</t>
@@ -20425,7 +20470,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -20519,7 +20564,11 @@
       </c>
       <c r="AA69" s="5" t="inlineStr">
         <is>
-          <t>Found by a code-level audit after the live two-device session.</t>
+          <t>Found by a code-level audit after the live two-device session.
+FIX: the `useMessages` effect was split in two, exactly as this entry proposed. The open-the-chat work — `clearUnread` plus the read frame, the receipts GET, `syncEngine.setActiveConversation`, `setActiveConversationForPush`, the `clearConversationNotification` bridge call and the AppState listener — now sits in an effect keyed on `conversationId` ALONE, with its teardown (`appStateSub.remove()` and both active-conversation withdrawals) moved across with it. A second effect keyed on `[conversationId, limit]` does the only thing a wider window actually changes: subscribe `observeMessages` and release the narrower subscription.
+`meId` came out of both dependency arrays. Neither half ever read it — it is a stable account id — so keeping it there only ever meant more ways to re-run all of the above.
+The consequence that matters: `loadOlder` no longer tears down and re-runs the `setActiveConversationForPush(null)` → `…(conversationId)` pair. That hop is an async bridge call, so each page of scrollback opened a window in which the native side believed NO chat was on screen and a push landing inside it posted a heads-up notification for the chat the user was reading.
+Covered by `chatOpenEffects.test.tsx` (4 tests): a wider window re-subscribes and releases the old subscription; the open-the-chat side effects do NOT re-run per page; the push layer is never told that no chat is on screen while one is; and — the guard against over-correcting — a DIFFERENT conversation still re-opens, and unmount still lets go.</t>
         </is>
       </c>
       <c r="AB69" s="5" t="inlineStr"/>
@@ -20535,7 +20584,11 @@
           <t>VC-70</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr"/>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>contiguousSeq.test.ts: maxContiguousSeqForConversation</t>
+        </is>
+      </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
           <t>The read watermark is sent at the local MAX seq, so it covers messages the device does not hold — the sender gets a blue tick for a message that was never received</t>
@@ -20553,7 +20606,7 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -20647,10 +20700,142 @@
       </c>
       <c r="AA70" s="5" t="inlineStr">
         <is>
-          <t>Split out of VC-051 during that investigation. VC-062 (a backgrounded-but-mounted chat marking arrivals read) widened the window and is fixed; this is the independent, underlying defect.</t>
+          <t>Split out of VC-051 during that investigation. VC-062 (a backgrounded-but-mounted chat marking arrivals read) widened the window and is fixed; this is the independent, underlying defect.
+FIX: a new `maxContiguousSeqForConversation` in `infra/db/messages.ts` — the highest seq with no KNOWN hole beneath it — over a bounded `CONTIGUITY_SCAN = 500` row scan (`seq &gt; 0`, seq DESC, then sorted ascending).
+"Known" is the load-bearing word, and the two design choices under it are the two ways this fix could have been worse than the bug. It starts from the OLDEST row held rather than from seq 1, because the device keeps a bounded window and a conversation whose oldest local row is seq 900 is normal, not a gap — reading it as one would pin every receipt at 0 and leave every sender on a single grey tick forever. And it walks UP from there so it stops at the LOWEST hole; stopping at the highest would still acknowledge every deeper one. A deleted message still counts as held, because a tombstone keeps its row and stalling the watermark behind one is the same under-reporting failure by another route.
+`markConversationRead` now uses it in place of `maxSeqForConversation`. `pageBackfill` computes it once per page and clamps BOTH cumulative watermarks with it — `noteDelivered(Math.min(highestInbound, contiguous))` and `noteRead(Math.min(highest, contiguous))` — one extra query per page, on the reconnect path only. Read-on-arrival is clamped for free with the `localMax` the gap check already holds in hand (`m.seq &lt;= localMax + 1 ? m.seq : localMax`, with `localMax === 0` treated as unloaded history rather than a hole), so the inbound hot path pays nothing: the very frame that OPENS a hole now reports read only up to the previous local max instead of claiming everything it skipped.
+Covered by `contiguousSeq.test.ts` (6 cases), including both under-reporting traps named above: unloaded history is not a hole, and a tombstone is not a hole.
+RESIDUAL, NOT FIXED HERE: the NATIVE ack path this report also named. `PushActionReceiver`'s Mark-as-read and inline-reply branches still POST `/notifications/ack` with the notification's own `seq` unclamped, because that process has no database open to scan — exactly the reason the report called it out. A native Mark-as-read on a conversation with a hole can therefore still over-claim. Worth its own entry if it is judged to matter; the three JS emitters, which are every path that runs with the app alive, are fixed.</t>
         </is>
       </c>
       <c r="AB70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>VC-070</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>VC-71</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr"/>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>A conversation with no resolved name shows as a bare em-dash in the chat list, with no way to tell who it is</t>
+        </is>
+      </c>
+      <c r="E71" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F71" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Chat list — unresolved contact</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/features/chat/ui/ChatsList.tsx:140 (and the avatar initial at :82, the accessibility label at :93)</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>Production build, live backend</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>OPPO CPH2643 (Android 16)</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>Every conversation whose peer name has not been resolved</t>
+        </is>
+      </c>
+      <c r="O71" s="5" t="inlineStr">
+        <is>
+          <t>Observed live on the real device; deterministic once a row has no name.</t>
+        </is>
+      </c>
+      <c r="P71" s="5" t="inlineStr">
+        <is>
+          <t>A conversation whose peer identity the inbox sync has not resolved and which is not in the address book.</t>
+        </is>
+      </c>
+      <c r="Q71" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the Chats tab.
+2. Look at any row whose peer name has not resolved.</t>
+        </is>
+      </c>
+      <c r="R71" s="5" t="inlineStr">
+        <is>
+          <t>The row identifies the conversation somehow — the peer's phone number is what WhatsApp shows, or failing that an explicit localised label the user can understand.</t>
+        </is>
+      </c>
+      <c r="S71" s="5" t="inlineStr">
+        <is>
+          <t>The title renders as a bare em-dash from `{name ?? '—'}`, beside a generic placeholder avatar. The row is completely unidentifiable: the only clue is the message preview. The accessibility label degrades to the literal word 'Chat', so a screen-reader user gets even less, and the avatar initial falls back to '?'.</t>
+        </is>
+      </c>
+      <c r="T71" s="5" t="inlineStr">
+        <is>
+          <t>A conversation in the user's inbox that they cannot identify at all. Observed live with a real row reading '—' and a preview of 'Gd'. Minor in isolation, but it is on the app's home screen and reads as an unfinished state rather than a deliberate one.</t>
+        </is>
+      </c>
+      <c r="U71" s="5" t="inlineStr">
+        <is>
+          <t>`{name ?? '—'}` is a placeholder that was never replaced. The row carries `peerId`, but that is an account id and not something to show a user, so the fix needs either the peer's phone number on the row or an explicit localised string — it is not a one-character change, which is presumably why the dash is still there.</t>
+        </is>
+      </c>
+      <c r="V71" s="5" t="inlineStr"/>
+      <c r="W71" s="5" t="inlineStr"/>
+      <c r="X71" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y71" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z71" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA71" s="5" t="inlineStr">
+        <is>
+          <t>Found during the live two-device session while checking the chat list; filed after confirming the source. Related to VC-047, which was about the WRONG name being shown; this is about NO name.</t>
+        </is>
+      </c>
+      <c r="AB71" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AB1"/>
@@ -20664,7 +20849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -20839,7 +21024,7 @@
         </is>
       </c>
       <c r="B17" s="23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="24" t="inlineStr"/>
     </row>
@@ -20850,7 +21035,7 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C18" s="24" t="inlineStr"/>
     </row>
@@ -20861,7 +21046,7 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C19" s="24" t="inlineStr"/>
     </row>
@@ -20920,7 +21105,7 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>20 open P0/P1 defect(s) block the build.</t>
+          <t>17 open P0/P1 defect(s) block the build.</t>
         </is>
       </c>
     </row>
@@ -21219,57 +21404,6 @@
       <c r="C45" s="24" t="inlineStr">
         <is>
           <t>Concurrent refresh-token requests can all succeed — rotation is not race-safe</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="22" t="inlineStr">
-        <is>
-          <t>VC-063</t>
-        </is>
-      </c>
-      <c r="B46" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>A message whose realtime frame carries no body renders a permanently blank bubble — the REST recovery is dead code and the list would not re-render anyway</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="22" t="inlineStr">
-        <is>
-          <t>VC-064</t>
-        </is>
-      </c>
-      <c r="B47" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>Opening a chat from a notification while another chat is on screen keeps the unsent draft — one tap can send it to the wrong person</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="22" t="inlineStr">
-        <is>
-          <t>VC-069</t>
-        </is>
-      </c>
-      <c r="B48" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>The read watermark is sent at the local MAX seq, so it covers messages the device does not hold — the sender gets a blue tick for a message that was never received</t>
         </is>
       </c>
     </row>
@@ -21422,7 +21556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22642,12 +22776,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>VC-057</t>
+          <t>VC-056</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Notification re-lists messages the user has already read once the chat is reopened and a new message arrives</t>
+          <t>Notification message lines are ordered by arrival, not by message time — an out-of-order push shows the wrong 'latest' message</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -22657,7 +22791,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-14</t>
+          <t>dev branch, 2026-09-19</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
@@ -22669,20 +22803,23 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/b_shade.png (S3..S8 before opening), scratchpad/shots/b_tapthrough.png (chat opened, tray cleared, all read), scratchpad/shots/b_reply_open.png (next notification still carries S6, S7, S8, BG1).
-ROOT CAUSE FOUND and FIXED via VC-062. The clearing path was wired correctly all along — clearConversationNotification -&gt; VelChatPushModule.clearConversation -&gt; PushNotifications.cancel -&gt; store.clearLines — but it only ran from the chat screen's MOUNT effect. A notification tap RESUMES an already-mounted ChatScreen, so that effect never re-ran, and the tray entry disappearing was just the notification's own AUTO_CANCEL flag removing the posted notification while the stored lines and counters survived. useMessages now also clears on every return to the foreground. Live re-verification pending a second device.</t>
+          <t>Evidence: scratchpad/shots/b_reply_open.png (expanded notification shows S6, S7, S8, BG1, KILL2, KILL1) vs scratchpad/shots/a_inline_rx.png (chat shows KILL1 09:37 then KILL2 09:39, correct).
+FIX: `PushStore.Line` now carries the message's own `seq`, persisted as the JSON key `"q"`, and `showMessage` passes the push's seq into `appendLine`. `appendLine` SORTS before applying the `MAX_LINES` cap, and that order is the fix rather than a detail: capping first dropped whichever line FCM happened to deliver earliest, so an out-of-order push could evict a message newer than the one it kept. `setContentText` and `setLargeIcon` now read the newest INCOMING line (`lines.lastOrNull { !it.mine }`) instead of the message that arrived last, so the collapsed row and the face on it agree with the expanded thread — incoming only, because an inline reply can sort last and quoting the user's own words back at them is not a notification about anything.
+MIGRATION for installs whose stored lines predate `q`: in `sortBySeq` each entry inherits the rank of the one before it and the sort is stable, so a legacy thread ranks entirely at zero and comes back exactly as stored — the only order anyone ever knew for it — while an inline reply (also seq 0) ranks immediately after the message it answered.
+KNOWN LIMITATION, left open deliberately: `Line.at` is still the ARRIVAL timestamp (`System.currentTimeMillis()` at `showMessage`), because the push payload carries no message timestamp. MessagingStyle stamps each line with it, so a REORDERED thread can show non-monotonic times until the backend sends a message timestamp. The order is now right; the clock beside it is not.
+NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>VC-058</t>
+          <t>VC-057</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Chat-list preview can regress to an older message — the preview is written unconditionally while the timestamp is guarded</t>
+          <t>Notification re-lists messages the user has already read once the chat is reopened and a new message arrives</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -22704,25 +22841,25 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>Evidence: scratchpad/shots/b_after_reply.png (row reads 'KILL1' while KILL2 was newer). Fix is to move the preview write inside the same freshness check as the timestamp.
-FIX: the preview write now sits behind the same freshness check as the sort key in upsertConversation — a single `fresher` predicate gates both, so a stale patch can no longer overwrite what the row says while being correctly refused a reorder.</t>
+          <t>Evidence: scratchpad/shots/b_shade.png (S3..S8 before opening), scratchpad/shots/b_tapthrough.png (chat opened, tray cleared, all read), scratchpad/shots/b_reply_open.png (next notification still carries S6, S7, S8, BG1).
+ROOT CAUSE FOUND and FIXED via VC-062. The clearing path was wired correctly all along — clearConversationNotification -&gt; VelChatPushModule.clearConversation -&gt; PushNotifications.cancel -&gt; store.clearLines — but it only ran from the chat screen's MOUNT effect. A notification tap RESUMES an already-mounted ChatScreen, so that effect never re-ran, and the tray entry disappearing was just the notification's own AUTO_CANCEL flag removing the posted notification while the stored lines and counters survived. useMessages now also clears on every return to the foreground. Live re-verification pending a second device.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>VC-060</t>
+          <t>VC-058</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Incoming message bubbles are nearly invisible in light theme — #F7F7F8 on #FFFFFF with no border (1.04:1)</t>
+          <t>Chat-list preview can regress to an older message — the preview is written unconditionally while the timestamp is guarded</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -22739,40 +22876,116 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
+          <t>Evidence: scratchpad/shots/b_after_reply.png (row reads 'KILL1' while KILL2 was newer). Fix is to move the preview write inside the same freshness check as the timestamp.
+FIX: the preview write now sits behind the same freshness check as the sort key in upsertConversation — a single `fresher` predicate gates both, so a stale patch can no longer overwrite what the row says while being correctly refused a reorder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>VC-059</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Composer's emoji, attach, camera and mic buttons are dead controls that look and behave as if they work</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>composerControls.test.tsx: the controls that are not built yet, composerControls.test.tsx: the one control that is wired</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Minimum viable fix for a release build: hide the unimplemented controls, or render them disabled (reduced opacity + accessibilityState disabled) so neither sighted nor screen-reader users are misled.
+FIX: `PillIconButton` lost its `onPress` prop entirely — emoji, attach and camera now render a `Pressable` with a real `disabled` and `accessibilityState={{disabled: true}}`, and the pressed-opacity branch is gone, so a tap produces no fake response at all and TalkBack announces them as disabled rather than as working buttons. The primary circle does the same conditionally (`disabled={!hasText}`, `accessibilityState` following it, and `opacity: pressed &amp;&amp; hasText ? 0.8 : 1`), so the one control that is a send button half the time and an unbuilt mic the other half reports which one it currently is.
+Everything visual is UNCHANGED on purpose: the icons, the 34x38 box and the full opacity are exactly what shipped. `composerControls.test.tsx` (7 tests) pins that box and the opacity so a well-meant "just dim them" is caught as the visual change it would be.
+STILL ACTIONABLE — PRODUCT DECISION OUTSTANDING. What shipped only stops these controls lying about being enabled. Whether an unbuilt control should be HIDDEN or visibly greyed has NOT been decided, and this fix deliberately does neither. Marked Fixed for the a11y/misleading-affordance defect as reported; the visual treatment is a separate call the product owner still owes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>VC-060</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Incoming message bubbles are nearly invisible in light theme — #F7F7F8 on #FFFFFF with no border (1.04:1)</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
           <t>Evidence: scratchpad/shots/a_relaunch.png — the 'kkr' and 'h' bubbles in light theme. Fix options: give the incoming bubble a hairline in BOTH schemes, or darken `bgSubtle` for this use.
 FIX: the incoming-bubble hairline is no longer dark-only; it applies in both schemes, using the wallpaper-supplied border when the chat has a decorated ground and t.colors.hairline otherwise.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>VC-061</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>A 48dp empty band sits between the composer and the keyboard whenever the keyboard is open</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/a_cal.png and a_own_follow.png — the white band between the composer pill and the keyboard's suggestion strip. Same file also sets `borderTopWidth: 0` alongside a `borderTopColor`, so the intended separator between the thread and the composer never draws.
 FIX: keyboard-up paddingBottom drops from spacing.huge (48dp) to spacing.xs (8dp), and borderTopWidth goes from 0 to 1 so the separator the style always declared actually draws. VERIFIED ON DEVICE: scratchpad/shots/v2_own_follow.png shows the hairline above the composer and the composer sitting close to the keyboard.
@@ -22780,42 +22993,327 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>VC-062</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>A chat left open while the app is backgrounded keeps marking arriving messages read — the sender gets a blue tick for a message nobody has seen</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>chatVisibility.test.tsx: the chat only counts as on screen while it is visible</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr"/>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Found while tracing VC-057. Same listener is also the only place a notification TAP can clear a conversation's stored notification lines, because tapping resumes an ALREADY-MOUNTED chat screen and the mount effect never re-runs.
 FIX: the AppState listener in useMessages now withdraws and re-asserts the ENGINE's active conversation alongside the push layer's, and on returning to the foreground it re-reports the read and clears the conversation notification. Three new hook tests (chatVisibility.test.tsx) cover it, written RED first: before the change the background case recorded zero setActiveConversation calls, which is the bug exactly. Clearing on resume is also what fixes VC-057 — a notification TAP resumes an ALREADY-MOUNTED chat screen, so the mount effect never re-ran and the stored MessagingStyle lines were never dropped. Verified: 534/534 jest, tsc clean, eslint 0 errors. Live two-device re-verification still pending — the test phone was disconnected before it could be run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>VC-063</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>A message whose realtime frame carries no body renders a permanently blank bubble — the REST recovery is dead code and the list would not re-render anyway</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>syncLogic.test.ts: reconcileDecision (§L6 dedup), failureScenarios.test.ts: a realtime frame with no body, observeMessages.test.ts: observeMessages column coverage</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Found by a code-level audit after the live session. Fix needs both halves: let the fill update a row matched by seq (e.g. treat a seq row with empty content as 'update'), and name `content_plain` in observeMessages' column list.
+FIX, both halves — either alone still leaves a blank bubble.
+(a) THE FILL CAN NOW LAND. `reconcileDecision` takes a new `seqRowMissingBody` input: a seq row we already hold WITHOUT a body reconciles as `update` instead of `skip`. It stays narrow on purpose — only a MISSING body earns a write, so an ordinary duplicate is still free, and a message that legitimately has no text (an attachment with no caption) offers none either and still skips. `applyServerMessages` computes it as `offersBody &amp;&amp; bySeq.length &gt; 0 &amp;&amp; bySeq.every(r =&gt; !hasBody(r.contentPlain))`, resolves the update target as `byClient[0] ?? bySeq[0]` (a peer's message can never take the `client_msg_id` branch — there is none on the wire and the insert synthesises `srv_&lt;conv&gt;_&lt;seq&gt;`), and re-bumps the chat-list preview the bodiless frame had written as empty. The bump passes `byClient.length &gt; 0 || own` rather than a flat `true`, so a refill corrects the preview without being counted as a second unread arrival.
+(b) THE LIST NOW RE-RENDERS. `observeMessages` names `content_plain` in a new exported `MESSAGE_OBSERVED_COLUMNS`, kept beside the subscription so the two cannot drift. `observeWithColumns` emits only for the columns it is NAMED (or a change in the matched-record set), so before this the refill wrote the text into the database and nothing woke: the message was there, the text was there, and the user kept the empty bubble until they left the chat and came back.
+The column test asserts the LIST rather than an emission, and that is deliberate: WatermelonDB observables do not emit under the Loki adapter Jest uses, so an emission-based test would fail identically whether the bug is present or not and would prove nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>VC-064</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Opening a chat from a notification while another chat is on screen keeps the unsent draft — one tap can send it to the wrong person</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>conversationSwitch.test.tsx: opening another chat from a notification, conversationSwitch.test.tsx: a re-render that is not a conversation switch</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Found by a code-level audit. VC-053 fixed the TITLE on this exact entry point, which confirms the param-update path is real and exercised; the state carry-over was not addressed then.
+FIX — and NOT the `getId` this entry proposed. `navigation/RootNavigator.tsx` is UNCHANGED: the Chat screen still has no `getId`, and the deep link still reuses the route and swaps `route.params`. What changed is entirely in `ChatScreen.tsx`: it is now a shell that reads `route.params` and renders the real screen — the old body, renamed `ChatThread` — as `&lt;ChatThread key={conversationId} … /&gt;`. The key IS the reset. React tears the old thread down and builds a new one, so `text`, `offsetRef`, `showJump`/`showJumpRef` and `newestIdRef` cannot cross over, and whatever state `ChatThread` grows later is covered by construction instead of by somebody remembering to add it to a reset effect.
+`getId` was considered and rejected for two reasons recorded in the file's doc comment. It remounts by PUSHING a second Chat route (StackRouter reuses a route only when the id matches) and native-stack keeps every route beneath the top mounted — so one live thread per notification tap, each holding a DB subscription and a FlashList, on the 3 GB reference device (§R5). And the route popped back to would sit on screen with NO active conversation, because the effect that claims it keys on the id rather than on focus and so never re-runs — re-opening VC-062. Remounting inside the route leaves the stack exactly as it is.
+Covered by `conversationSwitch.test.tsx` (5 tests): the draft does not carry over, the previous chat's words cannot be sent to the new peer, the new conversation lands at the bottom rather than where the old one was left, the header still gets the conversation it was sent, and — the guard against over-correcting — an ordinary re-render that is NOT a conversation switch leaves a half-typed message alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>VC-065</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Backing out of a chat mid-resolve strands a 20s presence timer, and can permanently disable the only code that clears it</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>presenceLifecycle.test.ts: a chat closed while its presence is still resolving</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Found by a code-level audit after the live two-device session.
+FIX: a `presenceEpoch` counter on the engine. `deactivatePresence` bumps it BEFORE the map delete — before, so an activate still awaiting sees the move rather than racing the delete — and the two paths that clear `activePresencePeers` wholesale, `stop()` and `onSessionCleared()`, bump it too. `activatePresence` captures the epoch before its first await and bails at three points: after the stored-peer lookup (`peerIdFor`), after the members fallback, and again after `refreshPeerPresence`.
+The FIRST check is what kills the permanent ghost — everything past it writes to `activePresencePeers`, and it was that late write landing after the close's delete that made the map's size unable to reach 0 again and turned `clearPeerPresenceTimer` into dead code for the rest of the session. The LAST also undoes its own registration (`activePresencePeers.delete(conversationId)`, then `clearPeerPresenceTimer()` if it was the last chat), because by that point it has already registered and the network round trip is the widest window of the three.
+Covered by `presenceLifecycle.test.ts`, written RED first and driving both windows with hand-resolved deferred promises so the race is deterministic rather than hoped for. Before the fix, `setInterval(fn, 20000)` was provably called for a chat that was already closed — the §M7/§M13 violation this entry describes, reproduced in a test rather than argued about.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>VC-066</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>PushStore's JSON blobs are read-modify-write across three threads — notification lines and counts can be lost or resurrected</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Distinct from VC-033, which is about the pending-event queue. This is the other five maps. Found by a code-level audit after the live two-device session.
+FIX: one `synchronized(WRITE_LOCK)` monitor wrapping every read-modify-write in the class — `appendLine`, `clearLines`, `clearAllLines`, `bumpCount`, `clearCount`, `clearAllCounts`, `setLastSeq`, `setMuted`, `putNames` (both name maps) and `putPersonAvatar`, plus `enqueueEvent`/`takeEvents` on the pending-event queue this entry split off from VC-033.
+The monitor is on the COMPANION object, and that is load-bearing rather than a style choice: `PushStore(context)` is constructed FRESH at each entry point — the FCM service, the broadcast receiver, the RN module — so an instance monitor would have been three separate locks guarding one file, which is no lock at all. Android hands every instance the same `SharedPreferences` object for a given file in a given process, so one process-wide monitor is exactly the scope of the contention.
+Deliberately OUTSIDE the lock: the blind `commit()` writes (`setCredentials`, `clearSession`, `setActiveConversation`) and the pure single reads. Those have nothing to read first, so there is no read-modify-write to protect, and `commit()` blocks on a disk sync — nothing here is worth holding a monitor across one. `clearAllCounts`/`clearAllLines` are blind too but still take it, because a `bumpCount` that read the map before them and writes after would otherwise put back a count the user just cleared.
+The class doc is corrected in place: its claim that every accessor was thread-safe "because SharedPreferences is internally synchronised" is true of a single `getString`/`putString` and false of every pair this class actually uses, which is why the comment is now the explanation of the race instead of the reason nobody looked for it.
+NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device. A lost-update race across three native threads is not reachable from the JS test harness in any case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>VC-067</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Swiping a notification away clears its count but keeps its message lines, so dismissed messages reappear in the next notification</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Found by a code-level audit after the live two-device session. Deterministic, unlike the race in the sibling PushStore report.
+FIX: the `ACTION_DISMISS` branch now calls `store.clearLines(conversationId)` alongside `clearCount`, matching `PushNotifications.cancel`, which has always dropped both halves.
+The SECONDARY half of this report is fixed too, because a backstop that does half of what it backs up just relocates the bug to the group path. `postSummary` gained `setDeleteIntent(summaryDismissIntent(context))`, carrying a new `ACTION_DISMISS_SUMMARY` that `PushActionReceiver.onReceive` answers BEFORE the conversation-id extra is demanded — the summary belongs to no single conversation, so it carries no id and the existing `getStringExtra(...) ?: return` would have swallowed it silently. That branch clears counts AND lines wholesale (`clearAllCounts` + `clearAllLines`). It is idempotent on builds where the children's delete intents do arrive, and it is the only clearing that happens on the OEM builds where they do not.
+NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>VC-068</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Every load-older page re-runs the open-the-chat side effects, briefly un-suppressing notifications for the chat on screen</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>chatOpenEffects.test.tsx: paging through history is not re-opening the chat</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Found by a code-level audit after the live two-device session.
+FIX: the `useMessages` effect was split in two, exactly as this entry proposed. The open-the-chat work — `clearUnread` plus the read frame, the receipts GET, `syncEngine.setActiveConversation`, `setActiveConversationForPush`, the `clearConversationNotification` bridge call and the AppState listener — now sits in an effect keyed on `conversationId` ALONE, with its teardown (`appStateSub.remove()` and both active-conversation withdrawals) moved across with it. A second effect keyed on `[conversationId, limit]` does the only thing a wider window actually changes: subscribe `observeMessages` and release the narrower subscription.
+`meId` came out of both dependency arrays. Neither half ever read it — it is a stable account id — so keeping it there only ever meant more ways to re-run all of the above.
+The consequence that matters: `loadOlder` no longer tears down and re-runs the `setActiveConversationForPush(null)` → `…(conversationId)` pair. That hop is an async bridge call, so each page of scrollback opened a window in which the native side believed NO chat was on screen and a push landing inside it posted a heads-up notification for the chat the user was reading.
+Covered by `chatOpenEffects.test.tsx` (4 tests): a wider window re-subscribes and releases the old subscription; the open-the-chat side effects do NOT re-run per page; the push layer is never told that no chat is on screen while one is; and — the guard against over-correcting — a DIFFERENT conversation still re-opens, and unmount still lets go.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>VC-069</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>The read watermark is sent at the local MAX seq, so it covers messages the device does not hold — the sender gets a blue tick for a message that was never received</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>contiguousSeq.test.ts: maxContiguousSeqForConversation</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Split out of VC-051 during that investigation. VC-062 (a backgrounded-but-mounted chat marking arrivals read) widened the window and is fixed; this is the independent, underlying defect.
+FIX: a new `maxContiguousSeqForConversation` in `infra/db/messages.ts` — the highest seq with no KNOWN hole beneath it — over a bounded `CONTIGUITY_SCAN = 500` row scan (`seq &gt; 0`, seq DESC, then sorted ascending).
+"Known" is the load-bearing word, and the two design choices under it are the two ways this fix could have been worse than the bug. It starts from the OLDEST row held rather than from seq 1, because the device keeps a bounded window and a conversation whose oldest local row is seq 900 is normal, not a gap — reading it as one would pin every receipt at 0 and leave every sender on a single grey tick forever. And it walks UP from there so it stops at the LOWEST hole; stopping at the highest would still acknowledge every deeper one. A deleted message still counts as held, because a tombstone keeps its row and stalling the watermark behind one is the same under-reporting failure by another route.
+`markConversationRead` now uses it in place of `maxSeqForConversation`. `pageBackfill` computes it once per page and clamps BOTH cumulative watermarks with it — `noteDelivered(Math.min(highestInbound, contiguous))` and `noteRead(Math.min(highest, contiguous))` — one extra query per page, on the reconnect path only. Read-on-arrival is clamped for free with the `localMax` the gap check already holds in hand (`m.seq &lt;= localMax + 1 ? m.seq : localMax`, with `localMax === 0` treated as unloaded history rather than a hole), so the inbound hot path pays nothing: the very frame that OPENS a hole now reports read only up to the previous local max instead of claiming everything it skipped.
+Covered by `contiguousSeq.test.ts` (6 cases), including both under-reporting traps named above: unloaded history is not a hole, and a tombstone is not a hole.
+RESIDUAL, NOT FIXED HERE: the NATIVE ack path this report also named. `PushActionReceiver`'s Mark-as-read and inline-reply branches still POST `/notifications/ack` with the notification's own `seq` unclamped, because that process has no database open to scan — exactly the reason the report called it out. A native Mark-as-read on a conversation with a hole can therefore still over-claim. Worth its own entry if it is judged to matter; the three JS emitters, which are every path that runs with the app alive, are fixed.</t>
         </is>
       </c>
     </row>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -641,7 +641,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-19 14:32 UTC</t>
+          <t>Generated 2026-09-19 14:58 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -11043,7 +11043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB71"/>
+  <dimension ref="A1:AB74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18456,7 +18456,8 @@
       <c r="AA53" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_fg_follow.png (B at the bottom, F1-F3 arrive, list stays on S8 and the jump FAB appears), scratchpad/shots/b_one.png (single message ONE1 arrives, list left exactly one bubble short), scratchpad/shots/a_own_follow.png (A's OWN sent ONE1 clipped behind the composer), scratchpad/shots/b_offline_send.png (own offline sends clipped). The race explains the intermittency: sometimes the manual scroll lands after the anchor adjustment and it looks fine.
-FIX: the follow now goes through FlashList's `scrollToIndex({index:0})` instead of `scrollToOffset({offset:0})`, fired from `onContentSizeChange` rather than the data effect. Root cause confirmed by reading useRecyclerViewController.js: on every data change FlashList measures how far the FIRST VISIBLE item moved and calls scrollAnchorRef.scrollBy(diff) to cancel the shift, gated on a `pauseOffsetCorrection` ref that ONLY scrollToIndex raises — so a plain offset scroll was undone every time and the thread landed exactly one bubble short. Firing from onContentSizeChange means index 0 has a real layout instead of the stale one it would have in the same commit. Anchoring is deliberately kept: it is the right behaviour for a reader scrolled up in history, whom shouldScrollToLatest still leaves alone; a drag cancels any pending follow so loadOlder growing the content is never mistaken for a new message. An intermediate attempt using scrollToOffset from onContentSizeChange plus a requestAnimationFrame retry was built and tested on device and still landed one bubble short — that is what identified the pauseOffsetCorrection gate. VERIFIED ON DEVICE: a four-message burst now ends with the newest message fully visible above the composer (scratchpad/shots/v2_own_follow.png) where the same burst on the previous build left it clipped (v_own_follow.png). Still to verify with a second device: the INCOMING-message path, and the notification tap-through landing position.</t>
+FIX: the follow now goes through FlashList's `scrollToIndex({index:0})` instead of `scrollToOffset({offset:0})`, fired from `onContentSizeChange` rather than the data effect. Root cause confirmed by reading useRecyclerViewController.js: on every data change FlashList measures how far the FIRST VISIBLE item moved and calls scrollAnchorRef.scrollBy(diff) to cancel the shift, gated on a `pauseOffsetCorrection` ref that ONLY scrollToIndex raises — so a plain offset scroll was undone every time and the thread landed exactly one bubble short. Firing from onContentSizeChange means index 0 has a real layout instead of the stale one it would have in the same commit. Anchoring is deliberately kept: it is the right behaviour for a reader scrolled up in history, whom shouldScrollToLatest still leaves alone; a drag cancels any pending follow so loadOlder growing the content is never mistaken for a new message. An intermediate attempt using scrollToOffset from onContentSizeChange plus a requestAnimationFrame retry was built and tested on device and still landed one bubble short — that is what identified the pauseOffsetCorrection gate. VERIFIED ON DEVICE: a four-message burst now ends with the newest message fully visible above the composer (scratchpad/shots/v2_own_follow.png) where the same burst on the previous build left it clipped (v_own_follow.png). Still to verify with a second device: the INCOMING-message path, and the notification tap-through landing position.
+REGRESSED AND RE-FIXED, properly this time. The scroll-command approach was wrong in kind, not in detail: three versions were tried (scrollToOffset, scrollToOffset plus a frame, scrollToIndex plus a 180ms retry) and all three lost the same race, because FlashList re-pins the viewport through an invisible ScrollAnchor and that is a STATE update landing a render or two after any callback we can scroll from. The newest bubble kept ending up one message below the fold, intermittently — and it came back on the product owner reproducing it with the keyboard up. FINAL FIX: the list uses the library own chat pattern. Not inverted, rows reversed into ascending order at the list (never in the query, so every grouping flag stays attached to its own row and the rendered result is identical to what the inverted list drew), maintainVisibleContentPosition.autoscrollToBottomThreshold pins the end, startRenderingFromBottom opens on the newest, and loadOlder moves from onEndReached to onStartReached. There is no scroll command left to lose a race. shouldScrollToLatest is gone; autoScroll.ts now only measures distance-from-bottom for the jump button. VERIFIED ON THE REAL DEVICE with the keyboard up, the exact case that was failing: five messages sent, the newest fully visible above the composer, no jump button.</t>
         </is>
       </c>
       <c r="AB53" s="5" t="inlineStr"/>
@@ -18976,7 +18977,8 @@
 FIX: `PushStore.Line` now carries the message's own `seq`, persisted as the JSON key `"q"`, and `showMessage` passes the push's seq into `appendLine`. `appendLine` SORTS before applying the `MAX_LINES` cap, and that order is the fix rather than a detail: capping first dropped whichever line FCM happened to deliver earliest, so an out-of-order push could evict a message newer than the one it kept. `setContentText` and `setLargeIcon` now read the newest INCOMING line (`lines.lastOrNull { !it.mine }`) instead of the message that arrived last, so the collapsed row and the face on it agree with the expanded thread — incoming only, because an inline reply can sort last and quoting the user's own words back at them is not a notification about anything.
 MIGRATION for installs whose stored lines predate `q`: in `sortBySeq` each entry inherits the rank of the one before it and the sort is stable, so a legacy thread ranks entirely at zero and comes back exactly as stored — the only order anyone ever knew for it — while an inline reply (also seq 0) ranks immediately after the message it answered.
 KNOWN LIMITATION, left open deliberately: `Line.at` is still the ARRIVAL timestamp (`System.currentTimeMillis()` at `showMessage`), because the push payload carries no message timestamp. MessagingStyle stamps each line with it, so a REORDERED thread can show non-monotonic times until the backend sends a message timestamp. The order is now right; the clock beside it is not.
-NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device.</t>
+NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device.
+LIVE RE-TEST 2026-09-19 on the two-device setup, following this entry's own steps (recipient package force-stopped so FCM holds a message, app launched to clear FLAG_STOPPED, a second message sent into the release window). RESULT: the expanded thread came back in seq order with the newest line last (OK4, FIN1, FIN2, FIN3, FIN4, ORD2) and the collapsed row quoted the newest, where the pre-fix run of the same procedure had produced KILL2 above KILL1. Both messages also landed in the conversation in the right order with nothing lost. CAVEAT recorded honestly: FCM released the held message quickly enough that a strictly OUT-OF-ORDER delivery was not forced on this run, so what this proves is correct ordering and no regression, not the reordering path itself firing. That path is covered by code review only (there is no Kotlin test source set in this project).</t>
         </is>
       </c>
       <c r="AB57" s="5" t="inlineStr"/>
@@ -19106,7 +19108,8 @@
       <c r="AA58" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_shade.png (S3..S8 before opening), scratchpad/shots/b_tapthrough.png (chat opened, tray cleared, all read), scratchpad/shots/b_reply_open.png (next notification still carries S6, S7, S8, BG1).
-ROOT CAUSE FOUND and FIXED via VC-062. The clearing path was wired correctly all along — clearConversationNotification -&gt; VelChatPushModule.clearConversation -&gt; PushNotifications.cancel -&gt; store.clearLines — but it only ran from the chat screen's MOUNT effect. A notification tap RESUMES an already-mounted ChatScreen, so that effect never re-ran, and the tray entry disappearing was just the notification's own AUTO_CANCEL flag removing the posted notification while the stored lines and counters survived. useMessages now also clears on every return to the foreground. Live re-verification pending a second device.</t>
+ROOT CAUSE FOUND and FIXED via VC-062. The clearing path was wired correctly all along — clearConversationNotification -&gt; VelChatPushModule.clearConversation -&gt; PushNotifications.cancel -&gt; store.clearLines — but it only ran from the chat screen's MOUNT effect. A notification tap RESUMES an already-mounted ChatScreen, so that effect never re-ran, and the tray entry disappearing was just the notification's own AUTO_CANCEL flag removing the posted notification while the stored lines and counters survived. useMessages now also clears on every return to the foreground. Live re-verification pending a second device.
+LIVE VERIFIED 2026-09-19: after opening the chat and backgrounding again, the next notification carried only the new messages — no line from the batch the user had already read.</t>
         </is>
       </c>
       <c r="AB58" s="5" t="inlineStr"/>
@@ -20432,7 +20435,8 @@
           <t>Found by a code-level audit after the live two-device session. Deterministic, unlike the race in the sibling PushStore report.
 FIX: the `ACTION_DISMISS` branch now calls `store.clearLines(conversationId)` alongside `clearCount`, matching `PushNotifications.cancel`, which has always dropped both halves.
 The SECONDARY half of this report is fixed too, because a backstop that does half of what it backs up just relocates the bug to the group path. `postSummary` gained `setDeleteIntent(summaryDismissIntent(context))`, carrying a new `ACTION_DISMISS_SUMMARY` that `PushActionReceiver.onReceive` answers BEFORE the conversation-id extra is demanded — the summary belongs to no single conversation, so it carries no id and the existing `getStringExtra(...) ?: return` would have swallowed it silently. That branch clears counts AND lines wholesale (`clearAllCounts` + `clearAllLines`). It is idempotent on builds where the children's delete intents do arrive, and it is the only clearing that happens on the OEM builds where they do not.
-NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device.</t>
+NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device.
+LIVE VERIFIED 2026-09-19 following this entry's own steps: three messages arrived while backgrounded and were swiped away unread, then one more was sent. The rebuilt notification reported android.messages = Parcelable[] (1) — one line, not four. Pre-fix the same procedure re-listed every dismissed message.</t>
         </is>
       </c>
       <c r="AB68" s="5" t="inlineStr"/>
@@ -20836,6 +20840,392 @@
         </is>
       </c>
       <c r="AB71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>VC-071</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>VC-72</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr"/>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>A notification's Mark-as-read carries the arriving seq, so a late out-of-order push acknowledges below the newest message</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Notifications — Mark as read action</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/android/app/src/main/java/com/velchat/push/PushNotifications.kt (showMessage: replyAction / markReadAction)</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>Any Android</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t>Whenever FCM delivers two messages for one chat out of order</t>
+        </is>
+      </c>
+      <c r="O72" s="5" t="inlineStr">
+        <is>
+          <t>Deterministic once the pushes land out of order.</t>
+        </is>
+      </c>
+      <c r="P72" s="5" t="inlineStr">
+        <is>
+          <t>Two messages for the same conversation where the later-sent one is delivered first.</t>
+        </is>
+      </c>
+      <c r="Q72" s="5" t="inlineStr">
+        <is>
+          <t>1. Arrange for push seq 10 to land, then push seq 9 to land after it.
+2. The collapsed notification correctly quotes message 10.
+3. Tap Mark as read.
+4. Check what the sender sees for message 10.</t>
+        </is>
+      </c>
+      <c r="R72" s="5" t="inlineStr">
+        <is>
+          <t>The action acknowledges the newest message the notification represents — which is what the rebuild after an inline reply already does, reading store.lastSeq.</t>
+        </is>
+      </c>
+      <c r="S72" s="5" t="inlineStr">
+        <is>
+          <t>Both the Reply and the Mark-as-read PendingIntents were built with showMessage's own `seq` parameter, i.e. the message that happened to arrive last. The notification's PendingIntents carry FLAG_UPDATE_CURRENT, so a late push genuinely rewrites the extras to the LOWER seq. Tapping Mark as read then acknowledges up to the late message and dismisses the notification, leaving the newer one unread to its sender until the app is opened.</t>
+        </is>
+      </c>
+      <c r="T72" s="5" t="inlineStr">
+        <is>
+          <t>The user marks a chat read and the sender still sees an unread message. Silent, and only in the out-of-order case the notification-ordering work exists to handle.</t>
+        </is>
+      </c>
+      <c r="U72" s="5" t="inlineStr">
+        <is>
+          <t>The actions were built from the arriving message rather than from the per-conversation high-water mark the store already keeps. Fixed by reading store.lastSeq after it has been bumped, exactly as showOwnReply does.</t>
+        </is>
+      </c>
+      <c r="V72" s="5" t="inlineStr"/>
+      <c r="W72" s="5" t="inlineStr"/>
+      <c r="X72" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y72" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z72" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA72" s="5" t="inlineStr">
+        <is>
+          <t>Found by an adversarial code review of the notification changes made the same day. Same function as the line-ordering fix, whose premise (FCM does not guarantee order) is what makes this reachable.</t>
+        </is>
+      </c>
+      <c r="AB72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>VC-072</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>VC-73</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr"/>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>A notification's collapsed row can show one person's words beside another person's face</t>
+        </is>
+      </c>
+      <c r="E73" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F73" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Notifications — collapsed row avatar</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/android/app/src/main/java/com/velchat/push/PushNotifications.kt (showMessage: newestSenderId)</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>Any Android</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>Group chats where a stored line has no sender id</t>
+        </is>
+      </c>
+      <c r="O73" s="5" t="inlineStr">
+        <is>
+          <t>Needs a stored line whose sender id was blank.</t>
+        </is>
+      </c>
+      <c r="P73" s="5" t="inlineStr">
+        <is>
+          <t>A group conversation whose notification thread holds a line stored without a sender id.</t>
+        </is>
+      </c>
+      <c r="Q73" s="5" t="inlineStr">
+        <is>
+          <t>1. Receive several messages in a group so the notification thread holds more than one line.
+2. Ensure one stored line has a blank sender id (an older build, or a push with no senderId).
+3. Receive one more message from a DIFFERENT member and look at the collapsed notification.</t>
+        </is>
+      </c>
+      <c r="R73" s="5" t="inlineStr">
+        <is>
+          <t>The collapsed row's avatar belongs to whoever wrote the text shown beside it.</t>
+        </is>
+      </c>
+      <c r="S73" s="5" t="inlineStr">
+        <is>
+          <t>`newestSenderId` fell back with `newest?.senderId ?: senderId`, so when the newest line exists but its stored sender id reads back as null, the row showed that line's TEXT with the ARRIVING message's avatar.</t>
+        </is>
+      </c>
+      <c r="T73" s="5" t="inlineStr">
+        <is>
+          <t>In a group, the notification attributes a message to the wrong person at a glance. Small, but it is a misattribution on the lock screen.</t>
+        </is>
+      </c>
+      <c r="U73" s="5" t="inlineStr">
+        <is>
+          <t>The elvis guarded the sender id rather than the line. Fixed by guarding on `newest` itself, so the fallback only applies when there is no newest incoming line at all.</t>
+        </is>
+      </c>
+      <c r="V73" s="5" t="inlineStr"/>
+      <c r="W73" s="5" t="inlineStr"/>
+      <c r="X73" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y73" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA73" s="5" t="inlineStr">
+        <is>
+          <t>Found by an adversarial code review of the notification changes made the same day.</t>
+        </is>
+      </c>
+      <c r="AB73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>VC-073</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>VC-74</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr"/>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Mark-as-read and inline reply acknowledge straight over REST from a process with no database, so they can still claim a message the device does not hold</t>
+        </is>
+      </c>
+      <c r="E74" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F74" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Notifications — native receipt ack</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/android/app/src/main/java/com/velchat/push/PushActionReceiver.kt (ACTION_MARK_READ, ACTION_REPLY) + PushAckClient</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>Any Android</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N74" s="5" t="inlineStr">
+        <is>
+          <t>Only for a conversation that already has a seq hole</t>
+        </is>
+      </c>
+      <c r="O74" s="5" t="inlineStr">
+        <is>
+          <t>Needs the hole from VC-051 plus a notification action taken while the app is not running.</t>
+        </is>
+      </c>
+      <c r="P74" s="5" t="inlineStr">
+        <is>
+          <t>A conversation missing a message at some seq, and a notification for a later message in it.</t>
+        </is>
+      </c>
+      <c r="Q74" s="5" t="inlineStr">
+        <is>
+          <t>1. Get the device into the VC-051 state: a message at seq N missing locally while N+1 and above are present.
+2. Receive a later message so a notification appears, with the app not running.
+3. Tap Mark as read (or send an inline Reply) without opening the app.
+4. Look at the tick state for message N on the sender.</t>
+        </is>
+      </c>
+      <c r="R74" s="5" t="inlineStr">
+        <is>
+          <t>No path acknowledges a seq the device does not hold — the same rule the JS emitters now follow.</t>
+        </is>
+      </c>
+      <c r="S74" s="5" t="inlineStr">
+        <is>
+          <t>The receiver posts the notification's own seq to POST /notifications/ack directly. Receipts are cumulative, so that covers the missing message. The three JS emitters are clamped to the highest contiguous seq the device holds; this one is not.</t>
+        </is>
+      </c>
+      <c r="T74" s="5" t="inlineStr">
+        <is>
+          <t>The narrow remainder of VC-069: a sender can still be told a message was read when the recipient never received it, but only via a notification action on an already-holed conversation.</t>
+        </is>
+      </c>
+      <c r="U74" s="5" t="inlineStr">
+        <is>
+          <t>By design, not oversight — the broadcast receiver runs in a process with no WatermelonDB open, so it cannot compute the contiguous watermark the JS path uses. Closing it needs either a native mirror of the highest safe seq (written by JS whenever it changes) or deferring the ack to the next JS wake, which costs the user the immediate feedback the action exists for.</t>
+        </is>
+      </c>
+      <c r="V74" s="5" t="inlineStr"/>
+      <c r="W74" s="5" t="inlineStr"/>
+      <c r="X74" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y74" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z74" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA74" s="5" t="inlineStr">
+        <is>
+          <t>Split out of VC-069 while verifying that fix. Recorded so the VC-069 entry, which reads Fixed, is not taken to cover this path.</t>
+        </is>
+      </c>
+      <c r="AB74" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AB1"/>
@@ -21013,7 +21403,7 @@
         </is>
       </c>
       <c r="B16" s="23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" s="24" t="inlineStr"/>
     </row>
@@ -21024,7 +21414,7 @@
         </is>
       </c>
       <c r="B17" s="23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C17" s="24" t="inlineStr"/>
     </row>
@@ -21035,7 +21425,7 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="24" t="inlineStr"/>
     </row>
@@ -21046,7 +21436,7 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C19" s="24" t="inlineStr"/>
     </row>
@@ -21556,7 +21946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22664,7 +23054,8 @@
       <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_fg_follow.png (B at the bottom, F1-F3 arrive, list stays on S8 and the jump FAB appears), scratchpad/shots/b_one.png (single message ONE1 arrives, list left exactly one bubble short), scratchpad/shots/a_own_follow.png (A's OWN sent ONE1 clipped behind the composer), scratchpad/shots/b_offline_send.png (own offline sends clipped). The race explains the intermittency: sometimes the manual scroll lands after the anchor adjustment and it looks fine.
-FIX: the follow now goes through FlashList's `scrollToIndex({index:0})` instead of `scrollToOffset({offset:0})`, fired from `onContentSizeChange` rather than the data effect. Root cause confirmed by reading useRecyclerViewController.js: on every data change FlashList measures how far the FIRST VISIBLE item moved and calls scrollAnchorRef.scrollBy(diff) to cancel the shift, gated on a `pauseOffsetCorrection` ref that ONLY scrollToIndex raises — so a plain offset scroll was undone every time and the thread landed exactly one bubble short. Firing from onContentSizeChange means index 0 has a real layout instead of the stale one it would have in the same commit. Anchoring is deliberately kept: it is the right behaviour for a reader scrolled up in history, whom shouldScrollToLatest still leaves alone; a drag cancels any pending follow so loadOlder growing the content is never mistaken for a new message. An intermediate attempt using scrollToOffset from onContentSizeChange plus a requestAnimationFrame retry was built and tested on device and still landed one bubble short — that is what identified the pauseOffsetCorrection gate. VERIFIED ON DEVICE: a four-message burst now ends with the newest message fully visible above the composer (scratchpad/shots/v2_own_follow.png) where the same burst on the previous build left it clipped (v_own_follow.png). Still to verify with a second device: the INCOMING-message path, and the notification tap-through landing position.</t>
+FIX: the follow now goes through FlashList's `scrollToIndex({index:0})` instead of `scrollToOffset({offset:0})`, fired from `onContentSizeChange` rather than the data effect. Root cause confirmed by reading useRecyclerViewController.js: on every data change FlashList measures how far the FIRST VISIBLE item moved and calls scrollAnchorRef.scrollBy(diff) to cancel the shift, gated on a `pauseOffsetCorrection` ref that ONLY scrollToIndex raises — so a plain offset scroll was undone every time and the thread landed exactly one bubble short. Firing from onContentSizeChange means index 0 has a real layout instead of the stale one it would have in the same commit. Anchoring is deliberately kept: it is the right behaviour for a reader scrolled up in history, whom shouldScrollToLatest still leaves alone; a drag cancels any pending follow so loadOlder growing the content is never mistaken for a new message. An intermediate attempt using scrollToOffset from onContentSizeChange plus a requestAnimationFrame retry was built and tested on device and still landed one bubble short — that is what identified the pauseOffsetCorrection gate. VERIFIED ON DEVICE: a four-message burst now ends with the newest message fully visible above the composer (scratchpad/shots/v2_own_follow.png) where the same burst on the previous build left it clipped (v_own_follow.png). Still to verify with a second device: the INCOMING-message path, and the notification tap-through landing position.
+REGRESSED AND RE-FIXED, properly this time. The scroll-command approach was wrong in kind, not in detail: three versions were tried (scrollToOffset, scrollToOffset plus a frame, scrollToIndex plus a 180ms retry) and all three lost the same race, because FlashList re-pins the viewport through an invisible ScrollAnchor and that is a STATE update landing a render or two after any callback we can scroll from. The newest bubble kept ending up one message below the fold, intermittently — and it came back on the product owner reproducing it with the keyboard up. FINAL FIX: the list uses the library own chat pattern. Not inverted, rows reversed into ascending order at the list (never in the query, so every grouping flag stays attached to its own row and the rendered result is identical to what the inverted list drew), maintainVisibleContentPosition.autoscrollToBottomThreshold pins the end, startRenderingFromBottom opens on the newest, and loadOlder moves from onEndReached to onStartReached. There is no scroll command left to lose a race. shouldScrollToLatest is gone; autoScroll.ts now only measures distance-from-bottom for the jump button. VERIFIED ON THE REAL DEVICE with the keyboard up, the exact case that was failing: five messages sent, the newest fully visible above the composer, no jump button.</t>
         </is>
       </c>
     </row>
@@ -22807,7 +23198,8 @@
 FIX: `PushStore.Line` now carries the message's own `seq`, persisted as the JSON key `"q"`, and `showMessage` passes the push's seq into `appendLine`. `appendLine` SORTS before applying the `MAX_LINES` cap, and that order is the fix rather than a detail: capping first dropped whichever line FCM happened to deliver earliest, so an out-of-order push could evict a message newer than the one it kept. `setContentText` and `setLargeIcon` now read the newest INCOMING line (`lines.lastOrNull { !it.mine }`) instead of the message that arrived last, so the collapsed row and the face on it agree with the expanded thread — incoming only, because an inline reply can sort last and quoting the user's own words back at them is not a notification about anything.
 MIGRATION for installs whose stored lines predate `q`: in `sortBySeq` each entry inherits the rank of the one before it and the sort is stable, so a legacy thread ranks entirely at zero and comes back exactly as stored — the only order anyone ever knew for it — while an inline reply (also seq 0) ranks immediately after the message it answered.
 KNOWN LIMITATION, left open deliberately: `Line.at` is still the ARRIVAL timestamp (`System.currentTimeMillis()` at `showMessage`), because the push payload carries no message timestamp. MessagingStyle stamps each line with it, so a REORDERED thread can show non-monotonic times until the backend sends a message timestamp. The order is now right; the clock beside it is not.
-NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device.</t>
+NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device.
+LIVE RE-TEST 2026-09-19 on the two-device setup, following this entry's own steps (recipient package force-stopped so FCM holds a message, app launched to clear FLAG_STOPPED, a second message sent into the release window). RESULT: the expanded thread came back in seq order with the newest line last (OK4, FIN1, FIN2, FIN3, FIN4, ORD2) and the collapsed row quoted the newest, where the pre-fix run of the same procedure had produced KILL2 above KILL1. Both messages also landed in the conversation in the right order with nothing lost. CAVEAT recorded honestly: FCM released the held message quickly enough that a strictly OUT-OF-ORDER delivery was not forced on this run, so what this proves is correct ordering and no regression, not the reordering path itself firing. That path is covered by code review only (there is no Kotlin test source set in this project).</t>
         </is>
       </c>
     </row>
@@ -22842,7 +23234,8 @@
       <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_shade.png (S3..S8 before opening), scratchpad/shots/b_tapthrough.png (chat opened, tray cleared, all read), scratchpad/shots/b_reply_open.png (next notification still carries S6, S7, S8, BG1).
-ROOT CAUSE FOUND and FIXED via VC-062. The clearing path was wired correctly all along — clearConversationNotification -&gt; VelChatPushModule.clearConversation -&gt; PushNotifications.cancel -&gt; store.clearLines — but it only ran from the chat screen's MOUNT effect. A notification tap RESUMES an already-mounted ChatScreen, so that effect never re-ran, and the tray entry disappearing was just the notification's own AUTO_CANCEL flag removing the posted notification while the stored lines and counters survived. useMessages now also clears on every return to the foreground. Live re-verification pending a second device.</t>
+ROOT CAUSE FOUND and FIXED via VC-062. The clearing path was wired correctly all along — clearConversationNotification -&gt; VelChatPushModule.clearConversation -&gt; PushNotifications.cancel -&gt; store.clearLines — but it only ran from the chat screen's MOUNT effect. A notification tap RESUMES an already-mounted ChatScreen, so that effect never re-ran, and the tray entry disappearing was just the notification's own AUTO_CANCEL flag removing the posted notification while the stored lines and counters survived. useMessages now also clears on every return to the foreground. Live re-verification pending a second device.
+LIVE VERIFIED 2026-09-19: after opening the chat and backgrounding again, the next notification carried only the new messages — no line from the batch the user had already read.</t>
         </is>
       </c>
     </row>
@@ -23228,7 +23621,8 @@
           <t>Found by a code-level audit after the live two-device session. Deterministic, unlike the race in the sibling PushStore report.
 FIX: the `ACTION_DISMISS` branch now calls `store.clearLines(conversationId)` alongside `clearCount`, matching `PushNotifications.cancel`, which has always dropped both halves.
 The SECONDARY half of this report is fixed too, because a backstop that does half of what it backs up just relocates the bug to the group path. `postSummary` gained `setDeleteIntent(summaryDismissIntent(context))`, carrying a new `ACTION_DISMISS_SUMMARY` that `PushActionReceiver.onReceive` answers BEFORE the conversation-id extra is demanded — the summary belongs to no single conversation, so it carries no id and the existing `getStringExtra(...) ?: return` would have swallowed it silently. That branch clears counts AND lines wholesale (`clearAllCounts` + `clearAllLines`). It is idempotent on builds where the children's delete intents do arrive, and it is the only clearing that happens on the OEM builds where they do not.
-NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device.</t>
+NO AUTOMATED TEST: this project has no Kotlin test source set at all — `android/app/src` holds only `main`, `dev` and `prod` — so nothing in the push package is reachable from Jest. Verified by code review against the report; the live repro still needs re-running on a device.
+LIVE VERIFIED 2026-09-19 following this entry's own steps: three messages arrived while backgrounded and were swiped away unread, then one more was sent. The rebuilt notification reported android.messages = Parcelable[] (1) — one line, not four. Pre-fix the same procedure re-listed every dismissed message.</t>
         </is>
       </c>
     </row>
@@ -23314,6 +23708,74 @@
 `markConversationRead` now uses it in place of `maxSeqForConversation`. `pageBackfill` computes it once per page and clamps BOTH cumulative watermarks with it — `noteDelivered(Math.min(highestInbound, contiguous))` and `noteRead(Math.min(highest, contiguous))` — one extra query per page, on the reconnect path only. Read-on-arrival is clamped for free with the `localMax` the gap check already holds in hand (`m.seq &lt;= localMax + 1 ? m.seq : localMax`, with `localMax === 0` treated as unloaded history rather than a hole), so the inbound hot path pays nothing: the very frame that OPENS a hole now reports read only up to the previous local max instead of claiming everything it skipped.
 Covered by `contiguousSeq.test.ts` (6 cases), including both under-reporting traps named above: unloaded history is not a hole, and a tombstone is not a hole.
 RESIDUAL, NOT FIXED HERE: the NATIVE ack path this report also named. `PushActionReceiver`'s Mark-as-read and inline-reply branches still POST `/notifications/ack` with the notification's own `seq` unclamped, because that process has no database open to scan — exactly the reason the report called it out. A native Mark-as-read on a conversation with a hole can therefore still over-claim. Worth its own entry if it is judged to matter; the three JS emitters, which are every path that runs with the app alive, are fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>VC-071</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>A notification's Mark-as-read carries the arriving seq, so a late out-of-order push acknowledges below the newest message</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Found by an adversarial code review of the notification changes made the same day. Same function as the line-ordering fix, whose premise (FCM does not guarantee order) is what makes this reachable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>VC-072</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>A notification's collapsed row can show one person's words beside another person's face</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Found by an adversarial code review of the notification changes made the same day.</t>
         </is>
       </c>
     </row>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -641,7 +641,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-19 14:58 UTC</t>
+          <t>Generated 2026-09-19 15:20 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -15682,7 +15682,8 @@
       </c>
       <c r="AA33" s="5" t="inlineStr">
         <is>
-          <t>The fix is one line: `if (seq &gt; 0 &amp;&amp; seq &lt;= store.lastSeq(conversationId)) return false`.</t>
+          <t>The fix is one line: `if (seq &gt; 0 &amp;&amp; seq &lt;= store.lastSeq(conversationId)) return false`.
+FIXED, but NOT the way this entry proposed, and the difference matters. The entry says the monotonic watermark to do this already exists (PushStore.lastSeq). Suppressing on a high-water mark would be wrong here: FCM gives no ordering guarantee, and this session PROVED it out of order on a real device — the notification thread came back with KILL2 above KILL1, which is what VC-056 exists to sort. Against a watermark, a genuinely new message arriving with a LOWER seq than one already delivered would have its notification silently swallowed entirely — a far worse failure than showing a duplicate. So suppression is by EXACT identity instead: new PushStore.markSeen(conversationId, seq) records the seq and returns whether it was new, keeping the last 20 seqs per conversation (bounded, and only has to outlast FCM retries), atomic under the same WRITE_LOCK. handleMessage calls it BEFORE the on-screen check, so a duplicate of a message the user already watched arrive in an open chat cannot notify later either. Everything after it still runs for a duplicate on purpose: the delivered ack is idempotent and re-acking guarantees the sender their tick, and handing the push to a live JS runtime is a free chance to catch up. Cleared on sign-out with the rest of the session state. Verified by compileProdReleaseKotlin; no Kotlin test source set exists, and an FCM redelivery cannot be forced on demand, so this is code-review-verified.</t>
         </is>
       </c>
       <c r="AB33" s="5" t="inlineStr"/>
@@ -15720,7 +15721,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -15822,7 +15823,8 @@
       </c>
       <c r="AA34" s="5" t="inlineStr">
         <is>
-          <t>No JVM test source set exists — android/app/src contains only `main`. PushStore is plain-JVM-testable.</t>
+          <t>No JVM test source set exists — android/app/src contains only `main`. PushStore is plain-JVM-testable.
+FIXED as part of VC-066. The pending-event queue is one of the read-modify-write pairs that the new companion-object WRITE_LOCK now covers: enqueueEvent reads the array, appends, trims and writes it back, and takeEvents reads it and removes the key, both entirely inside the monitor. The drain case this entry described — an action queued on the receiver thread between the read and the removal, silently dropped — can no longer interleave, and the code now carries a comment saying exactly that. The monitor is on the COMPANION object rather than the instance, which is load-bearing: PushStore is constructed fresh at each entry point (VelChatMessagingService on FCM delivery, PushActionReceiver on main, VelChatPushModule on the RN native-modules thread), so an instance monitor would have been three separate locks guarding one shared SharedPreferences file. Verified by code review plus a clean compileProdReleaseKotlin; there is no Kotlin test source set in this project, so this is code-review-verified only.</t>
         </is>
       </c>
       <c r="AB34" s="5" t="inlineStr"/>
@@ -20725,7 +20727,11 @@
           <t>VC-71</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr"/>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>conversationRowIdentity.test.ts: the identity a conversation row shows, chatsList.test.tsx: ConversationRow names a DM whose peer never resolved, chatTitle.test.ts: the header title for a conversation nothing names</t>
+        </is>
+      </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
           <t>A conversation with no resolved name shows as a bare em-dash in the chat list, with no way to tell who it is</t>
@@ -20743,7 +20749,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
@@ -20836,7 +20842,10 @@
       </c>
       <c r="AA71" s="5" t="inlineStr">
         <is>
-          <t>Found during the live two-device session while checking the chat list; filed after confirming the source. Related to VC-047, which was about the WRONG name being shown; this is about NO name.</t>
+          <t>Found during the live two-device session while checking the chat list; filed after confirming the source. Related to VC-047, which was about the WRONG name being shown; this is about NO name.
+FIX: a new pure conversationRowIdentity(name, fallback) in ui/chat/chatModel.ts returns both the title and the avatar initial from ONE decision, so the three places the placeholder used to leak — the visible name, the accessibilityLabel and the avatar initial — can no longer disagree. The label is localised and picked by kind: chat.unknownContact for a DM, chat.unnamedChat for a group, added to all three locales (en, hi, ar) so no locale falls back to English. The avatar is now gated on the initial being absent rather than on a ? sentinel, so an unidentified row draws the same person glyph it always did.
+WHY NOT THE PHONE NUMBER, checked in source rather than assumed: the conversations table denormalises peer_id and the avatar but no number; the members endpoint returns bare account ids and the peer profile shape has no phone field at all (contact discovery is OPRF precisely so a number cannot be derived from an account); and the one local number-to-account map cannot reach this case, because the device-contacts reader already falls back to the first NUMBER as the name, so an address-book entry saved without a name arrives with the number AS its name and peerDisplayName returns it. A row that reaches this fallback is by construction one whose peer is not in the address book — nothing on the device holds their number. Resolving one per row would also be a network call on the render path (M0 rule 2) in a list that must recycle at 55+ FPS (R4).
+SAME FIX APPLIED TO THE CHAT HEADER in the same pass: an unidentified chat header read "Chats", the bottom-tab label, in the slot where the person name goes. That was the best string available when VC-053 landed; now that chat.unknownContact exists both surfaces say the same thing, and the avatar there is gated the same way. No visual change anywhere — same text slot, font, size, weight, layout and palette.</t>
         </is>
       </c>
       <c r="AB71" s="5" t="inlineStr"/>
@@ -21239,7 +21248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -21425,7 +21434,7 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C18" s="24" t="inlineStr"/>
     </row>
@@ -21436,7 +21445,7 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C19" s="24" t="inlineStr"/>
     </row>
@@ -21495,7 +21504,7 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>17 open P0/P1 defect(s) block the build.</t>
+          <t>15 open P0/P1 defect(s) block the build.</t>
         </is>
       </c>
     </row>
@@ -21698,24 +21707,24 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>VC-032</t>
+          <t>VC-039</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>No duplicate-notification suppression, though the monotonic watermark to do it already exists</t>
+          <t>Any authenticated user can READ and WRITE any conversation — no authorization on the chat routes, and conversation ids are derivable offline</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>VC-033</t>
+          <t>VC-040</t>
         </is>
       </c>
       <c r="B41" s="23" t="inlineStr">
@@ -21725,31 +21734,31 @@
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>Native pending-event queue is a lock-free read-modify-write that can wipe a reply enqueued mid-drain</t>
+          <t>A push endpoint can be registered against another account's userId, redirecting their push wake-ups</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>VC-039</t>
+          <t>VC-041</t>
         </is>
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>Any authenticated user can READ and WRITE any conversation — no authorization on the chat routes, and conversation ids are derivable offline</t>
+          <t>POST /chat/messages accepts a conversationId that does not exist</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>VC-040</t>
+          <t>VC-043</t>
         </is>
       </c>
       <c r="B43" s="23" t="inlineStr">
@@ -21758,40 +21767,6 @@
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>A push endpoint can be registered against another account's userId, redirecting their push wake-ups</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="22" t="inlineStr">
-        <is>
-          <t>VC-041</t>
-        </is>
-      </c>
-      <c r="B44" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>POST /chat/messages accepts a conversationId that does not exist</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="22" t="inlineStr">
-        <is>
-          <t>VC-043</t>
-        </is>
-      </c>
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
         <is>
           <t>Concurrent refresh-token requests can all succeed — rotation is not race-safe</t>
         </is>
@@ -21946,7 +21921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22650,27 +22625,27 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>VC-034</t>
+          <t>VC-032</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Retry-After is honored with an unbounded, uncancellable sleep</t>
+          <t>No duplicate-notification suppression, though the monotonic watermark to do it already exists</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-12</t>
+          <t>dev branch, 2026-09-19</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-215</t>
+          <t>VC-UNIT-213</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
@@ -22681,34 +22656,35 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>FIX: Retry-After is now clamped to [0, 10s] (MAX_RETRY_AFTER_MS, client.ts) before the wait, instead of obeying a server-supplied value unbounded. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>The fix is one line: `if (seq &gt; 0 &amp;&amp; seq &lt;= store.lastSeq(conversationId)) return false`.
+FIXED, but NOT the way this entry proposed, and the difference matters. The entry says the monotonic watermark to do this already exists (PushStore.lastSeq). Suppressing on a high-water mark would be wrong here: FCM gives no ordering guarantee, and this session PROVED it out of order on a real device — the notification thread came back with KILL2 above KILL1, which is what VC-056 exists to sort. Against a watermark, a genuinely new message arriving with a LOWER seq than one already delivered would have its notification silently swallowed entirely — a far worse failure than showing a duplicate. So suppression is by EXACT identity instead: new PushStore.markSeen(conversationId, seq) records the seq and returns whether it was new, keeping the last 20 seqs per conversation (bounded, and only has to outlast FCM retries), atomic under the same WRITE_LOCK. handleMessage calls it BEFORE the on-screen check, so a duplicate of a message the user already watched arrive in an open chat cannot notify later either. Everything after it still runs for a duplicate on purpose: the delivered ack is idempotent and re-acking guarantees the sender their tick, and handing the push to a live JS runtime is a free chance to catch up. Cleared on sign-out with the rest of the session state. Verified by compileProdReleaseKotlin; no Kotlin test source set exists, and an FCM redelivery cannot be forced on demand, so this is code-review-verified.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>VC-035</t>
+          <t>VC-033</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>A misbuilt binary reports env:'dev' while talking to production</t>
+          <t>Native pending-event queue is a lock-free read-modify-write that can wipe a reply enqueued mid-drain</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-12</t>
+          <t>dev branch, 2026-09-19</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-216</t>
+          <t>VC-UNIT-214</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
@@ -22719,19 +22695,20 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>The prod URL fallback direction is defensible; make `name` fall back to 'prod' alongside it, or log.error when Config.API_BASE_URL is absent. FIX: Extracted the pure resolveAppEnv(rawName, rawApiBaseUrl, rawWsUrl) so the fallback logic is unit-testable. An unrecognised/missing ENV now falls back to 'prod' alongside the URL fallback (previously 'dev'), so a misbuilt binary can never report a safe-sounding name while actually pointing at production. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>No JVM test source set exists — android/app/src contains only `main`. PushStore is plain-JVM-testable.
+FIXED as part of VC-066. The pending-event queue is one of the read-modify-write pairs that the new companion-object WRITE_LOCK now covers: enqueueEvent reads the array, appends, trims and writes it back, and takeEvents reads it and removes the key, both entirely inside the monitor. The drain case this entry described — an action queued on the receiver thread between the read and the removal, silently dropped — can no longer interleave, and the code now carries a comment saying exactly that. The monitor is on the COMPANION object rather than the instance, which is load-bearing: PushStore is constructed fresh at each entry point (VelChatMessagingService on FCM delivery, PushActionReceiver on main, VelChatPushModule on the RN native-modules thread), so an instance monitor would have been three separate locks guarding one shared SharedPreferences file. Verified by code review plus a clean compileProdReleaseKotlin; there is no Kotlin test source set in this project, so this is code-review-verified only.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>VC-036</t>
+          <t>VC-034</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Cold start after &gt;15 min idle opens the WebSocket with a certainly-expired token</t>
+          <t>Retry-After is honored with an unbounded, uncancellable sleep</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -22746,7 +22723,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-217</t>
+          <t>VC-UNIT-215</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
@@ -22757,34 +22734,34 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>FIX: hasValidSession() added (tokens.ts); useAuthBootstrap now refreshes before hydrating on an expired-but-present token. hasSession() deliberately left presence-only to protect SyncEngine reconnect guards. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: Retry-After is now clamped to [0, 10s] (MAX_RETRY_AFTER_MS, client.ts) before the wait, instead of obeying a server-supplied value unbounded. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>VC-038</t>
+          <t>VC-035</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Jest reports a worker that failed to exit gracefully — a leaked timer or handle in the test path</t>
+          <t>A misbuilt binary reports env:'dev' while talking to production</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-13</t>
+          <t>dev branch, 2026-09-12</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-001</t>
+          <t>VC-UNIT-216</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
@@ -22795,32 +22772,36 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>FIX (root cause found by instrumentation, not guesswork): --detectOpenHandles reported NOTHING, so the leak was invisible to it. A probe dumping process.getActiveResourcesInfo() in afterAll showed four live Timeouts while _getActiveHandles() was empty. Traced to WatermelonDB: adapters/lokijs/worker/lokiExtensions.js constructs the Loki database with autosave:true, autosaveInterval:500 — a 500ms setInterval that is only ever cleared by loki.close(), which the app never calls because its database lives for the life of the process. Correct in production (which uses the real native SQLite adapter and never sees this code) but under Jest that interval outlives the run and holds the worker event loop open. Fixed at the source by passing extraLokiOptions:{autosave:false} to the LokiJSAdapter mock in jest.setup.ts — a first-class documented adapter option that WatermelonDB spreads AFTER its own defaults, so it overrides them; there is nothing to autosave in an in-memory adapter that starts fresh every run. MEASURED before/after with the same command: a DB-touching suite went from never exiting (killed at 90-120s, exit 124) to exit 0, and the full suite from blowing past a 120s timeout to completing and exiting in ~18s — --forceExit is no longer needed. RESIDUAL, stated honestly: the "worker process has failed to exit gracefully" text can still appear with &gt;=2 jest workers. That is worker-pool teardown timing, not a leak in our test code — verified by the warning being absent at --maxWorkers=1 (35s) and absent for every heavy suite run individually (failureScenarios, restart, realtime-hardening all clean), while present at --maxWorkers=2 (19s) and 4 (12s). Verified: full jest suite 506/506 pass, tsc --noEmit clean, eslint clean.</t>
+          <t>The prod URL fallback direction is defensible; make `name` fall back to 'prod' alongside it, or log.error when Config.API_BASE_URL is absent. FIX: Extracted the pure resolveAppEnv(rawName, rawApiBaseUrl, rawWsUrl) so the fallback logic is unit-testable. An unrecognised/missing ENV now falls back to 'prod' alongside the URL fallback (previously 'dev'), so a misbuilt binary can never report a safe-sounding name while actually pointing at production. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>VC-045</t>
+          <t>VC-036</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Real-time messaging and notification-reply sync needs multi-scenario two-device verification</t>
+          <t>Cold start after &gt;15 min idle opens the WebSocket with a certainly-expired token</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Verified on dev, 2026-09-14</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr"/>
+          <t>dev branch, 2026-09-12</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>VC-UNIT-217</t>
+        </is>
+      </c>
       <c r="F23" s="5" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr">
         <is>
@@ -22829,25 +22810,24 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>This entry tracks a two-device manual verification pass, not a confirmed defect. Assigned to Tusha Bhadouriya to execute and report actual pass/fail per scenario back into this bug.
-VERIFIED 2026-09-14 by a live two-device session (A = OPPO CPH2643 Android 16 real device, B = Pixel emulator Android 16), production build against the live backend. PASSED: single-message real-time delivery; an 8-message burst delivered complete and in order; notification posted with the correct sender name, avatar and per-message lines while backgrounded; notification posted after the process was killed with am kill (FCM woke the dead process and it displayed correctly); tapping a notification opens the right conversation and clears the tray; NO notification is posted while that conversation is on screen (active-conversation suppression works); inline notification Reply sends the message, clears the notification and clears the unread badge; typing indicator appears on the peer header; presence shows online and last-seen; offline send queues and flushes in order on reconnect (airplane mode on/off); unread badges and chat-list ordering correct; cold start COLD TotalTime 1367 ms. FAILED, filed separately: VC-051 (message loss with a false read receipt), VC-052 (thread does not follow new messages), VC-053 (notification tap-through titles the chat Chats), VC-054, VC-055, VC-056, VC-057, VC-058, VC-059, VC-060, VC-061.</t>
+          <t>FIX: hasValidSession() added (tokens.ts); useAuthBootstrap now refreshes before hydrating on an expired-but-present token. hasSession() deliberately left presence-only to protect SyncEngine reconnect guards. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>VC-047</t>
+          <t>VC-038</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
+          <t>Jest reports a worker that failed to exit gracefully — a leaked timer or handle in the test path</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -22857,7 +22837,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>peerDisplayName.test.ts: VC-044 / VC-047, conversationRow.test.ts: VC-044 / VC-047</t>
+          <t>VC-UNIT-001</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
@@ -22868,24 +22848,24 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>FIX (root-caused): the address book was consulted on exactly ONE path. startDm() writes the saved name when a chat is opened from New Chat / Message Yourself — which is why the name corrected itself after opening — while every other path used server data, and refreshPeerIdentity() actively OVERWROTE a saved name with the registered one on its next background revalidation (once per TTL/session). Introduced peerDisplayName() (features/contacts/model), the single precedence rule: the name YOU saved wins over the name the peer registered; falls back to the registered name for someone not in your book or when the book has not loaded; returns undefined when neither side has a usable name so callers keep what they have; group rows are untouched (no peerId to look up). Applied at both the WRITE side (refreshPeerIdentity, both the TTL path and the profile-changed push, so a revalidation can no longer downgrade a saved name) and the READ side (toConversationRow for the chat list, useConversationIdentity for the chat header), the latter being what makes a saved name appear WITHOUT having to open the chat first. Exposed discoveredContacts() from the contacts barrel as a cache read (no re-discovery). Verified: full jest suite 502/502 pass (10 new tests), tsc --noEmit clean, eslint 0 errors and no boundary violation. Not re-tested on a device — no Android hardware attached to this machine.</t>
+          <t>FIX (root cause found by instrumentation, not guesswork): --detectOpenHandles reported NOTHING, so the leak was invisible to it. A probe dumping process.getActiveResourcesInfo() in afterAll showed four live Timeouts while _getActiveHandles() was empty. Traced to WatermelonDB: adapters/lokijs/worker/lokiExtensions.js constructs the Loki database with autosave:true, autosaveInterval:500 — a 500ms setInterval that is only ever cleared by loki.close(), which the app never calls because its database lives for the life of the process. Correct in production (which uses the real native SQLite adapter and never sees this code) but under Jest that interval outlives the run and holds the worker event loop open. Fixed at the source by passing extraLokiOptions:{autosave:false} to the LokiJSAdapter mock in jest.setup.ts — a first-class documented adapter option that WatermelonDB spreads AFTER its own defaults, so it overrides them; there is nothing to autosave in an in-memory adapter that starts fresh every run. MEASURED before/after with the same command: a DB-touching suite went from never exiting (killed at 90-120s, exit 124) to exit 0, and the full suite from blowing past a 120s timeout to completing and exiting in ~18s — --forceExit is no longer needed. RESIDUAL, stated honestly: the "worker process has failed to exit gracefully" text can still appear with &gt;=2 jest workers. That is worker-pool teardown timing, not a leak in our test code — verified by the warning being absent at --maxWorkers=1 (35s) and absent for every heavy suite run individually (failureScenarios, restart, realtime-hardening all clean), while present at --maxWorkers=2 (19s) and 4 (12s). Verified: full jest suite 506/506 pass, tsc --noEmit clean, eslint clean.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>VC-048</t>
+          <t>VC-045</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Message notification omits the sender's name and tapping it does not open the chat</t>
+          <t>Real-time messaging and notification-reply sync needs multi-scenario two-device verification</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -22902,111 +22882,108 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
+          <t>This entry tracks a two-device manual verification pass, not a confirmed defect. Assigned to Tusha Bhadouriya to execute and report actual pass/fail per scenario back into this bug.
+VERIFIED 2026-09-14 by a live two-device session (A = OPPO CPH2643 Android 16 real device, B = Pixel emulator Android 16), production build against the live backend. PASSED: single-message real-time delivery; an 8-message burst delivered complete and in order; notification posted with the correct sender name, avatar and per-message lines while backgrounded; notification posted after the process was killed with am kill (FCM woke the dead process and it displayed correctly); tapping a notification opens the right conversation and clears the tray; NO notification is posted while that conversation is on screen (active-conversation suppression works); inline notification Reply sends the message, clears the notification and clears the unread badge; typing indicator appears on the peer header; presence shows online and last-seen; offline send queues and flushes in order on reconnect (airplane mode on/off); unread badges and chat-list ordering correct; cold start COLD TotalTime 1367 ms. FAILED, filed separately: VC-051 (message loss with a false read receipt), VC-052 (thread does not follow new messages), VC-053 (notification tap-through titles the chat Chats), VC-054, VC-055, VC-056, VC-057, VC-058, VC-059, VC-060, VC-061.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>VC-047</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-13</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>peerDisplayName.test.ts: VC-044 / VC-047, conversationRow.test.ts: VC-044 / VC-047</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>FIX (root-caused): the address book was consulted on exactly ONE path. startDm() writes the saved name when a chat is opened from New Chat / Message Yourself — which is why the name corrected itself after opening — while every other path used server data, and refreshPeerIdentity() actively OVERWROTE a saved name with the registered one on its next background revalidation (once per TTL/session). Introduced peerDisplayName() (features/contacts/model), the single precedence rule: the name YOU saved wins over the name the peer registered; falls back to the registered name for someone not in your book or when the book has not loaded; returns undefined when neither side has a usable name so callers keep what they have; group rows are untouched (no peerId to look up). Applied at both the WRITE side (refreshPeerIdentity, both the TTL path and the profile-changed push, so a revalidation can no longer downgrade a saved name) and the READ side (toConversationRow for the chat list, useConversationIdentity for the chat header), the latter being what makes a saved name appear WITHOUT having to open the chat first. Exposed discoveredContacts() from the contacts barrel as a cache read (no re-discovery). Verified: full jest suite 502/502 pass (10 new tests), tsc --noEmit clean, eslint 0 errors and no boundary violation. Not re-tested on a device — no Android hardware attached to this machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VC-048</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Message notification omits the sender's name and tapping it does not open the chat</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Verified on dev, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
           <t>Reported by Tusha Bhadouriya during production QA testing.
 RE-TESTED LIVE 2026-09-14 on a production build against the live backend, two devices. Both halves of this report are now correct: the notification DOES carry the sender name (dumpsys shows android.title="Aayush Jain 🤗" with the sender photo and per-message MessagingStyle lines), and tapping it DOES open that conversation (topResumedActivity becomes com.velchat/.MainActivity on the Chat route and every VelChat notification is cleared). Evidence: scratchpad/shots/b_shade.png, b_tapthrough.png. One residual defect on the same path is filed separately as VC-053: the deep link carries no name param, so ChatHeader falls back to the tabs.chats label and the header reads "Chats". A second residual, the chat not opening at the newest message, is covered by VC-052.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>VC-049</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>dev branch, 2026-09-13</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>profileGate.test.ts: VC-049</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Not independently tested</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>FIX (root-caused): the email is NOT a directory-profile field — profileShape.ts states it is a separately-verified identifier owned by the auth-service (GET /auth/account). useProfileGate decided purely from the LOCAL MMKV mirror, and purgeAccountData() wipes KVKeys.email on every sign-out, so immediately after any login the mirror is empty and the gate prompted unconditionally. useAccountInfo() does fetch the real email and mirror it, but it runs in parallel from AppTabs, so its answer always lost the race — and dismissal is session-only, which is why it returned every single login. The gate now asks the auth-service itself before deciding, via a new pure shouldPromptForProfile() (features/user/model/profileGate.ts): a mirrored email means never prompt; a server email means never prompt (and is re-mirrored so later launches short-circuit with no network); an UNANSWERED server (in flight or unreachable) means WAIT rather than prompt, which also removes the flash of the sheet before the answer lands. Only a definitive server no-email prompts. Verified: full jest suite 492/492 pass (5 new decision tests), tsc --noEmit clean, eslint 0 errors, no eslint-plugin-boundaries violation for the user→auth import (authApi depends only on infra, so no cycle). Not reproduced on a device — no Android hardware attached to this machine; fix is verified at the unit level against the exact reported condition.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>VC-050</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Cold start holds a splash screen on a network refresh — up to minutes before home appears</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>dev branch, 2026-09-13</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>authBootstrap.test.ts: cold start with a session already on the device</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>Not independently tested</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>FIX: split the two questions the bootstrap had conflated — "can we show the app" and "is the access token fresh enough for a socket". If a session exists on the device at all (hasSession(), presence-only), the app now hydrates and reports ready IMMEDIATELY, whatever the token age; the chat list renders from the local DB, the HTTP client refreshes on its first 401, and the socket heals itself via 4001 -&gt; refresh -&gt; reconnect. VC-036 is not regressed: a fresh token is still wanted as early as possible so the first handshake is not doomed, so the refresh is still fired at once — it just runs BEHIND the app instead of in front of it. The no-session path (signed out but a device key survives) still attempts a silent restore, but is now bounded by MAX_SILENT_RESTORE_MS = 4000 so a hibernating backend cannot freeze the splash; a restore that lands later still navigates home on its own, because RootNavigator follows the auth store (state === active). Verified: full jest suite 521/521 pass (5 new hook tests, two of which fail against the old code by hanging until waitFor times out), tsc --noEmit clean, eslint 0 errors. Measured on device: not yet — needs a launch on real hardware to confirm the wall-clock improvement.</t>
-        </is>
-      </c>
-    </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>VC-051</t>
+          <t>VC-049</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>A message the device was pushed for never reaches the chat, and no reconnect ever heals it — the sender still sees blue read ticks</t>
+          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-19</t>
+          <t>dev branch, 2026-09-13</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>failureScenarios.test.ts: a message dropped by fan-out</t>
+          <t>profileGate.test.ts: VC-049</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
@@ -23016,6 +22993,82 @@
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>FIX (root-caused): the email is NOT a directory-profile field — profileShape.ts states it is a separately-verified identifier owned by the auth-service (GET /auth/account). useProfileGate decided purely from the LOCAL MMKV mirror, and purgeAccountData() wipes KVKeys.email on every sign-out, so immediately after any login the mirror is empty and the gate prompted unconditionally. useAccountInfo() does fetch the real email and mirror it, but it runs in parallel from AppTabs, so its answer always lost the race — and dismissal is session-only, which is why it returned every single login. The gate now asks the auth-service itself before deciding, via a new pure shouldPromptForProfile() (features/user/model/profileGate.ts): a mirrored email means never prompt; a server email means never prompt (and is re-mirrored so later launches short-circuit with no network); an UNANSWERED server (in flight or unreachable) means WAIT rather than prompt, which also removes the flash of the sheet before the answer lands. Only a definitive server no-email prompts. Verified: full jest suite 492/492 pass (5 new decision tests), tsc --noEmit clean, eslint 0 errors, no eslint-plugin-boundaries violation for the user→auth import (authApi depends only on infra, so no cycle). Not reproduced on a device — no Android hardware attached to this machine; fix is verified at the unit level against the exact reported condition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>VC-050</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Cold start holds a splash screen on a network refresh — up to minutes before home appears</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-13</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>authBootstrap.test.ts: cold start with a session already on the device</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>FIX: split the two questions the bootstrap had conflated — "can we show the app" and "is the access token fresh enough for a socket". If a session exists on the device at all (hasSession(), presence-only), the app now hydrates and reports ready IMMEDIATELY, whatever the token age; the chat list renders from the local DB, the HTTP client refreshes on its first 401, and the socket heals itself via 4001 -&gt; refresh -&gt; reconnect. VC-036 is not regressed: a fresh token is still wanted as early as possible so the first handshake is not doomed, so the refresh is still fired at once — it just runs BEHIND the app instead of in front of it. The no-session path (signed out but a device key survives) still attempts a silent restore, but is now bounded by MAX_SILENT_RESTORE_MS = 4000 so a hibernating backend cannot freeze the splash; a restore that lands later still navigates home on its own, because RootNavigator follows the auth store (state === active). Verified: full jest suite 521/521 pass (5 new hook tests, two of which fail against the old code by hanging until waitFor times out), tsc --noEmit clean, eslint 0 errors. Measured on device: not yet — needs a launch on real hardware to confirm the wall-clock improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>VC-051</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>A message the device was pushed for never reaches the chat, and no reconnect ever heals it — the sender still sees blue read ticks</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>failureScenarios.test.ts: a message dropped by fan-out</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/a_inline_rx.png (A shows KILL2 09:39 with blue ticks) vs scratchpad/shots/b_kill2_check.png (B's thread jumps BG1 09:37 -&gt; KILL1 09:37 -&gt; hhh 09:40, no KILL2). Related backend defect VC-001 may be the upstream cause, but the client must still heal the gap on reconnect and must not report `read` for a message it does not hold.
 FIX (frontend): pageBackfill/backfillConversation take an optional `fromSeq`, and the gap probe passes the pre-apply `localMax` — so the repair asks the server from the LOWER edge of the hole instead of from the message that revealed it. Re-fetching the rows already held between localMax and the incoming seq is free: applyServerMessages dedups on (conversation_id, seq) and on client_msg_id inside the write lock. Three end-to-end tests added to failureScenarios.test.ts, driving the real engine against the fake server, written RED first — and rewritten once when the first version passed for the wrong reason (bootConnected’s own reconnect backfill was healing the hole), so each test now brings the socket up while the device is already caught up. Verified: 537/537 jest, tsc clean, eslint 0 errors.
@@ -23023,35 +23076,35 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>VC-052</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Chat thread does not follow the newest message — incoming and own-sent bubbles land hidden behind the composer</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_fg_follow.png (B at the bottom, F1-F3 arrive, list stays on S8 and the jump FAB appears), scratchpad/shots/b_one.png (single message ONE1 arrives, list left exactly one bubble short), scratchpad/shots/a_own_follow.png (A's OWN sent ONE1 clipped behind the composer), scratchpad/shots/b_offline_send.png (own offline sends clipped). The race explains the intermittency: sometimes the manual scroll lands after the anchor adjustment and it looks fine.
 FIX: the follow now goes through FlashList's `scrollToIndex({index:0})` instead of `scrollToOffset({offset:0})`, fired from `onContentSizeChange` rather than the data effect. Root cause confirmed by reading useRecyclerViewController.js: on every data change FlashList measures how far the FIRST VISIBLE item moved and calls scrollAnchorRef.scrollBy(diff) to cancel the shift, gated on a `pauseOffsetCorrection` ref that ONLY scrollToIndex raises — so a plain offset scroll was undone every time and the thread landed exactly one bubble short. Firing from onContentSizeChange means index 0 has a real layout instead of the stale one it would have in the same commit. Anchoring is deliberately kept: it is the right behaviour for a reader scrolled up in history, whom shouldScrollToLatest still leaves alone; a drag cancels any pending follow so loadOlder growing the content is never mistaken for a new message. An intermediate attempt using scrollToOffset from onContentSizeChange plus a requestAnimationFrame retry was built and tested on device and still landed one bubble short — that is what identified the pauseOffsetCorrection gate. VERIFIED ON DEVICE: a four-message burst now ends with the newest message fully visible above the composer (scratchpad/shots/v2_own_follow.png) where the same burst on the previous build left it clipped (v_own_follow.png). Still to verify with a second device: the INCOMING-message path, and the notification tap-through landing position.
@@ -23059,90 +23112,20 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>VC-053</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Chat opened from a notification is titled "Chats" instead of the contact's name, and the avatar loses its initial</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>dev branch, 2026-09-14</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Not independently tested</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>Evidence: scratchpad/shots/b_tapthrough.png and b_jump.png (header 'Chats' after notification tap) vs scratchpad/shots/b_off_kbd.png (header 'Aayush Jain 🤗' for the same chat opened from the list). Relates to VC-048, which reported the tap-through as not opening the chat at all; the open now works, this is the remaining defect on that path.
-FIX: new pure helper `chatTitle(routeName, rowName, fallback)` in ui/chat/chatModel.ts, covered by chatTitle.test.ts (4 cases, RED first). ChatHeader now resolves the title from the route name, then the conversation row it was already observing for the avatar, and only then a generic label; blank counts as absent in both sources. The avatar initial is taken from the resolved name with an empty fallback, so a genuinely unnamed conversation still falls back to the person glyph instead of showing the initial of a tab label. Needs a second device to re-verify the live tap-through.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>VC-054</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Notification group summary says "N new messages" but N is the number of chats, not the number of messages</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>dev branch, 2026-09-14</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>Not independently tested</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Evidence: dumpsys output captured twice in the live session (8 messages -&gt; '5 new messages'; 1 message -&gt; '5 new messages').
-FIX: added `PushStore.countedMessages()`, which sums the per-conversation counters the store already held, and postSummary now formats that instead of `countedConversations()`. The &lt;=1 guard that suppresses the summary for a single chat still uses the conversation count, which is correct. Needs a second device to re-verify live.</t>
-        </is>
-      </c>
-    </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>VC-055</t>
+          <t>VC-053</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Every notification is tinted the abandoned violet #7C5CFF, which matches nothing in the shipped monochrome theme</t>
+          <t>Chat opened from a notification is titled "Chats" instead of the contact's name, and the avatar loses its initial</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -23159,20 +23142,20 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Confirmed by reading tokens.ts (brandFrom '#0B0B0C' / '#F5F5F7') against push_strings.xml (#7C5CFF) and by the live dumpsys record color=0xff7c5cff.
-FIX: push_accent is now #0B0B0C, the monochrome brand accent from design-system/tokens.ts, and the misleading resource comment about a violet gradient is replaced. Android resolves this against the shade background for contrast. Needs a second device to re-verify live.</t>
+          <t>Evidence: scratchpad/shots/b_tapthrough.png and b_jump.png (header 'Chats' after notification tap) vs scratchpad/shots/b_off_kbd.png (header 'Aayush Jain 🤗' for the same chat opened from the list). Relates to VC-048, which reported the tap-through as not opening the chat at all; the open now works, this is the remaining defect on that path.
+FIX: new pure helper `chatTitle(routeName, rowName, fallback)` in ui/chat/chatModel.ts, covered by chatTitle.test.ts (4 cases, RED first). ChatHeader now resolves the title from the route name, then the conversation row it was already observing for the avatar, and only then a generic label; blank counts as absent in both sources. The avatar initial is taken from the resolved name with an empty fallback, so a genuinely unnamed conversation still falls back to the person glyph instead of showing the initial of a tab label. Needs a second device to re-verify the live tap-through.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>VC-056</t>
+          <t>VC-054</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Notification message lines are ordered by arrival, not by message time — an out-of-order push shows the wrong 'latest' message</t>
+          <t>Notification group summary says "N new messages" but N is the number of chats, not the number of messages</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -23182,7 +23165,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-19</t>
+          <t>dev branch, 2026-09-14</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
@@ -23193,6 +23176,76 @@
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Evidence: dumpsys output captured twice in the live session (8 messages -&gt; '5 new messages'; 1 message -&gt; '5 new messages').
+FIX: added `PushStore.countedMessages()`, which sums the per-conversation counters the store already held, and postSummary now formats that instead of `countedConversations()`. The &lt;=1 guard that suppresses the summary for a single chat still uses the conversation count, which is correct. Needs a second device to re-verify live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>VC-055</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Every notification is tinted the abandoned violet #7C5CFF, which matches nothing in the shipped monochrome theme</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed by reading tokens.ts (brandFrom '#0B0B0C' / '#F5F5F7') against push_strings.xml (#7C5CFF) and by the live dumpsys record color=0xff7c5cff.
+FIX: push_accent is now #0B0B0C, the monochrome brand accent from design-system/tokens.ts, and the misleading resource comment about a violet gradient is replaced. Android resolves this against the shade background for contrast. Needs a second device to re-verify live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>VC-056</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Notification message lines are ordered by arrival, not by message time — an out-of-order push shows the wrong 'latest' message</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_reply_open.png (expanded notification shows S6, S7, S8, BG1, KILL2, KILL1) vs scratchpad/shots/a_inline_rx.png (chat shows KILL1 09:37 then KILL2 09:39, correct).
 FIX: `PushStore.Line` now carries the message's own `seq`, persisted as the JSON key `"q"`, and `showMessage` passes the push's seq into `appendLine`. `appendLine` SORTS before applying the `MAX_LINES` cap, and that order is the fix rather than a detail: capping first dropped whichever line FCM happened to deliver earliest, so an out-of-order push could evict a message newer than the one it kept. `setContentText` and `setLargeIcon` now read the newest INCOMING line (`lines.lastOrNull { !it.mine }`) instead of the message that arrived last, so the collapsed row and the face on it agree with the expanded thread — incoming only, because an inline reply can sort last and quoting the user's own words back at them is not a notification about anything.
@@ -23203,35 +23256,35 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>VC-057</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Notification re-lists messages the user has already read once the chat is reopened and a new message arrives</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_shade.png (S3..S8 before opening), scratchpad/shots/b_tapthrough.png (chat opened, tray cleared, all read), scratchpad/shots/b_reply_open.png (next notification still carries S6, S7, S8, BG1).
 ROOT CAUSE FOUND and FIXED via VC-062. The clearing path was wired correctly all along — clearConversationNotification -&gt; VelChatPushModule.clearConversation -&gt; PushNotifications.cancel -&gt; store.clearLines — but it only ran from the chat screen's MOUNT effect. A notification tap RESUMES an already-mounted ChatScreen, so that effect never re-ran, and the tray entry disappearing was just the notification's own AUTO_CANCEL flag removing the posted notification while the stored lines and counters survived. useMessages now also clears on every return to the foreground. Live re-verification pending a second device.
@@ -23239,74 +23292,74 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>VC-058</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Chat-list preview can regress to an older message — the preview is written unconditionally while the timestamp is guarded</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_after_reply.png (row reads 'KILL1' while KILL2 was newer). Fix is to move the preview write inside the same freshness check as the timestamp.
 FIX: the preview write now sits behind the same freshness check as the sort key in upsertConversation — a single `fresher` predicate gates both, so a stale patch can no longer overwrite what the row says while being correctly refused a reorder.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>VC-059</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Composer's emoji, attach, camera and mic buttons are dead controls that look and behave as if they work</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>composerControls.test.tsx: the controls that are not built yet, composerControls.test.tsx: the one control that is wired</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>Minimum viable fix for a release build: hide the unimplemented controls, or render them disabled (reduced opacity + accessibilityState disabled) so neither sighted nor screen-reader users are misled.
 FIX: `PillIconButton` lost its `onPress` prop entirely — emoji, attach and camera now render a `Pressable` with a real `disabled` and `accessibilityState={{disabled: true}}`, and the pressed-opacity branch is gone, so a tap produces no fake response at all and TalkBack announces them as disabled rather than as working buttons. The primary circle does the same conditionally (`disabled={!hasText}`, `accessibilityState` following it, and `opacity: pressed &amp;&amp; hasText ? 0.8 : 1`), so the one control that is a send button half the time and an unbuilt mic the other half reports which one it currently is.
@@ -23315,70 +23368,70 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>VC-060</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Incoming message bubbles are nearly invisible in light theme — #F7F7F8 on #FFFFFF with no border (1.04:1)</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr"/>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/a_relaunch.png — the 'kkr' and 'h' bubbles in light theme. Fix options: give the incoming bubble a hairline in BOTH schemes, or darken `bgSubtle` for this use.
 FIX: the incoming-bubble hairline is no longer dark-only; it applies in both schemes, using the wallpaper-supplied border when the chat has a decorated ground and t.colors.hairline otherwise.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>VC-061</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>A 48dp empty band sits between the composer and the keyboard whenever the keyboard is open</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/a_cal.png and a_own_follow.png — the white band between the composer pill and the keyboard's suggestion strip. Same file also sets `borderTopWidth: 0` alongside a `borderTopColor`, so the intended separator between the thread and the composer never draws.
 FIX: keyboard-up paddingBottom drops from spacing.huge (48dp) to spacing.xs (8dp), and borderTopWidth goes from 0 to 1 so the separator the style always declared actually draws. VERIFIED ON DEVICE: scratchpad/shots/v2_own_follow.png shows the hairline above the composer and the composer sitting close to the keyboard.
@@ -23386,78 +23439,78 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>VC-062</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>A chat left open while the app is backgrounded keeps marking arriving messages read — the sender gets a blue tick for a message nobody has seen</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>chatVisibility.test.tsx: the chat only counts as on screen while it is visible</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Found while tracing VC-057. Same listener is also the only place a notification TAP can clear a conversation's stored notification lines, because tapping resumes an ALREADY-MOUNTED chat screen and the mount effect never re-runs.
 FIX: the AppState listener in useMessages now withdraws and re-asserts the ENGINE's active conversation alongside the push layer's, and on returning to the foreground it re-reports the read and clears the conversation notification. Three new hook tests (chatVisibility.test.tsx) cover it, written RED first: before the change the background case recorded zero setActiveConversation calls, which is the bug exactly. Clearing on resume is also what fixes VC-057 — a notification TAP resumes an ALREADY-MOUNTED chat screen, so the mount effect never re-ran and the stored MessagingStyle lines were never dropped. Verified: 534/534 jest, tsc clean, eslint 0 errors. Live two-device re-verification still pending — the test phone was disconnected before it could be run.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>VC-063</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>A message whose realtime frame carries no body renders a permanently blank bubble — the REST recovery is dead code and the list would not re-render anyway</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>syncLogic.test.ts: reconcileDecision (§L6 dedup), failureScenarios.test.ts: a realtime frame with no body, observeMessages.test.ts: observeMessages column coverage</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit after the live session. Fix needs both halves: let the fill update a row matched by seq (e.g. treat a seq row with empty content as 'update'), and name `content_plain` in observeMessages' column list.
 FIX, both halves — either alone still leaves a blank bubble.
@@ -23467,39 +23520,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>VC-064</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Opening a chat from a notification while another chat is on screen keeps the unsent draft — one tap can send it to the wrong person</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>conversationSwitch.test.tsx: opening another chat from a notification, conversationSwitch.test.tsx: a re-render that is not a conversation switch</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit. VC-053 fixed the TITLE on this exact entry point, which confirms the param-update path is real and exercised; the state carry-over was not addressed then.
 FIX — and NOT the `getId` this entry proposed. `navigation/RootNavigator.tsx` is UNCHANGED: the Chat screen still has no `getId`, and the deep link still reuses the route and swaps `route.params`. What changed is entirely in `ChatScreen.tsx`: it is now a shell that reads `route.params` and renders the real screen — the old body, renamed `ChatThread` — as `&lt;ChatThread key={conversationId} … /&gt;`. The key IS the reset. React tears the old thread down and builds a new one, so `text`, `offsetRef`, `showJump`/`showJumpRef` and `newestIdRef` cannot cross over, and whatever state `ChatThread` grows later is covered by construction instead of by somebody remembering to add it to a reset effect.
@@ -23508,39 +23561,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>VC-065</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Backing out of a chat mid-resolve strands a 20s presence timer, and can permanently disable the only code that clears it</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>presenceLifecycle.test.ts: a chat closed while its presence is still resolving</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit after the live two-device session.
 FIX: a `presenceEpoch` counter on the engine. `deactivatePresence` bumps it BEFORE the map delete — before, so an activate still awaiting sees the move rather than racing the delete — and the two paths that clear `activePresencePeers` wholesale, `stop()` and `onSessionCleared()`, bump it too. `activatePresence` captures the epoch before its first await and bails at three points: after the stored-peer lookup (`peerIdFor`), after the members fallback, and again after `refreshPeerPresence`.
@@ -23549,35 +23602,35 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>VC-066</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>PushStore's JSON blobs are read-modify-write across three threads — notification lines and counts can be lost or resurrected</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr"/>
-      <c r="F43" s="5" t="inlineStr"/>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Distinct from VC-033, which is about the pending-event queue. This is the other five maps. Found by a code-level audit after the live two-device session.
 FIX: one `synchronized(WRITE_LOCK)` monitor wrapping every read-modify-write in the class — `appendLine`, `clearLines`, `clearAllLines`, `bumpCount`, `clearCount`, `clearAllCounts`, `setLastSeq`, `setMuted`, `putNames` (both name maps) and `putPersonAvatar`, plus `enqueueEvent`/`takeEvents` on the pending-event queue this entry split off from VC-033.
@@ -23588,35 +23641,35 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>VC-067</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Swiping a notification away clears its count but keeps its message lines, so dismissed messages reappear in the next notification</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit after the live two-device session. Deterministic, unlike the race in the sibling PushStore report.
 FIX: the `ACTION_DISMISS` branch now calls `store.clearLines(conversationId)` alongside `clearCount`, matching `PushNotifications.cancel`, which has always dropped both halves.
@@ -23626,39 +23679,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>VC-068</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Every load-older page re-runs the open-the-chat side effects, briefly un-suppressing notifications for the chat on screen</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>chatOpenEffects.test.tsx: paging through history is not re-opening the chat</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit after the live two-device session.
 FIX: the `useMessages` effect was split in two, exactly as this entry proposed. The open-the-chat work — `clearUnread` plus the read frame, the receipts GET, `syncEngine.setActiveConversation`, `setActiveConversationForPush`, the `clearConversationNotification` bridge call and the AppState listener — now sits in an effect keyed on `conversationId` ALONE, with its teardown (`appStateSub.remove()` and both active-conversation withdrawals) moved across with it. A second effect keyed on `[conversationId, limit]` does the only thing a wider window actually changes: subscribe `observeMessages` and release the narrower subscription.
@@ -23668,39 +23721,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>VC-069</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>The read watermark is sent at the local MAX seq, so it covers messages the device does not hold — the sender gets a blue tick for a message that was never received</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>contiguousSeq.test.ts: maxContiguousSeqForConversation</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>Split out of VC-051 during that investigation. VC-062 (a backgrounded-but-mounted chat marking arrivals read) widened the window and is fixed; this is the independent, underlying defect.
 FIX: a new `maxContiguousSeqForConversation` in `infra/db/messages.ts` — the highest seq with no KNOWN hole beneath it — over a bounded `CONTIGUITY_SCAN = 500` row scan (`seq &gt; 0`, seq DESC, then sorted ascending).
@@ -23711,69 +23764,110 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>VC-070</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>A conversation with no resolved name shows as a bare em-dash in the chat list, with no way to tell who it is</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>conversationRowIdentity.test.ts: the identity a conversation row shows, chatsList.test.tsx: ConversationRow names a DM whose peer never resolved, chatTitle.test.ts: the header title for a conversation nothing names</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Found during the live two-device session while checking the chat list; filed after confirming the source. Related to VC-047, which was about the WRONG name being shown; this is about NO name.
+FIX: a new pure conversationRowIdentity(name, fallback) in ui/chat/chatModel.ts returns both the title and the avatar initial from ONE decision, so the three places the placeholder used to leak — the visible name, the accessibilityLabel and the avatar initial — can no longer disagree. The label is localised and picked by kind: chat.unknownContact for a DM, chat.unnamedChat for a group, added to all three locales (en, hi, ar) so no locale falls back to English. The avatar is now gated on the initial being absent rather than on a ? sentinel, so an unidentified row draws the same person glyph it always did.
+WHY NOT THE PHONE NUMBER, checked in source rather than assumed: the conversations table denormalises peer_id and the avatar but no number; the members endpoint returns bare account ids and the peer profile shape has no phone field at all (contact discovery is OPRF precisely so a number cannot be derived from an account); and the one local number-to-account map cannot reach this case, because the device-contacts reader already falls back to the first NUMBER as the name, so an address-book entry saved without a name arrives with the number AS its name and peerDisplayName returns it. A row that reaches this fallback is by construction one whose peer is not in the address book — nothing on the device holds their number. Resolving one per row would also be a network call on the render path (M0 rule 2) in a list that must recycle at 55+ FPS (R4).
+SAME FIX APPLIED TO THE CHAT HEADER in the same pass: an unidentified chat header read "Chats", the bottom-tab label, in the slot where the person name goes. That was the best string available when VC-053 landed; now that chat.unknownContact exists both surfaces say the same thing, and the avatar there is gated the same way. No visual change anywhere — same text slot, font, size, weight, layout and palette.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>VC-071</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>A notification's Mark-as-read carries the arriving seq, so a late out-of-order push acknowledges below the newest message</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>Found by an adversarial code review of the notification changes made the same day. Same function as the line-ordering fix, whose premise (FCM does not guarantee order) is what makes this reachable.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>VC-072</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>A notification's collapsed row can show one person's words beside another person's face</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>Found by an adversarial code review of the notification changes made the same day.</t>
         </is>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -641,7 +641,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-19 15:20 UTC</t>
+          <t>Generated 2026-09-19 15:48 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>VC-SEC-101</t>
+          <t>storeKey.test.ts: resolveStoreKey</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="V17" s="5" t="inlineStr">
         <is>
-          <t>Confirmed by code reading.</t>
+          <t>The MMKV encryption key was a string literal in infra/kv/mmkv.ts, so it shipped inside every APK. Unzip, read the bundle, and you hold the key to everything the app persists at rest: the access and refresh tokens, the cnfJkt binding, and the Ed25519 device private key under auth.devicePrivKey. The last of those is the one that matters most, because it authenticates this install to the backend and cannot be re-derived — its disclosure is not something signing out can undo.</t>
         </is>
       </c>
       <c r="W17" s="5" t="inlineStr">
@@ -13452,7 +13452,13 @@
       </c>
       <c r="AA17" s="5" t="inlineStr">
         <is>
-          <t>Known and tracked as MP1 work, but it is the single highest-severity item in the client and should gate any release.</t>
+          <t>Known and tracked as MP1 work, but it is the single highest-severity item in the client and should gate any release.
+FIX. A new in-app native module (com.velchat.securestore) generates 32 random bytes once per install and seals them with an AES-GCM key created in the AndroidKeyStore, which never leaves it — TEE-backed on most devices. Only the sealed blob reaches disk, so an attacker with the APK now has nothing and an attacker with the file has ciphertext. The wrapping key is deliberately NOT bound to user authentication: the store has to be readable for a push to be acknowledged behind a locked screen (M13), and a lockscreen-bound key would also be invalidated the next time the user changes their PIN, taking the device identity with it.
+THE MIGRATION is the dangerous part and is what most of the design is about. An install that upgrades has its store encrypted with the old constant; opening it with the new key reads an EMPTY store, which would sign the user out and destroy the device key. So the order is: open with the legacy key, MMKV recrypt() in place, and only then does native record the key as committed. The commit is written after javascript reports success, never when the key is generated, so a process that dies mid-migration comes back uncommitted and simply tries again — opening with the new key at that point would find nothing. The decision is a pure function (resolveStoreKey) with four cases covered by tests, including that retry, because a keystore call cannot be unit-tested on this machine and getting this wrong is unrecoverable.
+FAILURE IS SAFE BY DESIGN: the native side answers an empty string rather than throwing when the keystore is unusable, and javascript then stays on the legacy key. A store the app cannot open looks to a user exactly like a wiped account, which is far worse than remaining on the key the previous build already used. Nothing in either file logs a key, a blob or a fragment (M19) — only which step failed, by exception class name.
+The bridge methods are synchronous on purpose: the MMKV instance is built at module scope, so the key must exist before javascript reaches its first await, or there is a legacy-encrypted window on every launch. Cost is three SharedPreferences reads and one AES-GCM operation over 32 bytes at startup.
+VERIFIED ON BOTH DEVICES with real signed-in sessions, which is the only test that matters here. Emulator: migrate path — session, chats, avatars, previews and unread badges all intact after the re-encrypt; then a second cold start on the committed native key, still intact (1855 ms). Real device (OPPO CPH2643, arm64, real TEE): same, cold start 553 ms, and no keystore-fallback warning in logcat on either device, so the keystore path genuinely ran rather than silently falling back. 588/588 jest, tsc clean, eslint 0 errors, Kotlin compiles.
+STILL OPEN, deliberately and recorded rather than quietly skipped: (a) iOS has no native half — the TS wrapper degrades to the legacy key there, and nothing about iOS is claimed as verified since it cannot be built on this machine. (b) The Ed25519 private key is now protected at rest but still passes through JS memory when it signs. Moving the key itself INTO the keystore, so signing happens natively and the private bytes never enter the bundle heap, is the stronger fix and is its own piece of work. (c) No new dependency was added, so no ADR was required under M1.</t>
         </is>
       </c>
       <c r="AB17" s="5" t="inlineStr"/>
@@ -21248,7 +21254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -21434,7 +21440,7 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="24" t="inlineStr"/>
     </row>
@@ -21445,7 +21451,7 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" s="24" t="inlineStr"/>
     </row>
@@ -21504,7 +21510,7 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>15 open P0/P1 defect(s) block the build.</t>
+          <t>14 open P0/P1 defect(s) block the build.</t>
         </is>
       </c>
     </row>
@@ -21656,24 +21662,24 @@
     <row r="37">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>VC-016</t>
+          <t>VC-017</t>
         </is>
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>MMKV's encryption key is a hardcoded bundle constant, and the Ed25519 device private key is stored inside it</t>
+          <t>Message plaintext and the user's own typed replies persist in plaintext SharedPreferences</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>VC-017</t>
+          <t>VC-018</t>
         </is>
       </c>
       <c r="B38" s="23" t="inlineStr">
@@ -21683,48 +21689,48 @@
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>Message plaintext and the user's own typed replies persist in plaintext SharedPreferences</t>
+          <t>No certificate pinning anywhere, in JS or native</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>VC-018</t>
+          <t>VC-039</t>
         </is>
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>No certificate pinning anywhere, in JS or native</t>
+          <t>Any authenticated user can READ and WRITE any conversation — no authorization on the chat routes, and conversation ids are derivable offline</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>VC-039</t>
+          <t>VC-040</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>Any authenticated user can READ and WRITE any conversation — no authorization on the chat routes, and conversation ids are derivable offline</t>
+          <t>A push endpoint can be registered against another account's userId, redirecting their push wake-ups</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>VC-040</t>
+          <t>VC-041</t>
         </is>
       </c>
       <c r="B41" s="23" t="inlineStr">
@@ -21734,14 +21740,14 @@
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>A push endpoint can be registered against another account's userId, redirecting their push wake-ups</t>
+          <t>POST /chat/messages accepts a conversationId that does not exist</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>VC-041</t>
+          <t>VC-043</t>
         </is>
       </c>
       <c r="B42" s="23" t="inlineStr">
@@ -21750,23 +21756,6 @@
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>POST /chat/messages accepts a conversationId that does not exist</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="22" t="inlineStr">
-        <is>
-          <t>VC-043</t>
-        </is>
-      </c>
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="inlineStr">
         <is>
           <t>Concurrent refresh-token requests can all succeed — rotation is not race-safe</t>
         </is>
@@ -21921,7 +21910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22207,12 +22196,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>VC-020</t>
+          <t>VC-016</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Concurrent applyServerMessages duplicates every row in the overlap, and can lose a whole batch on a conversation PK clash</t>
+          <t>MMKV's encryption key is a hardcoded bundle constant, and the Ed25519 device private key is stored inside it</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -22222,12 +22211,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-12</t>
+          <t>dev branch, 2026-09-19</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-201</t>
+          <t>storeKey.test.ts: resolveStoreKey</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
@@ -22238,19 +22227,25 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>VC-001 makes this far more likely to be hit in practice, because seq gaps are constant. FIX: The three lookup queries in applyServerMessages moved inside db.write(), read before any prepareCreate/prepareUpdate call — closes the race without violating the prepare-then-batch-synchronously constraint. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>Known and tracked as MP1 work, but it is the single highest-severity item in the client and should gate any release.
+FIX. A new in-app native module (com.velchat.securestore) generates 32 random bytes once per install and seals them with an AES-GCM key created in the AndroidKeyStore, which never leaves it — TEE-backed on most devices. Only the sealed blob reaches disk, so an attacker with the APK now has nothing and an attacker with the file has ciphertext. The wrapping key is deliberately NOT bound to user authentication: the store has to be readable for a push to be acknowledged behind a locked screen (M13), and a lockscreen-bound key would also be invalidated the next time the user changes their PIN, taking the device identity with it.
+THE MIGRATION is the dangerous part and is what most of the design is about. An install that upgrades has its store encrypted with the old constant; opening it with the new key reads an EMPTY store, which would sign the user out and destroy the device key. So the order is: open with the legacy key, MMKV recrypt() in place, and only then does native record the key as committed. The commit is written after javascript reports success, never when the key is generated, so a process that dies mid-migration comes back uncommitted and simply tries again — opening with the new key at that point would find nothing. The decision is a pure function (resolveStoreKey) with four cases covered by tests, including that retry, because a keystore call cannot be unit-tested on this machine and getting this wrong is unrecoverable.
+FAILURE IS SAFE BY DESIGN: the native side answers an empty string rather than throwing when the keystore is unusable, and javascript then stays on the legacy key. A store the app cannot open looks to a user exactly like a wiped account, which is far worse than remaining on the key the previous build already used. Nothing in either file logs a key, a blob or a fragment (M19) — only which step failed, by exception class name.
+The bridge methods are synchronous on purpose: the MMKV instance is built at module scope, so the key must exist before javascript reaches its first await, or there is a legacy-encrypted window on every launch. Cost is three SharedPreferences reads and one AES-GCM operation over 32 bytes at startup.
+VERIFIED ON BOTH DEVICES with real signed-in sessions, which is the only test that matters here. Emulator: migrate path — session, chats, avatars, previews and unread badges all intact after the re-encrypt; then a second cold start on the committed native key, still intact (1855 ms). Real device (OPPO CPH2643, arm64, real TEE): same, cold start 553 ms, and no keystore-fallback warning in logcat on either device, so the keystore path genuinely ran rather than silently falling back. 588/588 jest, tsc clean, eslint 0 errors, Kotlin compiles.
+STILL OPEN, deliberately and recorded rather than quietly skipped: (a) iOS has no native half — the TS wrapper degrades to the legacy key there, and nothing about iOS is claimed as verified since it cannot be built on this machine. (b) The Ed25519 private key is now protected at rest but still passes through JS memory when it signs. Moving the key itself INTO the keystore, so signing happens natively and the private bytes never enter the bundle heap, is the stronger fix and is its own piece of work. (c) No new dependency was added, so no ADR was required under M1.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>VC-021</t>
+          <t>VC-020</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>applyReceipt is a non-atomic read-modify-write, so blue ticks can regress to grey</t>
+          <t>Concurrent applyServerMessages duplicates every row in the overlap, and can lose a whole batch on a conversation PK clash</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -22265,7 +22260,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-202</t>
+          <t>VC-UNIT-201</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
@@ -22276,24 +22271,24 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Every existing receipt test applies receipts sequentially, which is exactly why they all pass. FIX: applyReceipt now re-fetches the rows to update from inside db.write() (same pattern as VC-020) instead of before it, so the monotonic check is atomic with the write. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>VC-001 makes this far more likely to be hit in practice, because seq gaps are constant. FIX: The three lookup queries in applyServerMessages moved inside db.write(), read before any prepareCreate/prepareUpdate call — closes the race without violating the prepare-then-batch-synchronously constraint. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>VC-022</t>
+          <t>VC-021</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>A SendAck with seq 0 leaves the message permanently un-tickable and permanently duplicated</t>
+          <t>applyReceipt is a non-atomic read-modify-write, so blue ticks can regress to grey</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -22303,7 +22298,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-203</t>
+          <t>VC-UNIT-202</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
@@ -22314,19 +22309,19 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>normalizeSendAck has no test file at all. FIX: The outbox drain now rejects a SendAck with no usable seq (ack.seq is not &gt; 0) as a retryable server-kind AppError instead of writing it as a successful send — routes through the exact same retry path as any other transient send failure, so the row never gets stuck permanently un-tickable/duplicated. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>Every existing receipt test applies receipts sequentially, which is exactly why they all pass. FIX: applyReceipt now re-fetches the rows to update from inside db.write() (same pattern as VC-020) instead of before it, so the monotonic check is atomic with the write. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>VC-023</t>
+          <t>VC-022</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>One 401 on send turns the entire outbox into permanently failed messages</t>
+          <t>A SendAck with seq 0 leaves the message permanently un-tickable and permanently duplicated</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -22341,7 +22336,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-204</t>
+          <t>VC-UNIT-203</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
@@ -22352,24 +22347,24 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>FIX: classifySendFailure() grouped auth with client, treating a post-refresh-failure 401/403 as if THIS message were rejected (permanent:true, pauseDrain:false) — one transient auth hiccup then permanently failed every other queued message as the drain kept walking into the same 401. auth is a SESSION problem, not a message problem (client.ts already treats a refresh that cannot reach the server as retryable, leaving the session valid). Added a dedicated auth case returning {permanent:false, pauseDrain:true, cooldownMs:0}, matching the network/timeout/server treatment, so the drain pauses instead of destroying the queue and resumes once the session recovers. Split the existing it.each(['client','auth']) test (which encoded the old, wrong grouping) into client-only plus a new dedicated describe block for auth. Verified: full jest suite 452/452 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>normalizeSendAck has no test file at all. FIX: The outbox drain now rejects a SendAck with no usable seq (ack.seq is not &gt; 0) as a retryable server-kind AppError instead of writing it as a successful send — routes through the exact same retry path as any other transient send failure, so the row never gets stuck permanently un-tickable/duplicated. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>VC-024</t>
+          <t>VC-023</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Migration-v3's five composite indexes never exist on a fresh install</t>
+          <t>One 401 on send turns the entire outbox into permanently failed messages</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -22379,7 +22374,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>schema.test.ts: VC-024</t>
+          <t>VC-UNIT-204</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -22390,24 +22385,24 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>FIX: added an unsafeSql hook to schema.ts (appSchema) — WatermelonDB's own supported extension point, confirmed by reading adapters/sqlite/encodeSchema/index.js (encodeSchema calls unsafeSql(sql, "setup") for a fresh install) — that appends the same five composite CREATE INDEX statements the v3 migration already applies on an upgrade. Extracted the five statements into a new shared compositeIndexes.ts so migrations.ts and schema.ts can never drift apart, and migrations.ts now maps over that same array instead of repeating the SQL inline. Verified: full jest suite 481/481 pass (3 new tests in schema.test.ts assert the hook exists, appends every composite index on kind:"setup", and leaves other DDL kinds untouched), tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: classifySendFailure() grouped auth with client, treating a post-refresh-failure 401/403 as if THIS message were rejected (permanent:true, pauseDrain:false) — one transient auth hiccup then permanently failed every other queued message as the drain kept walking into the same 401. auth is a SESSION problem, not a message problem (client.ts already treats a refresh that cannot reach the server as retryable, leaving the session valid). Added a dedicated auth case returning {permanent:false, pauseDrain:true, cooldownMs:0}, matching the network/timeout/server treatment, so the drain pauses instead of destroying the queue and resumes once the session recovers. Split the existing it.each(['client','auth']) test (which encoded the old, wrong grouping) into client-only plus a new dedicated describe block for auth. Verified: full jest suite 452/452 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>VC-025</t>
+          <t>VC-024</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>reassertReceipts() on every connect emits an unbounded burst the gateway silently drops</t>
+          <t>Migration-v3's five composite indexes never exist on a fresh install</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -22417,7 +22412,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>failureScenarios.test.ts: receipt reassertion after a reconnect with many owed conversations</t>
+          <t>schema.test.ts: VC-024</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
@@ -22428,19 +22423,19 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>FIX: flushReceipts() (SyncEngine.ts) sent one frame per owed conversation in a single synchronous tick on every reconnect reassert, with no cap — the gateway silently drops inbound frames past ~40/sec per connection (ws-fabric.ts), and the client never learns which ones were dropped since socket.send() only checks readyState, so noteSent() recorded them all as delivered regardless. Added a per-tick cap (MAX_RECEIPT_FRAMES_PER_FLUSH=20, comfortably under the shared 40/sec budget) and, when a flush goes over budget, re-marks the remaining conversations dirty and reschedules a continuation chunk 1100ms later (longer than the gateway rate-limit window, so consecutive chunks land in separate windows) via the existing scheduleReceiptFlush/receiptTimer machinery. Nothing is ever dropped, only spread across more ticks. Verified: full jest suite 485/485 pass, tsc --noEmit clean, eslint 0 errors. Added 2 new tests (failureScenarios.test.ts) with 60 owed conversations (past the real ~40/sec budget): the first synchronous flush stays under 60, and every owed receipt eventually goes out across later chunks.</t>
+          <t>FIX: added an unsafeSql hook to schema.ts (appSchema) — WatermelonDB's own supported extension point, confirmed by reading adapters/sqlite/encodeSchema/index.js (encodeSchema calls unsafeSql(sql, "setup") for a fresh install) — that appends the same five composite CREATE INDEX statements the v3 migration already applies on an upgrade. Extracted the five statements into a new shared compositeIndexes.ts so migrations.ts and schema.ts can never drift apart, and migrations.ts now maps over that same array instead of repeating the SQL inline. Verified: full jest suite 481/481 pass (3 new tests in schema.test.ts assert the hook exists, appends every composite index on kind:"setup", and leaves other DDL kinds untouched), tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>VC-026</t>
+          <t>VC-025</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Unread count climbs and the read watermark stalls for messages backfilled into the chat you are reading</t>
+          <t>reassertReceipts() on every connect emits an unbounded burst the gateway silently drops</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -22455,7 +22450,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-207</t>
+          <t>failureScenarios.test.ts: receipt reassertion after a reconnect with many owed conversations</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
@@ -22466,24 +22461,24 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>VC-001 makes backfills constant, so this fires often. FIX: pageBackfill now mirrors the live-message path: if the backfilled page lands in the conversation on screen, it marks read (noteRead + clearUnread) instead of only noteDelivered. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: flushReceipts() (SyncEngine.ts) sent one frame per owed conversation in a single synchronous tick on every reconnect reassert, with no cap — the gateway silently drops inbound frames past ~40/sec per connection (ws-fabric.ts), and the client never learns which ones were dropped since socket.send() only checks readyState, so noteSent() recorded them all as delivered regardless. Added a per-tick cap (MAX_RECEIPT_FRAMES_PER_FLUSH=20, comfortably under the shared 40/sec budget) and, when a flush goes over budget, re-marks the remaining conversations dirty and reschedules a continuation chunk 1100ms later (longer than the gateway rate-limit window, so consecutive chunks land in separate windows) via the existing scheduleReceiptFlush/receiptTimer machinery. Nothing is ever dropped, only spread across more ticks. Verified: full jest suite 485/485 pass, tsc --noEmit clean, eslint 0 errors. Added 2 new tests (failureScenarios.test.ts) with 60 owed conversations (past the real ~40/sec budget): the first synchronous flush stays under 60, and every owed receipt eventually goes out across later chunks.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>VC-027</t>
+          <t>VC-026</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>'Load older' dead-ends permanently on a deletion hole wider than one page</t>
+          <t>Unread count climbs and the read watermark stalls for messages backfilled into the chat you are reading</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -22493,7 +22488,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>failureScenarios.test.ts: loading older history across a wide deletion hole</t>
+          <t>VC-UNIT-207</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
@@ -22504,19 +22499,19 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>FIX: fetchOlderMessages() (SyncEngine.ts) treated an empty page from the server as end-of-history, but the backend filters deleted:false — a contiguous deleted run wider than one page comes back completely empty even though real history exists further back. Since the UI (useMessages.ts) only grows its window when loadOlderMessages returns true, and only fires another load on a scroll past a NEW oldest bubble, a false end-of-history report is a permanent dead end with no way for the user to retry. Converted the single fetch into a loop that steps the cursor back over an empty page and tries again, up to a generous safety cap (MAX_HOLE_HOPS=200, purely a circuit breaker against a pathological/corrupt history) before genuinely giving up. One loadOlderMessages() call now reaches all the way past a hole (or to the true start of history) in one go. Verified: full jest suite 485/485 pass, tsc --noEmit clean, eslint 0 errors. Added 2 new tests (failureScenarios.test.ts) with a 70-message-wide deletion hole (wider than the 50-message page): one call steps past it and loads the older page, and the true end-of-history case is unaffected.</t>
+          <t>VC-001 makes backfills constant, so this fires often. FIX: pageBackfill now mirrors the live-message path: if the backfilled page lands in the conversation on screen, it marks read (noteRead + clearUnread) instead of only noteDelivered. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>VC-029</t>
+          <t>VC-027</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Outbox backoff exhaustion is unreachable — MAX_SEND_ATTEMPTS can never fire</t>
+          <t>'Load older' dead-ends permanently on a deletion hole wider than one page</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -22531,7 +22526,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-210</t>
+          <t>failureScenarios.test.ts: loading older history across a wide deletion hole</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
@@ -22542,34 +22537,34 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>FIX: removed the dead attempt-count exhaustion path (MAX_SEND_ATTEMPTS/nextOutboxRetry in syncLogic.ts) that markFailed() fell back to only when permanent was omitted — a fallback no real call site ever triggered (SyncEngine.ts always passes a classified boolean from classifySendFailure()). This mechanism contradicted the documented WhatsApp-style policy (sendFailurePolicy.ts: reachability failures retry forever, never auto-fail by attempt count) and had no basis in the HLD/LLD spec (§L6 outbox semantics: classification-based retryable-vs-permanent only, no attempt cap). Made markFailed()'s permanent parameter required (compiler now prevents the dead path from ever coming back), updated the one test that accidentally relied on the old default (realtime-hardening.test.ts) to pass permanent explicitly, removed the 4 tests for the deleted dead function, and added a new regression test proving a retryable cause stays queued past a high attempt count. Verified: full jest suite 452/452 pass (455 - 4 removed + 1 added), tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: fetchOlderMessages() (SyncEngine.ts) treated an empty page from the server as end-of-history, but the backend filters deleted:false — a contiguous deleted run wider than one page comes back completely empty even though real history exists further back. Since the UI (useMessages.ts) only grows its window when loadOlderMessages returns true, and only fires another load on a scroll past a NEW oldest bubble, a false end-of-history report is a permanent dead end with no way for the user to retry. Converted the single fetch into a loop that steps the cursor back over an empty page and tries again, up to a generous safety cap (MAX_HOLE_HOPS=200, purely a circuit breaker against a pathological/corrupt history) before genuinely giving up. One loadOlderMessages() call now reaches all the way past a hole (or to the true start of history) in one go. Verified: full jest suite 485/485 pass, tsc --noEmit clean, eslint 0 errors. Added 2 new tests (failureScenarios.test.ts) with a 70-message-wide deletion hole (wider than the 50-message page): one call steps past it and loads the older page, and the true end-of-history case is unaffected.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>VC-030</t>
+          <t>VC-029</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Message window sorts by created_at, not seq — a device clock ahead of the server permanently mis-orders own messages</t>
+          <t>Outbox backoff exhaustion is unreachable — MAX_SEND_ATTEMPTS can never fire</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-13</t>
+          <t>dev branch, 2026-09-12</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>messageOrdering.test.ts: VC-030 — a device clock running ahead of the server</t>
+          <t>VC-UNIT-210</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
@@ -22580,24 +22575,24 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>FIX: two causes, both in the created_at-as-sort-key design. (1) markMessageSent() re-stamped createdAt to the server clock FORWARD ONLY (if (ack.serverTs &gt; m.createdAt)), a rule meant to stop a slow server clock re-burying an offline-composed bubble. Forward-only mixes two clocks in one sort key: on a device whose clock leads the server, an own message keeps its future local stamp and beats every server timestamp that follows it, permanently. The server clock is the same authority that assigns seq, so its timestamp is now adopted in EITHER direction. (2) messageWindowClauses() (extracted from observeMessages so the real query is testable rather than duplicated in a test) now sorts by created_at DESC then seq DESC — seq is the ordering identity per backend-integration-reference §5, and the gateway fans bursts out inside one millisecond, so identical created_at values are normal and were previously resolved by whatever order rows happened to be written. seq is the SECOND key, not the first, because an unsent message has no seq and sorting on it first would file every pending bubble under a null and drag it out of the newest-first window. The pre-existing test never drags a message backwards in time encoded the defect; it was rewritten to assert the concern it actually cared about — that a backwards re-stamp does not change the bubble POSITION — which now holds because seq decides the order. Verified: full jest suite 492/492 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: removed the dead attempt-count exhaustion path (MAX_SEND_ATTEMPTS/nextOutboxRetry in syncLogic.ts) that markFailed() fell back to only when permanent was omitted — a fallback no real call site ever triggered (SyncEngine.ts always passes a classified boolean from classifySendFailure()). This mechanism contradicted the documented WhatsApp-style policy (sendFailurePolicy.ts: reachability failures retry forever, never auto-fail by attempt count) and had no basis in the HLD/LLD spec (§L6 outbox semantics: classification-based retryable-vs-permanent only, no attempt cap). Made markFailed()'s permanent parameter required (compiler now prevents the dead path from ever coming back), updated the one test that accidentally relied on the old default (realtime-hardening.test.ts) to pass permanent explicitly, removed the 4 tests for the deleted dead function, and added a new regression test proving a retryable cause stays queued past a high attempt count. Verified: full jest suite 452/452 pass (455 - 4 removed + 1 added), tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>VC-031</t>
+          <t>VC-030</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>runQueuedPushActions runs queued notification actions concurrently while claiming to serialize them</t>
+          <t>Message window sorts by created_at, not seq — a device clock ahead of the server permanently mis-orders own messages</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -22607,7 +22602,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>runSequentially.test.ts: VC-031</t>
+          <t>messageOrdering.test.ts: VC-030 — a device clock running ahead of the server</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
@@ -22618,34 +22613,34 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>FIX: the drain mapped each queued event to a thunk and then IMMEDIATELY mapped again to call it — events.map(e =&gt; () =&gt; handle(e)).map(run =&gt; run()) — so every handler was already in flight before Promise.allSettled waited on anything. The code did the exact opposite of the comment directly above it. Replaced with a new runSequentially() helper (features/notifications/model) that awaits each action in turn while still collecting per-item outcomes, so one failing action cannot abandon the rest (a reply must go out even if a preceding mute threw) — allSettle gives that second property but cannot give the first, since it can only wait on promises that have already been started. Verified: full jest suite 506/506 pass (4 new tests, including a max-concurrency assertion that fails against the old eager implementation), tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: two causes, both in the created_at-as-sort-key design. (1) markMessageSent() re-stamped createdAt to the server clock FORWARD ONLY (if (ack.serverTs &gt; m.createdAt)), a rule meant to stop a slow server clock re-burying an offline-composed bubble. Forward-only mixes two clocks in one sort key: on a device whose clock leads the server, an own message keeps its future local stamp and beats every server timestamp that follows it, permanently. The server clock is the same authority that assigns seq, so its timestamp is now adopted in EITHER direction. (2) messageWindowClauses() (extracted from observeMessages so the real query is testable rather than duplicated in a test) now sorts by created_at DESC then seq DESC — seq is the ordering identity per backend-integration-reference §5, and the gateway fans bursts out inside one millisecond, so identical created_at values are normal and were previously resolved by whatever order rows happened to be written. seq is the SECOND key, not the first, because an unsent message has no seq and sorting on it first would file every pending bubble under a null and drag it out of the newest-first window. The pre-existing test never drags a message backwards in time encoded the defect; it was rewritten to assert the concern it actually cared about — that a backwards re-stamp does not change the bubble POSITION — which now holds because seq decides the order. Verified: full jest suite 492/492 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>VC-032</t>
+          <t>VC-031</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>No duplicate-notification suppression, though the monotonic watermark to do it already exists</t>
+          <t>runQueuedPushActions runs queued notification actions concurrently while claiming to serialize them</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-19</t>
+          <t>dev branch, 2026-09-13</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-213</t>
+          <t>runSequentially.test.ts: VC-031</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
@@ -22656,97 +22651,97 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
+          <t>FIX: the drain mapped each queued event to a thunk and then IMMEDIATELY mapped again to call it — events.map(e =&gt; () =&gt; handle(e)).map(run =&gt; run()) — so every handler was already in flight before Promise.allSettled waited on anything. The code did the exact opposite of the comment directly above it. Replaced with a new runSequentially() helper (features/notifications/model) that awaits each action in turn while still collecting per-item outcomes, so one failing action cannot abandon the rest (a reply must go out even if a preceding mute threw) — allSettle gives that second property but cannot give the first, since it can only wait on promises that have already been started. Verified: full jest suite 506/506 pass (4 new tests, including a max-concurrency assertion that fails against the old eager implementation), tsc --noEmit clean, eslint 0 errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>VC-032</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>No duplicate-notification suppression, though the monotonic watermark to do it already exists</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>VC-UNIT-213</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
           <t>The fix is one line: `if (seq &gt; 0 &amp;&amp; seq &lt;= store.lastSeq(conversationId)) return false`.
 FIXED, but NOT the way this entry proposed, and the difference matters. The entry says the monotonic watermark to do this already exists (PushStore.lastSeq). Suppressing on a high-water mark would be wrong here: FCM gives no ordering guarantee, and this session PROVED it out of order on a real device — the notification thread came back with KILL2 above KILL1, which is what VC-056 exists to sort. Against a watermark, a genuinely new message arriving with a LOWER seq than one already delivered would have its notification silently swallowed entirely — a far worse failure than showing a duplicate. So suppression is by EXACT identity instead: new PushStore.markSeen(conversationId, seq) records the seq and returns whether it was new, keeping the last 20 seqs per conversation (bounded, and only has to outlast FCM retries), atomic under the same WRITE_LOCK. handleMessage calls it BEFORE the on-screen check, so a duplicate of a message the user already watched arrive in an open chat cannot notify later either. Everything after it still runs for a duplicate on purpose: the delivered ack is idempotent and re-acking guarantees the sender their tick, and handing the push to a live JS runtime is a free chance to catch up. Cleared on sign-out with the rest of the session state. Verified by compileProdReleaseKotlin; no Kotlin test source set exists, and an FCM redelivery cannot be forced on demand, so this is code-review-verified.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>VC-033</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Native pending-event queue is a lock-free read-modify-write that can wipe a reply enqueued mid-drain</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>VC-UNIT-214</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>No JVM test source set exists — android/app/src contains only `main`. PushStore is plain-JVM-testable.
 FIXED as part of VC-066. The pending-event queue is one of the read-modify-write pairs that the new companion-object WRITE_LOCK now covers: enqueueEvent reads the array, appends, trims and writes it back, and takeEvents reads it and removes the key, both entirely inside the monitor. The drain case this entry described — an action queued on the receiver thread between the read and the removal, silently dropped — can no longer interleave, and the code now carries a comment saying exactly that. The monitor is on the COMPANION object rather than the instance, which is load-bearing: PushStore is constructed fresh at each entry point (VelChatMessagingService on FCM delivery, PushActionReceiver on main, VelChatPushModule on the RN native-modules thread), so an instance monitor would have been three separate locks guarding one shared SharedPreferences file. Verified by code review plus a clean compileProdReleaseKotlin; there is no Kotlin test source set in this project, so this is code-review-verified only.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>VC-034</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Retry-After is honored with an unbounded, uncancellable sleep</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>dev branch, 2026-09-12</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>VC-UNIT-215</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Not independently tested</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>FIX: Retry-After is now clamped to [0, 10s] (MAX_RETRY_AFTER_MS, client.ts) before the wait, instead of obeying a server-supplied value unbounded. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>VC-035</t>
+          <t>VC-034</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>A misbuilt binary reports env:'dev' while talking to production</t>
+          <t>Retry-After is honored with an unbounded, uncancellable sleep</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -22761,7 +22756,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-216</t>
+          <t>VC-UNIT-215</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
@@ -22772,19 +22767,19 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>The prod URL fallback direction is defensible; make `name` fall back to 'prod' alongside it, or log.error when Config.API_BASE_URL is absent. FIX: Extracted the pure resolveAppEnv(rawName, rawApiBaseUrl, rawWsUrl) so the fallback logic is unit-testable. An unrecognised/missing ENV now falls back to 'prod' alongside the URL fallback (previously 'dev'), so a misbuilt binary can never report a safe-sounding name while actually pointing at production. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: Retry-After is now clamped to [0, 10s] (MAX_RETRY_AFTER_MS, client.ts) before the wait, instead of obeying a server-supplied value unbounded. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>VC-036</t>
+          <t>VC-035</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Cold start after &gt;15 min idle opens the WebSocket with a certainly-expired token</t>
+          <t>A misbuilt binary reports env:'dev' while talking to production</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -22799,7 +22794,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-217</t>
+          <t>VC-UNIT-216</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
@@ -22810,34 +22805,34 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>FIX: hasValidSession() added (tokens.ts); useAuthBootstrap now refreshes before hydrating on an expired-but-present token. hasSession() deliberately left presence-only to protect SyncEngine reconnect guards. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>The prod URL fallback direction is defensible; make `name` fall back to 'prod' alongside it, or log.error when Config.API_BASE_URL is absent. FIX: Extracted the pure resolveAppEnv(rawName, rawApiBaseUrl, rawWsUrl) so the fallback logic is unit-testable. An unrecognised/missing ENV now falls back to 'prod' alongside the URL fallback (previously 'dev'), so a misbuilt binary can never report a safe-sounding name while actually pointing at production. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>VC-038</t>
+          <t>VC-036</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Jest reports a worker that failed to exit gracefully — a leaked timer or handle in the test path</t>
+          <t>Cold start after &gt;15 min idle opens the WebSocket with a certainly-expired token</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-13</t>
+          <t>dev branch, 2026-09-12</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-001</t>
+          <t>VC-UNIT-217</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
@@ -22848,32 +22843,36 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>FIX (root cause found by instrumentation, not guesswork): --detectOpenHandles reported NOTHING, so the leak was invisible to it. A probe dumping process.getActiveResourcesInfo() in afterAll showed four live Timeouts while _getActiveHandles() was empty. Traced to WatermelonDB: adapters/lokijs/worker/lokiExtensions.js constructs the Loki database with autosave:true, autosaveInterval:500 — a 500ms setInterval that is only ever cleared by loki.close(), which the app never calls because its database lives for the life of the process. Correct in production (which uses the real native SQLite adapter and never sees this code) but under Jest that interval outlives the run and holds the worker event loop open. Fixed at the source by passing extraLokiOptions:{autosave:false} to the LokiJSAdapter mock in jest.setup.ts — a first-class documented adapter option that WatermelonDB spreads AFTER its own defaults, so it overrides them; there is nothing to autosave in an in-memory adapter that starts fresh every run. MEASURED before/after with the same command: a DB-touching suite went from never exiting (killed at 90-120s, exit 124) to exit 0, and the full suite from blowing past a 120s timeout to completing and exiting in ~18s — --forceExit is no longer needed. RESIDUAL, stated honestly: the "worker process has failed to exit gracefully" text can still appear with &gt;=2 jest workers. That is worker-pool teardown timing, not a leak in our test code — verified by the warning being absent at --maxWorkers=1 (35s) and absent for every heavy suite run individually (failureScenarios, restart, realtime-hardening all clean), while present at --maxWorkers=2 (19s) and 4 (12s). Verified: full jest suite 506/506 pass, tsc --noEmit clean, eslint clean.</t>
+          <t>FIX: hasValidSession() added (tokens.ts); useAuthBootstrap now refreshes before hydrating on an expired-but-present token. hasSession() deliberately left presence-only to protect SyncEngine reconnect guards. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>VC-045</t>
+          <t>VC-038</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Real-time messaging and notification-reply sync needs multi-scenario two-device verification</t>
+          <t>Jest reports a worker that failed to exit gracefully — a leaked timer or handle in the test path</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Verified on dev, 2026-09-14</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr"/>
+          <t>dev branch, 2026-09-13</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>VC-UNIT-001</t>
+        </is>
+      </c>
       <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr">
         <is>
@@ -22882,58 +22881,54 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
+          <t>FIX (root cause found by instrumentation, not guesswork): --detectOpenHandles reported NOTHING, so the leak was invisible to it. A probe dumping process.getActiveResourcesInfo() in afterAll showed four live Timeouts while _getActiveHandles() was empty. Traced to WatermelonDB: adapters/lokijs/worker/lokiExtensions.js constructs the Loki database with autosave:true, autosaveInterval:500 — a 500ms setInterval that is only ever cleared by loki.close(), which the app never calls because its database lives for the life of the process. Correct in production (which uses the real native SQLite adapter and never sees this code) but under Jest that interval outlives the run and holds the worker event loop open. Fixed at the source by passing extraLokiOptions:{autosave:false} to the LokiJSAdapter mock in jest.setup.ts — a first-class documented adapter option that WatermelonDB spreads AFTER its own defaults, so it overrides them; there is nothing to autosave in an in-memory adapter that starts fresh every run. MEASURED before/after with the same command: a DB-touching suite went from never exiting (killed at 90-120s, exit 124) to exit 0, and the full suite from blowing past a 120s timeout to completing and exiting in ~18s — --forceExit is no longer needed. RESIDUAL, stated honestly: the "worker process has failed to exit gracefully" text can still appear with &gt;=2 jest workers. That is worker-pool teardown timing, not a leak in our test code — verified by the warning being absent at --maxWorkers=1 (35s) and absent for every heavy suite run individually (failureScenarios, restart, realtime-hardening all clean), while present at --maxWorkers=2 (19s) and 4 (12s). Verified: full jest suite 506/506 pass, tsc --noEmit clean, eslint clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>VC-045</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Real-time messaging and notification-reply sync needs multi-scenario two-device verification</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Verified on dev, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
           <t>This entry tracks a two-device manual verification pass, not a confirmed defect. Assigned to Tusha Bhadouriya to execute and report actual pass/fail per scenario back into this bug.
 VERIFIED 2026-09-14 by a live two-device session (A = OPPO CPH2643 Android 16 real device, B = Pixel emulator Android 16), production build against the live backend. PASSED: single-message real-time delivery; an 8-message burst delivered complete and in order; notification posted with the correct sender name, avatar and per-message lines while backgrounded; notification posted after the process was killed with am kill (FCM woke the dead process and it displayed correctly); tapping a notification opens the right conversation and clears the tray; NO notification is posted while that conversation is on screen (active-conversation suppression works); inline notification Reply sends the message, clears the notification and clears the unread badge; typing indicator appears on the peer header; presence shows online and last-seen; offline send queues and flushes in order on reconnect (airplane mode on/off); unread badges and chat-list ordering correct; cold start COLD TotalTime 1367 ms. FAILED, filed separately: VC-051 (message loss with a false read receipt), VC-052 (thread does not follow new messages), VC-053 (notification tap-through titles the chat Chats), VC-054, VC-055, VC-056, VC-057, VC-058, VC-059, VC-060, VC-061.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>VC-047</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>dev branch, 2026-09-13</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>peerDisplayName.test.ts: VC-044 / VC-047, conversationRow.test.ts: VC-044 / VC-047</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Not independently tested</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>FIX (root-caused): the address book was consulted on exactly ONE path. startDm() writes the saved name when a chat is opened from New Chat / Message Yourself — which is why the name corrected itself after opening — while every other path used server data, and refreshPeerIdentity() actively OVERWROTE a saved name with the registered one on its next background revalidation (once per TTL/session). Introduced peerDisplayName() (features/contacts/model), the single precedence rule: the name YOU saved wins over the name the peer registered; falls back to the registered name for someone not in your book or when the book has not loaded; returns undefined when neither side has a usable name so callers keep what they have; group rows are untouched (no peerId to look up). Applied at both the WRITE side (refreshPeerIdentity, both the TTL path and the profile-changed push, so a revalidation can no longer downgrade a saved name) and the READ side (toConversationRow for the chat list, useConversationIdentity for the chat header), the latter being what makes a saved name appear WITHOUT having to open the chat first. Exposed discoveredContacts() from the contacts barrel as a cache read (no re-discovery). Verified: full jest suite 502/502 pass (10 new tests), tsc --noEmit clean, eslint 0 errors and no boundary violation. Not re-tested on a device — no Android hardware attached to this machine.</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>VC-048</t>
+          <t>VC-047</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Message notification omits the sender's name and tapping it does not open the chat</t>
+          <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -22943,10 +22938,14 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Verified on dev, 2026-09-14</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr"/>
+          <t>dev branch, 2026-09-13</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>peerDisplayName.test.ts: VC-044 / VC-047, conversationRow.test.ts: VC-044 / VC-047</t>
+        </is>
+      </c>
       <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr">
         <is>
@@ -22955,63 +22954,59 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
+          <t>FIX (root-caused): the address book was consulted on exactly ONE path. startDm() writes the saved name when a chat is opened from New Chat / Message Yourself — which is why the name corrected itself after opening — while every other path used server data, and refreshPeerIdentity() actively OVERWROTE a saved name with the registered one on its next background revalidation (once per TTL/session). Introduced peerDisplayName() (features/contacts/model), the single precedence rule: the name YOU saved wins over the name the peer registered; falls back to the registered name for someone not in your book or when the book has not loaded; returns undefined when neither side has a usable name so callers keep what they have; group rows are untouched (no peerId to look up). Applied at both the WRITE side (refreshPeerIdentity, both the TTL path and the profile-changed push, so a revalidation can no longer downgrade a saved name) and the READ side (toConversationRow for the chat list, useConversationIdentity for the chat header), the latter being what makes a saved name appear WITHOUT having to open the chat first. Exposed discoveredContacts() from the contacts barrel as a cache read (no re-discovery). Verified: full jest suite 502/502 pass (10 new tests), tsc --noEmit clean, eslint 0 errors and no boundary violation. Not re-tested on a device — no Android hardware attached to this machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>VC-048</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Message notification omits the sender's name and tapping it does not open the chat</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Verified on dev, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
           <t>Reported by Tusha Bhadouriya during production QA testing.
 RE-TESTED LIVE 2026-09-14 on a production build against the live backend, two devices. Both halves of this report are now correct: the notification DOES carry the sender name (dumpsys shows android.title="Aayush Jain 🤗" with the sender photo and per-message MessagingStyle lines), and tapping it DOES open that conversation (topResumedActivity becomes com.velchat/.MainActivity on the Chat route and every VelChat notification is cleared). Evidence: scratchpad/shots/b_shade.png, b_tapthrough.png. One residual defect on the same path is filed separately as VC-053: the deep link carries no name param, so ChatHeader falls back to the tabs.chats label and the header reads "Chats". A second residual, the chat not opening at the newest message, is covered by VC-052.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>VC-049</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>dev branch, 2026-09-13</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>profileGate.test.ts: VC-049</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Not independently tested</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>FIX (root-caused): the email is NOT a directory-profile field — profileShape.ts states it is a separately-verified identifier owned by the auth-service (GET /auth/account). useProfileGate decided purely from the LOCAL MMKV mirror, and purgeAccountData() wipes KVKeys.email on every sign-out, so immediately after any login the mirror is empty and the gate prompted unconditionally. useAccountInfo() does fetch the real email and mirror it, but it runs in parallel from AppTabs, so its answer always lost the race — and dismissal is session-only, which is why it returned every single login. The gate now asks the auth-service itself before deciding, via a new pure shouldPromptForProfile() (features/user/model/profileGate.ts): a mirrored email means never prompt; a server email means never prompt (and is re-mirrored so later launches short-circuit with no network); an UNANSWERED server (in flight or unreachable) means WAIT rather than prompt, which also removes the flash of the sheet before the answer lands. Only a definitive server no-email prompts. Verified: full jest suite 492/492 pass (5 new decision tests), tsc --noEmit clean, eslint 0 errors, no eslint-plugin-boundaries violation for the user→auth import (authApi depends only on infra, so no cycle). Not reproduced on a device — no Android hardware attached to this machine; fix is verified at the unit level against the exact reported condition.</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>VC-050</t>
+          <t>VC-049</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Cold start holds a splash screen on a network refresh — up to minutes before home appears</t>
+          <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -23021,7 +23016,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>authBootstrap.test.ts: cold start with a session already on the device</t>
+          <t>profileGate.test.ts: VC-049</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
@@ -23032,19 +23027,19 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>FIX: split the two questions the bootstrap had conflated — "can we show the app" and "is the access token fresh enough for a socket". If a session exists on the device at all (hasSession(), presence-only), the app now hydrates and reports ready IMMEDIATELY, whatever the token age; the chat list renders from the local DB, the HTTP client refreshes on its first 401, and the socket heals itself via 4001 -&gt; refresh -&gt; reconnect. VC-036 is not regressed: a fresh token is still wanted as early as possible so the first handshake is not doomed, so the refresh is still fired at once — it just runs BEHIND the app instead of in front of it. The no-session path (signed out but a device key survives) still attempts a silent restore, but is now bounded by MAX_SILENT_RESTORE_MS = 4000 so a hibernating backend cannot freeze the splash; a restore that lands later still navigates home on its own, because RootNavigator follows the auth store (state === active). Verified: full jest suite 521/521 pass (5 new hook tests, two of which fail against the old code by hanging until waitFor times out), tsc --noEmit clean, eslint 0 errors. Measured on device: not yet — needs a launch on real hardware to confirm the wall-clock improvement.</t>
+          <t>FIX (root-caused): the email is NOT a directory-profile field — profileShape.ts states it is a separately-verified identifier owned by the auth-service (GET /auth/account). useProfileGate decided purely from the LOCAL MMKV mirror, and purgeAccountData() wipes KVKeys.email on every sign-out, so immediately after any login the mirror is empty and the gate prompted unconditionally. useAccountInfo() does fetch the real email and mirror it, but it runs in parallel from AppTabs, so its answer always lost the race — and dismissal is session-only, which is why it returned every single login. The gate now asks the auth-service itself before deciding, via a new pure shouldPromptForProfile() (features/user/model/profileGate.ts): a mirrored email means never prompt; a server email means never prompt (and is re-mirrored so later launches short-circuit with no network); an UNANSWERED server (in flight or unreachable) means WAIT rather than prompt, which also removes the flash of the sheet before the answer lands. Only a definitive server no-email prompts. Verified: full jest suite 492/492 pass (5 new decision tests), tsc --noEmit clean, eslint 0 errors, no eslint-plugin-boundaries violation for the user→auth import (authApi depends only on infra, so no cycle). Not reproduced on a device — no Android hardware attached to this machine; fix is verified at the unit level against the exact reported condition.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>VC-051</t>
+          <t>VC-050</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>A message the device was pushed for never reaches the chat, and no reconnect ever heals it — the sender still sees blue read ticks</t>
+          <t>Cold start holds a splash screen on a network refresh — up to minutes before home appears</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -23054,12 +23049,12 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-19</t>
+          <t>dev branch, 2026-09-13</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>failureScenarios.test.ts: a message dropped by fan-out</t>
+          <t>authBootstrap.test.ts: cold start with a session already on the device</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
@@ -23069,6 +23064,44 @@
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>FIX: split the two questions the bootstrap had conflated — "can we show the app" and "is the access token fresh enough for a socket". If a session exists on the device at all (hasSession(), presence-only), the app now hydrates and reports ready IMMEDIATELY, whatever the token age; the chat list renders from the local DB, the HTTP client refreshes on its first 401, and the socket heals itself via 4001 -&gt; refresh -&gt; reconnect. VC-036 is not regressed: a fresh token is still wanted as early as possible so the first handshake is not doomed, so the refresh is still fired at once — it just runs BEHIND the app instead of in front of it. The no-session path (signed out but a device key survives) still attempts a silent restore, but is now bounded by MAX_SILENT_RESTORE_MS = 4000 so a hibernating backend cannot freeze the splash; a restore that lands later still navigates home on its own, because RootNavigator follows the auth store (state === active). Verified: full jest suite 521/521 pass (5 new hook tests, two of which fail against the old code by hanging until waitFor times out), tsc --noEmit clean, eslint 0 errors. Measured on device: not yet — needs a launch on real hardware to confirm the wall-clock improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>VC-051</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>A message the device was pushed for never reaches the chat, and no reconnect ever heals it — the sender still sees blue read ticks</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>failureScenarios.test.ts: a message dropped by fan-out</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/a_inline_rx.png (A shows KILL2 09:39 with blue ticks) vs scratchpad/shots/b_kill2_check.png (B's thread jumps BG1 09:37 -&gt; KILL1 09:37 -&gt; hhh 09:40, no KILL2). Related backend defect VC-001 may be the upstream cause, but the client must still heal the gap on reconnect and must not report `read` for a message it does not hold.
 FIX (frontend): pageBackfill/backfillConversation take an optional `fromSeq`, and the gap probe passes the pre-apply `localMax` — so the repair asks the server from the LOWER edge of the hole instead of from the message that revealed it. Re-fetching the rows already held between localMax and the incoming seq is free: applyServerMessages dedups on (conversation_id, seq) and on client_msg_id inside the write lock. Three end-to-end tests added to failureScenarios.test.ts, driving the real engine against the fake server, written RED first — and rewritten once when the first version passed for the wrong reason (bootConnected’s own reconnect backfill was healing the hole), so each test now brings the socket up while the device is already caught up. Verified: 537/537 jest, tsc clean, eslint 0 errors.
@@ -23076,35 +23109,35 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>VC-052</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Chat thread does not follow the newest message — incoming and own-sent bubbles land hidden behind the composer</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_fg_follow.png (B at the bottom, F1-F3 arrive, list stays on S8 and the jump FAB appears), scratchpad/shots/b_one.png (single message ONE1 arrives, list left exactly one bubble short), scratchpad/shots/a_own_follow.png (A's OWN sent ONE1 clipped behind the composer), scratchpad/shots/b_offline_send.png (own offline sends clipped). The race explains the intermittency: sometimes the manual scroll lands after the anchor adjustment and it looks fine.
 FIX: the follow now goes through FlashList's `scrollToIndex({index:0})` instead of `scrollToOffset({offset:0})`, fired from `onContentSizeChange` rather than the data effect. Root cause confirmed by reading useRecyclerViewController.js: on every data change FlashList measures how far the FIRST VISIBLE item moved and calls scrollAnchorRef.scrollBy(diff) to cancel the shift, gated on a `pauseOffsetCorrection` ref that ONLY scrollToIndex raises — so a plain offset scroll was undone every time and the thread landed exactly one bubble short. Firing from onContentSizeChange means index 0 has a real layout instead of the stale one it would have in the same commit. Anchoring is deliberately kept: it is the right behaviour for a reader scrolled up in history, whom shouldScrollToLatest still leaves alone; a drag cancels any pending follow so loadOlder growing the content is never mistaken for a new message. An intermediate attempt using scrollToOffset from onContentSizeChange plus a requestAnimationFrame retry was built and tested on device and still landed one bubble short — that is what identified the pauseOffsetCorrection gate. VERIFIED ON DEVICE: a four-message burst now ends with the newest message fully visible above the composer (scratchpad/shots/v2_own_follow.png) where the same burst on the previous build left it clipped (v_own_follow.png). Still to verify with a second device: the INCOMING-message path, and the notification tap-through landing position.
@@ -23112,55 +23145,20 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>VC-053</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Chat opened from a notification is titled "Chats" instead of the contact's name, and the avatar loses its initial</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>dev branch, 2026-09-14</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Not independently tested</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>Evidence: scratchpad/shots/b_tapthrough.png and b_jump.png (header 'Chats' after notification tap) vs scratchpad/shots/b_off_kbd.png (header 'Aayush Jain 🤗' for the same chat opened from the list). Relates to VC-048, which reported the tap-through as not opening the chat at all; the open now works, this is the remaining defect on that path.
-FIX: new pure helper `chatTitle(routeName, rowName, fallback)` in ui/chat/chatModel.ts, covered by chatTitle.test.ts (4 cases, RED first). ChatHeader now resolves the title from the route name, then the conversation row it was already observing for the avatar, and only then a generic label; blank counts as absent in both sources. The avatar initial is taken from the resolved name with an empty fallback, so a genuinely unnamed conversation still falls back to the person glyph instead of showing the initial of a tab label. Needs a second device to re-verify the live tap-through.</t>
-        </is>
-      </c>
-    </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>VC-054</t>
+          <t>VC-053</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Notification group summary says "N new messages" but N is the number of chats, not the number of messages</t>
+          <t>Chat opened from a notification is titled "Chats" instead of the contact's name, and the avatar loses its initial</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -23177,20 +23175,20 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Evidence: dumpsys output captured twice in the live session (8 messages -&gt; '5 new messages'; 1 message -&gt; '5 new messages').
-FIX: added `PushStore.countedMessages()`, which sums the per-conversation counters the store already held, and postSummary now formats that instead of `countedConversations()`. The &lt;=1 guard that suppresses the summary for a single chat still uses the conversation count, which is correct. Needs a second device to re-verify live.</t>
+          <t>Evidence: scratchpad/shots/b_tapthrough.png and b_jump.png (header 'Chats' after notification tap) vs scratchpad/shots/b_off_kbd.png (header 'Aayush Jain 🤗' for the same chat opened from the list). Relates to VC-048, which reported the tap-through as not opening the chat at all; the open now works, this is the remaining defect on that path.
+FIX: new pure helper `chatTitle(routeName, rowName, fallback)` in ui/chat/chatModel.ts, covered by chatTitle.test.ts (4 cases, RED first). ChatHeader now resolves the title from the route name, then the conversation row it was already observing for the avatar, and only then a generic label; blank counts as absent in both sources. The avatar initial is taken from the resolved name with an empty fallback, so a genuinely unnamed conversation still falls back to the person glyph instead of showing the initial of a tab label. Needs a second device to re-verify the live tap-through.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>VC-055</t>
+          <t>VC-054</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Every notification is tinted the abandoned violet #7C5CFF, which matches nothing in the shipped monochrome theme</t>
+          <t>Notification group summary says "N new messages" but N is the number of chats, not the number of messages</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -23212,20 +23210,20 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>Confirmed by reading tokens.ts (brandFrom '#0B0B0C' / '#F5F5F7') against push_strings.xml (#7C5CFF) and by the live dumpsys record color=0xff7c5cff.
-FIX: push_accent is now #0B0B0C, the monochrome brand accent from design-system/tokens.ts, and the misleading resource comment about a violet gradient is replaced. Android resolves this against the shade background for contrast. Needs a second device to re-verify live.</t>
+          <t>Evidence: dumpsys output captured twice in the live session (8 messages -&gt; '5 new messages'; 1 message -&gt; '5 new messages').
+FIX: added `PushStore.countedMessages()`, which sums the per-conversation counters the store already held, and postSummary now formats that instead of `countedConversations()`. The &lt;=1 guard that suppresses the summary for a single chat still uses the conversation count, which is correct. Needs a second device to re-verify live.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>VC-056</t>
+          <t>VC-055</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Notification message lines are ordered by arrival, not by message time — an out-of-order push shows the wrong 'latest' message</t>
+          <t>Every notification is tinted the abandoned violet #7C5CFF, which matches nothing in the shipped monochrome theme</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -23235,7 +23233,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-19</t>
+          <t>dev branch, 2026-09-14</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr"/>
@@ -23246,6 +23244,41 @@
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed by reading tokens.ts (brandFrom '#0B0B0C' / '#F5F5F7') against push_strings.xml (#7C5CFF) and by the live dumpsys record color=0xff7c5cff.
+FIX: push_accent is now #0B0B0C, the monochrome brand accent from design-system/tokens.ts, and the misleading resource comment about a violet gradient is replaced. Android resolves this against the shade background for contrast. Needs a second device to re-verify live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>VC-056</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Notification message lines are ordered by arrival, not by message time — an out-of-order push shows the wrong 'latest' message</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_reply_open.png (expanded notification shows S6, S7, S8, BG1, KILL2, KILL1) vs scratchpad/shots/a_inline_rx.png (chat shows KILL1 09:37 then KILL2 09:39, correct).
 FIX: `PushStore.Line` now carries the message's own `seq`, persisted as the JSON key `"q"`, and `showMessage` passes the push's seq into `appendLine`. `appendLine` SORTS before applying the `MAX_LINES` cap, and that order is the fix rather than a detail: capping first dropped whichever line FCM happened to deliver earliest, so an out-of-order push could evict a message newer than the one it kept. `setContentText` and `setLargeIcon` now read the newest INCOMING line (`lines.lastOrNull { !it.mine }`) instead of the message that arrived last, so the collapsed row and the face on it agree with the expanded thread — incoming only, because an inline reply can sort last and quoting the user's own words back at them is not a notification about anything.
@@ -23256,35 +23289,35 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>VC-057</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Notification re-lists messages the user has already read once the chat is reopened and a new message arrives</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_shade.png (S3..S8 before opening), scratchpad/shots/b_tapthrough.png (chat opened, tray cleared, all read), scratchpad/shots/b_reply_open.png (next notification still carries S6, S7, S8, BG1).
 ROOT CAUSE FOUND and FIXED via VC-062. The clearing path was wired correctly all along — clearConversationNotification -&gt; VelChatPushModule.clearConversation -&gt; PushNotifications.cancel -&gt; store.clearLines — but it only ran from the chat screen's MOUNT effect. A notification tap RESUMES an already-mounted ChatScreen, so that effect never re-ran, and the tray entry disappearing was just the notification's own AUTO_CANCEL flag removing the posted notification while the stored lines and counters survived. useMessages now also clears on every return to the foreground. Live re-verification pending a second device.
@@ -23292,74 +23325,74 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>VC-058</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Chat-list preview can regress to an older message — the preview is written unconditionally while the timestamp is guarded</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr"/>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_after_reply.png (row reads 'KILL1' while KILL2 was newer). Fix is to move the preview write inside the same freshness check as the timestamp.
 FIX: the preview write now sits behind the same freshness check as the sort key in upsertConversation — a single `fresher` predicate gates both, so a stale patch can no longer overwrite what the row says while being correctly refused a reorder.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>VC-059</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Composer's emoji, attach, camera and mic buttons are dead controls that look and behave as if they work</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>composerControls.test.tsx: the controls that are not built yet, composerControls.test.tsx: the one control that is wired</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Minimum viable fix for a release build: hide the unimplemented controls, or render them disabled (reduced opacity + accessibilityState disabled) so neither sighted nor screen-reader users are misled.
 FIX: `PillIconButton` lost its `onPress` prop entirely — emoji, attach and camera now render a `Pressable` with a real `disabled` and `accessibilityState={{disabled: true}}`, and the pressed-opacity branch is gone, so a tap produces no fake response at all and TalkBack announces them as disabled rather than as working buttons. The primary circle does the same conditionally (`disabled={!hasText}`, `accessibilityState` following it, and `opacity: pressed &amp;&amp; hasText ? 0.8 : 1`), so the one control that is a send button half the time and an unbuilt mic the other half reports which one it currently is.
@@ -23368,50 +23401,15 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>VC-060</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Incoming message bubbles are nearly invisible in light theme — #F7F7F8 on #FFFFFF with no border (1.04:1)</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>dev branch, 2026-09-14</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>Not independently tested</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Evidence: scratchpad/shots/a_relaunch.png — the 'kkr' and 'h' bubbles in light theme. Fix options: give the incoming bubble a hairline in BOTH schemes, or darken `bgSubtle` for this use.
-FIX: the incoming-bubble hairline is no longer dark-only; it applies in both schemes, using the wallpaper-supplied border when the chat has a decorated ground and t.colors.hairline otherwise.</t>
-        </is>
-      </c>
-    </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>VC-061</t>
+          <t>VC-060</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>A 48dp empty band sits between the composer and the keyboard whenever the keyboard is open</t>
+          <t>Incoming message bubbles are nearly invisible in light theme — #F7F7F8 on #FFFFFF with no border (1.04:1)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -23433,84 +23431,119 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
+          <t>Evidence: scratchpad/shots/a_relaunch.png — the 'kkr' and 'h' bubbles in light theme. Fix options: give the incoming bubble a hairline in BOTH schemes, or darken `bgSubtle` for this use.
+FIX: the incoming-bubble hairline is no longer dark-only; it applies in both schemes, using the wallpaper-supplied border when the chat has a decorated ground and t.colors.hairline otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>VC-061</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>A 48dp empty band sits between the composer and the keyboard whenever the keyboard is open</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
           <t>Evidence: scratchpad/shots/a_cal.png and a_own_follow.png — the white band between the composer pill and the keyboard's suggestion strip. Same file also sets `borderTopWidth: 0` alongside a `borderTopColor`, so the intended separator between the thread and the composer never draws.
 FIX: keyboard-up paddingBottom drops from spacing.huge (48dp) to spacing.xs (8dp), and borderTopWidth goes from 0 to 1 so the separator the style always declared actually draws. VERIFIED ON DEVICE: scratchpad/shots/v2_own_follow.png shows the hairline above the composer and the composer sitting close to the keyboard.
 CORRECTION after on-device testing. Only HALF of this was a defect. The borderTopWidth 0 -&gt; 1 fix is right and shipped: the separator the style always declared now draws. The 48dp padding is NOT over-generous, it is LOAD-BEARING — the parent lifts the bar by keyboardDidShow.endCoordinates.height, and under RN 0.86 Android edge-to-edge that value lands short of the keyboard the user actually sees. Trimming it to 8dp moved the input 40dp down and put it BEHIND the keyboard on a 3-button-nav CPH2643; caught on the device and reverted before it could ship. The white band is cosmetic and invisible against a light keyboard. The real fix is to correct the LIFT, not the padding, and that is separate work.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>VC-062</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>A chat left open while the app is backgrounded keeps marking arriving messages read — the sender gets a blue tick for a message nobody has seen</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>chatVisibility.test.tsx: the chat only counts as on screen while it is visible</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>Found while tracing VC-057. Same listener is also the only place a notification TAP can clear a conversation's stored notification lines, because tapping resumes an ALREADY-MOUNTED chat screen and the mount effect never re-runs.
 FIX: the AppState listener in useMessages now withdraws and re-asserts the ENGINE's active conversation alongside the push layer's, and on returning to the foreground it re-reports the read and clears the conversation notification. Three new hook tests (chatVisibility.test.tsx) cover it, written RED first: before the change the background case recorded zero setActiveConversation calls, which is the bug exactly. Clearing on resume is also what fixes VC-057 — a notification TAP resumes an ALREADY-MOUNTED chat screen, so the mount effect never re-ran and the stored MessagingStyle lines were never dropped. Verified: 534/534 jest, tsc clean, eslint 0 errors. Live two-device re-verification still pending — the test phone was disconnected before it could be run.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>VC-063</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>A message whose realtime frame carries no body renders a permanently blank bubble — the REST recovery is dead code and the list would not re-render anyway</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>syncLogic.test.ts: reconcileDecision (§L6 dedup), failureScenarios.test.ts: a realtime frame with no body, observeMessages.test.ts: observeMessages column coverage</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit after the live session. Fix needs both halves: let the fill update a row matched by seq (e.g. treat a seq row with empty content as 'update'), and name `content_plain` in observeMessages' column list.
 FIX, both halves — either alone still leaves a blank bubble.
@@ -23520,39 +23553,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>VC-064</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Opening a chat from a notification while another chat is on screen keeps the unsent draft — one tap can send it to the wrong person</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>conversationSwitch.test.tsx: opening another chat from a notification, conversationSwitch.test.tsx: a re-render that is not a conversation switch</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr"/>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit. VC-053 fixed the TITLE on this exact entry point, which confirms the param-update path is real and exercised; the state carry-over was not addressed then.
 FIX — and NOT the `getId` this entry proposed. `navigation/RootNavigator.tsx` is UNCHANGED: the Chat screen still has no `getId`, and the deep link still reuses the route and swaps `route.params`. What changed is entirely in `ChatScreen.tsx`: it is now a shell that reads `route.params` and renders the real screen — the old body, renamed `ChatThread` — as `&lt;ChatThread key={conversationId} … /&gt;`. The key IS the reset. React tears the old thread down and builds a new one, so `text`, `offsetRef`, `showJump`/`showJumpRef` and `newestIdRef` cannot cross over, and whatever state `ChatThread` grows later is covered by construction instead of by somebody remembering to add it to a reset effect.
@@ -23561,39 +23594,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>VC-065</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Backing out of a chat mid-resolve strands a 20s presence timer, and can permanently disable the only code that clears it</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>presenceLifecycle.test.ts: a chat closed while its presence is still resolving</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit after the live two-device session.
 FIX: a `presenceEpoch` counter on the engine. `deactivatePresence` bumps it BEFORE the map delete — before, so an activate still awaiting sees the move rather than racing the delete — and the two paths that clear `activePresencePeers` wholesale, `stop()` and `onSessionCleared()`, bump it too. `activatePresence` captures the epoch before its first await and bails at three points: after the stored-peer lookup (`peerIdFor`), after the members fallback, and again after `refreshPeerPresence`.
@@ -23602,35 +23635,35 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>VC-066</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>PushStore's JSON blobs are read-modify-write across three threads — notification lines and counts can be lost or resurrected</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Distinct from VC-033, which is about the pending-event queue. This is the other five maps. Found by a code-level audit after the live two-device session.
 FIX: one `synchronized(WRITE_LOCK)` monitor wrapping every read-modify-write in the class — `appendLine`, `clearLines`, `clearAllLines`, `bumpCount`, `clearCount`, `clearAllCounts`, `setLastSeq`, `setMuted`, `putNames` (both name maps) and `putPersonAvatar`, plus `enqueueEvent`/`takeEvents` on the pending-event queue this entry split off from VC-033.
@@ -23641,35 +23674,35 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>VC-067</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Swiping a notification away clears its count but keeps its message lines, so dismissed messages reappear in the next notification</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit after the live two-device session. Deterministic, unlike the race in the sibling PushStore report.
 FIX: the `ACTION_DISMISS` branch now calls `store.clearLines(conversationId)` alongside `clearCount`, matching `PushNotifications.cancel`, which has always dropped both halves.
@@ -23679,39 +23712,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>VC-068</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Every load-older page re-runs the open-the-chat side effects, briefly un-suppressing notifications for the chat on screen</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>chatOpenEffects.test.tsx: paging through history is not re-opening the chat</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit after the live two-device session.
 FIX: the `useMessages` effect was split in two, exactly as this entry proposed. The open-the-chat work — `clearUnread` plus the read frame, the receipts GET, `syncEngine.setActiveConversation`, `setActiveConversationForPush`, the `clearConversationNotification` bridge call and the AppState listener — now sits in an effect keyed on `conversationId` ALONE, with its teardown (`appStateSub.remove()` and both active-conversation withdrawals) moved across with it. A second effect keyed on `[conversationId, limit]` does the only thing a wider window actually changes: subscribe `observeMessages` and release the narrower subscription.
@@ -23721,39 +23754,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>VC-069</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>The read watermark is sent at the local MAX seq, so it covers messages the device does not hold — the sender gets a blue tick for a message that was never received</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>contiguousSeq.test.ts: maxContiguousSeqForConversation</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Split out of VC-051 during that investigation. VC-062 (a backgrounded-but-mounted chat marking arrivals read) widened the window and is fixed; this is the independent, underlying defect.
 FIX: a new `maxContiguousSeqForConversation` in `infra/db/messages.ts` — the highest seq with no KNOWN hole beneath it — over a bounded `CONTIGUITY_SCAN = 500` row scan (`seq &gt; 0`, seq DESC, then sorted ascending).
@@ -23764,39 +23797,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>VC-070</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>A conversation with no resolved name shows as a bare em-dash in the chat list, with no way to tell who it is</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>conversationRowIdentity.test.ts: the identity a conversation row shows, chatsList.test.tsx: ConversationRow names a DM whose peer never resolved, chatTitle.test.ts: the header title for a conversation nothing names</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>Found during the live two-device session while checking the chat list; filed after confirming the source. Related to VC-047, which was about the WRONG name being shown; this is about NO name.
 FIX: a new pure conversationRowIdentity(name, fallback) in ui/chat/chatModel.ts returns both the title and the avatar initial from ONE decision, so the three places the placeholder used to leak — the visible name, the accessibilityLabel and the avatar initial — can no longer disagree. The label is localised and picked by kind: chat.unknownContact for a DM, chat.unnamedChat for a group, added to all three locales (en, hi, ar) so no locale falls back to English. The avatar is now gated on the initial being absent rather than on a ? sentinel, so an unidentified row draws the same person glyph it always did.
@@ -23805,54 +23838,20 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>VC-071</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>A notification's Mark-as-read carries the arriving seq, so a late out-of-order push acknowledges below the newest message</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>dev branch, 2026-09-19</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>Not independently tested</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>Found by an adversarial code review of the notification changes made the same day. Same function as the line-ordering fix, whose premise (FCM does not guarantee order) is what makes this reachable.</t>
-        </is>
-      </c>
-    </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>VC-072</t>
+          <t>VC-071</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>A notification's collapsed row can show one person's words beside another person's face</t>
+          <t>A notification's Mark-as-read carries the arriving seq, so a late out-of-order push acknowledges below the newest message</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -23868,6 +23867,40 @@
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Found by an adversarial code review of the notification changes made the same day. Same function as the line-ordering fix, whose premise (FCM does not guarantee order) is what makes this reachable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>VC-072</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>A notification's collapsed row can show one person's words beside another person's face</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>Found by an adversarial code review of the notification changes made the same day.</t>
         </is>

--- a/QA/reports/VelChat-QA-Report.xlsx
+++ b/QA/reports/VelChat-QA-Report.xlsx
@@ -641,7 +641,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-19 15:48 UTC</t>
+          <t>Generated 2026-09-25 02:52 UTC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -11043,7 +11043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB74"/>
+  <dimension ref="A1:AB75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13496,7 +13496,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -13598,7 +13598,10 @@
       </c>
       <c r="AA18" s="5" t="inlineStr">
         <is>
-          <t>Needs an ADR or, at minimum, a scrub-on-cancel.</t>
+          <t>Needs an ADR or, at minimum, a scrub-on-cancel.
+FIX: the notification store now seals its CONTENT entries at rest with the same AndroidKeyStore-wrapped key introduced for VC-016. Five entries are protected — the MessagingStyle message bodies, the pending-event queue (which holds the reply the user typed into a notification while the app was dead), the conversation and person display names, and the avatar map, because those carry URLs and on-disk paths tied to a person. Counts, seq watermarks, mute-untils, seen-seqs and the active conversation id stay plain on purpose: they are numbers and opaque ids, and sealing them would put an AES operation on the notification hot path for nothing (activeConversationId alone is read on every inbound push).
+The upgrade needs no migration pass and no flag: a sealed value carries a v1: prefix, so a value without one is recognised as a legacy plaintext entry, returned as-is, and re-sealed the next time that entry is written. Sealing that fails stores the plaintext rather than dropping it — losing a queued reply is worse than storing it the way the previous build already did — and an unseal that fails returns empty, which every caller already treats as a corrupt entry rather than wedging notifications. Nothing logs a key, a blob or a fragment (M19).
+Verified: Kotlin compiles clean, 588/588 jest, tsc clean, eslint 0 errors. NOT yet re-verified on a device end-to-end after the seal landed, so the live notification path under sealed storage is still owed a two-device run.</t>
         </is>
       </c>
       <c r="AB18" s="5" t="inlineStr"/>
@@ -13636,7 +13639,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -13737,7 +13740,8 @@
       </c>
       <c r="AA19" s="5" t="inlineStr">
         <is>
-          <t>Grouped with VC-019: four of the five §A1/§D4 controls have no implementation.</t>
+          <t>Grouped with VC-019: four of the five §A1/§D4 controls have no implementation.
+PARTIAL — the MECHANISM ships, deliberately with ZERO pins. A platform network-security-config is declared in the manifest, which the OS enforces on every TLS socket in the process: the axios path, the WebSocket, and the killed-app PushAckClient raw HttpURLConnection are all covered by one declaration with no code on any request path. Hosts for all three flavors are listed from the .env files. NO PIN IS SHIPPED and none will be guessed: a pin only exists on a live certificate, and a wrong one brands every install permanently unreachable. NOTE the empty &lt;pin-set&gt; elements the first version carried had to be REMOVED — Android lint treats an empty pin-set as a FATAL error in a release build, so the app could not be assembled at all; absent and empty are identical at runtime. WHAT THE OWNER MUST SUPPLY before this can close: (1) what to pin for prod — velchat.duckdns.org is Caddy + Lets Encrypt, which rotates its key on every renewal by default, so pinning the leaf is a dead app roughly every 60 days; either pin the issuing CA SPKI or get a committed fixed key plus a published offline backup, which is a backend commitment not a client choice; (2) confirmation of the stage hosts, which .env.stage marks as placeholders in its own comments; (3) reconciliation of a contradiction — backend-integration-reference says prod is per-service on Render, .env.prod says a single Azure origin. A tripwire test asserts a backup pin and an expiry are mandatory, so the day a lone or non-expiring pin lands the board goes red. SIDE EFFECT: once a network-security-config exists, usesCleartextTraffic is ignored on minSdk 24+, so cleartext is restated there — denied except loopback and the emulator host aliases. Running Metro over a LAN IP instead of adb reverse now needs that IP added. ADR 0009.</t>
         </is>
       </c>
       <c r="AB19" s="5" t="inlineStr"/>
@@ -13775,7 +13779,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -13875,7 +13879,8 @@
       </c>
       <c r="AA20" s="5" t="inlineStr">
         <is>
-          <t>Stated as coverage, not as a regression.</t>
+          <t>Stated as coverage, not as a regression.
+PARTIAL, each of the four decided separately (ADR 0010). CLIPBOARD AUTO-CLEAR: shipped, 60s, one timer replaced per copy, disposer returned, no new dependency. Nothing in src writes to the clipboard today, so the helper exists so the first copy feature uses the clearing path — wiring a call site is still owed. ROOT/EMULATOR: shipped as a SIGNAL only, never a gate — no blocked field and no path that refuses anything; the raw Build values are thrown away and only closed lower-case reason codes leave the module, with a test asserting no device-identifying substring can escape (M19). FLAG_SECURE: mechanism shipped, DEFAULT OFF, and turning it on is the product owner call — WhatsApp does not set it globally, it aims at the wrong adversary (it stops the screenshot path, not a camera), and it would black out the recents thumbnail and break the screenshot-driven QA this project runs on both devices. What A1 actually wants is per-screen (phone entry, OTP), which needs a JS-callable module. PLAY INTEGRITY: NOT shipped, blocked — it needs a Play Console project and cloud number (this repo has no google-services.json for dev/stage), a backend verifier endpoint that the integration reference does not expose, and a policy for a failed verdict. Adding the dependency now would ship a call that always fails and a control that looks present in a security review while verifying nothing.</t>
         </is>
       </c>
       <c r="AB20" s="5" t="inlineStr"/>
@@ -17262,7 +17267,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -17362,7 +17367,8 @@
       </c>
       <c r="AA45" s="5" t="inlineStr">
         <is>
-          <t>PARTIALLY FIXED — still open pending the remaining half. The name-precedence half is done (see VC-047): a saved contact name now wins over the registered one and resolves at READ time in the chat list and chat header, so it no longer requires opening the chat first, and a background revalidation can no longer overwrite it. What is NOT fixed, and why this stays open: the residual complaint is DISCOVERY TIMING, not precedence — a contact saved in the phone while VelChat is running is not matched until the next discovery run (app resume / prewarm), so until then that peer is genuinely unknown to the client and still renders as the number. Making that immediate needs the address-book snapshot to notify its readers (or a contacts-changed observer) so an already-mounted chat list re-renders, which is a separate change and is deliberately NOT bolted on here. Re-test after the VC-047 fix: the wrong-name-shown symptoms should be gone; only the just-saved-while-app-open case should remain.</t>
+          <t>PARTIALLY FIXED — still open pending the remaining half. The name-precedence half is done (see VC-047): a saved contact name now wins over the registered one and resolves at READ time in the chat list and chat header, so it no longer requires opening the chat first, and a background revalidation can no longer overwrite it. What is NOT fixed, and why this stays open: the residual complaint is DISCOVERY TIMING, not precedence — a contact saved in the phone while VelChat is running is not matched until the next discovery run (app resume / prewarm), so until then that peer is genuinely unknown to the client and still renders as the number. Making that immediate needs the address-book snapshot to notify its readers (or a contacts-changed observer) so an already-mounted chat list re-renders, which is a separate change and is deliberately NOT bolted on here. Re-test after the VC-047 fix: the wrong-name-shown symptoms should be gone; only the just-saved-while-app-open case should remain.
+FIXED. The residual was two things, both downstream of the VC-047 precedence fix. (1) Nothing ever asked for a re-sweep: discovery ran only at app mount, sign-in, and the New Chat screen, so a contact saved while VelChat was already running was in no sweep — the reporters workaround of sending a message and leaving the chat was just doing something else until a sweep happened to run. (2) Even a successful sweep could not reach a mounted screen: the saved name lives in the phone address book, so the conversation row never changes and there is no DB write that would re-emit it. FIX: a pure sameContactNames gate on would any DM be titled differently, a subscribeDiscoveredContacts notification fired only when that gate says a title could change, and a requestContactsRefresh with four cost gates in order — nothing to gain, 60s throttle, off the render path, and incremental so only a number with no remembered outcome goes to OPRF (one round trip, not the book). The chat list and the chat header both re-title on the notification and ask for a sweep on return to the foreground; app-returned deliberately bypasses the throttle, because another app is the only place a contact can be saved. NOT DONE: a native contacts ContentObserver, which would need an ADR. DEVICE RE-TEST STILL OWED: with a chat open showing a bare number, save that number in the phone contacts, switch back, and the title should change with nothing else touched.</t>
         </is>
       </c>
       <c r="AB45" s="5" t="inlineStr">
@@ -17538,7 +17544,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -17636,7 +17642,8 @@
       <c r="AA47" s="5" t="inlineStr">
         <is>
           <t>INVESTIGATED — left OPEN deliberately, no code change. The client side is already correct: activatePresence() does a LEADING await refreshPeerPresence() before it starts the interval, so there is no missing first read, and the poll is correctly scoped to the open chat and paused when suspended/offline (§M13 battery). The delay is architectural and has two additive parts. (1) There is NO live presence push to wait for: the realtime gateway FanoutConsumer subscribes to message/receipt/caption only, never presence.changed, so a presence change cannot reach a socket — this is already documented at the top of infra/network/presence.ts and is why a REST snapshot poll exists at all. (2) The numbers: peer COMES ONLINE is seen at the next poll, PEER_PRESENCE_POLL_MS = 20s, so up to ~20s. Peer GOES OFFLINE is worse, because nobody publishes a leaving event — their online:{userId} Redis key has to EXPIRE server-side (PRESENCE_ONLINE_TTL_MS = 30s from their last 20s heartbeat) and only then can our next poll observe it, so up to ~50s. That matches the reported "noticeable delay" exactly. THE REAL FIX IS BACKEND: have the gateway fan out presence.changed over the WS; the client already has the receiving path (onInboundPresence + normalizePresenceEvent are written and forward-compatible), so it would light up with no client change. The only client-side lever is lowering PEER_PRESENCE_POLL_MS, which buys latency with a REST request per interval per open chat and is a direct trade against the §R5/§R6 battery and request budgets on the 3GB reference device — a product call, not one to make silently, so it is NOT done here. Needs a decision: accept the delay, lower the poll interval (say what latency is acceptable), or schedule the backend fan-out.
-LIVE CHECK 2026-09-14 (two devices, production build): presence did update — the chat header showed "online" while the peer had the app open and switched to "last seen 9:39 am" after the peer backgrounded, and the typing indicator appeared within about 2 s of the peer typing. Latency was not instrumented, so this observation does not close the report; it narrows it to a latency question rather than a functional failure.</t>
+LIVE CHECK 2026-09-14 (two devices, production build): presence did update — the chat header showed "online" while the peer had the app open and switched to "last seen 9:39 am" after the peer backgrounded, and the typing indicator appeared within about 2 s of the peer typing. Latency was not instrumented, so this observation does not close the report; it narrows it to a latency question rather than a functional failure.
+FIXED — but not the way this entry assumed, and the earlier investigation note was wrong on one point. The architectural claim was VERIFIED against the running backend rather than the doc: the fan-out consumer subscribes to conversation, channel-member, message sent/delivered/read, contact.registered and call.caption, and there is NO presence.changed subscription — while the presence service DOES publish that event to the bus. So the event exists and the gateway simply never picks it up; the client receiving path is already written and would light up with one bus.subscribe line on the backend. CORRECTION to the earlier note: its peer-goes-offline figure only applies to an ungraceful exit; on a normal background the client posts /presence/offline immediately, so server state is right at once. THE REAL CLIENT DEFECT the earlier note missed: the open chat presence poll is torn down by every path that releases the link — network loss and the M13 background suspend both clear the timer — and NOTHING ever started it again. The only caller of activatePresence is the header mount effect, and neither returning from the background nor from a tunnel remounts a screen. A chat held open across a single interruption showed the presence it had read BEFORE the interruption for as long as the user stayed in it. Reported as updates with a delay; it was actually stops updating. FIX: resumePeerPresence re-subscribes (the server subscriber set expires after 300s), does a leading refresh and re-arms the interval, called from onForeground and from the network-restored branch. Keyed off activePresencePeers and NOT activeConversationId, because useMessages re-asserts the active id AFTER the engine handles the same transition — a resume keyed on it would no-op on the one transition that needs it most. The 20s interval is unchanged: halving it buys ~10s of average latency for a REST GET plus a subscribe POST every 10s per open chat on the 3 GB reference device (R5/R6), and still would not produce a live update. The remaining steady-state latency is backend-blocked, with the evidence above. DEVICE RE-TEST STILL OWED, observer-side: open a chat, background for 40s or toggle airplane mode, return, and confirm the peer status still tracks instead of freezing.</t>
         </is>
       </c>
       <c r="AB47" s="5" t="inlineStr">
@@ -21241,6 +21248,137 @@
         </is>
       </c>
       <c r="AB74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>VC-074</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>VC-75</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr"/>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Deep links are not gated on a session existing, so a notification could be honoured on a signed-out install</t>
+        </is>
+      </c>
+      <c r="E75" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F75" s="19" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Notifications — deep link / auth gate</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>apps/mobile/src/navigation/RootNavigator.tsx (linking config)</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>Production build</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>Pixel emulator (Android 16)</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>Every notification tapped while the app has no session</t>
+        </is>
+      </c>
+      <c r="O75" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P75" s="5" t="inlineStr">
+        <is>
+          <t>A notification in the tray and no active session — a sign-out, or any state where the app opens on the sign-in screen while an older notification is still posted.</t>
+        </is>
+      </c>
+      <c r="Q75" s="5" t="inlineStr">
+        <is>
+          <t>1. Have a message notification in the tray.
+2. Get the app into a signed-out state, so it opens on Enter-your-number.
+3. Tap the notification.</t>
+        </is>
+      </c>
+      <c r="R75" s="5" t="inlineStr">
+        <is>
+          <t>A signed-out app opens at sign-in. A deep link into a conversation must not be honoured without a session.</t>
+        </is>
+      </c>
+      <c r="S75" s="5" t="inlineStr">
+        <is>
+          <t>NOT REPRODUCED as originally reported, and the entry is corrected rather than left standing. The report was written from a live observation — the product owner was looking at the Enter-your-number screen, tapped a notification, and landed in a chat. Checked immediately afterwards on the same emulator: three consecutive force-stop + cold starts all landed on the signed-in chat list (confirmed by uiautomator dump, not by eye), so the install HAD a session throughout and the deep link taking it to the chat was correct behaviour, not a bypass. The sign-in screen was a one-off that did not recur; what put it there is still unexplained and is the part actually worth watching.
+What IS real, found while checking: the linking config had no session predicate at all. React Navigation resolves an incoming URL against linking.config independently of initialRouteName, so on a genuinely signed-out install the auth gate is not in that path — and notifications outlive a sign-out, because the native side keeps its own credentials to acknowledge a push with no JS alive.</t>
+        </is>
+      </c>
+      <c r="T75" s="5" t="inlineStr">
+        <is>
+          <t>The sign-in gate can be walked around with one tap. Whatever the local database still holds for the previous session is rendered to whoever is holding the phone, and the screen's own effects run against an account that is no longer authenticated.</t>
+        </is>
+      </c>
+      <c r="U75" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED. `initialRouteName` is chosen from the auth store, but `linking.config` maps `Chat: 'chat/:conversationId'` unconditionally, and React Navigation resolves an incoming URL against that config without consulting the stack's initial route. Notifications outlive a sign-out — the native side keeps its own credentials so it can acknowledge a push with no JS alive — so a stale notification is exactly the trigger.</t>
+        </is>
+      </c>
+      <c r="V75" s="5" t="inlineStr"/>
+      <c r="W75" s="5" t="inlineStr"/>
+      <c r="X75" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Y75" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z75" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA75" s="5" t="inlineStr">
+        <is>
+          <t>Found by the product owner on a device that had been signed out, during the two-device verification pass. Fixed by giving the linking config a `filter` that reads the auth store when a URL arrives, so a link is only honoured while a session is active.
+FIX (defence in depth, not a reproduced-bug fix): linking now carries filter: () =&gt; hasSession(). The predicate is deliberately hasSession() — tokens present on the device — and NOT the auth store reporting active. A notification tapped from COLD arrives at the navigation container before the store has hydrated, so asking the store would drop exactly the link this path exists for and land the user on the chat list instead of the chat they tapped, regressing VC-048/VC-053. hasSession reads MMKV synchronously, so it is already true for anyone who has signed in. The first version of this fix did ask the store; it was caught and changed before it shipped.
+HONEST STATUS: the gate is correct and cheap, but it closes a hole that was reasoned about rather than observed. The unexplained sign-in screen is NOT explained by it and should be treated as still open if it recurs.</t>
+        </is>
+      </c>
+      <c r="AB75" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AB1"/>
@@ -21254,7 +21392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -21429,7 +21567,7 @@
         </is>
       </c>
       <c r="B17" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="24" t="inlineStr"/>
     </row>
@@ -21440,7 +21578,7 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C18" s="24" t="inlineStr"/>
     </row>
@@ -21451,7 +21589,7 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C19" s="24" t="inlineStr"/>
     </row>
@@ -21510,7 +21648,7 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>14 open P0/P1 defect(s) block the build.</t>
+          <t>12 open P0/P1 defect(s) block the build.</t>
         </is>
       </c>
     </row>
@@ -21662,24 +21800,24 @@
     <row r="37">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>VC-017</t>
+          <t>VC-039</t>
         </is>
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>Message plaintext and the user's own typed replies persist in plaintext SharedPreferences</t>
+          <t>Any authenticated user can READ and WRITE any conversation — no authorization on the chat routes, and conversation ids are derivable offline</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>VC-018</t>
+          <t>VC-040</t>
         </is>
       </c>
       <c r="B38" s="23" t="inlineStr">
@@ -21689,31 +21827,31 @@
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>No certificate pinning anywhere, in JS or native</t>
+          <t>A push endpoint can be registered against another account's userId, redirecting their push wake-ups</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>VC-039</t>
+          <t>VC-041</t>
         </is>
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>Any authenticated user can READ and WRITE any conversation — no authorization on the chat routes, and conversation ids are derivable offline</t>
+          <t>POST /chat/messages accepts a conversationId that does not exist</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>VC-040</t>
+          <t>VC-043</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
@@ -21722,40 +21860,6 @@
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>A push endpoint can be registered against another account's userId, redirecting their push wake-ups</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="22" t="inlineStr">
-        <is>
-          <t>VC-041</t>
-        </is>
-      </c>
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>POST /chat/messages accepts a conversationId that does not exist</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="22" t="inlineStr">
-        <is>
-          <t>VC-043</t>
-        </is>
-      </c>
-      <c r="B42" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
         <is>
           <t>Concurrent refresh-token requests can all succeed — rotation is not race-safe</t>
         </is>
@@ -21910,7 +22014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22240,27 +22344,27 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>VC-020</t>
+          <t>VC-017</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Concurrent applyServerMessages duplicates every row in the overlap, and can lose a whole batch on a conversation PK clash</t>
+          <t>Message plaintext and the user's own typed replies persist in plaintext SharedPreferences</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-12</t>
+          <t>dev branch, 2026-09-25</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-201</t>
+          <t>VC-SEC-102</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
@@ -22271,34 +22375,37 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>VC-001 makes this far more likely to be hit in practice, because seq gaps are constant. FIX: The three lookup queries in applyServerMessages moved inside db.write(), read before any prepareCreate/prepareUpdate call — closes the race without violating the prepare-then-batch-synchronously constraint. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>Needs an ADR or, at minimum, a scrub-on-cancel.
+FIX: the notification store now seals its CONTENT entries at rest with the same AndroidKeyStore-wrapped key introduced for VC-016. Five entries are protected — the MessagingStyle message bodies, the pending-event queue (which holds the reply the user typed into a notification while the app was dead), the conversation and person display names, and the avatar map, because those carry URLs and on-disk paths tied to a person. Counts, seq watermarks, mute-untils, seen-seqs and the active conversation id stay plain on purpose: they are numbers and opaque ids, and sealing them would put an AES operation on the notification hot path for nothing (activeConversationId alone is read on every inbound push).
+The upgrade needs no migration pass and no flag: a sealed value carries a v1: prefix, so a value without one is recognised as a legacy plaintext entry, returned as-is, and re-sealed the next time that entry is written. Sealing that fails stores the plaintext rather than dropping it — losing a queued reply is worse than storing it the way the previous build already did — and an unseal that fails returns empty, which every caller already treats as a corrupt entry rather than wedging notifications. Nothing logs a key, a blob or a fragment (M19).
+Verified: Kotlin compiles clean, 588/588 jest, tsc clean, eslint 0 errors. NOT yet re-verified on a device end-to-end after the seal landed, so the live notification path under sealed storage is still owed a two-device run.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>VC-021</t>
+          <t>VC-018</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>applyReceipt is a non-atomic read-modify-write, so blue ticks can regress to grey</t>
+          <t>No certificate pinning anywhere, in JS or native</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-12</t>
+          <t>dev branch, 2026-09-25</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-202</t>
+          <t>VC-SEC-103</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
@@ -22309,34 +22416,35 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Every existing receipt test applies receipts sequentially, which is exactly why they all pass. FIX: applyReceipt now re-fetches the rows to update from inside db.write() (same pattern as VC-020) instead of before it, so the monotonic check is atomic with the write. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>Grouped with VC-019: four of the five §A1/§D4 controls have no implementation.
+PARTIAL — the MECHANISM ships, deliberately with ZERO pins. A platform network-security-config is declared in the manifest, which the OS enforces on every TLS socket in the process: the axios path, the WebSocket, and the killed-app PushAckClient raw HttpURLConnection are all covered by one declaration with no code on any request path. Hosts for all three flavors are listed from the .env files. NO PIN IS SHIPPED and none will be guessed: a pin only exists on a live certificate, and a wrong one brands every install permanently unreachable. NOTE the empty &lt;pin-set&gt; elements the first version carried had to be REMOVED — Android lint treats an empty pin-set as a FATAL error in a release build, so the app could not be assembled at all; absent and empty are identical at runtime. WHAT THE OWNER MUST SUPPLY before this can close: (1) what to pin for prod — velchat.duckdns.org is Caddy + Lets Encrypt, which rotates its key on every renewal by default, so pinning the leaf is a dead app roughly every 60 days; either pin the issuing CA SPKI or get a committed fixed key plus a published offline backup, which is a backend commitment not a client choice; (2) confirmation of the stage hosts, which .env.stage marks as placeholders in its own comments; (3) reconciliation of a contradiction — backend-integration-reference says prod is per-service on Render, .env.prod says a single Azure origin. A tripwire test asserts a backup pin and an expiry are mandatory, so the day a lone or non-expiring pin lands the board goes red. SIDE EFFECT: once a network-security-config exists, usesCleartextTraffic is ignored on minSdk 24+, so cleartext is restated there — denied except loopback and the emulator host aliases. Running Metro over a LAN IP instead of adb reverse now needs that IP added. ADR 0009.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>VC-022</t>
+          <t>VC-019</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>A SendAck with seq 0 leaves the message permanently un-tickable and permanently duplicated</t>
+          <t>Threat-model controls absent: no FLAG_SECURE, no Play Integrity, no clipboard auto-clear, no root signal</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-12</t>
+          <t>dev branch, 2026-09-25</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-203</t>
+          <t>VC-SEC-104</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
@@ -22347,24 +22455,25 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>normalizeSendAck has no test file at all. FIX: The outbox drain now rejects a SendAck with no usable seq (ack.seq is not &gt; 0) as a retryable server-kind AppError instead of writing it as a successful send — routes through the exact same retry path as any other transient send failure, so the row never gets stuck permanently un-tickable/duplicated. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>Stated as coverage, not as a regression.
+PARTIAL, each of the four decided separately (ADR 0010). CLIPBOARD AUTO-CLEAR: shipped, 60s, one timer replaced per copy, disposer returned, no new dependency. Nothing in src writes to the clipboard today, so the helper exists so the first copy feature uses the clearing path — wiring a call site is still owed. ROOT/EMULATOR: shipped as a SIGNAL only, never a gate — no blocked field and no path that refuses anything; the raw Build values are thrown away and only closed lower-case reason codes leave the module, with a test asserting no device-identifying substring can escape (M19). FLAG_SECURE: mechanism shipped, DEFAULT OFF, and turning it on is the product owner call — WhatsApp does not set it globally, it aims at the wrong adversary (it stops the screenshot path, not a camera), and it would black out the recents thumbnail and break the screenshot-driven QA this project runs on both devices. What A1 actually wants is per-screen (phone entry, OTP), which needs a JS-callable module. PLAY INTEGRITY: NOT shipped, blocked — it needs a Play Console project and cloud number (this repo has no google-services.json for dev/stage), a backend verifier endpoint that the integration reference does not expose, and a policy for a failed verdict. Adding the dependency now would ship a call that always fails and a control that looks present in a security review while verifying nothing.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>VC-023</t>
+          <t>VC-020</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>One 401 on send turns the entire outbox into permanently failed messages</t>
+          <t>Concurrent applyServerMessages duplicates every row in the overlap, and can lose a whole batch on a conversation PK clash</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -22374,7 +22483,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-204</t>
+          <t>VC-UNIT-201</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -22385,24 +22494,24 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>FIX: classifySendFailure() grouped auth with client, treating a post-refresh-failure 401/403 as if THIS message were rejected (permanent:true, pauseDrain:false) — one transient auth hiccup then permanently failed every other queued message as the drain kept walking into the same 401. auth is a SESSION problem, not a message problem (client.ts already treats a refresh that cannot reach the server as retryable, leaving the session valid). Added a dedicated auth case returning {permanent:false, pauseDrain:true, cooldownMs:0}, matching the network/timeout/server treatment, so the drain pauses instead of destroying the queue and resumes once the session recovers. Split the existing it.each(['client','auth']) test (which encoded the old, wrong grouping) into client-only plus a new dedicated describe block for auth. Verified: full jest suite 452/452 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>VC-001 makes this far more likely to be hit in practice, because seq gaps are constant. FIX: The three lookup queries in applyServerMessages moved inside db.write(), read before any prepareCreate/prepareUpdate call — closes the race without violating the prepare-then-batch-synchronously constraint. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>VC-024</t>
+          <t>VC-021</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Migration-v3's five composite indexes never exist on a fresh install</t>
+          <t>applyReceipt is a non-atomic read-modify-write, so blue ticks can regress to grey</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -22412,7 +22521,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>schema.test.ts: VC-024</t>
+          <t>VC-UNIT-202</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
@@ -22423,19 +22532,19 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>FIX: added an unsafeSql hook to schema.ts (appSchema) — WatermelonDB's own supported extension point, confirmed by reading adapters/sqlite/encodeSchema/index.js (encodeSchema calls unsafeSql(sql, "setup") for a fresh install) — that appends the same five composite CREATE INDEX statements the v3 migration already applies on an upgrade. Extracted the five statements into a new shared compositeIndexes.ts so migrations.ts and schema.ts can never drift apart, and migrations.ts now maps over that same array instead of repeating the SQL inline. Verified: full jest suite 481/481 pass (3 new tests in schema.test.ts assert the hook exists, appends every composite index on kind:"setup", and leaves other DDL kinds untouched), tsc --noEmit clean, eslint 0 errors.</t>
+          <t>Every existing receipt test applies receipts sequentially, which is exactly why they all pass. FIX: applyReceipt now re-fetches the rows to update from inside db.write() (same pattern as VC-020) instead of before it, so the monotonic check is atomic with the write. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>VC-025</t>
+          <t>VC-022</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>reassertReceipts() on every connect emits an unbounded burst the gateway silently drops</t>
+          <t>A SendAck with seq 0 leaves the message permanently un-tickable and permanently duplicated</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -22450,7 +22559,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>failureScenarios.test.ts: receipt reassertion after a reconnect with many owed conversations</t>
+          <t>VC-UNIT-203</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
@@ -22461,19 +22570,19 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>FIX: flushReceipts() (SyncEngine.ts) sent one frame per owed conversation in a single synchronous tick on every reconnect reassert, with no cap — the gateway silently drops inbound frames past ~40/sec per connection (ws-fabric.ts), and the client never learns which ones were dropped since socket.send() only checks readyState, so noteSent() recorded them all as delivered regardless. Added a per-tick cap (MAX_RECEIPT_FRAMES_PER_FLUSH=20, comfortably under the shared 40/sec budget) and, when a flush goes over budget, re-marks the remaining conversations dirty and reschedules a continuation chunk 1100ms later (longer than the gateway rate-limit window, so consecutive chunks land in separate windows) via the existing scheduleReceiptFlush/receiptTimer machinery. Nothing is ever dropped, only spread across more ticks. Verified: full jest suite 485/485 pass, tsc --noEmit clean, eslint 0 errors. Added 2 new tests (failureScenarios.test.ts) with 60 owed conversations (past the real ~40/sec budget): the first synchronous flush stays under 60, and every owed receipt eventually goes out across later chunks.</t>
+          <t>normalizeSendAck has no test file at all. FIX: The outbox drain now rejects a SendAck with no usable seq (ack.seq is not &gt; 0) as a retryable server-kind AppError instead of writing it as a successful send — routes through the exact same retry path as any other transient send failure, so the row never gets stuck permanently un-tickable/duplicated. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>VC-026</t>
+          <t>VC-023</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Unread count climbs and the read watermark stalls for messages backfilled into the chat you are reading</t>
+          <t>One 401 on send turns the entire outbox into permanently failed messages</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -22488,7 +22597,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-207</t>
+          <t>VC-UNIT-204</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
@@ -22499,19 +22608,19 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>VC-001 makes backfills constant, so this fires often. FIX: pageBackfill now mirrors the live-message path: if the backfilled page lands in the conversation on screen, it marks read (noteRead + clearUnread) instead of only noteDelivered. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: classifySendFailure() grouped auth with client, treating a post-refresh-failure 401/403 as if THIS message were rejected (permanent:true, pauseDrain:false) — one transient auth hiccup then permanently failed every other queued message as the drain kept walking into the same 401. auth is a SESSION problem, not a message problem (client.ts already treats a refresh that cannot reach the server as retryable, leaving the session valid). Added a dedicated auth case returning {permanent:false, pauseDrain:true, cooldownMs:0}, matching the network/timeout/server treatment, so the drain pauses instead of destroying the queue and resumes once the session recovers. Split the existing it.each(['client','auth']) test (which encoded the old, wrong grouping) into client-only plus a new dedicated describe block for auth. Verified: full jest suite 452/452 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>VC-027</t>
+          <t>VC-024</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>'Load older' dead-ends permanently on a deletion hole wider than one page</t>
+          <t>Migration-v3's five composite indexes never exist on a fresh install</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -22526,7 +22635,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>failureScenarios.test.ts: loading older history across a wide deletion hole</t>
+          <t>schema.test.ts: VC-024</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
@@ -22537,24 +22646,24 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>FIX: fetchOlderMessages() (SyncEngine.ts) treated an empty page from the server as end-of-history, but the backend filters deleted:false — a contiguous deleted run wider than one page comes back completely empty even though real history exists further back. Since the UI (useMessages.ts) only grows its window when loadOlderMessages returns true, and only fires another load on a scroll past a NEW oldest bubble, a false end-of-history report is a permanent dead end with no way for the user to retry. Converted the single fetch into a loop that steps the cursor back over an empty page and tries again, up to a generous safety cap (MAX_HOLE_HOPS=200, purely a circuit breaker against a pathological/corrupt history) before genuinely giving up. One loadOlderMessages() call now reaches all the way past a hole (or to the true start of history) in one go. Verified: full jest suite 485/485 pass, tsc --noEmit clean, eslint 0 errors. Added 2 new tests (failureScenarios.test.ts) with a 70-message-wide deletion hole (wider than the 50-message page): one call steps past it and loads the older page, and the true end-of-history case is unaffected.</t>
+          <t>FIX: added an unsafeSql hook to schema.ts (appSchema) — WatermelonDB's own supported extension point, confirmed by reading adapters/sqlite/encodeSchema/index.js (encodeSchema calls unsafeSql(sql, "setup") for a fresh install) — that appends the same five composite CREATE INDEX statements the v3 migration already applies on an upgrade. Extracted the five statements into a new shared compositeIndexes.ts so migrations.ts and schema.ts can never drift apart, and migrations.ts now maps over that same array instead of repeating the SQL inline. Verified: full jest suite 481/481 pass (3 new tests in schema.test.ts assert the hook exists, appends every composite index on kind:"setup", and leaves other DDL kinds untouched), tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>VC-029</t>
+          <t>VC-025</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Outbox backoff exhaustion is unreachable — MAX_SEND_ATTEMPTS can never fire</t>
+          <t>reassertReceipts() on every connect emits an unbounded burst the gateway silently drops</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -22564,7 +22673,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-210</t>
+          <t>failureScenarios.test.ts: receipt reassertion after a reconnect with many owed conversations</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
@@ -22575,19 +22684,19 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>FIX: removed the dead attempt-count exhaustion path (MAX_SEND_ATTEMPTS/nextOutboxRetry in syncLogic.ts) that markFailed() fell back to only when permanent was omitted — a fallback no real call site ever triggered (SyncEngine.ts always passes a classified boolean from classifySendFailure()). This mechanism contradicted the documented WhatsApp-style policy (sendFailurePolicy.ts: reachability failures retry forever, never auto-fail by attempt count) and had no basis in the HLD/LLD spec (§L6 outbox semantics: classification-based retryable-vs-permanent only, no attempt cap). Made markFailed()'s permanent parameter required (compiler now prevents the dead path from ever coming back), updated the one test that accidentally relied on the old default (realtime-hardening.test.ts) to pass permanent explicitly, removed the 4 tests for the deleted dead function, and added a new regression test proving a retryable cause stays queued past a high attempt count. Verified: full jest suite 452/452 pass (455 - 4 removed + 1 added), tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: flushReceipts() (SyncEngine.ts) sent one frame per owed conversation in a single synchronous tick on every reconnect reassert, with no cap — the gateway silently drops inbound frames past ~40/sec per connection (ws-fabric.ts), and the client never learns which ones were dropped since socket.send() only checks readyState, so noteSent() recorded them all as delivered regardless. Added a per-tick cap (MAX_RECEIPT_FRAMES_PER_FLUSH=20, comfortably under the shared 40/sec budget) and, when a flush goes over budget, re-marks the remaining conversations dirty and reschedules a continuation chunk 1100ms later (longer than the gateway rate-limit window, so consecutive chunks land in separate windows) via the existing scheduleReceiptFlush/receiptTimer machinery. Nothing is ever dropped, only spread across more ticks. Verified: full jest suite 485/485 pass, tsc --noEmit clean, eslint 0 errors. Added 2 new tests (failureScenarios.test.ts) with 60 owed conversations (past the real ~40/sec budget): the first synchronous flush stays under 60, and every owed receipt eventually goes out across later chunks.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>VC-030</t>
+          <t>VC-026</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Message window sorts by created_at, not seq — a device clock ahead of the server permanently mis-orders own messages</t>
+          <t>Unread count climbs and the read watermark stalls for messages backfilled into the chat you are reading</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -22597,12 +22706,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-13</t>
+          <t>dev branch, 2026-09-12</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>messageOrdering.test.ts: VC-030 — a device clock running ahead of the server</t>
+          <t>VC-UNIT-207</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
@@ -22613,19 +22722,19 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>FIX: two causes, both in the created_at-as-sort-key design. (1) markMessageSent() re-stamped createdAt to the server clock FORWARD ONLY (if (ack.serverTs &gt; m.createdAt)), a rule meant to stop a slow server clock re-burying an offline-composed bubble. Forward-only mixes two clocks in one sort key: on a device whose clock leads the server, an own message keeps its future local stamp and beats every server timestamp that follows it, permanently. The server clock is the same authority that assigns seq, so its timestamp is now adopted in EITHER direction. (2) messageWindowClauses() (extracted from observeMessages so the real query is testable rather than duplicated in a test) now sorts by created_at DESC then seq DESC — seq is the ordering identity per backend-integration-reference §5, and the gateway fans bursts out inside one millisecond, so identical created_at values are normal and were previously resolved by whatever order rows happened to be written. seq is the SECOND key, not the first, because an unsent message has no seq and sorting on it first would file every pending bubble under a null and drag it out of the newest-first window. The pre-existing test never drags a message backwards in time encoded the defect; it was rewritten to assert the concern it actually cared about — that a backwards re-stamp does not change the bubble POSITION — which now holds because seq decides the order. Verified: full jest suite 492/492 pass, tsc --noEmit clean, eslint 0 errors.</t>
+          <t>VC-001 makes backfills constant, so this fires often. FIX: pageBackfill now mirrors the live-message path: if the backfilled page lands in the conversation on screen, it marks read (noteRead + clearUnread) instead of only noteDelivered. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>VC-031</t>
+          <t>VC-027</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>runQueuedPushActions runs queued notification actions concurrently while claiming to serialize them</t>
+          <t>'Load older' dead-ends permanently on a deletion hole wider than one page</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -22635,12 +22744,12 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-13</t>
+          <t>dev branch, 2026-09-12</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>runSequentially.test.ts: VC-031</t>
+          <t>failureScenarios.test.ts: loading older history across a wide deletion hole</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
@@ -22651,34 +22760,34 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>FIX: the drain mapped each queued event to a thunk and then IMMEDIATELY mapped again to call it — events.map(e =&gt; () =&gt; handle(e)).map(run =&gt; run()) — so every handler was already in flight before Promise.allSettled waited on anything. The code did the exact opposite of the comment directly above it. Replaced with a new runSequentially() helper (features/notifications/model) that awaits each action in turn while still collecting per-item outcomes, so one failing action cannot abandon the rest (a reply must go out even if a preceding mute threw) — allSettle gives that second property but cannot give the first, since it can only wait on promises that have already been started. Verified: full jest suite 506/506 pass (4 new tests, including a max-concurrency assertion that fails against the old eager implementation), tsc --noEmit clean, eslint 0 errors.</t>
+          <t>FIX: fetchOlderMessages() (SyncEngine.ts) treated an empty page from the server as end-of-history, but the backend filters deleted:false — a contiguous deleted run wider than one page comes back completely empty even though real history exists further back. Since the UI (useMessages.ts) only grows its window when loadOlderMessages returns true, and only fires another load on a scroll past a NEW oldest bubble, a false end-of-history report is a permanent dead end with no way for the user to retry. Converted the single fetch into a loop that steps the cursor back over an empty page and tries again, up to a generous safety cap (MAX_HOLE_HOPS=200, purely a circuit breaker against a pathological/corrupt history) before genuinely giving up. One loadOlderMessages() call now reaches all the way past a hole (or to the true start of history) in one go. Verified: full jest suite 485/485 pass, tsc --noEmit clean, eslint 0 errors. Added 2 new tests (failureScenarios.test.ts) with a 70-message-wide deletion hole (wider than the 50-message page): one call steps past it and loads the older page, and the true end-of-history case is unaffected.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>VC-032</t>
+          <t>VC-029</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>No duplicate-notification suppression, though the monotonic watermark to do it already exists</t>
+          <t>Outbox backoff exhaustion is unreachable — MAX_SEND_ATTEMPTS can never fire</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-19</t>
+          <t>dev branch, 2026-09-12</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-213</t>
+          <t>VC-UNIT-210</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
@@ -22689,188 +22798,188 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
+          <t>FIX: removed the dead attempt-count exhaustion path (MAX_SEND_ATTEMPTS/nextOutboxRetry in syncLogic.ts) that markFailed() fell back to only when permanent was omitted — a fallback no real call site ever triggered (SyncEngine.ts always passes a classified boolean from classifySendFailure()). This mechanism contradicted the documented WhatsApp-style policy (sendFailurePolicy.ts: reachability failures retry forever, never auto-fail by attempt count) and had no basis in the HLD/LLD spec (§L6 outbox semantics: classification-based retryable-vs-permanent only, no attempt cap). Made markFailed()'s permanent parameter required (compiler now prevents the dead path from ever coming back), updated the one test that accidentally relied on the old default (realtime-hardening.test.ts) to pass permanent explicitly, removed the 4 tests for the deleted dead function, and added a new regression test proving a retryable cause stays queued past a high attempt count. Verified: full jest suite 452/452 pass (455 - 4 removed + 1 added), tsc --noEmit clean, eslint 0 errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>VC-030</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Message window sorts by created_at, not seq — a device clock ahead of the server permanently mis-orders own messages</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-13</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>messageOrdering.test.ts: VC-030 — a device clock running ahead of the server</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>FIX: two causes, both in the created_at-as-sort-key design. (1) markMessageSent() re-stamped createdAt to the server clock FORWARD ONLY (if (ack.serverTs &gt; m.createdAt)), a rule meant to stop a slow server clock re-burying an offline-composed bubble. Forward-only mixes two clocks in one sort key: on a device whose clock leads the server, an own message keeps its future local stamp and beats every server timestamp that follows it, permanently. The server clock is the same authority that assigns seq, so its timestamp is now adopted in EITHER direction. (2) messageWindowClauses() (extracted from observeMessages so the real query is testable rather than duplicated in a test) now sorts by created_at DESC then seq DESC — seq is the ordering identity per backend-integration-reference §5, and the gateway fans bursts out inside one millisecond, so identical created_at values are normal and were previously resolved by whatever order rows happened to be written. seq is the SECOND key, not the first, because an unsent message has no seq and sorting on it first would file every pending bubble under a null and drag it out of the newest-first window. The pre-existing test never drags a message backwards in time encoded the defect; it was rewritten to assert the concern it actually cared about — that a backwards re-stamp does not change the bubble POSITION — which now holds because seq decides the order. Verified: full jest suite 492/492 pass, tsc --noEmit clean, eslint 0 errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>VC-031</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>runQueuedPushActions runs queued notification actions concurrently while claiming to serialize them</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-13</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>runSequentially.test.ts: VC-031</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>FIX: the drain mapped each queued event to a thunk and then IMMEDIATELY mapped again to call it — events.map(e =&gt; () =&gt; handle(e)).map(run =&gt; run()) — so every handler was already in flight before Promise.allSettled waited on anything. The code did the exact opposite of the comment directly above it. Replaced with a new runSequentially() helper (features/notifications/model) that awaits each action in turn while still collecting per-item outcomes, so one failing action cannot abandon the rest (a reply must go out even if a preceding mute threw) — allSettle gives that second property but cannot give the first, since it can only wait on promises that have already been started. Verified: full jest suite 506/506 pass (4 new tests, including a max-concurrency assertion that fails against the old eager implementation), tsc --noEmit clean, eslint 0 errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>VC-032</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>No duplicate-notification suppression, though the monotonic watermark to do it already exists</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-19</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>VC-UNIT-213</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
           <t>The fix is one line: `if (seq &gt; 0 &amp;&amp; seq &lt;= store.lastSeq(conversationId)) return false`.
 FIXED, but NOT the way this entry proposed, and the difference matters. The entry says the monotonic watermark to do this already exists (PushStore.lastSeq). Suppressing on a high-water mark would be wrong here: FCM gives no ordering guarantee, and this session PROVED it out of order on a real device — the notification thread came back with KILL2 above KILL1, which is what VC-056 exists to sort. Against a watermark, a genuinely new message arriving with a LOWER seq than one already delivered would have its notification silently swallowed entirely — a far worse failure than showing a duplicate. So suppression is by EXACT identity instead: new PushStore.markSeen(conversationId, seq) records the seq and returns whether it was new, keeping the last 20 seqs per conversation (bounded, and only has to outlast FCM retries), atomic under the same WRITE_LOCK. handleMessage calls it BEFORE the on-screen check, so a duplicate of a message the user already watched arrive in an open chat cannot notify later either. Everything after it still runs for a duplicate on purpose: the delivered ack is idempotent and re-acking guarantees the sender their tick, and handing the push to a live JS runtime is a free chance to catch up. Cleared on sign-out with the rest of the session state. Verified by compileProdReleaseKotlin; no Kotlin test source set exists, and an FCM redelivery cannot be forced on demand, so this is code-review-verified.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>VC-033</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Native pending-event queue is a lock-free read-modify-write that can wipe a reply enqueued mid-drain</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>VC-UNIT-214</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>No JVM test source set exists — android/app/src contains only `main`. PushStore is plain-JVM-testable.
 FIXED as part of VC-066. The pending-event queue is one of the read-modify-write pairs that the new companion-object WRITE_LOCK now covers: enqueueEvent reads the array, appends, trims and writes it back, and takeEvents reads it and removes the key, both entirely inside the monitor. The drain case this entry described — an action queued on the receiver thread between the read and the removal, silently dropped — can no longer interleave, and the code now carries a comment saying exactly that. The monitor is on the COMPANION object rather than the instance, which is load-bearing: PushStore is constructed fresh at each entry point (VelChatMessagingService on FCM delivery, PushActionReceiver on main, VelChatPushModule on the RN native-modules thread), so an instance monitor would have been three separate locks guarding one shared SharedPreferences file. Verified by code review plus a clean compileProdReleaseKotlin; there is no Kotlin test source set in this project, so this is code-review-verified only.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>VC-034</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Retry-After is honored with an unbounded, uncancellable sleep</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>dev branch, 2026-09-12</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>VC-UNIT-215</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Not independently tested</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>FIX: Retry-After is now clamped to [0, 10s] (MAX_RETRY_AFTER_MS, client.ts) before the wait, instead of obeying a server-supplied value unbounded. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>VC-035</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>A misbuilt binary reports env:'dev' while talking to production</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>dev branch, 2026-09-12</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>VC-UNIT-216</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Not independently tested</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>The prod URL fallback direction is defensible; make `name` fall back to 'prod' alongside it, or log.error when Config.API_BASE_URL is absent. FIX: Extracted the pure resolveAppEnv(rawName, rawApiBaseUrl, rawWsUrl) so the fallback logic is unit-testable. An unrecognised/missing ENV now falls back to 'prod' alongside the URL fallback (previously 'dev'), so a misbuilt binary can never report a safe-sounding name while actually pointing at production. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>VC-036</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Cold start after &gt;15 min idle opens the WebSocket with a certainly-expired token</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>dev branch, 2026-09-12</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>VC-UNIT-217</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Not independently tested</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>FIX: hasValidSession() added (tokens.ts); useAuthBootstrap now refreshes before hydrating on an expired-but-present token. hasSession() deliberately left presence-only to protect SyncEngine reconnect guards. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>VC-038</t>
+          <t>VC-034</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Jest reports a worker that failed to exit gracefully — a leaked timer or handle in the test path</t>
+          <t>Retry-After is honored with an unbounded, uncancellable sleep</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>dev branch, 2026-09-13</t>
+          <t>dev branch, 2026-09-12</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>VC-UNIT-001</t>
+          <t>VC-UNIT-215</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
@@ -22881,32 +22990,36 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>FIX (root cause found by instrumentation, not guesswork): --detectOpenHandles reported NOTHING, so the leak was invisible to it. A probe dumping process.getActiveResourcesInfo() in afterAll showed four live Timeouts while _getActiveHandles() was empty. Traced to WatermelonDB: adapters/lokijs/worker/lokiExtensions.js constructs the Loki database with autosave:true, autosaveInterval:500 — a 500ms setInterval that is only ever cleared by loki.close(), which the app never calls because its database lives for the life of the process. Correct in production (which uses the real native SQLite adapter and never sees this code) but under Jest that interval outlives the run and holds the worker event loop open. Fixed at the source by passing extraLokiOptions:{autosave:false} to the LokiJSAdapter mock in jest.setup.ts — a first-class documented adapter option that WatermelonDB spreads AFTER its own defaults, so it overrides them; there is nothing to autosave in an in-memory adapter that starts fresh every run. MEASURED before/after with the same command: a DB-touching suite went from never exiting (killed at 90-120s, exit 124) to exit 0, and the full suite from blowing past a 120s timeout to completing and exiting in ~18s — --forceExit is no longer needed. RESIDUAL, stated honestly: the "worker process has failed to exit gracefully" text can still appear with &gt;=2 jest workers. That is worker-pool teardown timing, not a leak in our test code — verified by the warning being absent at --maxWorkers=1 (35s) and absent for every heavy suite run individually (failureScenarios, restart, realtime-hardening all clean), while present at --maxWorkers=2 (19s) and 4 (12s). Verified: full jest suite 506/506 pass, tsc --noEmit clean, eslint clean.</t>
+          <t>FIX: Retry-After is now clamped to [0, 10s] (MAX_RETRY_AFTER_MS, client.ts) before the wait, instead of obeying a server-supplied value unbounded. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>VC-045</t>
+          <t>VC-035</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Real-time messaging and notification-reply sync needs multi-scenario two-device verification</t>
+          <t>A misbuilt binary reports env:'dev' while talking to production</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Verified on dev, 2026-09-14</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
+          <t>dev branch, 2026-09-12</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>VC-UNIT-216</t>
+        </is>
+      </c>
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr">
         <is>
@@ -22915,193 +23028,374 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
+          <t>The prod URL fallback direction is defensible; make `name` fall back to 'prod' alongside it, or log.error when Config.API_BASE_URL is absent. FIX: Extracted the pure resolveAppEnv(rawName, rawApiBaseUrl, rawWsUrl) so the fallback logic is unit-testable. An unrecognised/missing ENV now falls back to 'prod' alongside the URL fallback (previously 'dev'), so a misbuilt binary can never report a safe-sounding name while actually pointing at production. Verified: full jest suite 455/455 pass, tsc --noEmit clean, eslint 0 errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VC-036</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Cold start after &gt;15 min idle opens the WebSocket with a certainly-expired token</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-12</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>VC-UNIT-217</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>FIX: hasValidSession() added (tokens.ts); useAuthBootstrap now refreshes before hydrating on an expired-but-present token. hasSession() deliberately left presence-only to protect SyncEngine reconnect guards. Verified: full jest suite 454/454 pass, tsc --noEmit clean, eslint 0 errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>VC-038</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Jest reports a worker that failed to exit gracefully — a leaked timer or handle in the test path</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-13</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>VC-UNIT-001</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>FIX (root cause found by instrumentation, not guesswork): --detectOpenHandles reported NOTHING, so the leak was invisible to it. A probe dumping process.getActiveResourcesInfo() in afterAll showed four live Timeouts while _getActiveHandles() was empty. Traced to WatermelonDB: adapters/lokijs/worker/lokiExtensions.js constructs the Loki database with autosave:true, autosaveInterval:500 — a 500ms setInterval that is only ever cleared by loki.close(), which the app never calls because its database lives for the life of the process. Correct in production (which uses the real native SQLite adapter and never sees this code) but under Jest that interval outlives the run and holds the worker event loop open. Fixed at the source by passing extraLokiOptions:{autosave:false} to the LokiJSAdapter mock in jest.setup.ts — a first-class documented adapter option that WatermelonDB spreads AFTER its own defaults, so it overrides them; there is nothing to autosave in an in-memory adapter that starts fresh every run. MEASURED before/after with the same command: a DB-touching suite went from never exiting (killed at 90-120s, exit 124) to exit 0, and the full suite from blowing past a 120s timeout to completing and exiting in ~18s — --forceExit is no longer needed. RESIDUAL, stated honestly: the "worker process has failed to exit gracefully" text can still appear with &gt;=2 jest workers. That is worker-pool teardown timing, not a leak in our test code — verified by the warning being absent at --maxWorkers=1 (35s) and absent for every heavy suite run individually (failureScenarios, restart, realtime-hardening all clean), while present at --maxWorkers=2 (19s) and 4 (12s). Verified: full jest suite 506/506 pass, tsc --noEmit clean, eslint clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>VC-044</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Contact name/contact update does not sync immediately in chat UI</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-25</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY FIXED — still open pending the remaining half. The name-precedence half is done (see VC-047): a saved contact name now wins over the registered one and resolves at READ time in the chat list and chat header, so it no longer requires opening the chat first, and a background revalidation can no longer overwrite it. What is NOT fixed, and why this stays open: the residual complaint is DISCOVERY TIMING, not precedence — a contact saved in the phone while VelChat is running is not matched until the next discovery run (app resume / prewarm), so until then that peer is genuinely unknown to the client and still renders as the number. Making that immediate needs the address-book snapshot to notify its readers (or a contacts-changed observer) so an already-mounted chat list re-renders, which is a separate change and is deliberately NOT bolted on here. Re-test after the VC-047 fix: the wrong-name-shown symptoms should be gone; only the just-saved-while-app-open case should remain.
+FIXED. The residual was two things, both downstream of the VC-047 precedence fix. (1) Nothing ever asked for a re-sweep: discovery ran only at app mount, sign-in, and the New Chat screen, so a contact saved while VelChat was already running was in no sweep — the reporters workaround of sending a message and leaving the chat was just doing something else until a sweep happened to run. (2) Even a successful sweep could not reach a mounted screen: the saved name lives in the phone address book, so the conversation row never changes and there is no DB write that would re-emit it. FIX: a pure sameContactNames gate on would any DM be titled differently, a subscribeDiscoveredContacts notification fired only when that gate says a title could change, and a requestContactsRefresh with four cost gates in order — nothing to gain, 60s throttle, off the render path, and incremental so only a number with no remembered outcome goes to OPRF (one round trip, not the book). The chat list and the chat header both re-title on the notification and ask for a sweep on return to the foreground; app-returned deliberately bypasses the throttle, because another app is the only place a contact can be saved. NOT DONE: a native contacts ContentObserver, which would need an ADR. DEVICE RE-TEST STILL OWED: with a chat open showing a bare number, save that number in the phone contacts, switch back, and the title should change with nothing else touched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>VC-045</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Real-time messaging and notification-reply sync needs multi-scenario two-device verification</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Verified on dev, 2026-09-14</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
           <t>This entry tracks a two-device manual verification pass, not a confirmed defect. Assigned to Tusha Bhadouriya to execute and report actual pass/fail per scenario back into this bug.
 VERIFIED 2026-09-14 by a live two-device session (A = OPPO CPH2643 Android 16 real device, B = Pixel emulator Android 16), production build against the live backend. PASSED: single-message real-time delivery; an 8-message burst delivered complete and in order; notification posted with the correct sender name, avatar and per-message lines while backgrounded; notification posted after the process was killed with am kill (FCM woke the dead process and it displayed correctly); tapping a notification opens the right conversation and clears the tray; NO notification is posted while that conversation is on screen (active-conversation suppression works); inline notification Reply sends the message, clears the notification and clears the unread badge; typing indicator appears on the peer header; presence shows online and last-seen; offline send queues and flushes in order on reconnect (airplane mode on/off); unread badges and chat-list ordering correct; cold start COLD TotalTime 1367 ms. FAILED, filed separately: VC-051 (message loss with a false read receipt), VC-052 (thread does not follow new messages), VC-053 (notification tap-through titles the chat Chats), VC-054, VC-055, VC-056, VC-057, VC-058, VC-059, VC-060, VC-061.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>VC-046</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Online/offline presence status updates with a noticeable delay</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-25</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>INVESTIGATED — left OPEN deliberately, no code change. The client side is already correct: activatePresence() does a LEADING await refreshPeerPresence() before it starts the interval, so there is no missing first read, and the poll is correctly scoped to the open chat and paused when suspended/offline (§M13 battery). The delay is architectural and has two additive parts. (1) There is NO live presence push to wait for: the realtime gateway FanoutConsumer subscribes to message/receipt/caption only, never presence.changed, so a presence change cannot reach a socket — this is already documented at the top of infra/network/presence.ts and is why a REST snapshot poll exists at all. (2) The numbers: peer COMES ONLINE is seen at the next poll, PEER_PRESENCE_POLL_MS = 20s, so up to ~20s. Peer GOES OFFLINE is worse, because nobody publishes a leaving event — their online:{userId} Redis key has to EXPIRE server-side (PRESENCE_ONLINE_TTL_MS = 30s from their last 20s heartbeat) and only then can our next poll observe it, so up to ~50s. That matches the reported "noticeable delay" exactly. THE REAL FIX IS BACKEND: have the gateway fan out presence.changed over the WS; the client already has the receiving path (onInboundPresence + normalizePresenceEvent are written and forward-compatible), so it would light up with no client change. The only client-side lever is lowering PEER_PRESENCE_POLL_MS, which buys latency with a REST request per interval per open chat and is a direct trade against the §R5/§R6 battery and request budgets on the 3GB reference device — a product call, not one to make silently, so it is NOT done here. Needs a decision: accept the delay, lower the poll interval (say what latency is acceptable), or schedule the backend fan-out.
+LIVE CHECK 2026-09-14 (two devices, production build): presence did update — the chat header showed "online" while the peer had the app open and switched to "last seen 9:39 am" after the peer backgrounded, and the typing indicator appeared within about 2 s of the peer typing. Latency was not instrumented, so this observation does not close the report; it narrows it to a latency question rather than a functional failure.
+FIXED — but not the way this entry assumed, and the earlier investigation note was wrong on one point. The architectural claim was VERIFIED against the running backend rather than the doc: the fan-out consumer subscribes to conversation, channel-member, message sent/delivered/read, contact.registered and call.caption, and there is NO presence.changed subscription — while the presence service DOES publish that event to the bus. So the event exists and the gateway simply never picks it up; the client receiving path is already written and would light up with one bus.subscribe line on the backend. CORRECTION to the earlier note: its peer-goes-offline figure only applies to an ungraceful exit; on a normal background the client posts /presence/offline immediately, so server state is right at once. THE REAL CLIENT DEFECT the earlier note missed: the open chat presence poll is torn down by every path that releases the link — network loss and the M13 background suspend both clear the timer — and NOTHING ever started it again. The only caller of activatePresence is the header mount effect, and neither returning from the background nor from a tunnel remounts a screen. A chat held open across a single interruption showed the presence it had read BEFORE the interruption for as long as the user stayed in it. Reported as updates with a delay; it was actually stops updating. FIX: resumePeerPresence re-subscribes (the server subscriber set expires after 300s), does a leading refresh and re-arms the interval, called from onForeground and from the network-restored branch. Keyed off activePresencePeers and NOT activeConversationId, because useMessages re-asserts the active id AFTER the engine handles the same transition — a resume keyed on it would no-op on the one transition that needs it most. The 20s interval is unchanged: halving it buys ~10s of average latency for a REST GET plus a subscribe POST every 10s per open chat on the 3 GB reference device (R5/R6), and still would not produce a live update. The remaining steady-state latency is backend-blocked, with the evidence above. DEVICE RE-TEST STILL OWED, observer-side: open a chat, background for 40s or toggle airplane mode, return, and confirm the peer status still tracks instead of freezing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>VC-047</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Chat List shows the registered VelChat name instead of the saved contact name until a chat is opened</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-13</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>peerDisplayName.test.ts: VC-044 / VC-047, conversationRow.test.ts: VC-044 / VC-047</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>FIX (root-caused): the address book was consulted on exactly ONE path. startDm() writes the saved name when a chat is opened from New Chat / Message Yourself — which is why the name corrected itself after opening — while every other path used server data, and refreshPeerIdentity() actively OVERWROTE a saved name with the registered one on its next background revalidation (once per TTL/session). Introduced peerDisplayName() (features/contacts/model), the single precedence rule: the name YOU saved wins over the name the peer registered; falls back to the registered name for someone not in your book or when the book has not loaded; returns undefined when neither side has a usable name so callers keep what they have; group rows are untouched (no peerId to look up). Applied at both the WRITE side (refreshPeerIdentity, both the TTL path and the profile-changed push, so a revalidation can no longer downgrade a saved name) and the READ side (toConversationRow for the chat list, useConversationIdentity for the chat header), the latter being what makes a saved name appear WITHOUT having to open the chat first. Exposed discoveredContacts() from the contacts barrel as a cache read (no re-discovery). Verified: full jest suite 502/502 pass (10 new tests), tsc --noEmit clean, eslint 0 errors and no boundary violation. Not re-tested on a device — no Android hardware attached to this machine.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>VC-048</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Message notification omits the sender's name and tapping it does not open the chat</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Verified on dev, 2026-09-14</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Reported by Tusha Bhadouriya during production QA testing.
 RE-TESTED LIVE 2026-09-14 on a production build against the live backend, two devices. Both halves of this report are now correct: the notification DOES carry the sender name (dumpsys shows android.title="Aayush Jain 🤗" with the sender photo and per-message MessagingStyle lines), and tapping it DOES open that conversation (topResumedActivity becomes com.velchat/.MainActivity on the Chat route and every VelChat notification is cleared). Evidence: scratchpad/shots/b_shade.png, b_tapthrough.png. One residual defect on the same path is filed separately as VC-053: the deep link carries no name param, so ChatHeader falls back to the tabs.chats label and the header reads "Chats". A second residual, the chat not opening at the newest message, is covered by VC-052.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>VC-049</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Email-prompt bottom sheet reappears on every login even when an email is already saved</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-13</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>profileGate.test.ts: VC-049</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>FIX (root-caused): the email is NOT a directory-profile field — profileShape.ts states it is a separately-verified identifier owned by the auth-service (GET /auth/account). useProfileGate decided purely from the LOCAL MMKV mirror, and purgeAccountData() wipes KVKeys.email on every sign-out, so immediately after any login the mirror is empty and the gate prompted unconditionally. useAccountInfo() does fetch the real email and mirror it, but it runs in parallel from AppTabs, so its answer always lost the race — and dismissal is session-only, which is why it returned every single login. The gate now asks the auth-service itself before deciding, via a new pure shouldPromptForProfile() (features/user/model/profileGate.ts): a mirrored email means never prompt; a server email means never prompt (and is re-mirrored so later launches short-circuit with no network); an UNANSWERED server (in flight or unreachable) means WAIT rather than prompt, which also removes the flash of the sheet before the answer lands. Only a definitive server no-email prompts. Verified: full jest suite 492/492 pass (5 new decision tests), tsc --noEmit clean, eslint 0 errors, no eslint-plugin-boundaries violation for the user→auth import (authApi depends only on infra, so no cycle). Not reproduced on a device — no Android hardware attached to this machine; fix is verified at the unit level against the exact reported condition.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>VC-050</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Cold start holds a splash screen on a network refresh — up to minutes before home appears</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-13</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>authBootstrap.test.ts: cold start with a session already on the device</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>FIX: split the two questions the bootstrap had conflated — "can we show the app" and "is the access token fresh enough for a socket". If a session exists on the device at all (hasSession(), presence-only), the app now hydrates and reports ready IMMEDIATELY, whatever the token age; the chat list renders from the local DB, the HTTP client refreshes on its first 401, and the socket heals itself via 4001 -&gt; refresh -&gt; reconnect. VC-036 is not regressed: a fresh token is still wanted as early as possible so the first handshake is not doomed, so the refresh is still fired at once — it just runs BEHIND the app instead of in front of it. The no-session path (signed out but a device key survives) still attempts a silent restore, but is now bounded by MAX_SILENT_RESTORE_MS = 4000 so a hibernating backend cannot freeze the splash; a restore that lands later still navigates home on its own, because RootNavigator follows the auth store (state === active). Verified: full jest suite 521/521 pass (5 new hook tests, two of which fail against the old code by hanging until waitFor times out), tsc --noEmit clean, eslint 0 errors. Measured on device: not yet — needs a launch on real hardware to confirm the wall-clock improvement.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>VC-051</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>A message the device was pushed for never reaches the chat, and no reconnect ever heals it — the sender still sees blue read ticks</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>failureScenarios.test.ts: a message dropped by fan-out</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/a_inline_rx.png (A shows KILL2 09:39 with blue ticks) vs scratchpad/shots/b_kill2_check.png (B's thread jumps BG1 09:37 -&gt; KILL1 09:37 -&gt; hhh 09:40, no KILL2). Related backend defect VC-001 may be the upstream cause, but the client must still heal the gap on reconnect and must not report `read` for a message it does not hold.
 FIX (frontend): pageBackfill/backfillConversation take an optional `fromSeq`, and the gap probe passes the pre-apply `localMax` — so the repair asks the server from the LOWER edge of the hole instead of from the message that revealed it. Re-fetching the rows already held between localMax and the incoming seq is free: applyServerMessages dedups on (conversation_id, seq) and on client_msg_id inside the write lock. Three end-to-end tests added to failureScenarios.test.ts, driving the real engine against the fake server, written RED first — and rewritten once when the first version passed for the wrong reason (bootConnected’s own reconnect backfill was healing the hole), so each test now brings the socket up while the device is already caught up. Verified: 537/537 jest, tsc clean, eslint 0 errors.
@@ -23109,35 +23403,35 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>VC-052</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Chat thread does not follow the newest message — incoming and own-sent bubbles land hidden behind the composer</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_fg_follow.png (B at the bottom, F1-F3 arrive, list stays on S8 and the jump FAB appears), scratchpad/shots/b_one.png (single message ONE1 arrives, list left exactly one bubble short), scratchpad/shots/a_own_follow.png (A's OWN sent ONE1 clipped behind the composer), scratchpad/shots/b_offline_send.png (own offline sends clipped). The race explains the intermittency: sometimes the manual scroll lands after the anchor adjustment and it looks fine.
 FIX: the follow now goes through FlashList's `scrollToIndex({index:0})` instead of `scrollToOffset({offset:0})`, fired from `onContentSizeChange` rather than the data effect. Root cause confirmed by reading useRecyclerViewController.js: on every data change FlashList measures how far the FIRST VISIBLE item moved and calls scrollAnchorRef.scrollBy(diff) to cancel the shift, gated on a `pauseOffsetCorrection` ref that ONLY scrollToIndex raises — so a plain offset scroll was undone every time and the thread landed exactly one bubble short. Firing from onContentSizeChange means index 0 has a real layout instead of the stale one it would have in the same commit. Anchoring is deliberately kept: it is the right behaviour for a reader scrolled up in history, whom shouldScrollToLatest still leaves alone; a drag cancels any pending follow so loadOlder growing the content is never mistaken for a new message. An intermediate attempt using scrollToOffset from onContentSizeChange plus a requestAnimationFrame retry was built and tested on device and still landed one bubble short — that is what identified the pauseOffsetCorrection gate. VERIFIED ON DEVICE: a four-message burst now ends with the newest message fully visible above the composer (scratchpad/shots/v2_own_follow.png) where the same burst on the previous build left it clipped (v_own_follow.png). Still to verify with a second device: the INCOMING-message path, and the notification tap-through landing position.
@@ -23145,140 +23439,140 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>VC-053</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Chat opened from a notification is titled "Chats" instead of the contact's name, and the avatar loses its initial</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="5" t="inlineStr"/>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_tapthrough.png and b_jump.png (header 'Chats' after notification tap) vs scratchpad/shots/b_off_kbd.png (header 'Aayush Jain 🤗' for the same chat opened from the list). Relates to VC-048, which reported the tap-through as not opening the chat at all; the open now works, this is the remaining defect on that path.
 FIX: new pure helper `chatTitle(routeName, rowName, fallback)` in ui/chat/chatModel.ts, covered by chatTitle.test.ts (4 cases, RED first). ChatHeader now resolves the title from the route name, then the conversation row it was already observing for the avatar, and only then a generic label; blank counts as absent in both sources. The avatar initial is taken from the resolved name with an empty fallback, so a genuinely unnamed conversation still falls back to the person glyph instead of showing the initial of a tab label. Needs a second device to re-verify the live tap-through.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>VC-054</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Notification group summary says "N new messages" but N is the number of chats, not the number of messages</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Evidence: dumpsys output captured twice in the live session (8 messages -&gt; '5 new messages'; 1 message -&gt; '5 new messages').
 FIX: added `PushStore.countedMessages()`, which sums the per-conversation counters the store already held, and postSummary now formats that instead of `countedConversations()`. The &lt;=1 guard that suppresses the summary for a single chat still uses the conversation count, which is correct. Needs a second device to re-verify live.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>VC-055</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Every notification is tinted the abandoned violet #7C5CFF, which matches nothing in the shipped monochrome theme</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>Confirmed by reading tokens.ts (brandFrom '#0B0B0C' / '#F5F5F7') against push_strings.xml (#7C5CFF) and by the live dumpsys record color=0xff7c5cff.
 FIX: push_accent is now #0B0B0C, the monochrome brand accent from design-system/tokens.ts, and the misleading resource comment about a violet gradient is replaced. Android resolves this against the shade background for contrast. Needs a second device to re-verify live.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>VC-056</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Notification message lines are ordered by arrival, not by message time — an out-of-order push shows the wrong 'latest' message</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_reply_open.png (expanded notification shows S6, S7, S8, BG1, KILL2, KILL1) vs scratchpad/shots/a_inline_rx.png (chat shows KILL1 09:37 then KILL2 09:39, correct).
 FIX: `PushStore.Line` now carries the message's own `seq`, persisted as the JSON key `"q"`, and `showMessage` passes the push's seq into `appendLine`. `appendLine` SORTS before applying the `MAX_LINES` cap, and that order is the fix rather than a detail: capping first dropped whichever line FCM happened to deliver earliest, so an out-of-order push could evict a message newer than the one it kept. `setContentText` and `setLargeIcon` now read the newest INCOMING line (`lines.lastOrNull { !it.mine }`) instead of the message that arrived last, so the collapsed row and the face on it agree with the expanded thread — incoming only, because an inline reply can sort last and quoting the user's own words back at them is not a notification about anything.
@@ -23289,35 +23583,35 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>VC-057</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Notification re-lists messages the user has already read once the chat is reopened and a new message arrives</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr"/>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_shade.png (S3..S8 before opening), scratchpad/shots/b_tapthrough.png (chat opened, tray cleared, all read), scratchpad/shots/b_reply_open.png (next notification still carries S6, S7, S8, BG1).
 ROOT CAUSE FOUND and FIXED via VC-062. The clearing path was wired correctly all along — clearConversationNotification -&gt; VelChatPushModule.clearConversation -&gt; PushNotifications.cancel -&gt; store.clearLines — but it only ran from the chat screen's MOUNT effect. A notification tap RESUMES an already-mounted ChatScreen, so that effect never re-ran, and the tray entry disappearing was just the notification's own AUTO_CANCEL flag removing the posted notification while the stored lines and counters survived. useMessages now also clears on every return to the foreground. Live re-verification pending a second device.
@@ -23325,74 +23619,74 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>VC-058</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Chat-list preview can regress to an older message — the preview is written unconditionally while the timestamp is guarded</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/b_after_reply.png (row reads 'KILL1' while KILL2 was newer). Fix is to move the preview write inside the same freshness check as the timestamp.
 FIX: the preview write now sits behind the same freshness check as the sort key in upsertConversation — a single `fresher` predicate gates both, so a stale patch can no longer overwrite what the row says while being correctly refused a reorder.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>VC-059</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Composer's emoji, attach, camera and mic buttons are dead controls that look and behave as if they work</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>composerControls.test.tsx: the controls that are not built yet, composerControls.test.tsx: the one control that is wired</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>Minimum viable fix for a release build: hide the unimplemented controls, or render them disabled (reduced opacity + accessibilityState disabled) so neither sighted nor screen-reader users are misled.
 FIX: `PillIconButton` lost its `onPress` prop entirely — emoji, attach and camera now render a `Pressable` with a real `disabled` and `accessibilityState={{disabled: true}}`, and the pressed-opacity branch is gone, so a tap produces no fake response at all and TalkBack announces them as disabled rather than as working buttons. The primary circle does the same conditionally (`disabled={!hasText}`, `accessibilityState` following it, and `opacity: pressed &amp;&amp; hasText ? 0.8 : 1`), so the one control that is a send button half the time and an unbuilt mic the other half reports which one it currently is.
@@ -23401,70 +23695,70 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>VC-060</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Incoming message bubbles are nearly invisible in light theme — #F7F7F8 on #FFFFFF with no border (1.04:1)</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/a_relaunch.png — the 'kkr' and 'h' bubbles in light theme. Fix options: give the incoming bubble a hairline in BOTH schemes, or darken `bgSubtle` for this use.
 FIX: the incoming-bubble hairline is no longer dark-only; it applies in both schemes, using the wallpaper-supplied border when the chat has a decorated ground and t.colors.hairline otherwise.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>VC-061</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>A 48dp empty band sits between the composer and the keyboard whenever the keyboard is open</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Evidence: scratchpad/shots/a_cal.png and a_own_follow.png — the white band between the composer pill and the keyboard's suggestion strip. Same file also sets `borderTopWidth: 0` alongside a `borderTopColor`, so the intended separator between the thread and the composer never draws.
 FIX: keyboard-up paddingBottom drops from spacing.huge (48dp) to spacing.xs (8dp), and borderTopWidth goes from 0 to 1 so the separator the style always declared actually draws. VERIFIED ON DEVICE: scratchpad/shots/v2_own_follow.png shows the hairline above the composer and the composer sitting close to the keyboard.
@@ -23472,78 +23766,78 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>VC-062</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>A chat left open while the app is backgrounded keeps marking arriving messages read — the sender gets a blue tick for a message nobody has seen</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-14</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>chatVisibility.test.tsx: the chat only counts as on screen while it is visible</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>Found while tracing VC-057. Same listener is also the only place a notification TAP can clear a conversation's stored notification lines, because tapping resumes an ALREADY-MOUNTED chat screen and the mount effect never re-runs.
 FIX: the AppState listener in useMessages now withdraws and re-asserts the ENGINE's active conversation alongside the push layer's, and on returning to the foreground it re-reports the read and clears the conversation notification. Three new hook tests (chatVisibility.test.tsx) cover it, written RED first: before the change the background case recorded zero setActiveConversation calls, which is the bug exactly. Clearing on resume is also what fixes VC-057 — a notification TAP resumes an ALREADY-MOUNTED chat screen, so the mount effect never re-ran and the stored MessagingStyle lines were never dropped. Verified: 534/534 jest, tsc clean, eslint 0 errors. Live two-device re-verification still pending — the test phone was disconnected before it could be run.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>VC-063</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>A message whose realtime frame carries no body renders a permanently blank bubble — the REST recovery is dead code and the list would not re-render anyway</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>syncLogic.test.ts: reconcileDecision (§L6 dedup), failureScenarios.test.ts: a realtime frame with no body, observeMessages.test.ts: observeMessages column coverage</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr"/>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit after the live session. Fix needs both halves: let the fill update a row matched by seq (e.g. treat a seq row with empty content as 'update'), and name `content_plain` in observeMessages' column list.
 FIX, both halves — either alone still leaves a blank bubble.
@@ -23553,39 +23847,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>VC-064</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Opening a chat from a notification while another chat is on screen keeps the unsent draft — one tap can send it to the wrong person</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>conversationSwitch.test.tsx: opening another chat from a notification, conversationSwitch.test.tsx: a re-render that is not a conversation switch</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit. VC-053 fixed the TITLE on this exact entry point, which confirms the param-update path is real and exercised; the state carry-over was not addressed then.
 FIX — and NOT the `getId` this entry proposed. `navigation/RootNavigator.tsx` is UNCHANGED: the Chat screen still has no `getId`, and the deep link still reuses the route and swaps `route.params`. What changed is entirely in `ChatScreen.tsx`: it is now a shell that reads `route.params` and renders the real screen — the old body, renamed `ChatThread` — as `&lt;ChatThread key={conversationId} … /&gt;`. The key IS the reset. React tears the old thread down and builds a new one, so `text`, `offsetRef`, `showJump`/`showJumpRef` and `newestIdRef` cannot cross over, and whatever state `ChatThread` grows later is covered by construction instead of by somebody remembering to add it to a reset effect.
@@ -23594,39 +23888,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>VC-065</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Backing out of a chat mid-resolve strands a 20s presence timer, and can permanently disable the only code that clears it</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>presenceLifecycle.test.ts: a chat closed while its presence is still resolving</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit after the live two-device session.
 FIX: a `presenceEpoch` counter on the engine. `deactivatePresence` bumps it BEFORE the map delete — before, so an activate still awaiting sees the move rather than racing the delete — and the two paths that clear `activePresencePeers` wholesale, `stop()` and `onSessionCleared()`, bump it too. `activatePresence` captures the epoch before its first await and bails at three points: after the stored-peer lookup (`peerIdFor`), after the members fallback, and again after `refreshPeerPresence`.
@@ -23635,35 +23929,35 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>VC-066</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>PushStore's JSON blobs are read-modify-write across three threads — notification lines and counts can be lost or resurrected</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>Distinct from VC-033, which is about the pending-event queue. This is the other five maps. Found by a code-level audit after the live two-device session.
 FIX: one `synchronized(WRITE_LOCK)` monitor wrapping every read-modify-write in the class — `appendLine`, `clearLines`, `clearAllLines`, `bumpCount`, `clearCount`, `clearAllCounts`, `setLastSeq`, `setMuted`, `putNames` (both name maps) and `putPersonAvatar`, plus `enqueueEvent`/`takeEvents` on the pending-event queue this entry split off from VC-033.
@@ -23674,35 +23968,35 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>VC-067</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Swiping a notification away clears its count but keeps its message lines, so dismissed messages reappear in the next notification</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit after the live two-device session. Deterministic, unlike the race in the sibling PushStore report.
 FIX: the `ACTION_DISMISS` branch now calls `store.clearLines(conversationId)` alongside `clearCount`, matching `PushNotifications.cancel`, which has always dropped both halves.
@@ -23712,39 +24006,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>VC-068</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Every load-older page re-runs the open-the-chat side effects, briefly un-suppressing notifications for the chat on screen</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>chatOpenEffects.test.tsx: paging through history is not re-opening the chat</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>Found by a code-level audit after the live two-device session.
 FIX: the `useMessages` effect was split in two, exactly as this entry proposed. The open-the-chat work — `clearUnread` plus the read frame, the receipts GET, `syncEngine.setActiveConversation`, `setActiveConversationForPush`, the `clearConversationNotification` bridge call and the AppState listener — now sits in an effect keyed on `conversationId` ALONE, with its teardown (`appStateSub.remove()` and both active-conversation withdrawals) moved across with it. A second effect keyed on `[conversationId, limit]` does the only thing a wider window actually changes: subscribe `observeMessages` and release the narrower subscription.
@@ -23754,39 +24048,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>VC-069</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>The read watermark is sent at the local MAX seq, so it covers messages the device does not hold — the sender gets a blue tick for a message that was never received</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>contiguousSeq.test.ts: maxContiguousSeqForConversation</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>Split out of VC-051 during that investigation. VC-062 (a backgrounded-but-mounted chat marking arrivals read) widened the window and is fixed; this is the independent, underlying defect.
 FIX: a new `maxContiguousSeqForConversation` in `infra/db/messages.ts` — the highest seq with no KNOWN hole beneath it — over a bounded `CONTIGUITY_SCAN = 500` row scan (`seq &gt; 0`, seq DESC, then sorted ascending).
@@ -23797,39 +24091,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>VC-070</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>A conversation with no resolved name shows as a bare em-dash in the chat list, with no way to tell who it is</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>conversationRowIdentity.test.ts: the identity a conversation row shows, chatsList.test.tsx: ConversationRow names a DM whose peer never resolved, chatTitle.test.ts: the header title for a conversation nothing names</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>Found during the live two-device session while checking the chat list; filed after confirming the source. Related to VC-047, which was about the WRONG name being shown; this is about NO name.
 FIX: a new pure conversationRowIdentity(name, fallback) in ui/chat/chatModel.ts returns both the title and the avatar initial from ONE decision, so the three places the placeholder used to leak — the visible name, the accessibilityLabel and the avatar initial — can no longer disagree. The label is localised and picked by kind: chat.unknownContact for a DM, chat.unnamedChat for a group, added to all three locales (en, hi, ar) so no locale falls back to English. The avatar is now gated on the initial being absent rather than on a ? sentinel, so an unidentified row draws the same person glyph it always did.
@@ -23838,71 +24132,107 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>VC-071</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>A notification's Mark-as-read carries the arriving seq, so a late out-of-order push acknowledges below the newest message</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>Found by an adversarial code review of the notification changes made the same day. Same function as the line-ordering fix, whose premise (FCM does not guarantee order) is what makes this reachable.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>VC-072</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>A notification's collapsed row can show one person's words beside another person's face</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>dev branch, 2026-09-19</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>Not independently tested</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>Found by an adversarial code review of the notification changes made the same day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>VC-074</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Deep links are not gated on a session existing, so a notification could be honoured on a signed-out install</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>dev branch, 2026-09-25</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Not independently tested</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Found by the product owner on a device that had been signed out, during the two-device verification pass. Fixed by giving the linking config a `filter` that reads the auth store when a URL arrives, so a link is only honoured while a session is active.
+FIX (defence in depth, not a reproduced-bug fix): linking now carries filter: () =&gt; hasSession(). The predicate is deliberately hasSession() — tokens present on the device — and NOT the auth store reporting active. A notification tapped from COLD arrives at the navigation container before the store has hydrated, so asking the store would drop exactly the link this path exists for and land the user on the chat list instead of the chat they tapped, regressing VC-048/VC-053. hasSession reads MMKV synchronously, so it is already true for anyone who has signed in. The first version of this fix did ask the store; it was caught and changed before it shipped.
+HONEST STATUS: the gate is correct and cheap, but it closes a hole that was reasoned about rather than observed. The unexplained sign-in screen is NOT explained by it and should be treated as still open if it recurs.</t>
         </is>
       </c>
     </row>
